--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — DESEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 23 APRIL 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 24 APRIL 2026</t>
   </si>
 </sst>
 </file>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19580,11 +19580,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>228680684.94456199</v>
+        <v>246290231.808541</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>35001210.683972999</v>
+        <v>36070926.893973</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -19603,11 +19603,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>381160866.71155703</v>
+        <v>406504821.75153196</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>85717036.28373</v>
+        <v>87606856.103726998</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -19615,26 +19615,26 @@
         <v>113</v>
       </c>
       <c r="C10" s="174">
-        <v>224610070.15044501</v>
+        <v>241854889.973326</v>
       </c>
       <c r="D10" s="174">
-        <v>18528994.284492001</v>
+        <v>21552994.284492001</v>
       </c>
       <c r="E10" s="174">
-        <v>41602827.579980001</v>
+        <v>48243818.519979998</v>
       </c>
       <c r="F10" s="174">
-        <v>284741892.01491702</v>
+        <v>311651702.777798</v>
       </c>
       <c r="G10"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>392749277.47480798</v>
+        <v>420632888.60480601</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>17392227.579762999</v>
+        <v>18258380.749756001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -19642,22 +19642,22 @@
         <v>114</v>
       </c>
       <c r="C11" s="174">
-        <v>224832722.72200999</v>
+        <v>229667438.89206299</v>
       </c>
       <c r="D11" s="174">
-        <v>84021028.886584997</v>
+        <v>85286416.286568999</v>
       </c>
       <c r="E11" s="174">
         <v>34053355</v>
       </c>
       <c r="F11" s="174">
-        <v>342907106.60859501</v>
+        <v>349007210.17863202</v>
       </c>
       <c r="G11"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>241247743.57999301</v>
+        <v>255770265.839993</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -19669,26 +19669,26 @@
         <v>70</v>
       </c>
       <c r="C12" s="174">
-        <v>181889424.13394099</v>
+        <v>196623063.70394099</v>
       </c>
       <c r="D12" s="174">
-        <v>54330577.373896003</v>
+        <v>54953437.733896002</v>
       </c>
       <c r="E12" s="174">
-        <v>63243242</v>
+        <v>66143242</v>
       </c>
       <c r="F12" s="174">
-        <v>299463243.507837</v>
+        <v>317719743.437837</v>
       </c>
       <c r="G12"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>320800940.97424603</v>
+        <v>334431917.58384198</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>39994197.137378</v>
+        <v>43061962.927372001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -19696,26 +19696,26 @@
         <v>115</v>
       </c>
       <c r="C13" s="174">
-        <v>199271442.57761601</v>
+        <v>209881758.047591</v>
       </c>
       <c r="D13" s="174">
-        <v>31386458.909834001</v>
+        <v>32653418.369831</v>
       </c>
       <c r="E13" s="174">
         <v>5733873.7999999998</v>
       </c>
       <c r="F13" s="174">
-        <v>236391775.28744999</v>
+        <v>248269050.21742201</v>
       </c>
       <c r="G13"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>735946387.35961795</v>
+        <v>798074040.27580798</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>37027322.469917998</v>
+        <v>41655590.999917999</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -19723,26 +19723,26 @@
         <v>116</v>
       </c>
       <c r="C14" s="174">
-        <v>392749277.47480798</v>
+        <v>420632888.60480601</v>
       </c>
       <c r="D14" s="174">
-        <v>17392227.579762999</v>
+        <v>18258380.749756001</v>
       </c>
       <c r="E14" s="174">
-        <v>45719513.009985</v>
+        <v>52117711.149985</v>
       </c>
       <c r="F14" s="174">
-        <v>455861018.064556</v>
+        <v>491008980.504547</v>
       </c>
       <c r="G14"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>291827773.17281801</v>
+        <v>307739449.46131498</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>45214295.689974003</v>
+        <v>47952136.249973997</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -19759,11 +19759,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>224832722.72200999</v>
+        <v>229667438.89206299</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>84021028.886584997</v>
+        <v>85286416.286568999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -19771,26 +19771,26 @@
         <v>74</v>
       </c>
       <c r="C16" s="174">
-        <v>320800940.97424603</v>
+        <v>334431917.58384198</v>
       </c>
       <c r="D16" s="174">
-        <v>39994197.137378</v>
+        <v>43061962.927372001</v>
       </c>
       <c r="E16" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F16" s="174">
-        <v>360795138.111624</v>
+        <v>377493880.51121402</v>
       </c>
       <c r="G16"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>349747815.26205099</v>
+        <v>372126112.94157797</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>33596881.103970997</v>
+        <v>35479531.103970997</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -19798,7 +19798,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="174">
-        <v>241247743.57999301</v>
+        <v>255770265.839993</v>
       </c>
       <c r="D17" s="174">
         <v>38549567.509999998</v>
@@ -19807,17 +19807,17 @@
         <v>170</v>
       </c>
       <c r="F17" s="174">
-        <v>279797311.089993</v>
+        <v>294319833.34999299</v>
       </c>
       <c r="G17"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>224610070.15044501</v>
+        <v>241854889.973326</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>18528994.284492001</v>
+        <v>21552994.284492001</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
@@ -19825,26 +19825,26 @@
         <v>119</v>
       </c>
       <c r="C18" s="174">
-        <v>1120864055.6898439</v>
+        <v>1130504566.3698339</v>
       </c>
       <c r="D18" s="174">
         <v>8425432.7548970003</v>
       </c>
       <c r="E18" s="174">
-        <v>524324.31999999995</v>
+        <v>1835135.12</v>
       </c>
       <c r="F18" s="174">
-        <v>1129813812.7647409</v>
+        <v>1140765134.2447309</v>
       </c>
       <c r="G18"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>556057347.75544596</v>
+        <v>558636301.53544605</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>142236292.66712999</v>
+        <v>149549438.62712601</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
@@ -19852,26 +19852,26 @@
         <v>121</v>
       </c>
       <c r="C19" s="174">
-        <v>735946387.35961795</v>
+        <v>798074040.27580798</v>
       </c>
       <c r="D19" s="174">
-        <v>37027322.469917998</v>
+        <v>41655590.999917999</v>
       </c>
       <c r="E19" s="174">
-        <v>9455855.6500000004</v>
+        <v>71382881.099999994</v>
       </c>
       <c r="F19" s="174">
-        <v>782429565.47953606</v>
+        <v>911112512.37572598</v>
       </c>
       <c r="G19"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>122674509.714931</v>
+        <v>123899988.51493099</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>98311766.353484005</v>
+        <v>114171394.96325701</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
@@ -19879,22 +19879,22 @@
         <v>123</v>
       </c>
       <c r="C20" s="174">
-        <v>77471661.714930996</v>
+        <v>78537400.514930993</v>
       </c>
       <c r="D20" s="174">
-        <v>13424396.249822</v>
+        <v>13948889.939819001</v>
       </c>
       <c r="E20" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F20" s="174">
-        <v>90896057.964753002</v>
+        <v>92486290.454750001</v>
       </c>
       <c r="G20"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>310879805.19997603</v>
+        <v>310992417.80997604</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -19905,22 +19905,22 @@
         <v>124</v>
       </c>
       <c r="C21" s="174">
-        <v>45202848</v>
+        <v>45362588</v>
       </c>
       <c r="D21" s="174">
-        <v>84887370.103661999</v>
+        <v>100222505.02343801</v>
       </c>
       <c r="E21" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F21" s="174">
-        <v>130090218.103662</v>
+        <v>145585093.02343801</v>
       </c>
       <c r="G21"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>731746890.61302996</v>
+        <v>740872710.54296207</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -19952,7 +19952,7 @@
         <v>175</v>
       </c>
       <c r="C23" s="174">
-        <v>75340784.659999996</v>
+        <v>77048823.620000005</v>
       </c>
       <c r="D23" s="174" t="s">
         <v>170</v>
@@ -19961,7 +19961,7 @@
         <v>13608107.9</v>
       </c>
       <c r="F23" s="174">
-        <v>88948892.560000002</v>
+        <v>90656931.519999996</v>
       </c>
       <c r="G23"/>
       <c r="J23" s="116"/>
@@ -19973,16 +19973,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="174">
-        <v>228680684.94456199</v>
+        <v>246290231.808541</v>
       </c>
       <c r="D24" s="174">
-        <v>35001210.683972999</v>
+        <v>36070926.893973</v>
       </c>
       <c r="E24" s="174">
-        <v>8855098.9399919994</v>
+        <v>14098342.139992001</v>
       </c>
       <c r="F24" s="174">
-        <v>272536994.56852698</v>
+        <v>296459500.84250599</v>
       </c>
       <c r="G24"/>
       <c r="J24" s="116"/>
@@ -19992,16 +19992,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="174">
-        <v>291827773.17281801</v>
+        <v>307739449.46131498</v>
       </c>
       <c r="D25" s="174">
-        <v>45214295.689974003</v>
+        <v>47952136.249973997</v>
       </c>
       <c r="E25" s="174">
-        <v>16310504.299995</v>
+        <v>17896089.859995</v>
       </c>
       <c r="F25" s="174">
-        <v>353352573.16278702</v>
+        <v>373587675.571284</v>
       </c>
       <c r="G25"/>
       <c r="J25" s="116"/>
@@ -20011,16 +20011,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="174">
-        <v>349747815.26205099</v>
+        <v>372126112.94157797</v>
       </c>
       <c r="D26" s="174">
-        <v>33596881.103970997</v>
+        <v>35479531.103970997</v>
       </c>
       <c r="E26" s="174">
-        <v>44335136.559940003</v>
+        <v>48438740.129940003</v>
       </c>
       <c r="F26" s="174">
-        <v>427679832.92596197</v>
+        <v>456044384.17548901</v>
       </c>
       <c r="G26"/>
       <c r="J26" s="116"/>
@@ -20030,16 +20030,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="174">
-        <v>556057347.75544596</v>
+        <v>558636301.53544605</v>
       </c>
       <c r="D27" s="174">
-        <v>142236292.66712999</v>
+        <v>149549438.62712601</v>
       </c>
       <c r="E27" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F27" s="174">
-        <v>698293640.42257595</v>
+        <v>708185740.16257203</v>
       </c>
       <c r="G27"/>
       <c r="J27" s="116"/>
@@ -20060,14 +20060,16 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="76"/>
-      <c r="C31" s="112"/>
+      <c r="C31" s="174">
+        <v>112612.61</v>
+      </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
       <c r="C32" s="174">
-        <v>160437126.188869</v>
+        <v>168477998.51885799</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
@@ -20075,7 +20077,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="174">
-        <v>358109822.376854</v>
+        <v>376402138.15180397</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
@@ -20083,7 +20085,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="174">
-        <v>255270723.584618</v>
+        <v>262272038.98456201</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
@@ -20091,7 +20093,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="174">
-        <v>165596361.82843599</v>
+        <v>167608253.74842399</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
@@ -20121,7 +20123,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.76666666666666672</v>
+        <v>0.8</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20162,19 +20164,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4192452572.6824856</v>
+        <v>4419452819.0031805</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.63336994281842685</v>
+        <v>0.66766374353276969</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2426826760.3823757</v>
+        <v>2199826514.0616808</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>346689537.19748223</v>
+        <v>366637752.34361345</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20190,19 +20192,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>675590820.65039814</v>
+        <v>719195196.70013499</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.53205922024518171</v>
+        <v>0.5663996961829183</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>594175391.34960186</v>
+        <v>550571015.29986501</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>84882198.764228836</v>
+        <v>91761835.88331084</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20218,19 +20220,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1250293839.1787529</v>
+        <v>1285752847.213624</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.69790748742756958</v>
+        <v>0.71770052041615562</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>541195522.52337551</v>
+        <v>505736514.48850441</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>77313646.074767932</v>
+        <v>84289419.081417397</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20244,33 +20246,33 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6118337232.5116367</v>
+        <v>6424400862.9169397</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.63202470642760988</v>
+        <v>0.6636411029752175</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>3562197674.255353</v>
+        <v>3256134043.85005</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>508885382.036479</v>
+        <v>542689007.30834162</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
       <c r="K48" s="221"/>
       <c r="L48" s="222"/>
       <c r="M48" s="222"/>
@@ -20359,35 +20361,35 @@
       </c>
       <c r="G51" s="177">
         <f>M8</f>
-        <v>228680684.94456199</v>
+        <v>246290231.808541</v>
       </c>
       <c r="H51" s="177">
         <f>N8</f>
-        <v>35001210.683972999</v>
+        <v>36070926.893973</v>
       </c>
       <c r="I51" s="177">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>263681895.62853497</v>
+        <v>282361158.70251399</v>
       </c>
       <c r="J51" s="178">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.59085442274220956</v>
+        <v>0.63271063427511609</v>
       </c>
       <c r="K51" s="164">
         <f t="shared" ref="K51:K64" si="3">D51-G51</f>
-        <v>168002793.38165471</v>
+        <v>150393246.5176757</v>
       </c>
       <c r="L51" s="164">
         <f t="shared" ref="L51:L64" si="4">E51-H51</f>
-        <v>14587498.316027001</v>
+        <v>13517782.106027</v>
       </c>
       <c r="M51" s="164">
         <f t="shared" ref="M51:M64" si="5">F51-I51</f>
-        <v>182590291.69768173</v>
+        <v>163911028.6237027</v>
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>26084327.385383103</v>
+        <v>27318504.770617116</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20411,35 +20413,35 @@
       </c>
       <c r="G52" s="177">
         <f>M9</f>
-        <v>381160866.71155703</v>
+        <v>406504821.75153196</v>
       </c>
       <c r="H52" s="177">
         <f>N9</f>
-        <v>85717036.28373</v>
+        <v>87606856.103726998</v>
       </c>
       <c r="I52" s="177">
         <f t="shared" si="1"/>
-        <v>466877902.99528706</v>
+        <v>494111677.85525894</v>
       </c>
       <c r="J52" s="178">
         <f t="shared" si="2"/>
-        <v>0.65938786224460644</v>
+        <v>0.69785106744356618</v>
       </c>
       <c r="K52" s="165">
         <f t="shared" si="3"/>
-        <v>154021504.28844297</v>
+        <v>128677549.24846804</v>
       </c>
       <c r="L52" s="165">
         <f t="shared" si="4"/>
-        <v>87148055.71627</v>
+        <v>85258235.896273002</v>
       </c>
       <c r="M52" s="165">
         <f t="shared" si="5"/>
-        <v>241169560.00471294</v>
+        <v>213935785.14474106</v>
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>34452794.286387563</v>
+        <v>35655964.190790176</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20491,7 +20493,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>27813945.685714286</v>
+        <v>32449603.300000001</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20515,35 +20517,35 @@
       </c>
       <c r="G54" s="177">
         <f>M10</f>
-        <v>392749277.47480798</v>
+        <v>420632888.60480601</v>
       </c>
       <c r="H54" s="177">
         <f t="shared" ref="H54:H58" si="6">N10</f>
-        <v>17392227.579762999</v>
+        <v>18258380.749756001</v>
       </c>
       <c r="I54" s="177">
         <f t="shared" si="1"/>
-        <v>410141505.05457097</v>
+        <v>438891269.35456198</v>
       </c>
       <c r="J54" s="178">
         <f t="shared" si="2"/>
-        <v>0.66268080576627442</v>
+        <v>0.70913286374410223</v>
       </c>
       <c r="K54" s="165">
         <f>D54-G54</f>
-        <v>197963194.44808924</v>
+        <v>170079583.31809121</v>
       </c>
       <c r="L54" s="165">
         <f t="shared" si="4"/>
-        <v>10807907.420237001</v>
+        <v>9941754.2502439991</v>
       </c>
       <c r="M54" s="165">
         <f t="shared" si="5"/>
-        <v>208771101.86832625</v>
+        <v>180021337.56833524</v>
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>29824443.124046605</v>
+        <v>30003556.261389207</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20567,7 +20569,7 @@
       </c>
       <c r="G55" s="177">
         <f>M11</f>
-        <v>241247743.57999301</v>
+        <v>255770265.839993</v>
       </c>
       <c r="H55" s="177">
         <f t="shared" si="6"/>
@@ -20575,15 +20577,15 @@
       </c>
       <c r="I55" s="177">
         <f t="shared" si="1"/>
-        <v>279797311.089993</v>
+        <v>294319833.34999299</v>
       </c>
       <c r="J55" s="178">
         <f t="shared" si="2"/>
-        <v>0.59710250806661858</v>
+        <v>0.62809435152329229</v>
       </c>
       <c r="K55" s="165">
         <f t="shared" si="3"/>
-        <v>153815540.61153114</v>
+        <v>139293018.35153115</v>
       </c>
       <c r="L55" s="165">
         <f t="shared" si="4"/>
@@ -20591,11 +20593,11 @@
       </c>
       <c r="M55" s="165">
         <f t="shared" si="5"/>
-        <v>188794442.10153115</v>
+        <v>174271919.84153116</v>
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>26970634.585933022</v>
+        <v>29045319.973588526</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20619,35 +20621,35 @@
       </c>
       <c r="G56" s="177">
         <f>M12</f>
-        <v>320800940.97424603</v>
+        <v>334431917.58384198</v>
       </c>
       <c r="H56" s="177">
         <f t="shared" si="6"/>
-        <v>39994197.137378</v>
+        <v>43061962.927372001</v>
       </c>
       <c r="I56" s="177">
         <f t="shared" si="1"/>
-        <v>360795138.111624</v>
+        <v>377493880.51121396</v>
       </c>
       <c r="J56" s="178">
         <f t="shared" si="2"/>
-        <v>0.67335467548483519</v>
+        <v>0.70451966381680653</v>
       </c>
       <c r="K56" s="165">
         <f t="shared" si="3"/>
-        <v>143117891.14840758</v>
+        <v>129486914.53881162</v>
       </c>
       <c r="L56" s="165">
         <f t="shared" si="4"/>
-        <v>31904350.862622</v>
+        <v>28836585.072627999</v>
       </c>
       <c r="M56" s="165">
         <f t="shared" si="5"/>
-        <v>175022242.0110296</v>
+        <v>158323499.61143965</v>
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>25003177.430147085</v>
+        <v>26387249.935239941</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20671,35 +20673,35 @@
       </c>
       <c r="G57" s="177">
         <f>M13</f>
-        <v>735946387.35961795</v>
+        <v>798074040.27580798</v>
       </c>
       <c r="H57" s="177">
         <f t="shared" si="6"/>
-        <v>37027322.469917998</v>
+        <v>41655590.999917999</v>
       </c>
       <c r="I57" s="177">
         <f t="shared" si="1"/>
-        <v>772973709.82953596</v>
+        <v>839729631.27572596</v>
       </c>
       <c r="J57" s="178">
         <f t="shared" si="2"/>
-        <v>0.76154652942271883</v>
+        <v>0.82731557130510436</v>
       </c>
       <c r="K57" s="165">
         <f t="shared" si="3"/>
-        <v>205811958.08510077</v>
+        <v>143684305.16891074</v>
       </c>
       <c r="L57" s="165">
         <f t="shared" si="4"/>
-        <v>36219561.530082002</v>
+        <v>31591293.000082001</v>
       </c>
       <c r="M57" s="165">
         <f t="shared" si="5"/>
-        <v>242031519.61518276</v>
+        <v>175275598.16899276</v>
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>34575931.37359754</v>
+        <v>29212599.694832128</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20723,35 +20725,35 @@
       </c>
       <c r="G58" s="177">
         <f>M14</f>
-        <v>291827773.17281801</v>
+        <v>307739449.46131498</v>
       </c>
       <c r="H58" s="177">
         <f t="shared" si="6"/>
-        <v>45214295.689974003</v>
+        <v>47952136.249973997</v>
       </c>
       <c r="I58" s="177">
         <f>G58+H58</f>
-        <v>337042068.86279202</v>
+        <v>355691585.71128899</v>
       </c>
       <c r="J58" s="178">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.63546469725730026</v>
+        <v>0.67062680511556161</v>
       </c>
       <c r="K58" s="165">
         <f t="shared" si="3"/>
-        <v>193459285.82718199</v>
+        <v>177547609.53868502</v>
       </c>
       <c r="L58" s="165">
         <f t="shared" si="4"/>
-        <v>-114583.68997400254</v>
+        <v>-2852424.2499739975</v>
       </c>
       <c r="M58" s="165">
         <f t="shared" si="5"/>
-        <v>193344702.13720798</v>
+        <v>174695185.28871101</v>
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>27620671.733886857</v>
+        <v>29115864.21478517</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20775,7 +20777,7 @@
       </c>
       <c r="G59" s="177">
         <f>C23</f>
-        <v>75340784.659999996</v>
+        <v>77048823.620000005</v>
       </c>
       <c r="H59" s="177">
         <f>IF(D23="",0,D23)</f>
@@ -20783,15 +20785,15 @@
       </c>
       <c r="I59" s="177">
         <f>G59+H59</f>
-        <v>75340784.659999996</v>
+        <v>77048823.620000005</v>
       </c>
       <c r="J59" s="178">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.18642541161827092</v>
+        <v>0.19065183250856332</v>
       </c>
       <c r="K59" s="165">
         <f>D59-G59</f>
-        <v>328792879.34000003</v>
+        <v>327084840.38</v>
       </c>
       <c r="L59" s="165">
         <f>E59-H59</f>
@@ -20799,11 +20801,11 @@
       </c>
       <c r="M59" s="165">
         <f>F59-I59</f>
-        <v>328792879.34000003</v>
+        <v>327084840.38</v>
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>46970411.334285721</v>
+        <v>54514140.063333333</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20827,35 +20829,35 @@
       </c>
       <c r="G60" s="177">
         <f>M15</f>
-        <v>224832722.72200999</v>
+        <v>229667438.89206299</v>
       </c>
       <c r="H60" s="177">
         <f t="shared" ref="H60:H64" si="7">N15</f>
-        <v>84021028.886584997</v>
+        <v>85286416.286568999</v>
       </c>
       <c r="I60" s="177">
         <f t="shared" si="1"/>
-        <v>308853751.60859501</v>
+        <v>314953855.17863202</v>
       </c>
       <c r="J60" s="178">
         <f t="shared" si="2"/>
-        <v>0.61304832695295797</v>
+        <v>0.62515651171151687</v>
       </c>
       <c r="K60" s="165">
         <f t="shared" si="3"/>
-        <v>159184586.60154775</v>
+        <v>154349870.43149474</v>
       </c>
       <c r="L60" s="165">
         <f t="shared" si="4"/>
-        <v>35761669.113415003</v>
+        <v>34496281.713431001</v>
       </c>
       <c r="M60" s="165">
         <f t="shared" si="5"/>
-        <v>194946255.71496272</v>
+        <v>188846152.14492571</v>
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>27849465.102137532</v>
+        <v>31474358.690820951</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20879,35 +20881,35 @@
       </c>
       <c r="G61" s="177">
         <f>M16</f>
-        <v>349747815.26205099</v>
+        <v>372126112.94157797</v>
       </c>
       <c r="H61" s="177">
         <f t="shared" si="7"/>
-        <v>33596881.103970997</v>
+        <v>35479531.103970997</v>
       </c>
       <c r="I61" s="177">
         <f t="shared" si="1"/>
-        <v>383344696.36602199</v>
+        <v>407605644.04554898</v>
       </c>
       <c r="J61" s="178">
         <f t="shared" si="2"/>
-        <v>0.58823211604883763</v>
+        <v>0.62545988710231304</v>
       </c>
       <c r="K61" s="165">
         <f t="shared" si="3"/>
-        <v>261881780.45413661</v>
+        <v>239503482.77460963</v>
       </c>
       <c r="L61" s="165">
         <f t="shared" si="4"/>
-        <v>6463027.896029003</v>
+        <v>4580377.896029003</v>
       </c>
       <c r="M61" s="165">
         <f t="shared" si="5"/>
-        <v>268344808.35016561</v>
+        <v>244083860.67063862</v>
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>38334972.621452227</v>
+        <v>40680643.445106439</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20931,35 +20933,35 @@
       </c>
       <c r="G62" s="177">
         <f>M17</f>
-        <v>224610070.15044501</v>
+        <v>241854889.973326</v>
       </c>
       <c r="H62" s="177">
         <f t="shared" si="7"/>
-        <v>18528994.284492001</v>
+        <v>21552994.284492001</v>
       </c>
       <c r="I62" s="177">
         <f t="shared" si="1"/>
-        <v>243139064.434937</v>
+        <v>263407884.25781798</v>
       </c>
       <c r="J62" s="178">
         <f t="shared" si="2"/>
-        <v>0.5906802974071178</v>
+        <v>0.63992122275531249</v>
       </c>
       <c r="K62" s="165">
         <f t="shared" si="3"/>
-        <v>141932952.75493118</v>
+        <v>124688132.9320502</v>
       </c>
       <c r="L62" s="165">
         <f t="shared" si="4"/>
-        <v>26553468.715507999</v>
+        <v>23529468.715507999</v>
       </c>
       <c r="M62" s="165">
         <f t="shared" si="5"/>
-        <v>168486421.4704392</v>
+        <v>148217601.64755821</v>
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>24069488.781491313</v>
+        <v>24702933.607926369</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20983,35 +20985,35 @@
       </c>
       <c r="G63" s="177">
         <f>M18</f>
-        <v>556057347.75544596</v>
+        <v>558636301.53544605</v>
       </c>
       <c r="H63" s="177">
         <f t="shared" si="7"/>
-        <v>142236292.66712999</v>
+        <v>149549438.62712601</v>
       </c>
       <c r="I63" s="177">
         <f t="shared" si="1"/>
-        <v>698293640.42257595</v>
+        <v>708185740.16257203</v>
       </c>
       <c r="J63" s="178">
         <f t="shared" si="2"/>
-        <v>0.79852790085852121</v>
+        <v>0.80983992947112893</v>
       </c>
       <c r="K63" s="165">
         <f t="shared" si="3"/>
-        <v>7293594.3428337574</v>
+        <v>4714640.5628336668</v>
       </c>
       <c r="L63" s="165">
         <f t="shared" si="4"/>
-        <v>168888960.33287001</v>
+        <v>161575814.37287399</v>
       </c>
       <c r="M63" s="165">
         <f t="shared" si="5"/>
-        <v>176182554.67570376</v>
+        <v>166290454.93570769</v>
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>25168936.382243395</v>
+        <v>27715075.822617948</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21035,35 +21037,35 @@
       </c>
       <c r="G64" s="177">
         <f>M19</f>
-        <v>122674509.714931</v>
+        <v>123899988.51493099</v>
       </c>
       <c r="H64" s="177">
         <f t="shared" si="7"/>
-        <v>98311766.353484005</v>
+        <v>114171394.96325701</v>
       </c>
       <c r="I64" s="177">
         <f t="shared" si="1"/>
-        <v>220986276.06841499</v>
+        <v>238071383.47818801</v>
       </c>
       <c r="J64" s="178">
         <f t="shared" si="2"/>
-        <v>0.46152840701793219</v>
+        <v>0.49721054324308683</v>
       </c>
       <c r="K64" s="165">
         <f t="shared" si="3"/>
-        <v>116851179.29851778</v>
+        <v>115625700.49851778</v>
       </c>
       <c r="L64" s="165">
         <f t="shared" si="4"/>
-        <v>140976573.646516</v>
+        <v>125116945.03674299</v>
       </c>
       <c r="M64" s="165">
         <f t="shared" si="5"/>
-        <v>257827752.94503379</v>
+        <v>240742645.53526077</v>
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>36832536.135004826</v>
+        <v>40123774.255876794</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21085,35 +21087,35 @@
       </c>
       <c r="G65" s="182">
         <f>SUM(G51:G64)</f>
-        <v>4192452572.6824856</v>
+        <v>4419452819.0031805</v>
       </c>
       <c r="H65" s="182">
         <f>SUM(H51:H64)</f>
-        <v>675590820.65039814</v>
+        <v>719195196.70013499</v>
       </c>
       <c r="I65" s="182">
         <f>SUM(I51:I64)</f>
-        <v>4868043393.3328819</v>
+        <v>5138648015.7033148</v>
       </c>
       <c r="J65" s="183">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.61706366955609437</v>
+        <v>0.65136498279159905</v>
       </c>
       <c r="K65" s="166">
         <f>SUM(K51:K64)</f>
-        <v>2426826760.3823752</v>
+        <v>2199826514.0616798</v>
       </c>
       <c r="L65" s="166">
         <f>SUM(L51:L64)</f>
-        <v>594175391.34960198</v>
+        <v>550571015.29986501</v>
       </c>
       <c r="M65" s="166">
         <f>SUM(M51:M64)</f>
-        <v>3021002151.7319775</v>
+        <v>2750397529.3615441</v>
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>431571735.96171105</v>
+        <v>458399588.226924</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21159,7 +21161,7 @@
       </c>
       <c r="D70" s="192">
         <f>IF(E24="",0,E24)</f>
-        <v>8855098.9399919994</v>
+        <v>14098342.139992001</v>
       </c>
     </row>
     <row r="71" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21171,7 +21173,7 @@
       </c>
       <c r="D71" s="193">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>68977115.799999997</v>
+        <v>71877115.799999997</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21195,7 +21197,7 @@
       </c>
       <c r="D73" s="192">
         <f>IF(E14="",0,E14)</f>
-        <v>45719513.009985</v>
+        <v>52117711.149985</v>
       </c>
     </row>
     <row r="74" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21231,7 +21233,7 @@
       </c>
       <c r="D76" s="193">
         <f>IF(E19="",0,E19)</f>
-        <v>9455855.6500000004</v>
+        <v>71382881.099999994</v>
       </c>
     </row>
     <row r="77" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21243,7 +21245,7 @@
       </c>
       <c r="D77" s="192">
         <f>IF(E25="",0,E25)</f>
-        <v>16310504.299995</v>
+        <v>17896089.859995</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21279,7 +21281,7 @@
       </c>
       <c r="D80" s="192">
         <f>IF(E26="",0,E26)</f>
-        <v>44335136.559940003</v>
+        <v>48438740.129940003</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21291,7 +21293,7 @@
       </c>
       <c r="D81" s="193">
         <f>IF(E10="",0,E10)</f>
-        <v>41602827.579980001</v>
+        <v>48243818.519979998</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21325,17 +21327,17 @@
       <c r="C84" s="191"/>
       <c r="D84" s="194">
         <f>SUM(D70:D83)</f>
-        <v>291290487.57989204</v>
+        <v>380089134.43989199</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="221" t="s">
+      <c r="B87" s="228" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="222"/>
-      <c r="D87" s="222"/>
-      <c r="E87" s="222"/>
-      <c r="F87" s="223"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="230"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21377,19 +21379,19 @@
       </c>
       <c r="E89" s="177">
         <f>IFERROR(C32,0)</f>
-        <v>160437126.188869</v>
+        <v>168477998.51885799</v>
       </c>
       <c r="F89" s="178">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
-        <v>0.57423686541459096</v>
+        <v>0.60301677086201311</v>
       </c>
       <c r="G89" s="171">
         <f>D89-E89</f>
-        <v>118954769.1277712</v>
+        <v>110913896.79778221</v>
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>16993538.446824457</v>
+        <v>18485649.466297034</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21406,19 +21408,19 @@
       </c>
       <c r="E90" s="177">
         <f>IFERROR(C33,0)</f>
-        <v>358109822.376854</v>
+        <v>376402138.15180397</v>
       </c>
       <c r="F90" s="178">
         <f t="shared" si="9"/>
-        <v>0.85343092481595706</v>
+        <v>0.89702433385798197</v>
       </c>
       <c r="G90" s="172">
         <f>D90-E90</f>
-        <v>61502136.791464865</v>
+        <v>43209821.016514897</v>
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>8786019.5416378379</v>
+        <v>7201636.8360858159</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21435,19 +21437,19 @@
       </c>
       <c r="E91" s="177">
         <f>M21+M7</f>
-        <v>731746890.61302996</v>
+        <v>740872710.54296207</v>
       </c>
       <c r="F91" s="178">
         <f t="shared" si="9"/>
-        <v>0.66980008959292303</v>
+        <v>0.67815335365880325</v>
       </c>
       <c r="G91" s="171">
         <f>D91-E91</f>
-        <v>360738616.60413933</v>
+        <v>351612796.67420721</v>
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>51534088.086305618</v>
+        <v>58602132.779034533</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21520,19 +21522,19 @@
       </c>
       <c r="E94" s="198">
         <f>SUM(E89:E93)</f>
-        <v>1250293839.1787529</v>
+        <v>1285752847.213624</v>
       </c>
       <c r="F94" s="175">
         <f t="shared" si="9"/>
-        <v>0.69790748742756958</v>
+        <v>0.71770052041615562</v>
       </c>
       <c r="G94" s="173">
         <f>SUM(G89:G93)</f>
-        <v>541195522.52337539</v>
+        <v>505736514.48850429</v>
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>77313646.074767917</v>
+        <v>84289419.081417382</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21618,7 +21620,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23675,7 +23677,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -25732,7 +25734,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — DESEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 24 APRIL 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 25 APRIL 2026</t>
   </si>
 </sst>
 </file>
@@ -1870,13 +1870,13 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1891,13 +1891,13 @@
     <xf numFmtId="0" fontId="37" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -3552,17 +3552,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -4836,6 +4836,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4843,11 +4848,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -5609,17 +5609,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -6893,6 +6893,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6900,11 +6905,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -7666,17 +7666,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -8950,6 +8950,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8957,11 +8962,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9723,17 +9723,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -11007,6 +11007,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11014,11 +11019,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11779,17 +11779,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -13049,6 +13049,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13056,11 +13061,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19580,11 +19580,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>246290231.808541</v>
+        <v>255518993.06414101</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>36070926.893973</v>
+        <v>39885217.923969001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -19603,11 +19603,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>406504821.75153196</v>
+        <v>436278989.281528</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>87606856.103726998</v>
+        <v>99826919.693726003</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -19615,26 +19615,26 @@
         <v>113</v>
       </c>
       <c r="C10" s="174">
-        <v>241854889.973326</v>
+        <v>253483370.12761399</v>
       </c>
       <c r="D10" s="174">
         <v>21552994.284492001</v>
       </c>
       <c r="E10" s="174">
-        <v>48243818.519979998</v>
+        <v>50908683.359980002</v>
       </c>
       <c r="F10" s="174">
-        <v>311651702.777798</v>
+        <v>325945047.77208602</v>
       </c>
       <c r="G10"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>420632888.60480601</v>
+        <v>448000806.91979802</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>18258380.749756001</v>
+        <v>20953488.849736001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -19642,16 +19642,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="174">
-        <v>229667438.89206299</v>
+        <v>249864579.49204299</v>
       </c>
       <c r="D11" s="174">
-        <v>85286416.286568999</v>
+        <v>87626294.656564996</v>
       </c>
       <c r="E11" s="174">
         <v>34053355</v>
       </c>
       <c r="F11" s="174">
-        <v>349007210.17863202</v>
+        <v>371544229.14860803</v>
       </c>
       <c r="G11"/>
       <c r="J11" s="116"/>
@@ -19669,26 +19669,26 @@
         <v>70</v>
       </c>
       <c r="C12" s="174">
-        <v>196623063.70394099</v>
+        <v>221913114.06393701</v>
       </c>
       <c r="D12" s="174">
-        <v>54953437.733896002</v>
+        <v>67173501.323895007</v>
       </c>
       <c r="E12" s="174">
-        <v>66143242</v>
+        <v>71143242</v>
       </c>
       <c r="F12" s="174">
-        <v>317719743.437837</v>
+        <v>360229857.38783199</v>
       </c>
       <c r="G12"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>334431917.58384198</v>
+        <v>372425668.92464</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>43061962.927372001</v>
+        <v>43271972.007371001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -19696,7 +19696,7 @@
         <v>115</v>
       </c>
       <c r="C13" s="174">
-        <v>209881758.047591</v>
+        <v>214365875.21759099</v>
       </c>
       <c r="D13" s="174">
         <v>32653418.369831</v>
@@ -19705,13 +19705,13 @@
         <v>5733873.7999999998</v>
       </c>
       <c r="F13" s="174">
-        <v>248269050.21742201</v>
+        <v>252753167.387422</v>
       </c>
       <c r="G13"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>798074040.27580798</v>
+        <v>805458804.18249297</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -19723,26 +19723,26 @@
         <v>116</v>
       </c>
       <c r="C14" s="174">
-        <v>420632888.60480601</v>
+        <v>448000806.91979802</v>
       </c>
       <c r="D14" s="174">
-        <v>18258380.749756001</v>
+        <v>20953488.849736001</v>
       </c>
       <c r="E14" s="174">
-        <v>52117711.149985</v>
+        <v>57386179.549984999</v>
       </c>
       <c r="F14" s="174">
-        <v>491008980.504547</v>
+        <v>526340475.31951898</v>
       </c>
       <c r="G14"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>307739449.46131498</v>
+        <v>320568728.633407</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>47952136.249973997</v>
+        <v>52190986.249973997</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -19759,11 +19759,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>229667438.89206299</v>
+        <v>249864579.49204299</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>85286416.286568999</v>
+        <v>87626294.656564996</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -19771,26 +19771,26 @@
         <v>74</v>
       </c>
       <c r="C16" s="174">
-        <v>334431917.58384198</v>
+        <v>372425668.92464</v>
       </c>
       <c r="D16" s="174">
-        <v>43061962.927372001</v>
+        <v>43271972.007371001</v>
       </c>
       <c r="E16" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F16" s="174">
-        <v>377493880.51121402</v>
+        <v>415697640.93201101</v>
       </c>
       <c r="G16"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>372126112.94157797</v>
+        <v>382172318.87552702</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>35479531.103970997</v>
+        <v>38660763.533970997</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -19813,7 +19813,7 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>241854889.973326</v>
+        <v>253483370.12761399</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
@@ -19825,26 +19825,26 @@
         <v>119</v>
       </c>
       <c r="C18" s="174">
-        <v>1130504566.3698339</v>
+        <v>1195387993.289794</v>
       </c>
       <c r="D18" s="174">
-        <v>8425432.7548970003</v>
+        <v>8662432.7548970003</v>
       </c>
       <c r="E18" s="174">
         <v>1835135.12</v>
       </c>
       <c r="F18" s="174">
-        <v>1140765134.2447309</v>
+        <v>1205885561.164691</v>
       </c>
       <c r="G18"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>558636301.53544605</v>
+        <v>564832788.25544405</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>149549438.62712601</v>
+        <v>156779562.95306599</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
@@ -19852,26 +19852,26 @@
         <v>121</v>
       </c>
       <c r="C19" s="174">
-        <v>798074040.27580798</v>
+        <v>805458804.18249297</v>
       </c>
       <c r="D19" s="174">
         <v>41655590.999917999</v>
       </c>
       <c r="E19" s="174">
-        <v>71382881.099999994</v>
+        <v>90842339.400000006</v>
       </c>
       <c r="F19" s="174">
-        <v>911112512.37572598</v>
+        <v>937956734.58241105</v>
       </c>
       <c r="G19"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>123899988.51493099</v>
+        <v>129216007.474931</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>114171394.96325701</v>
+        <v>115058690.743251</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
@@ -19879,22 +19879,22 @@
         <v>123</v>
       </c>
       <c r="C20" s="174">
-        <v>78537400.514930993</v>
+        <v>83564319.474931002</v>
       </c>
       <c r="D20" s="174">
-        <v>13948889.939819001</v>
+        <v>14451727.799813</v>
       </c>
       <c r="E20" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F20" s="174">
-        <v>92486290.454750001</v>
+        <v>98016047.274744004</v>
       </c>
       <c r="G20"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>310992417.80997604</v>
+        <v>310879805.19997603</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -19905,22 +19905,22 @@
         <v>124</v>
       </c>
       <c r="C21" s="174">
-        <v>45362588</v>
+        <v>45651688</v>
       </c>
       <c r="D21" s="174">
-        <v>100222505.02343801</v>
+        <v>100606962.94343799</v>
       </c>
       <c r="E21" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F21" s="174">
-        <v>145585093.02343801</v>
+        <v>146258650.94343799</v>
       </c>
       <c r="G21"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>740872710.54296207</v>
+        <v>744324395.22494411</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -19952,16 +19952,16 @@
         <v>175</v>
       </c>
       <c r="C23" s="174">
-        <v>77048823.620000005</v>
+        <v>97280513.420000002</v>
       </c>
       <c r="D23" s="174" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="174">
-        <v>13608107.9</v>
+        <v>15680179.92</v>
       </c>
       <c r="F23" s="174">
-        <v>90656931.519999996</v>
+        <v>112960693.34</v>
       </c>
       <c r="G23"/>
       <c r="J23" s="116"/>
@@ -19973,16 +19973,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="174">
-        <v>246290231.808541</v>
+        <v>255518993.06414101</v>
       </c>
       <c r="D24" s="174">
-        <v>36070926.893973</v>
+        <v>39885217.923969001</v>
       </c>
       <c r="E24" s="174">
-        <v>14098342.139992001</v>
+        <v>15143387.159992</v>
       </c>
       <c r="F24" s="174">
-        <v>296459500.84250599</v>
+        <v>310547598.14810199</v>
       </c>
       <c r="G24"/>
       <c r="J24" s="116"/>
@@ -19992,16 +19992,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="174">
-        <v>307739449.46131498</v>
+        <v>320568728.633407</v>
       </c>
       <c r="D25" s="174">
-        <v>47952136.249973997</v>
+        <v>52190986.249973997</v>
       </c>
       <c r="E25" s="174">
-        <v>17896089.859995</v>
+        <v>18706900.659995001</v>
       </c>
       <c r="F25" s="174">
-        <v>373587675.571284</v>
+        <v>391466615.54337603</v>
       </c>
       <c r="G25"/>
       <c r="J25" s="116"/>
@@ -20011,16 +20011,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="174">
-        <v>372126112.94157797</v>
+        <v>382172318.87552702</v>
       </c>
       <c r="D26" s="174">
-        <v>35479531.103970997</v>
+        <v>38660763.533970997</v>
       </c>
       <c r="E26" s="174">
-        <v>48438740.129940003</v>
+        <v>49217118.49994</v>
       </c>
       <c r="F26" s="174">
-        <v>456044384.17548901</v>
+        <v>470050200.90943801</v>
       </c>
       <c r="G26"/>
       <c r="J26" s="116"/>
@@ -20030,16 +20030,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="174">
-        <v>558636301.53544605</v>
+        <v>564832788.25544405</v>
       </c>
       <c r="D27" s="174">
-        <v>149549438.62712601</v>
+        <v>156779562.95306599</v>
       </c>
       <c r="E27" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F27" s="174">
-        <v>708185740.16257203</v>
+        <v>721612351.20851004</v>
       </c>
       <c r="G27"/>
       <c r="J27" s="116"/>
@@ -20060,16 +20060,14 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="76"/>
-      <c r="C31" s="174">
-        <v>112612.61</v>
-      </c>
+      <c r="C31" s="174"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
       <c r="C32" s="174">
-        <v>168477998.51885799</v>
+        <v>169243403.87884599</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
@@ -20077,7 +20075,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="174">
-        <v>376402138.15180397</v>
+        <v>409188756.12131798</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
@@ -20085,7 +20083,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="174">
-        <v>262272038.98456201</v>
+        <v>264409309.23654401</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
@@ -20093,7 +20091,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="174">
-        <v>167608253.74842399</v>
+        <v>169035280.78842399</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
@@ -20123,7 +20121,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20164,19 +20162,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4419452819.0031805</v>
+        <v>4617647482.6915588</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.66766374353276969</v>
+        <v>0.69760577403423973</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2199826514.0616808</v>
+        <v>2001631850.3733025</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>366637752.34361345</v>
+        <v>400326370.07466048</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20192,19 +20190,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>719195196.70013499</v>
+        <v>756012049.406039</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.5663996961829183</v>
+        <v>0.59539468152586106</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>550571015.29986501</v>
+        <v>513754162.593961</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>91761835.88331084</v>
+        <v>102750832.5187922</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20220,19 +20218,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1285752847.213624</v>
+        <v>1322756555.2251081</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.71770052041615562</v>
+        <v>0.73835579685962061</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>505736514.48850441</v>
+        <v>468732806.47702026</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>84289419.081417397</v>
+        <v>93746561.295404047</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20246,37 +20244,37 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6424400862.9169397</v>
+        <v>6696416087.3227062</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.6636411029752175</v>
+        <v>0.69174029656581337</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>3256134043.85005</v>
+        <v>2984118819.4442835</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>542689007.30834162</v>
+        <v>596823763.88885665</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="221"/>
-      <c r="L48" s="222"/>
-      <c r="M48" s="222"/>
-      <c r="N48" s="223"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="228"/>
+      <c r="L48" s="229"/>
+      <c r="M48" s="229"/>
+      <c r="N48" s="230"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="227" t="s">
@@ -20361,35 +20359,35 @@
       </c>
       <c r="G51" s="177">
         <f>M8</f>
-        <v>246290231.808541</v>
+        <v>255518993.06414101</v>
       </c>
       <c r="H51" s="177">
         <f>N8</f>
-        <v>36070926.893973</v>
+        <v>39885217.923969001</v>
       </c>
       <c r="I51" s="177">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>282361158.70251399</v>
+        <v>295404210.98811001</v>
       </c>
       <c r="J51" s="178">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.63271063427511609</v>
+        <v>0.66193730951056329</v>
       </c>
       <c r="K51" s="164">
         <f t="shared" ref="K51:K64" si="3">D51-G51</f>
-        <v>150393246.5176757</v>
+        <v>141164485.26207569</v>
       </c>
       <c r="L51" s="164">
         <f t="shared" ref="L51:L64" si="4">E51-H51</f>
-        <v>13517782.106027</v>
+        <v>9703491.0760309994</v>
       </c>
       <c r="M51" s="164">
         <f t="shared" ref="M51:M64" si="5">F51-I51</f>
-        <v>163911028.6237027</v>
+        <v>150867976.33810669</v>
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>27318504.770617116</v>
+        <v>30173595.267621338</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20413,35 +20411,35 @@
       </c>
       <c r="G52" s="177">
         <f>M9</f>
-        <v>406504821.75153196</v>
+        <v>436278989.281528</v>
       </c>
       <c r="H52" s="177">
         <f>N9</f>
-        <v>87606856.103726998</v>
+        <v>99826919.693726003</v>
       </c>
       <c r="I52" s="177">
         <f t="shared" si="1"/>
-        <v>494111677.85525894</v>
+        <v>536105908.975254</v>
       </c>
       <c r="J52" s="178">
         <f t="shared" si="2"/>
-        <v>0.69785106744356618</v>
+        <v>0.75716097718050013</v>
       </c>
       <c r="K52" s="165">
         <f t="shared" si="3"/>
-        <v>128677549.24846804</v>
+        <v>98903381.718472004</v>
       </c>
       <c r="L52" s="165">
         <f t="shared" si="4"/>
-        <v>85258235.896273002</v>
+        <v>73038172.306273997</v>
       </c>
       <c r="M52" s="165">
         <f t="shared" si="5"/>
-        <v>213935785.14474106</v>
+        <v>171941554.024746</v>
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>35655964.190790176</v>
+        <v>34388310.804949202</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20493,7 +20491,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>32449603.300000001</v>
+        <v>38939523.960000001</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20517,35 +20515,35 @@
       </c>
       <c r="G54" s="177">
         <f>M10</f>
-        <v>420632888.60480601</v>
+        <v>448000806.91979802</v>
       </c>
       <c r="H54" s="177">
         <f t="shared" ref="H54:H58" si="6">N10</f>
-        <v>18258380.749756001</v>
+        <v>20953488.849736001</v>
       </c>
       <c r="I54" s="177">
         <f t="shared" si="1"/>
-        <v>438891269.35456198</v>
+        <v>468954295.76953399</v>
       </c>
       <c r="J54" s="178">
         <f t="shared" si="2"/>
-        <v>0.70913286374410223</v>
+        <v>0.75770680791440925</v>
       </c>
       <c r="K54" s="165">
         <f>D54-G54</f>
-        <v>170079583.31809121</v>
+        <v>142711665.0030992</v>
       </c>
       <c r="L54" s="165">
         <f t="shared" si="4"/>
-        <v>9941754.2502439991</v>
+        <v>7246646.1502639987</v>
       </c>
       <c r="M54" s="165">
         <f t="shared" si="5"/>
-        <v>180021337.56833524</v>
+        <v>149958311.15336323</v>
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>30003556.261389207</v>
+        <v>29991662.230672646</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20597,7 +20595,7 @@
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>29045319.973588526</v>
+        <v>34854383.968306229</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20621,35 +20619,35 @@
       </c>
       <c r="G56" s="177">
         <f>M12</f>
-        <v>334431917.58384198</v>
+        <v>372425668.92464</v>
       </c>
       <c r="H56" s="177">
         <f t="shared" si="6"/>
-        <v>43061962.927372001</v>
+        <v>43271972.007371001</v>
       </c>
       <c r="I56" s="177">
         <f t="shared" si="1"/>
-        <v>377493880.51121396</v>
+        <v>415697640.93201101</v>
       </c>
       <c r="J56" s="178">
         <f t="shared" si="2"/>
-        <v>0.70451966381680653</v>
+        <v>0.77581962876391564</v>
       </c>
       <c r="K56" s="165">
         <f t="shared" si="3"/>
-        <v>129486914.53881162</v>
+        <v>91493163.198013604</v>
       </c>
       <c r="L56" s="165">
         <f t="shared" si="4"/>
-        <v>28836585.072627999</v>
+        <v>28626575.992628999</v>
       </c>
       <c r="M56" s="165">
         <f t="shared" si="5"/>
-        <v>158323499.61143965</v>
+        <v>120119739.1906426</v>
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>26387249.935239941</v>
+        <v>24023947.838128518</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20673,7 +20671,7 @@
       </c>
       <c r="G57" s="177">
         <f>M13</f>
-        <v>798074040.27580798</v>
+        <v>805458804.18249297</v>
       </c>
       <c r="H57" s="177">
         <f t="shared" si="6"/>
@@ -20681,15 +20679,15 @@
       </c>
       <c r="I57" s="177">
         <f t="shared" si="1"/>
-        <v>839729631.27572596</v>
+        <v>847114395.18241096</v>
       </c>
       <c r="J57" s="178">
         <f t="shared" si="2"/>
-        <v>0.82731557130510436</v>
+        <v>0.834591163284788</v>
       </c>
       <c r="K57" s="165">
         <f t="shared" si="3"/>
-        <v>143684305.16891074</v>
+        <v>136299541.26222575</v>
       </c>
       <c r="L57" s="165">
         <f t="shared" si="4"/>
@@ -20697,11 +20695,11 @@
       </c>
       <c r="M57" s="165">
         <f t="shared" si="5"/>
-        <v>175275598.16899276</v>
+        <v>167890834.26230776</v>
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>29212599.694832128</v>
+        <v>33578166.852461554</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20725,35 +20723,35 @@
       </c>
       <c r="G58" s="177">
         <f>M14</f>
-        <v>307739449.46131498</v>
+        <v>320568728.633407</v>
       </c>
       <c r="H58" s="177">
         <f t="shared" si="6"/>
-        <v>47952136.249973997</v>
+        <v>52190986.249973997</v>
       </c>
       <c r="I58" s="177">
         <f>G58+H58</f>
-        <v>355691585.71128899</v>
+        <v>372759714.88338101</v>
       </c>
       <c r="J58" s="178">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.67062680511556161</v>
+        <v>0.70280733846467114</v>
       </c>
       <c r="K58" s="165">
         <f t="shared" si="3"/>
-        <v>177547609.53868502</v>
+        <v>164718330.366593</v>
       </c>
       <c r="L58" s="165">
         <f t="shared" si="4"/>
-        <v>-2852424.2499739975</v>
+        <v>-7091274.2499739975</v>
       </c>
       <c r="M58" s="165">
         <f t="shared" si="5"/>
-        <v>174695185.28871101</v>
+        <v>157627056.11661899</v>
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>29115864.21478517</v>
+        <v>31525411.2233238</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20777,7 +20775,7 @@
       </c>
       <c r="G59" s="177">
         <f>C23</f>
-        <v>77048823.620000005</v>
+        <v>97280513.420000002</v>
       </c>
       <c r="H59" s="177">
         <f>IF(D23="",0,D23)</f>
@@ -20785,15 +20783,15 @@
       </c>
       <c r="I59" s="177">
         <f>G59+H59</f>
-        <v>77048823.620000005</v>
+        <v>97280513.420000002</v>
       </c>
       <c r="J59" s="178">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.19065183250856332</v>
+        <v>0.24071370956120103</v>
       </c>
       <c r="K59" s="165">
         <f>D59-G59</f>
-        <v>327084840.38</v>
+        <v>306853150.57999998</v>
       </c>
       <c r="L59" s="165">
         <f>E59-H59</f>
@@ -20801,11 +20799,11 @@
       </c>
       <c r="M59" s="165">
         <f>F59-I59</f>
-        <v>327084840.38</v>
+        <v>306853150.57999998</v>
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>54514140.063333333</v>
+        <v>61370630.115999997</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20829,35 +20827,35 @@
       </c>
       <c r="G60" s="177">
         <f>M15</f>
-        <v>229667438.89206299</v>
+        <v>249864579.49204299</v>
       </c>
       <c r="H60" s="177">
         <f t="shared" ref="H60:H64" si="7">N15</f>
-        <v>85286416.286568999</v>
+        <v>87626294.656564996</v>
       </c>
       <c r="I60" s="177">
         <f t="shared" si="1"/>
-        <v>314953855.17863202</v>
+        <v>337490874.14860797</v>
       </c>
       <c r="J60" s="178">
         <f t="shared" si="2"/>
-        <v>0.62515651171151687</v>
+        <v>0.66989057015209552</v>
       </c>
       <c r="K60" s="165">
         <f t="shared" si="3"/>
-        <v>154349870.43149474</v>
+        <v>134152729.83151475</v>
       </c>
       <c r="L60" s="165">
         <f t="shared" si="4"/>
-        <v>34496281.713431001</v>
+        <v>32156403.343435004</v>
       </c>
       <c r="M60" s="165">
         <f t="shared" si="5"/>
-        <v>188846152.14492571</v>
+        <v>166309133.17494977</v>
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>31474358.690820951</v>
+        <v>33261826.634989955</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20881,35 +20879,35 @@
       </c>
       <c r="G61" s="177">
         <f>M16</f>
-        <v>372126112.94157797</v>
+        <v>382172318.87552702</v>
       </c>
       <c r="H61" s="177">
         <f t="shared" si="7"/>
-        <v>35479531.103970997</v>
+        <v>38660763.533970997</v>
       </c>
       <c r="I61" s="177">
         <f t="shared" si="1"/>
-        <v>407605644.04554898</v>
+        <v>420833082.40949804</v>
       </c>
       <c r="J61" s="178">
         <f t="shared" si="2"/>
-        <v>0.62545988710231304</v>
+        <v>0.64575703515859428</v>
       </c>
       <c r="K61" s="165">
         <f t="shared" si="3"/>
-        <v>239503482.77460963</v>
+        <v>229457276.84066057</v>
       </c>
       <c r="L61" s="165">
         <f t="shared" si="4"/>
-        <v>4580377.896029003</v>
+        <v>1399145.4660290033</v>
       </c>
       <c r="M61" s="165">
         <f t="shared" si="5"/>
-        <v>244083860.67063862</v>
+        <v>230856422.30668956</v>
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>40680643.445106439</v>
+        <v>46171284.461337909</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20933,7 +20931,7 @@
       </c>
       <c r="G62" s="177">
         <f>M17</f>
-        <v>241854889.973326</v>
+        <v>253483370.12761399</v>
       </c>
       <c r="H62" s="177">
         <f t="shared" si="7"/>
@@ -20941,15 +20939,15 @@
       </c>
       <c r="I62" s="177">
         <f t="shared" si="1"/>
-        <v>263407884.25781798</v>
+        <v>275036364.41210598</v>
       </c>
       <c r="J62" s="178">
         <f t="shared" si="2"/>
-        <v>0.63992122275531249</v>
+        <v>0.66817136895000451</v>
       </c>
       <c r="K62" s="165">
         <f t="shared" si="3"/>
-        <v>124688132.9320502</v>
+        <v>113059652.7777622</v>
       </c>
       <c r="L62" s="165">
         <f t="shared" si="4"/>
@@ -20957,11 +20955,11 @@
       </c>
       <c r="M62" s="165">
         <f t="shared" si="5"/>
-        <v>148217601.64755821</v>
+        <v>136589121.49327022</v>
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>24702933.607926369</v>
+        <v>27317824.298654042</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20985,35 +20983,35 @@
       </c>
       <c r="G63" s="177">
         <f>M18</f>
-        <v>558636301.53544605</v>
+        <v>564832788.25544405</v>
       </c>
       <c r="H63" s="177">
         <f t="shared" si="7"/>
-        <v>149549438.62712601</v>
+        <v>156779562.95306599</v>
       </c>
       <c r="I63" s="177">
         <f t="shared" si="1"/>
-        <v>708185740.16257203</v>
+        <v>721612351.20851004</v>
       </c>
       <c r="J63" s="178">
         <f t="shared" si="2"/>
-        <v>0.80983992947112893</v>
+        <v>0.82519381917241352</v>
       </c>
       <c r="K63" s="165">
         <f t="shared" si="3"/>
-        <v>4714640.5628336668</v>
+        <v>-1481846.1571643353</v>
       </c>
       <c r="L63" s="165">
         <f t="shared" si="4"/>
-        <v>161575814.37287399</v>
+        <v>154345690.04693401</v>
       </c>
       <c r="M63" s="165">
         <f t="shared" si="5"/>
-        <v>166290454.93570769</v>
+        <v>152863843.88976967</v>
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>27715075.822617948</v>
+        <v>30572768.777953934</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21037,35 +21035,35 @@
       </c>
       <c r="G64" s="177">
         <f>M19</f>
-        <v>123899988.51493099</v>
+        <v>129216007.474931</v>
       </c>
       <c r="H64" s="177">
         <f t="shared" si="7"/>
-        <v>114171394.96325701</v>
+        <v>115058690.743251</v>
       </c>
       <c r="I64" s="177">
         <f t="shared" si="1"/>
-        <v>238071383.47818801</v>
+        <v>244274698.218182</v>
       </c>
       <c r="J64" s="178">
         <f t="shared" si="2"/>
-        <v>0.49721054324308683</v>
+        <v>0.51016612592051036</v>
       </c>
       <c r="K64" s="165">
         <f t="shared" si="3"/>
-        <v>115625700.49851778</v>
+        <v>110309681.53851777</v>
       </c>
       <c r="L64" s="165">
         <f t="shared" si="4"/>
-        <v>125116945.03674299</v>
+        <v>124229649.256749</v>
       </c>
       <c r="M64" s="165">
         <f t="shared" si="5"/>
-        <v>240742645.53526077</v>
+        <v>234539330.79526678</v>
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>40123774.255876794</v>
+        <v>46907866.159053355</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21087,35 +21085,35 @@
       </c>
       <c r="G65" s="182">
         <f>SUM(G51:G64)</f>
-        <v>4419452819.0031805</v>
+        <v>4617647482.6915588</v>
       </c>
       <c r="H65" s="182">
         <f>SUM(H51:H64)</f>
-        <v>719195196.70013499</v>
+        <v>756012049.406039</v>
       </c>
       <c r="I65" s="182">
         <f>SUM(I51:I64)</f>
-        <v>5138648015.7033148</v>
+        <v>5373659532.0975981</v>
       </c>
       <c r="J65" s="183">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.65136498279159905</v>
+        <v>0.68115458345391233</v>
       </c>
       <c r="K65" s="166">
         <f>SUM(K51:K64)</f>
-        <v>2199826514.0616798</v>
+        <v>2001631850.3733013</v>
       </c>
       <c r="L65" s="166">
         <f>SUM(L51:L64)</f>
-        <v>550571015.29986501</v>
+        <v>513754162.593961</v>
       </c>
       <c r="M65" s="166">
         <f>SUM(M51:M64)</f>
-        <v>2750397529.3615441</v>
+        <v>2515386012.9672618</v>
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>458399588.226924</v>
+        <v>503077202.59345233</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21161,7 +21159,7 @@
       </c>
       <c r="D70" s="192">
         <f>IF(E24="",0,E24)</f>
-        <v>14098342.139992001</v>
+        <v>15143387.159992</v>
       </c>
     </row>
     <row r="71" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21173,7 +21171,7 @@
       </c>
       <c r="D71" s="193">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>71877115.799999997</v>
+        <v>76877115.799999997</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21197,7 +21195,7 @@
       </c>
       <c r="D73" s="192">
         <f>IF(E14="",0,E14)</f>
-        <v>52117711.149985</v>
+        <v>57386179.549984999</v>
       </c>
     </row>
     <row r="74" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21233,7 +21231,7 @@
       </c>
       <c r="D76" s="193">
         <f>IF(E19="",0,E19)</f>
-        <v>71382881.099999994</v>
+        <v>90842339.400000006</v>
       </c>
     </row>
     <row r="77" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21245,7 +21243,7 @@
       </c>
       <c r="D77" s="192">
         <f>IF(E25="",0,E25)</f>
-        <v>17896089.859995</v>
+        <v>18706900.659995001</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21257,7 +21255,7 @@
       </c>
       <c r="D78" s="193">
         <f>IF(E23="",0,E23)</f>
-        <v>13608107.9</v>
+        <v>15680179.92</v>
       </c>
     </row>
     <row r="79" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21281,7 +21279,7 @@
       </c>
       <c r="D80" s="192">
         <f>IF(E26="",0,E26)</f>
-        <v>48438740.129940003</v>
+        <v>49217118.49994</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21293,7 +21291,7 @@
       </c>
       <c r="D81" s="193">
         <f>IF(E10="",0,E10)</f>
-        <v>48243818.519979998</v>
+        <v>50908683.359980002</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21327,17 +21325,17 @@
       <c r="C84" s="191"/>
       <c r="D84" s="194">
         <f>SUM(D70:D83)</f>
-        <v>380089134.43989199</v>
+        <v>417188232.18989193</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="228" t="s">
+      <c r="B87" s="221" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="229"/>
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="230"/>
+      <c r="C87" s="222"/>
+      <c r="D87" s="222"/>
+      <c r="E87" s="222"/>
+      <c r="F87" s="223"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21379,19 +21377,19 @@
       </c>
       <c r="E89" s="177">
         <f>IFERROR(C32,0)</f>
-        <v>168477998.51885799</v>
+        <v>169243403.87884599</v>
       </c>
       <c r="F89" s="178">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
-        <v>0.60301677086201311</v>
+        <v>0.60575631117373396</v>
       </c>
       <c r="G89" s="171">
         <f>D89-E89</f>
-        <v>110913896.79778221</v>
+        <v>110148491.43779421</v>
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>18485649.466297034</v>
+        <v>22029698.287558842</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21408,19 +21406,19 @@
       </c>
       <c r="E90" s="177">
         <f>IFERROR(C33,0)</f>
-        <v>376402138.15180397</v>
+        <v>409188756.12131798</v>
       </c>
       <c r="F90" s="178">
         <f t="shared" si="9"/>
-        <v>0.89702433385798197</v>
+        <v>0.97515989995218455</v>
       </c>
       <c r="G90" s="172">
         <f>D90-E90</f>
-        <v>43209821.016514897</v>
+        <v>10423203.047000885</v>
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>7201636.8360858159</v>
+        <v>2084640.6094001769</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21437,19 +21435,19 @@
       </c>
       <c r="E91" s="177">
         <f>M21+M7</f>
-        <v>740872710.54296207</v>
+        <v>744324395.22494411</v>
       </c>
       <c r="F91" s="178">
         <f t="shared" si="9"/>
-        <v>0.67815335365880325</v>
+        <v>0.6813128323513622</v>
       </c>
       <c r="G91" s="171">
         <f>D91-E91</f>
-        <v>351612796.67420721</v>
+        <v>348161111.99222517</v>
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>58602132.779034533</v>
+        <v>69632222.39844504</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21522,19 +21520,19 @@
       </c>
       <c r="E94" s="198">
         <f>SUM(E89:E93)</f>
-        <v>1285752847.213624</v>
+        <v>1322756555.2251081</v>
       </c>
       <c r="F94" s="175">
         <f t="shared" si="9"/>
-        <v>0.71770052041615562</v>
+        <v>0.73835579685962061</v>
       </c>
       <c r="G94" s="173">
         <f>SUM(G89:G93)</f>
-        <v>505736514.48850429</v>
+        <v>468732806.47702026</v>
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>84289419.081417382</v>
+        <v>93746561.295404047</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21620,7 +21618,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22313,17 +22311,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -23597,6 +23595,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23604,11 +23607,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23677,7 +23675,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -24370,17 +24368,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -25654,6 +25652,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25661,11 +25664,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25734,7 +25732,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -26427,17 +26425,17 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="234"/>
       <c r="L48" s="235"/>
       <c r="M48" s="235"/>
@@ -27711,6 +27709,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27718,11 +27721,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — DESEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 25 APRIL 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 27 APRIL 2026</t>
   </si>
 </sst>
 </file>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -4836,11 +4836,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4848,6 +4843,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -6893,11 +6893,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6905,6 +6900,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -8950,11 +8950,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8962,6 +8957,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11007,11 +11007,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11019,6 +11014,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -13049,11 +13049,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13061,6 +13056,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19580,11 +19580,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>255518993.06414101</v>
+        <v>259416350.98412701</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>39885217.923969001</v>
+        <v>41315217.923969001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -19603,11 +19603,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>436278989.281528</v>
+        <v>453952232.14149296</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>99826919.693726003</v>
+        <v>100272716.993726</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -19615,22 +19615,22 @@
         <v>113</v>
       </c>
       <c r="C10" s="174">
-        <v>253483370.12761399</v>
+        <v>258387613.393603</v>
       </c>
       <c r="D10" s="174">
-        <v>21552994.284492001</v>
+        <v>22056994.284492001</v>
       </c>
       <c r="E10" s="174">
-        <v>50908683.359980002</v>
+        <v>51908683.359980002</v>
       </c>
       <c r="F10" s="174">
-        <v>325945047.77208602</v>
+        <v>332353291.03807497</v>
       </c>
       <c r="G10"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>448000806.91979802</v>
+        <v>463195607.91979802</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -19642,22 +19642,22 @@
         <v>114</v>
       </c>
       <c r="C11" s="174">
-        <v>249864579.49204299</v>
+        <v>257676819.092033</v>
       </c>
       <c r="D11" s="174">
-        <v>87626294.656564996</v>
+        <v>89431321.466564998</v>
       </c>
       <c r="E11" s="174">
         <v>34053355</v>
       </c>
       <c r="F11" s="174">
-        <v>371544229.14860803</v>
+        <v>381161495.55859798</v>
       </c>
       <c r="G11"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>255770265.839993</v>
+        <v>289734229.18999302</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -19669,26 +19669,26 @@
         <v>70</v>
       </c>
       <c r="C12" s="174">
-        <v>221913114.06393701</v>
+        <v>230388249.16392699</v>
       </c>
       <c r="D12" s="174">
-        <v>67173501.323895007</v>
+        <v>67470798.623895004</v>
       </c>
       <c r="E12" s="174">
         <v>71143242</v>
       </c>
       <c r="F12" s="174">
-        <v>360229857.38783199</v>
+        <v>369002289.78782201</v>
       </c>
       <c r="G12"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>372425668.92464</v>
+        <v>400873434.68683398</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>43271972.007371001</v>
+        <v>49880188.247367002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -19696,26 +19696,26 @@
         <v>115</v>
       </c>
       <c r="C13" s="174">
-        <v>214365875.21759099</v>
+        <v>223563982.977566</v>
       </c>
       <c r="D13" s="174">
-        <v>32653418.369831</v>
+        <v>32801918.369831</v>
       </c>
       <c r="E13" s="174">
-        <v>5733873.7999999998</v>
+        <v>7306846.7599999998</v>
       </c>
       <c r="F13" s="174">
-        <v>252753167.387422</v>
+        <v>263672748.10739699</v>
       </c>
       <c r="G13"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>805458804.18249297</v>
+        <v>846052742.05182004</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>41655590.999917999</v>
+        <v>51156635.799857996</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -19723,7 +19723,7 @@
         <v>116</v>
       </c>
       <c r="C14" s="174">
-        <v>448000806.91979802</v>
+        <v>463195607.91979802</v>
       </c>
       <c r="D14" s="174">
         <v>20953488.849736001</v>
@@ -19732,17 +19732,17 @@
         <v>57386179.549984999</v>
       </c>
       <c r="F14" s="174">
-        <v>526340475.31951898</v>
+        <v>541535276.31951904</v>
       </c>
       <c r="G14"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>320568728.633407</v>
+        <v>334556563.810857</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>52190986.249973997</v>
+        <v>54790085.349973999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -19759,11 +19759,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>249864579.49204299</v>
+        <v>257676819.092033</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>87626294.656564996</v>
+        <v>89431321.466564998</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -19771,26 +19771,26 @@
         <v>74</v>
       </c>
       <c r="C16" s="174">
-        <v>372425668.92464</v>
+        <v>400873434.68683398</v>
       </c>
       <c r="D16" s="174">
-        <v>43271972.007371001</v>
+        <v>49880188.247367002</v>
       </c>
       <c r="E16" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F16" s="174">
-        <v>415697640.93201101</v>
+        <v>450753622.934201</v>
       </c>
       <c r="G16"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>382172318.87552702</v>
+        <v>399179134.232728</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>38660763.533970997</v>
+        <v>39627430.193971001</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -19798,7 +19798,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="174">
-        <v>255770265.839993</v>
+        <v>289734229.18999302</v>
       </c>
       <c r="D17" s="174">
         <v>38549567.509999998</v>
@@ -19807,17 +19807,17 @@
         <v>170</v>
       </c>
       <c r="F17" s="174">
-        <v>294319833.34999299</v>
+        <v>328283796.69999301</v>
       </c>
       <c r="G17"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>253483370.12761399</v>
+        <v>258387613.393603</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>21552994.284492001</v>
+        <v>22056994.284492001</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
@@ -19825,7 +19825,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="174">
-        <v>1195387993.289794</v>
+        <v>1247382774.9297941</v>
       </c>
       <c r="D18" s="174">
         <v>8662432.7548970003</v>
@@ -19834,13 +19834,13 @@
         <v>1835135.12</v>
       </c>
       <c r="F18" s="174">
-        <v>1205885561.164691</v>
+        <v>1257880342.8046911</v>
       </c>
       <c r="G18"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>564832788.25544405</v>
+        <v>573634588.45515394</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -19852,26 +19852,26 @@
         <v>121</v>
       </c>
       <c r="C19" s="174">
-        <v>805458804.18249297</v>
+        <v>846052742.05182004</v>
       </c>
       <c r="D19" s="174">
-        <v>41655590.999917999</v>
+        <v>51156635.799857996</v>
       </c>
       <c r="E19" s="174">
         <v>90842339.400000006</v>
       </c>
       <c r="F19" s="174">
-        <v>937956734.58241105</v>
+        <v>988051717.25167799</v>
       </c>
       <c r="G19"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>129216007.474931</v>
+        <v>142906117.71240199</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>115058690.743251</v>
+        <v>115588826.743251</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
@@ -19879,7 +19879,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="174">
-        <v>83564319.474931002</v>
+        <v>95172652.392401993</v>
       </c>
       <c r="D20" s="174">
         <v>14451727.799813</v>
@@ -19888,13 +19888,13 @@
         <v>170</v>
       </c>
       <c r="F20" s="174">
-        <v>98016047.274744004</v>
+        <v>109624380.192215</v>
       </c>
       <c r="G20"/>
       <c r="J20" s="116"/>
       <c r="M20" s="14">
         <f>IFERROR(C31,0)+IFERROR(C15,0)+IFERROR(C36,0)</f>
-        <v>310879805.19997603</v>
+        <v>311290805.19997603</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>120</v>
@@ -19905,22 +19905,22 @@
         <v>124</v>
       </c>
       <c r="C21" s="174">
-        <v>45651688</v>
+        <v>47733465.32</v>
       </c>
       <c r="D21" s="174">
-        <v>100606962.94343799</v>
+        <v>101137098.94343799</v>
       </c>
       <c r="E21" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F21" s="174">
-        <v>146258650.94343799</v>
+        <v>148870564.26343799</v>
       </c>
       <c r="G21"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>744324395.22494411</v>
+        <v>747738503.38492</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -19973,16 +19973,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="174">
-        <v>255518993.06414101</v>
+        <v>259416350.98412701</v>
       </c>
       <c r="D24" s="174">
-        <v>39885217.923969001</v>
+        <v>41315217.923969001</v>
       </c>
       <c r="E24" s="174">
         <v>15143387.159992</v>
       </c>
       <c r="F24" s="174">
-        <v>310547598.14810199</v>
+        <v>315874956.068088</v>
       </c>
       <c r="G24"/>
       <c r="J24" s="116"/>
@@ -19992,16 +19992,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="174">
-        <v>320568728.633407</v>
+        <v>334556563.810857</v>
       </c>
       <c r="D25" s="174">
-        <v>52190986.249973997</v>
+        <v>54790085.349973999</v>
       </c>
       <c r="E25" s="174">
-        <v>18706900.659995001</v>
+        <v>19583477.219994999</v>
       </c>
       <c r="F25" s="174">
-        <v>391466615.54337603</v>
+        <v>408930126.380826</v>
       </c>
       <c r="G25"/>
       <c r="J25" s="116"/>
@@ -20011,16 +20011,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="174">
-        <v>382172318.87552702</v>
+        <v>399179134.232728</v>
       </c>
       <c r="D26" s="174">
-        <v>38660763.533970997</v>
+        <v>39627430.193971001</v>
       </c>
       <c r="E26" s="174">
-        <v>49217118.49994</v>
+        <v>64357660.099909998</v>
       </c>
       <c r="F26" s="174">
-        <v>470050200.90943801</v>
+        <v>503164224.526609</v>
       </c>
       <c r="G26"/>
       <c r="J26" s="116"/>
@@ -20030,7 +20030,7 @@
         <v>128</v>
       </c>
       <c r="C27" s="174">
-        <v>564832788.25544405</v>
+        <v>573634588.45515394</v>
       </c>
       <c r="D27" s="174">
         <v>156779562.95306599</v>
@@ -20039,7 +20039,7 @@
         <v>170</v>
       </c>
       <c r="F27" s="174">
-        <v>721612351.20851004</v>
+        <v>730414151.40822005</v>
       </c>
       <c r="G27"/>
       <c r="J27" s="116"/>
@@ -20067,7 +20067,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="174">
-        <v>169243403.87884599</v>
+        <v>174072142.48878601</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
@@ -20075,7 +20075,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="174">
-        <v>409188756.12131798</v>
+        <v>445809428.55673301</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
@@ -20083,7 +20083,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="174">
-        <v>264409309.23654401</v>
+        <v>267412417.39651999</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
@@ -20099,7 +20099,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="174">
-        <v>310879805.19997603</v>
+        <v>311290805.19997603</v>
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.83333333333333337</v>
+        <v>0.9</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20162,19 +20162,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4617647482.6915588</v>
+        <v>4823621595.2908421</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.69760577403423973</v>
+        <v>0.72872307581819584</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2001631850.3733025</v>
+        <v>1795657737.7740192</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>400326370.07466048</v>
+        <v>448914434.44350481</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20190,19 +20190,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>756012049.406039</v>
+        <v>780402036.31597483</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.59539468152586106</v>
+        <v>0.61460293157964019</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>513754162.593961</v>
+        <v>489364175.68402517</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>102750832.5187922</v>
+        <v>122341043.92100629</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20218,19 +20218,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1322756555.2251081</v>
+        <v>1367620074.430439</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.73835579685962061</v>
+        <v>0.76339837883884332</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>468732806.47702026</v>
+        <v>423869287.27168941</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>93746561.295404047</v>
+        <v>105967321.81792235</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20244,19 +20244,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6696416087.3227062</v>
+        <v>6971643706.0372562</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.69174029656581337</v>
+        <v>0.72017133073543937</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2984118819.4442835</v>
+        <v>2708891200.7297339</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>596823763.88885665</v>
+        <v>677222800.18243349</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20359,35 +20359,35 @@
       </c>
       <c r="G51" s="177">
         <f>M8</f>
-        <v>255518993.06414101</v>
+        <v>259416350.98412701</v>
       </c>
       <c r="H51" s="177">
         <f>N8</f>
-        <v>39885217.923969001</v>
+        <v>41315217.923969001</v>
       </c>
       <c r="I51" s="177">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>295404210.98811001</v>
+        <v>300731568.90809602</v>
       </c>
       <c r="J51" s="178">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.66193730951056329</v>
+        <v>0.67387477294942155</v>
       </c>
       <c r="K51" s="164">
         <f t="shared" ref="K51:K64" si="3">D51-G51</f>
-        <v>141164485.26207569</v>
+        <v>137267127.34208968</v>
       </c>
       <c r="L51" s="164">
         <f t="shared" ref="L51:L64" si="4">E51-H51</f>
-        <v>9703491.0760309994</v>
+        <v>8273491.0760309994</v>
       </c>
       <c r="M51" s="164">
         <f t="shared" ref="M51:M64" si="5">F51-I51</f>
-        <v>150867976.33810669</v>
+        <v>145540618.41812068</v>
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>30173595.267621338</v>
+        <v>36385154.604530171</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20411,35 +20411,35 @@
       </c>
       <c r="G52" s="177">
         <f>M9</f>
-        <v>436278989.281528</v>
+        <v>453952232.14149296</v>
       </c>
       <c r="H52" s="177">
         <f>N9</f>
-        <v>99826919.693726003</v>
+        <v>100272716.993726</v>
       </c>
       <c r="I52" s="177">
         <f t="shared" si="1"/>
-        <v>536105908.975254</v>
+        <v>554224949.13521898</v>
       </c>
       <c r="J52" s="178">
         <f t="shared" si="2"/>
-        <v>0.75716097718050013</v>
+        <v>0.78275112629733268</v>
       </c>
       <c r="K52" s="165">
         <f t="shared" si="3"/>
-        <v>98903381.718472004</v>
+        <v>81230138.858507037</v>
       </c>
       <c r="L52" s="165">
         <f t="shared" si="4"/>
-        <v>73038172.306273997</v>
+        <v>72592375.006274</v>
       </c>
       <c r="M52" s="165">
         <f t="shared" si="5"/>
-        <v>171941554.024746</v>
+        <v>153822513.86478102</v>
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>34388310.804949202</v>
+        <v>38455628.466195256</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>38939523.960000001</v>
+        <v>48674404.950000003</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20515,7 +20515,7 @@
       </c>
       <c r="G54" s="177">
         <f>M10</f>
-        <v>448000806.91979802</v>
+        <v>463195607.91979802</v>
       </c>
       <c r="H54" s="177">
         <f t="shared" ref="H54:H58" si="6">N10</f>
@@ -20523,15 +20523,15 @@
       </c>
       <c r="I54" s="177">
         <f t="shared" si="1"/>
-        <v>468954295.76953399</v>
+        <v>484149096.76953399</v>
       </c>
       <c r="J54" s="178">
         <f t="shared" si="2"/>
-        <v>0.75770680791440925</v>
+        <v>0.78225761012790007</v>
       </c>
       <c r="K54" s="165">
         <f>D54-G54</f>
-        <v>142711665.0030992</v>
+        <v>127516864.0030992</v>
       </c>
       <c r="L54" s="165">
         <f t="shared" si="4"/>
@@ -20539,11 +20539,11 @@
       </c>
       <c r="M54" s="165">
         <f t="shared" si="5"/>
-        <v>149958311.15336323</v>
+        <v>134763510.15336323</v>
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>29991662.230672646</v>
+        <v>33690877.538340807</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="G55" s="177">
         <f>M11</f>
-        <v>255770265.839993</v>
+        <v>289734229.18999302</v>
       </c>
       <c r="H55" s="177">
         <f t="shared" si="6"/>
@@ -20575,15 +20575,15 @@
       </c>
       <c r="I55" s="177">
         <f t="shared" si="1"/>
-        <v>294319833.34999299</v>
+        <v>328283796.69999301</v>
       </c>
       <c r="J55" s="178">
         <f t="shared" si="2"/>
-        <v>0.62809435152329229</v>
+        <v>0.70057527573648082</v>
       </c>
       <c r="K55" s="165">
         <f t="shared" si="3"/>
-        <v>139293018.35153115</v>
+        <v>105329055.00153112</v>
       </c>
       <c r="L55" s="165">
         <f t="shared" si="4"/>
@@ -20591,11 +20591,11 @@
       </c>
       <c r="M55" s="165">
         <f t="shared" si="5"/>
-        <v>174271919.84153116</v>
+        <v>140307956.49153113</v>
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>34854383.968306229</v>
+        <v>35076989.122882783</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20619,35 +20619,35 @@
       </c>
       <c r="G56" s="177">
         <f>M12</f>
-        <v>372425668.92464</v>
+        <v>400873434.68683398</v>
       </c>
       <c r="H56" s="177">
         <f t="shared" si="6"/>
-        <v>43271972.007371001</v>
+        <v>49880188.247367002</v>
       </c>
       <c r="I56" s="177">
         <f t="shared" si="1"/>
-        <v>415697640.93201101</v>
+        <v>450753622.934201</v>
       </c>
       <c r="J56" s="178">
         <f t="shared" si="2"/>
-        <v>0.77581962876391564</v>
+        <v>0.8412448712115671</v>
       </c>
       <c r="K56" s="165">
         <f t="shared" si="3"/>
-        <v>91493163.198013604</v>
+        <v>63045397.435819626</v>
       </c>
       <c r="L56" s="165">
         <f t="shared" si="4"/>
-        <v>28626575.992628999</v>
+        <v>22018359.752632998</v>
       </c>
       <c r="M56" s="165">
         <f t="shared" si="5"/>
-        <v>120119739.1906426</v>
+        <v>85063757.188452601</v>
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>24023947.838128518</v>
+        <v>21265939.29711315</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20671,35 +20671,35 @@
       </c>
       <c r="G57" s="177">
         <f>M13</f>
-        <v>805458804.18249297</v>
+        <v>846052742.05182004</v>
       </c>
       <c r="H57" s="177">
         <f t="shared" si="6"/>
-        <v>41655590.999917999</v>
+        <v>51156635.799857996</v>
       </c>
       <c r="I57" s="177">
         <f t="shared" si="1"/>
-        <v>847114395.18241096</v>
+        <v>897209377.85167801</v>
       </c>
       <c r="J57" s="178">
         <f t="shared" si="2"/>
-        <v>0.834591163284788</v>
+        <v>0.88394557173120814</v>
       </c>
       <c r="K57" s="165">
         <f t="shared" si="3"/>
-        <v>136299541.26222575</v>
+        <v>95705603.392898679</v>
       </c>
       <c r="L57" s="165">
         <f t="shared" si="4"/>
-        <v>31591293.000082001</v>
+        <v>22090248.200142004</v>
       </c>
       <c r="M57" s="165">
         <f t="shared" si="5"/>
-        <v>167890834.26230776</v>
+        <v>117795851.5930407</v>
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>33578166.852461554</v>
+        <v>29448962.898260176</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20723,35 +20723,35 @@
       </c>
       <c r="G58" s="177">
         <f>M14</f>
-        <v>320568728.633407</v>
+        <v>334556563.810857</v>
       </c>
       <c r="H58" s="177">
         <f t="shared" si="6"/>
-        <v>52190986.249973997</v>
+        <v>54790085.349973999</v>
       </c>
       <c r="I58" s="177">
         <f>G58+H58</f>
-        <v>372759714.88338101</v>
+        <v>389346649.16083097</v>
       </c>
       <c r="J58" s="178">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.70280733846467114</v>
+        <v>0.73408061899196764</v>
       </c>
       <c r="K58" s="165">
         <f t="shared" si="3"/>
-        <v>164718330.366593</v>
+        <v>150730495.189143</v>
       </c>
       <c r="L58" s="165">
         <f t="shared" si="4"/>
-        <v>-7091274.2499739975</v>
+        <v>-9690373.349973999</v>
       </c>
       <c r="M58" s="165">
         <f t="shared" si="5"/>
-        <v>157627056.11661899</v>
+        <v>141040121.83916903</v>
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>31525411.2233238</v>
+        <v>35260030.459792256</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>61370630.115999997</v>
+        <v>76713287.644999996</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20827,35 +20827,35 @@
       </c>
       <c r="G60" s="177">
         <f>M15</f>
-        <v>249864579.49204299</v>
+        <v>257676819.092033</v>
       </c>
       <c r="H60" s="177">
         <f t="shared" ref="H60:H64" si="7">N15</f>
-        <v>87626294.656564996</v>
+        <v>89431321.466564998</v>
       </c>
       <c r="I60" s="177">
         <f t="shared" si="1"/>
-        <v>337490874.14860797</v>
+        <v>347108140.55859798</v>
       </c>
       <c r="J60" s="178">
         <f t="shared" si="2"/>
-        <v>0.66989057015209552</v>
+        <v>0.68898002285195115</v>
       </c>
       <c r="K60" s="165">
         <f t="shared" si="3"/>
-        <v>134152729.83151475</v>
+        <v>126340490.23152474</v>
       </c>
       <c r="L60" s="165">
         <f t="shared" si="4"/>
-        <v>32156403.343435004</v>
+        <v>30351376.533435002</v>
       </c>
       <c r="M60" s="165">
         <f t="shared" si="5"/>
-        <v>166309133.17494977</v>
+        <v>156691866.76495975</v>
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>33261826.634989955</v>
+        <v>39172966.691239938</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20879,35 +20879,35 @@
       </c>
       <c r="G61" s="177">
         <f>M16</f>
-        <v>382172318.87552702</v>
+        <v>399179134.232728</v>
       </c>
       <c r="H61" s="177">
         <f t="shared" si="7"/>
-        <v>38660763.533970997</v>
+        <v>39627430.193971001</v>
       </c>
       <c r="I61" s="177">
         <f t="shared" si="1"/>
-        <v>420833082.40949804</v>
+        <v>438806564.42669898</v>
       </c>
       <c r="J61" s="178">
         <f t="shared" si="2"/>
-        <v>0.64575703515859428</v>
+        <v>0.67333685942633115</v>
       </c>
       <c r="K61" s="165">
         <f t="shared" si="3"/>
-        <v>229457276.84066057</v>
+        <v>212450461.48345959</v>
       </c>
       <c r="L61" s="165">
         <f t="shared" si="4"/>
-        <v>1399145.4660290033</v>
+        <v>432478.80602899939</v>
       </c>
       <c r="M61" s="165">
         <f t="shared" si="5"/>
-        <v>230856422.30668956</v>
+        <v>212882940.28948861</v>
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>46171284.461337909</v>
+        <v>53220735.072372153</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20931,35 +20931,35 @@
       </c>
       <c r="G62" s="177">
         <f>M17</f>
-        <v>253483370.12761399</v>
+        <v>258387613.393603</v>
       </c>
       <c r="H62" s="177">
         <f t="shared" si="7"/>
-        <v>21552994.284492001</v>
+        <v>22056994.284492001</v>
       </c>
       <c r="I62" s="177">
         <f t="shared" si="1"/>
-        <v>275036364.41210598</v>
+        <v>280444607.67809498</v>
       </c>
       <c r="J62" s="178">
         <f t="shared" si="2"/>
-        <v>0.66817136895000451</v>
+        <v>0.68131011630937532</v>
       </c>
       <c r="K62" s="165">
         <f t="shared" si="3"/>
-        <v>113059652.7777622</v>
+        <v>108155409.5117732</v>
       </c>
       <c r="L62" s="165">
         <f t="shared" si="4"/>
-        <v>23529468.715507999</v>
+        <v>23025468.715507999</v>
       </c>
       <c r="M62" s="165">
         <f t="shared" si="5"/>
-        <v>136589121.49327022</v>
+        <v>131180878.22728121</v>
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>27317824.298654042</v>
+        <v>32795219.556820303</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="G63" s="177">
         <f>M18</f>
-        <v>564832788.25544405</v>
+        <v>573634588.45515394</v>
       </c>
       <c r="H63" s="177">
         <f t="shared" si="7"/>
@@ -20991,15 +20991,15 @@
       </c>
       <c r="I63" s="177">
         <f t="shared" si="1"/>
-        <v>721612351.20851004</v>
+        <v>730414151.40821993</v>
       </c>
       <c r="J63" s="178">
         <f t="shared" si="2"/>
-        <v>0.82519381917241352</v>
+        <v>0.83525904478867019</v>
       </c>
       <c r="K63" s="165">
         <f t="shared" si="3"/>
-        <v>-1481846.1571643353</v>
+        <v>-10283646.356874228</v>
       </c>
       <c r="L63" s="165">
         <f t="shared" si="4"/>
@@ -21007,11 +21007,11 @@
       </c>
       <c r="M63" s="165">
         <f t="shared" si="5"/>
-        <v>152863843.88976967</v>
+        <v>144062043.69005978</v>
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>30572768.777953934</v>
+        <v>36015510.922514945</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21035,35 +21035,35 @@
       </c>
       <c r="G64" s="177">
         <f>M19</f>
-        <v>129216007.474931</v>
+        <v>142906117.71240199</v>
       </c>
       <c r="H64" s="177">
         <f t="shared" si="7"/>
-        <v>115058690.743251</v>
+        <v>115588826.743251</v>
       </c>
       <c r="I64" s="177">
         <f t="shared" si="1"/>
-        <v>244274698.218182</v>
+        <v>258494944.45565298</v>
       </c>
       <c r="J64" s="178">
         <f t="shared" si="2"/>
-        <v>0.51016612592051036</v>
+        <v>0.53986501813294296</v>
       </c>
       <c r="K64" s="165">
         <f t="shared" si="3"/>
-        <v>110309681.53851777</v>
+        <v>96619571.301046789</v>
       </c>
       <c r="L64" s="165">
         <f t="shared" si="4"/>
-        <v>124229649.256749</v>
+        <v>123699513.256749</v>
       </c>
       <c r="M64" s="165">
         <f t="shared" si="5"/>
-        <v>234539330.79526678</v>
+        <v>220319084.55779579</v>
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>46907866.159053355</v>
+        <v>55079771.139448948</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21085,35 +21085,35 @@
       </c>
       <c r="G65" s="182">
         <f>SUM(G51:G64)</f>
-        <v>4617647482.6915588</v>
+        <v>4823621595.2908421</v>
       </c>
       <c r="H65" s="182">
         <f>SUM(H51:H64)</f>
-        <v>756012049.406039</v>
+        <v>780402036.31597483</v>
       </c>
       <c r="I65" s="182">
         <f>SUM(I51:I64)</f>
-        <v>5373659532.0975981</v>
+        <v>5604023631.6068172</v>
       </c>
       <c r="J65" s="183">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.68115458345391233</v>
+        <v>0.71035508663180658</v>
       </c>
       <c r="K65" s="166">
         <f>SUM(K51:K64)</f>
-        <v>2001631850.3733013</v>
+        <v>1795657737.7740185</v>
       </c>
       <c r="L65" s="166">
         <f>SUM(L51:L64)</f>
-        <v>513754162.593961</v>
+        <v>489364175.68402505</v>
       </c>
       <c r="M65" s="166">
         <f>SUM(M51:M64)</f>
-        <v>2515386012.9672618</v>
+        <v>2285021913.4580436</v>
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>503077202.59345233</v>
+        <v>571255478.36451089</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="D71" s="193">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>76877115.799999997</v>
+        <v>78450088.760000005</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="D77" s="192">
         <f>IF(E25="",0,E25)</f>
-        <v>18706900.659995001</v>
+        <v>19583477.219994999</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="D80" s="192">
         <f>IF(E26="",0,E26)</f>
-        <v>49217118.49994</v>
+        <v>64357660.099909998</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="D81" s="193">
         <f>IF(E10="",0,E10)</f>
-        <v>50908683.359980002</v>
+        <v>51908683.359980002</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21325,7 +21325,7 @@
       <c r="C84" s="191"/>
       <c r="D84" s="194">
         <f>SUM(D70:D83)</f>
-        <v>417188232.18989193</v>
+        <v>435778323.30986202</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21377,19 +21377,19 @@
       </c>
       <c r="E89" s="177">
         <f>IFERROR(C32,0)</f>
-        <v>169243403.87884599</v>
+        <v>174072142.48878601</v>
       </c>
       <c r="F89" s="178">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
-        <v>0.60575631117373396</v>
+        <v>0.62303934153675689</v>
       </c>
       <c r="G89" s="171">
         <f>D89-E89</f>
-        <v>110148491.43779421</v>
+        <v>105319752.82785419</v>
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>22029698.287558842</v>
+        <v>26329938.206963547</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21406,19 +21406,19 @@
       </c>
       <c r="E90" s="177">
         <f>IFERROR(C33,0)</f>
-        <v>409188756.12131798</v>
+        <v>445809428.55673301</v>
       </c>
       <c r="F90" s="178">
         <f t="shared" si="9"/>
-        <v>0.97515989995218455</v>
+        <v>1.0624326090236755</v>
       </c>
       <c r="G90" s="172">
         <f>D90-E90</f>
-        <v>10423203.047000885</v>
+        <v>-26197469.388414145</v>
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>2084640.6094001769</v>
+        <v>-6549367.3471035361</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21435,19 +21435,19 @@
       </c>
       <c r="E91" s="177">
         <f>M21+M7</f>
-        <v>744324395.22494411</v>
+        <v>747738503.38492</v>
       </c>
       <c r="F91" s="178">
         <f t="shared" si="9"/>
-        <v>0.6813128323513622</v>
+        <v>0.68443791560182332</v>
       </c>
       <c r="G91" s="171">
         <f>D91-E91</f>
-        <v>348161111.99222517</v>
+        <v>344747003.83224928</v>
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>69632222.39844504</v>
+        <v>86186750.958062321</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21520,19 +21520,19 @@
       </c>
       <c r="E94" s="198">
         <f>SUM(E89:E93)</f>
-        <v>1322756555.2251081</v>
+        <v>1367620074.430439</v>
       </c>
       <c r="F94" s="175">
         <f t="shared" si="9"/>
-        <v>0.73835579685962061</v>
+        <v>0.76339837883884332</v>
       </c>
       <c r="G94" s="173">
         <f>SUM(G89:G93)</f>
-        <v>468732806.47702026</v>
+        <v>423869287.2716893</v>
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>93746561.295404047</v>
+        <v>105967321.81792232</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23595,11 +23595,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23607,6 +23602,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -25652,11 +25652,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25664,6 +25659,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -27709,11 +27709,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27721,6 +27716,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PENCAPAIAN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA9E0FF-447E-4DA2-AAA5-263D8BFC4121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7455" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -27,18 +28,8 @@
     <sheet name="NOV" sheetId="13" r:id="rId13"/>
     <sheet name="DES" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -602,16 +593,16 @@
     <t>DATA PENCAPAIAN — GLOBAL — DESEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 27 APRIL 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 28 APRIL 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.#0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.#0"/>
   </numFmts>
   <fonts count="43" x14ac:knownFonts="1">
     <font>
@@ -1224,7 +1215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1262,7 +1253,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1549,7 +1540,7 @@
     <xf numFmtId="9" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,53 +1549,53 @@
     <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="41" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="33" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1655,19 +1646,19 @@
     <xf numFmtId="3" fontId="10" fillId="26" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1682,11 +1673,11 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="37" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1695,7 +1686,7 @@
     <xf numFmtId="0" fontId="37" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="37" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1710,50 +1701,47 @@
     <xf numFmtId="3" fontId="35" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="40" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1783,25 +1771,25 @@
     <xf numFmtId="0" fontId="41" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2666,7 +2654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:C18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2676,16 +2664,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="199" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="199"/>
+      <c r="B1" s="198" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="198"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="200"/>
+      <c r="C3" s="199"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2736,10 +2724,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="201" t="s">
+      <c r="B11" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="201"/>
+      <c r="C11" s="200"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -2809,7 +2797,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2859,7 +2847,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -3392,11 +3380,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3520,10 +3508,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3552,40 +3540,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3593,13 +3581,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3618,7 +3606,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3628,7 +3616,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4421,10 +4409,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4432,8 +4420,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -4627,13 +4615,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4836,6 +4824,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4843,11 +4836,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4866,7 +4854,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4916,7 +4904,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -5449,11 +5437,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5577,10 +5565,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5609,40 +5597,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5650,13 +5638,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5675,7 +5663,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5685,7 +5673,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6478,10 +6466,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6489,8 +6477,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -6684,13 +6672,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6893,6 +6881,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6900,11 +6893,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -6923,7 +6911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6973,7 +6961,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -7506,11 +7494,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7634,10 +7622,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7666,40 +7654,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7707,13 +7695,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7732,7 +7720,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7742,7 +7730,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8535,10 +8523,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8546,8 +8534,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -8741,13 +8729,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8950,6 +8938,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8957,11 +8950,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -8980,7 +8968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9030,7 +9018,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9563,11 +9551,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9691,10 +9679,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9723,40 +9711,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9764,13 +9752,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9789,7 +9777,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9799,7 +9787,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10592,10 +10580,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10603,8 +10591,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -10798,13 +10786,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11007,6 +10995,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11014,11 +11007,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11037,7 +11025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11087,7 +11075,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11620,11 +11608,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11747,10 +11735,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11779,40 +11767,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11820,13 +11808,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11845,7 +11833,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11855,7 +11843,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12634,10 +12622,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12645,8 +12633,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -12840,13 +12828,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13049,6 +13037,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13056,11 +13049,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13079,7 +13067,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA29"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13137,10 +13125,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="199" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="200"/>
+      <c r="C3" s="199"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14609,13 +14597,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="202" t="s">
+      <c r="B29" s="201" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="202"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="202"/>
-      <c r="F29" s="202"/>
+      <c r="C29" s="201"/>
+      <c r="D29" s="201"/>
+      <c r="E29" s="201"/>
+      <c r="F29" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14628,7 +14616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15145,10 +15133,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="204" t="s">
+      <c r="B44" s="203" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="205"/>
+      <c r="C44" s="204"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15188,23 +15176,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="206" t="s">
+      <c r="B47" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="206" t="s">
+      <c r="C47" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="207" t="s">
+      <c r="D47" s="206" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="208"/>
-      <c r="F47" s="209"/>
+      <c r="E47" s="207"/>
+      <c r="F47" s="208"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="206" t="s">
+      <c r="J47" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15212,13 +15200,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="203" t="s">
+      <c r="N47" s="202" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="206"/>
-      <c r="C48" s="206"/>
+      <c r="B48" s="205"/>
+      <c r="C48" s="205"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15237,7 +15225,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="206"/>
+      <c r="J48" s="205"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15247,7 +15235,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="203"/>
+      <c r="N48" s="202"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16162,7 +16150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16678,10 +16666,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="204" t="s">
+      <c r="B44" s="203" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="205"/>
+      <c r="C44" s="204"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16721,23 +16709,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="206" t="s">
+      <c r="B47" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="206" t="s">
+      <c r="C47" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="207" t="s">
+      <c r="D47" s="206" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="208"/>
-      <c r="F47" s="209"/>
+      <c r="E47" s="207"/>
+      <c r="F47" s="208"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="206" t="s">
+      <c r="J47" s="205" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16745,13 +16733,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="203" t="s">
+      <c r="N47" s="202" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="206"/>
-      <c r="C48" s="206"/>
+      <c r="B48" s="205"/>
+      <c r="C48" s="205"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16770,7 +16758,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="206"/>
+      <c r="J48" s="205"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16780,7 +16768,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="203"/>
+      <c r="N48" s="202"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -17695,7 +17683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18363,10 +18351,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="214" t="s">
+      <c r="B44" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="215"/>
+      <c r="C44" s="214"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18431,23 +18419,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="216" t="s">
+      <c r="B47" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="216" t="s">
+      <c r="C47" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="211" t="s">
+      <c r="D47" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="212"/>
-      <c r="F47" s="213"/>
+      <c r="E47" s="211"/>
+      <c r="F47" s="212"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="216" t="s">
+      <c r="J47" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18455,13 +18443,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="209" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="216"/>
-      <c r="C48" s="216"/>
+      <c r="B48" s="215"/>
+      <c r="C48" s="215"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18480,7 +18468,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="216"/>
+      <c r="J48" s="215"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18490,7 +18478,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="209"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -19469,7 +19457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:R94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19515,7 +19503,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19580,11 +19568,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>259416350.98412701</v>
+        <v>270907512.30340701</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>41315217.923969001</v>
+        <v>40589006.213964999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -19603,34 +19591,34 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>453952232.14149296</v>
+        <v>458942487.08149302</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>100272716.993726</v>
+        <v>105394829.648726</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="174">
-        <v>258387613.393603</v>
-      </c>
-      <c r="D10" s="174">
-        <v>22056994.284492001</v>
-      </c>
-      <c r="E10" s="174">
-        <v>51908683.359980002</v>
-      </c>
-      <c r="F10" s="174">
+      <c r="C10" s="15">
+        <v>274823941.20819598</v>
+      </c>
+      <c r="D10" s="15">
+        <v>23725280.784492001</v>
+      </c>
+      <c r="E10" s="15">
+        <v>56364538.979979999</v>
+      </c>
+      <c r="F10" s="15">
         <v>332353291.03807497</v>
       </c>
       <c r="G10"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>463195607.91979802</v>
+        <v>486268153.912296</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -19641,23 +19629,23 @@
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="174">
-        <v>257676819.092033</v>
-      </c>
-      <c r="D11" s="174">
-        <v>89431321.466564998</v>
-      </c>
-      <c r="E11" s="174">
+      <c r="C11" s="15">
+        <v>287597310.91703099</v>
+      </c>
+      <c r="D11" s="15">
+        <v>97263159.896546006</v>
+      </c>
+      <c r="E11" s="15">
         <v>34053355</v>
       </c>
-      <c r="F11" s="174">
+      <c r="F11" s="15">
         <v>381161495.55859798</v>
       </c>
       <c r="G11"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>289734229.18999302</v>
+        <v>292382877.82999301</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -19668,81 +19656,81 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="174">
-        <v>230388249.16392699</v>
-      </c>
-      <c r="D12" s="174">
-        <v>67470798.623895004</v>
-      </c>
-      <c r="E12" s="174">
+      <c r="C12" s="15">
+        <v>231715164.48392701</v>
+      </c>
+      <c r="D12" s="15">
+        <v>73395613.988894999</v>
+      </c>
+      <c r="E12" s="15">
         <v>71143242</v>
       </c>
-      <c r="F12" s="174">
+      <c r="F12" s="15">
         <v>369002289.78782201</v>
       </c>
       <c r="G12"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>400873434.68683398</v>
+        <v>409371656.25402802</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>49880188.247367002</v>
+        <v>50736809.865864001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="174">
-        <v>223563982.977566</v>
-      </c>
-      <c r="D13" s="174">
-        <v>32801918.369831</v>
-      </c>
-      <c r="E13" s="174">
-        <v>7306846.7599999998</v>
-      </c>
-      <c r="F13" s="174">
+      <c r="C13" s="15">
+        <v>227227322.59756601</v>
+      </c>
+      <c r="D13" s="15">
+        <v>31999215.659830999</v>
+      </c>
+      <c r="E13" s="15">
+        <v>9559098.9600000009</v>
+      </c>
+      <c r="F13" s="15">
         <v>263672748.10739699</v>
       </c>
       <c r="G13"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>846052742.05182004</v>
+        <v>879165470.53308499</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>51156635.799857996</v>
+        <v>53446535.799857996</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="174">
-        <v>463195607.91979802</v>
-      </c>
-      <c r="D14" s="174">
+      <c r="C14" s="15">
+        <v>486268153.912296</v>
+      </c>
+      <c r="D14" s="15">
         <v>20953488.849736001</v>
       </c>
-      <c r="E14" s="174">
-        <v>57386179.549984999</v>
-      </c>
-      <c r="F14" s="174">
+      <c r="E14" s="15">
+        <v>61073566.889985003</v>
+      </c>
+      <c r="F14" s="15">
         <v>541535276.31951904</v>
       </c>
       <c r="G14"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>334556563.810857</v>
+        <v>347510889.51785499</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>54790085.349973999</v>
+        <v>58038788.109973997</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -19759,135 +19747,135 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>257676819.092033</v>
+        <v>287597310.91703099</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>89431321.466564998</v>
+        <v>97263159.896546006</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="174">
-        <v>400873434.68683398</v>
-      </c>
-      <c r="D16" s="174">
-        <v>49880188.247367002</v>
-      </c>
-      <c r="E16" s="174" t="s">
+      <c r="C16" s="15">
+        <v>409371656.25402802</v>
+      </c>
+      <c r="D16" s="15">
+        <v>50736809.865864001</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="174">
+      <c r="F16" s="15">
         <v>450753622.934201</v>
       </c>
       <c r="G16"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>399179134.232728</v>
+        <v>424736895.09258002</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>39627430.193971001</v>
+        <v>42759954.493941002</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="174">
-        <v>289734229.18999302</v>
-      </c>
-      <c r="D17" s="174">
+      <c r="C17" s="15">
+        <v>292382877.82999301</v>
+      </c>
+      <c r="D17" s="15">
         <v>38549567.509999998</v>
       </c>
-      <c r="E17" s="174" t="s">
+      <c r="E17" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F17" s="174">
+      <c r="F17" s="15">
         <v>328283796.69999301</v>
       </c>
       <c r="G17"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>258387613.393603</v>
+        <v>274823941.20819598</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>22056994.284492001</v>
+        <v>23725280.784492001</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="174">
-        <v>1247382774.9297941</v>
-      </c>
-      <c r="D18" s="174">
-        <v>8662432.7548970003</v>
-      </c>
-      <c r="E18" s="174">
+      <c r="C18" s="15">
+        <v>1249137395.119791</v>
+      </c>
+      <c r="D18" s="15">
+        <v>8989432.7548970003</v>
+      </c>
+      <c r="E18" s="15">
         <v>1835135.12</v>
       </c>
-      <c r="F18" s="174">
+      <c r="F18" s="15">
         <v>1257880342.8046911</v>
       </c>
       <c r="G18"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>573634588.45515394</v>
+        <v>620725908.03147495</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>156779562.95306599</v>
+        <v>183075645.13976899</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="174">
-        <v>846052742.05182004</v>
-      </c>
-      <c r="D19" s="174">
-        <v>51156635.799857996</v>
-      </c>
-      <c r="E19" s="174">
+      <c r="C19" s="15">
+        <v>879165470.53308499</v>
+      </c>
+      <c r="D19" s="15">
+        <v>53446535.799857996</v>
+      </c>
+      <c r="E19" s="15">
         <v>90842339.400000006</v>
       </c>
-      <c r="F19" s="174">
+      <c r="F19" s="15">
         <v>988051717.25167799</v>
       </c>
       <c r="G19"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>142906117.71240199</v>
+        <v>153408407.40240198</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>115588826.743251</v>
+        <v>145578146.22700301</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="174">
-        <v>95172652.392401993</v>
-      </c>
-      <c r="D20" s="174">
-        <v>14451727.799813</v>
-      </c>
-      <c r="E20" s="174" t="s">
+      <c r="C20" s="15">
+        <v>97888417.982401997</v>
+      </c>
+      <c r="D20" s="15">
+        <v>16467727.799813</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F20" s="174">
+      <c r="F20" s="15">
         <v>109624380.192215</v>
       </c>
       <c r="G20"/>
@@ -19904,23 +19892,23 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="174">
-        <v>47733465.32</v>
-      </c>
-      <c r="D21" s="174">
-        <v>101137098.94343799</v>
-      </c>
-      <c r="E21" s="174" t="s">
+      <c r="C21" s="15">
+        <v>55519989.420000002</v>
+      </c>
+      <c r="D21" s="15">
+        <v>129110418.42719001</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="174">
+      <c r="F21" s="15">
         <v>148870564.26343799</v>
       </c>
       <c r="G21"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>747738503.38492</v>
+        <v>767572450.50459599</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -19930,16 +19918,16 @@
       <c r="B22" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="174">
-        <v>46775648.200000003</v>
-      </c>
-      <c r="D22" s="174" t="s">
+      <c r="C22" s="15">
+        <v>32665978</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="174">
-        <v>8372972.8399999999</v>
-      </c>
-      <c r="F22" s="174">
+      <c r="E22" s="15">
+        <v>12315315.119999999</v>
+      </c>
+      <c r="F22" s="15">
         <v>55148621.039999999</v>
       </c>
       <c r="G22"/>
@@ -19951,16 +19939,16 @@
       <c r="B23" s="74" t="s">
         <v>175</v>
       </c>
-      <c r="C23" s="174">
-        <v>97280513.420000002</v>
-      </c>
-      <c r="D23" s="174" t="s">
+      <c r="C23" s="15">
+        <v>97260882.519999996</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="174">
-        <v>15680179.92</v>
-      </c>
-      <c r="F23" s="174">
+      <c r="E23" s="15">
+        <v>17121621.32</v>
+      </c>
+      <c r="F23" s="15">
         <v>112960693.34</v>
       </c>
       <c r="G23"/>
@@ -19972,16 +19960,16 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="174">
-        <v>259416350.98412701</v>
-      </c>
-      <c r="D24" s="174">
-        <v>41315217.923969001</v>
-      </c>
-      <c r="E24" s="174">
-        <v>15143387.159992</v>
-      </c>
-      <c r="F24" s="174">
+      <c r="C24" s="15">
+        <v>270907512.30340701</v>
+      </c>
+      <c r="D24" s="15">
+        <v>40589006.213964999</v>
+      </c>
+      <c r="E24" s="15">
+        <v>17064107.859992001</v>
+      </c>
+      <c r="F24" s="15">
         <v>315874956.068088</v>
       </c>
       <c r="G24"/>
@@ -19991,16 +19979,16 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="174">
-        <v>334556563.810857</v>
-      </c>
-      <c r="D25" s="174">
-        <v>54790085.349973999</v>
-      </c>
-      <c r="E25" s="174">
-        <v>19583477.219994999</v>
-      </c>
-      <c r="F25" s="174">
+      <c r="C25" s="15">
+        <v>347510889.51785499</v>
+      </c>
+      <c r="D25" s="15">
+        <v>58038788.109973997</v>
+      </c>
+      <c r="E25" s="15">
+        <v>21835729.439994998</v>
+      </c>
+      <c r="F25" s="15">
         <v>408930126.380826</v>
       </c>
       <c r="G25"/>
@@ -20010,16 +19998,16 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="174">
-        <v>399179134.232728</v>
-      </c>
-      <c r="D26" s="174">
-        <v>39627430.193971001</v>
-      </c>
-      <c r="E26" s="174">
-        <v>64357660.099909998</v>
-      </c>
-      <c r="F26" s="174">
+      <c r="C26" s="15">
+        <v>424736895.09258002</v>
+      </c>
+      <c r="D26" s="15">
+        <v>42759954.493941002</v>
+      </c>
+      <c r="E26" s="15">
+        <v>88375679.199880004</v>
+      </c>
+      <c r="F26" s="15">
         <v>503164224.526609</v>
       </c>
       <c r="G26"/>
@@ -20029,16 +20017,16 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="174">
-        <v>573634588.45515394</v>
-      </c>
-      <c r="D27" s="174">
-        <v>156779562.95306599</v>
-      </c>
-      <c r="E27" s="174" t="s">
+      <c r="C27" s="15">
+        <v>620725908.03147495</v>
+      </c>
+      <c r="D27" s="15">
+        <v>183075645.13976899</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F27" s="174">
+      <c r="F27" s="15">
         <v>730414151.40822005</v>
       </c>
       <c r="G27"/>
@@ -20060,37 +20048,37 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="76"/>
-      <c r="C31" s="174"/>
+      <c r="C31" s="15"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="174">
-        <v>174072142.48878601</v>
+      <c r="C32" s="15">
+        <v>177330791.25874501</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="174">
-        <v>445809428.55673301</v>
+      <c r="C33" s="15">
+        <v>448679644.76670098</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="174">
-        <v>267412417.39651999</v>
+      <c r="C34" s="15">
+        <v>287246364.51619601</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="174">
+      <c r="C35" s="15">
         <v>169035280.78842399</v>
       </c>
     </row>
@@ -20098,7 +20086,7 @@
       <c r="B36" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="174">
+      <c r="C36" s="15">
         <v>311290805.19997603</v>
       </c>
     </row>
@@ -20111,17 +20099,17 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20162,19 +20150,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>4823621595.2908421</v>
+        <v>5035768370.6038408</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.72872307581819584</v>
+        <v>0.76077290551087495</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1795657737.7740192</v>
+        <v>1583510962.4610205</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>448914434.44350481</v>
+        <v>527836987.48700684</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20190,19 +20178,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>780402036.31597483</v>
+        <v>860111212.53987396</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.61460293157964019</v>
+        <v>0.67737761834528476</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>489364175.68402517</v>
+        <v>409654999.46012604</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>122341043.92100629</v>
+        <v>136551666.48670867</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20218,82 +20206,82 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1367620074.430439</v>
+        <v>1393582886.5300419</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.76339837883884332</v>
+        <v>0.77789068488018931</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>423869287.27168941</v>
+        <v>397906475.17208648</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>105967321.81792235</v>
+        <v>132635491.72402883</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>6971643706.0372562</v>
+        <v>7289462469.6737566</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.72017133073543937</v>
+        <v>0.75300203344943251</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2708891200.7297339</v>
+        <v>2391072437.0932331</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>677222800.18243349</v>
+        <v>797024145.69774437</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="228"/>
-      <c r="L48" s="229"/>
-      <c r="M48" s="229"/>
-      <c r="N48" s="230"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="227"/>
+      <c r="L48" s="228"/>
+      <c r="M48" s="228"/>
+      <c r="N48" s="229"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="227" t="s">
+      <c r="B49" s="226" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="227" t="s">
+      <c r="C49" s="226" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="224" t="s">
+      <c r="D49" s="223" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="225"/>
-      <c r="F49" s="226"/>
+      <c r="E49" s="224"/>
+      <c r="F49" s="225"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="227" t="s">
+      <c r="J49" s="226" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20301,13 +20289,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="220" t="s">
+      <c r="N49" s="219" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
+      <c r="B50" s="226"/>
+      <c r="C50" s="226"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20326,7 +20314,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="227"/>
+      <c r="J50" s="226"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20336,150 +20324,150 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="220"/>
+      <c r="N50" s="219"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="184" t="s">
+      <c r="B51" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="185" t="s">
+      <c r="C51" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="176">
+      <c r="D51" s="175">
         <f>TARGETS!J5</f>
         <v>396683478.3262167</v>
       </c>
-      <c r="E51" s="176">
+      <c r="E51" s="175">
         <f>TARGETS!K5</f>
         <v>49588709</v>
       </c>
-      <c r="F51" s="176">
+      <c r="F51" s="175">
         <f t="shared" ref="F51:F64" si="0">D51+E51</f>
         <v>446272187.3262167</v>
       </c>
-      <c r="G51" s="177">
+      <c r="G51" s="176">
         <f>M8</f>
-        <v>259416350.98412701</v>
-      </c>
-      <c r="H51" s="177">
+        <v>270907512.30340701</v>
+      </c>
+      <c r="H51" s="176">
         <f>N8</f>
-        <v>41315217.923969001</v>
-      </c>
-      <c r="I51" s="177">
+        <v>40589006.213964999</v>
+      </c>
+      <c r="I51" s="176">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>300731568.90809602</v>
-      </c>
-      <c r="J51" s="178">
+        <v>311496518.51737201</v>
+      </c>
+      <c r="J51" s="177">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.67387477294942155</v>
+        <v>0.69799670999813801</v>
       </c>
       <c r="K51" s="164">
         <f t="shared" ref="K51:K64" si="3">D51-G51</f>
-        <v>137267127.34208968</v>
+        <v>125775966.02280968</v>
       </c>
       <c r="L51" s="164">
         <f t="shared" ref="L51:L64" si="4">E51-H51</f>
-        <v>8273491.0760309994</v>
+        <v>8999702.7860350013</v>
       </c>
       <c r="M51" s="164">
         <f t="shared" ref="M51:M64" si="5">F51-I51</f>
-        <v>145540618.41812068</v>
+        <v>134775668.80884469</v>
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>36385154.604530171</v>
+        <v>44925222.936281562</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="186" t="s">
+      <c r="B52" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="187" t="s">
+      <c r="C52" s="186" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="179">
+      <c r="D52" s="178">
         <f>TARGETS!J6</f>
         <v>535182371</v>
       </c>
-      <c r="E52" s="179">
+      <c r="E52" s="178">
         <f>TARGETS!K6</f>
         <v>172865092</v>
       </c>
-      <c r="F52" s="179">
+      <c r="F52" s="178">
         <f t="shared" si="0"/>
         <v>708047463</v>
       </c>
-      <c r="G52" s="177">
+      <c r="G52" s="176">
         <f>M9</f>
-        <v>453952232.14149296</v>
-      </c>
-      <c r="H52" s="177">
+        <v>458942487.08149302</v>
+      </c>
+      <c r="H52" s="176">
         <f>N9</f>
-        <v>100272716.993726</v>
-      </c>
-      <c r="I52" s="177">
+        <v>105394829.648726</v>
+      </c>
+      <c r="I52" s="176">
         <f t="shared" si="1"/>
-        <v>554224949.13521898</v>
-      </c>
-      <c r="J52" s="178">
+        <v>564337316.73021901</v>
+      </c>
+      <c r="J52" s="177">
         <f t="shared" si="2"/>
-        <v>0.78275112629733268</v>
+        <v>0.79703317393317041</v>
       </c>
       <c r="K52" s="165">
         <f t="shared" si="3"/>
-        <v>81230138.858507037</v>
+        <v>76239883.91850698</v>
       </c>
       <c r="L52" s="165">
         <f t="shared" si="4"/>
-        <v>72592375.006274</v>
+        <v>67470262.351273999</v>
       </c>
       <c r="M52" s="165">
         <f t="shared" si="5"/>
-        <v>153822513.86478102</v>
+        <v>143710146.26978099</v>
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>38455628.466195256</v>
+        <v>47903382.089926995</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="188" t="s">
+      <c r="B53" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="C53" s="189" t="s">
+      <c r="C53" s="188" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="180">
+      <c r="D53" s="179">
         <f>TARGETS!J7</f>
         <v>241473268</v>
       </c>
-      <c r="E53" s="180">
+      <c r="E53" s="179">
         <f>TARGETS!K7</f>
         <v>0</v>
       </c>
-      <c r="F53" s="180">
+      <c r="F53" s="179">
         <f>D53+E53</f>
         <v>241473268</v>
       </c>
-      <c r="G53" s="177">
+      <c r="G53" s="176">
         <f>C22</f>
-        <v>46775648.200000003</v>
-      </c>
-      <c r="H53" s="177">
+        <v>32665978</v>
+      </c>
+      <c r="H53" s="176">
         <f>IF(D22="",0,D22)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="177">
+      <c r="I53" s="176">
         <f>G53+H53</f>
-        <v>46775648.200000003</v>
-      </c>
-      <c r="J53" s="178">
+        <v>32665978</v>
+      </c>
+      <c r="J53" s="177">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.19370942625417237</v>
+        <v>0.13527782296796514</v>
       </c>
       <c r="K53" s="165">
         <f>D53-G53</f>
-        <v>194697619.80000001</v>
+        <v>208807290</v>
       </c>
       <c r="L53" s="165">
         <f>E53-H53</f>
@@ -20487,51 +20475,51 @@
       </c>
       <c r="M53" s="165">
         <f>F53-I53</f>
-        <v>194697619.80000001</v>
+        <v>208807290</v>
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>48674404.950000003</v>
+        <v>69602430</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="186" t="s">
+      <c r="B54" s="185" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="187" t="s">
+      <c r="C54" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="179">
+      <c r="D54" s="178">
         <f>TARGETS!J8</f>
         <v>590712471.92289722</v>
       </c>
-      <c r="E54" s="179">
+      <c r="E54" s="178">
         <f>TARGETS!K8</f>
         <v>28200135</v>
       </c>
-      <c r="F54" s="179">
+      <c r="F54" s="178">
         <f t="shared" si="0"/>
         <v>618912606.92289722</v>
       </c>
-      <c r="G54" s="177">
+      <c r="G54" s="176">
         <f>M10</f>
-        <v>463195607.91979802</v>
-      </c>
-      <c r="H54" s="177">
+        <v>486268153.912296</v>
+      </c>
+      <c r="H54" s="176">
         <f t="shared" ref="H54:H58" si="6">N10</f>
         <v>20953488.849736001</v>
       </c>
-      <c r="I54" s="177">
+      <c r="I54" s="176">
         <f t="shared" si="1"/>
-        <v>484149096.76953399</v>
-      </c>
-      <c r="J54" s="178">
+        <v>507221642.76203197</v>
+      </c>
+      <c r="J54" s="177">
         <f t="shared" si="2"/>
-        <v>0.78225761012790007</v>
+        <v>0.81953677641796774</v>
       </c>
       <c r="K54" s="165">
         <f>D54-G54</f>
-        <v>127516864.0030992</v>
+        <v>104444318.01060122</v>
       </c>
       <c r="L54" s="165">
         <f t="shared" si="4"/>
@@ -20539,51 +20527,51 @@
       </c>
       <c r="M54" s="165">
         <f t="shared" si="5"/>
-        <v>134763510.15336323</v>
+        <v>111690964.16086525</v>
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>33690877.538340807</v>
+        <v>37230321.386955082</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="184" t="s">
+      <c r="B55" s="183" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="185" t="s">
+      <c r="C55" s="184" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="176">
+      <c r="D55" s="175">
         <f>TARGETS!J9</f>
         <v>395063284.19152415</v>
       </c>
-      <c r="E55" s="176">
+      <c r="E55" s="175">
         <f>TARGETS!K9</f>
         <v>73528469</v>
       </c>
-      <c r="F55" s="176">
+      <c r="F55" s="175">
         <f t="shared" si="0"/>
         <v>468591753.19152415</v>
       </c>
-      <c r="G55" s="177">
+      <c r="G55" s="176">
         <f>M11</f>
-        <v>289734229.18999302</v>
-      </c>
-      <c r="H55" s="177">
+        <v>292382877.82999301</v>
+      </c>
+      <c r="H55" s="176">
         <f t="shared" si="6"/>
         <v>38549567.509999998</v>
       </c>
-      <c r="I55" s="177">
+      <c r="I55" s="176">
         <f t="shared" si="1"/>
-        <v>328283796.69999301</v>
-      </c>
-      <c r="J55" s="178">
+        <v>330932445.339993</v>
+      </c>
+      <c r="J55" s="177">
         <f t="shared" si="2"/>
-        <v>0.70057527573648082</v>
+        <v>0.70622763436626967</v>
       </c>
       <c r="K55" s="165">
         <f t="shared" si="3"/>
-        <v>105329055.00153112</v>
+        <v>102680406.36153114</v>
       </c>
       <c r="L55" s="165">
         <f t="shared" si="4"/>
@@ -20591,207 +20579,207 @@
       </c>
       <c r="M55" s="165">
         <f t="shared" si="5"/>
-        <v>140307956.49153113</v>
+        <v>137659307.85153115</v>
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>35076989.122882783</v>
+        <v>45886435.950510383</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="186" t="s">
+      <c r="B56" s="185" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="187" t="s">
+      <c r="C56" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="179">
+      <c r="D56" s="178">
         <f>TARGETS!J10</f>
         <v>463918832.1226536</v>
       </c>
-      <c r="E56" s="179">
+      <c r="E56" s="178">
         <f>TARGETS!K10</f>
         <v>71898548</v>
       </c>
-      <c r="F56" s="179">
+      <c r="F56" s="178">
         <f t="shared" si="0"/>
         <v>535817380.1226536</v>
       </c>
-      <c r="G56" s="177">
+      <c r="G56" s="176">
         <f>M12</f>
-        <v>400873434.68683398</v>
-      </c>
-      <c r="H56" s="177">
+        <v>409371656.25402802</v>
+      </c>
+      <c r="H56" s="176">
         <f t="shared" si="6"/>
-        <v>49880188.247367002</v>
-      </c>
-      <c r="I56" s="177">
+        <v>50736809.865864001</v>
+      </c>
+      <c r="I56" s="176">
         <f t="shared" si="1"/>
-        <v>450753622.934201</v>
-      </c>
-      <c r="J56" s="178">
+        <v>460108466.119892</v>
+      </c>
+      <c r="J56" s="177">
         <f t="shared" si="2"/>
-        <v>0.8412448712115671</v>
+        <v>0.85870388529496533</v>
       </c>
       <c r="K56" s="165">
         <f t="shared" si="3"/>
-        <v>63045397.435819626</v>
+        <v>54547175.868625581</v>
       </c>
       <c r="L56" s="165">
         <f t="shared" si="4"/>
-        <v>22018359.752632998</v>
+        <v>21161738.134135999</v>
       </c>
       <c r="M56" s="165">
         <f t="shared" si="5"/>
-        <v>85063757.188452601</v>
+        <v>75708914.002761602</v>
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>21265939.29711315</v>
+        <v>25236304.667587202</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="184" t="s">
+      <c r="B57" s="183" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="185" t="s">
+      <c r="C57" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="176">
+      <c r="D57" s="175">
         <f>TARGETS!J11</f>
         <v>941758345.44471872</v>
       </c>
-      <c r="E57" s="176">
+      <c r="E57" s="175">
         <f>TARGETS!K11</f>
         <v>73246884</v>
       </c>
-      <c r="F57" s="176">
+      <c r="F57" s="175">
         <f t="shared" si="0"/>
         <v>1015005229.4447187</v>
       </c>
-      <c r="G57" s="177">
+      <c r="G57" s="176">
         <f>M13</f>
-        <v>846052742.05182004</v>
-      </c>
-      <c r="H57" s="177">
+        <v>879165470.53308499</v>
+      </c>
+      <c r="H57" s="176">
         <f t="shared" si="6"/>
-        <v>51156635.799857996</v>
-      </c>
-      <c r="I57" s="177">
+        <v>53446535.799857996</v>
+      </c>
+      <c r="I57" s="176">
         <f t="shared" si="1"/>
-        <v>897209377.85167801</v>
-      </c>
-      <c r="J57" s="178">
+        <v>932612006.33294296</v>
+      </c>
+      <c r="J57" s="177">
         <f t="shared" si="2"/>
-        <v>0.88394557173120814</v>
+        <v>0.9188248289549692</v>
       </c>
       <c r="K57" s="165">
         <f t="shared" si="3"/>
-        <v>95705603.392898679</v>
+        <v>62592874.91163373</v>
       </c>
       <c r="L57" s="165">
         <f t="shared" si="4"/>
-        <v>22090248.200142004</v>
+        <v>19800348.200142004</v>
       </c>
       <c r="M57" s="165">
         <f t="shared" si="5"/>
-        <v>117795851.5930407</v>
+        <v>82393223.111775756</v>
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>29448962.898260176</v>
+        <v>27464407.703925252</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="186" t="s">
+      <c r="B58" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="C58" s="187" t="s">
+      <c r="C58" s="186" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="179">
+      <c r="D58" s="178">
         <f>TARGETS!J12</f>
         <v>485287059</v>
       </c>
-      <c r="E58" s="179">
+      <c r="E58" s="178">
         <f>TARGETS!K12</f>
         <v>45099712</v>
       </c>
-      <c r="F58" s="179">
+      <c r="F58" s="178">
         <f t="shared" si="0"/>
         <v>530386771</v>
       </c>
-      <c r="G58" s="177">
+      <c r="G58" s="176">
         <f>M14</f>
-        <v>334556563.810857</v>
-      </c>
-      <c r="H58" s="177">
+        <v>347510889.51785499</v>
+      </c>
+      <c r="H58" s="176">
         <f t="shared" si="6"/>
-        <v>54790085.349973999</v>
-      </c>
-      <c r="I58" s="177">
+        <v>58038788.109973997</v>
+      </c>
+      <c r="I58" s="176">
         <f>G58+H58</f>
-        <v>389346649.16083097</v>
-      </c>
-      <c r="J58" s="178">
+        <v>405549677.62782896</v>
+      </c>
+      <c r="J58" s="177">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.73408061899196764</v>
+        <v>0.76463007714766129</v>
       </c>
       <c r="K58" s="165">
         <f t="shared" si="3"/>
-        <v>150730495.189143</v>
+        <v>137776169.48214501</v>
       </c>
       <c r="L58" s="165">
         <f t="shared" si="4"/>
-        <v>-9690373.349973999</v>
+        <v>-12939076.109973997</v>
       </c>
       <c r="M58" s="165">
         <f t="shared" si="5"/>
-        <v>141040121.83916903</v>
+        <v>124837093.37217104</v>
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>35260030.459792256</v>
+        <v>41612364.457390346</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="188" t="s">
+      <c r="B59" s="187" t="s">
         <v>177</v>
       </c>
-      <c r="C59" s="189" t="s">
+      <c r="C59" s="188" t="s">
         <v>179</v>
       </c>
-      <c r="D59" s="180">
+      <c r="D59" s="179">
         <f>TARGETS!J13</f>
         <v>404133664</v>
       </c>
-      <c r="E59" s="180">
+      <c r="E59" s="179">
         <f>TARGETS!K13</f>
         <v>0</v>
       </c>
-      <c r="F59" s="180">
+      <c r="F59" s="179">
         <f>D59+E59</f>
         <v>404133664</v>
       </c>
-      <c r="G59" s="177">
+      <c r="G59" s="176">
         <f>C23</f>
-        <v>97280513.420000002</v>
-      </c>
-      <c r="H59" s="177">
+        <v>97260882.519999996</v>
+      </c>
+      <c r="H59" s="176">
         <f>IF(D23="",0,D23)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="177">
+      <c r="I59" s="176">
         <f>G59+H59</f>
-        <v>97280513.420000002</v>
-      </c>
-      <c r="J59" s="178">
+        <v>97260882.519999996</v>
+      </c>
+      <c r="J59" s="177">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.24071370956120103</v>
+        <v>0.24066513429576605</v>
       </c>
       <c r="K59" s="165">
         <f>D59-G59</f>
-        <v>306853150.57999998</v>
+        <v>306872781.48000002</v>
       </c>
       <c r="L59" s="165">
         <f>E59-H59</f>
@@ -20799,321 +20787,321 @@
       </c>
       <c r="M59" s="165">
         <f>F59-I59</f>
-        <v>306853150.57999998</v>
+        <v>306872781.48000002</v>
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>76713287.644999996</v>
+        <v>102290927.16000001</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="186" t="s">
+      <c r="B60" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="187" t="s">
+      <c r="C60" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="179">
+      <c r="D60" s="178">
         <f>TARGETS!J14</f>
         <v>384017309.32355773</v>
       </c>
-      <c r="E60" s="179">
+      <c r="E60" s="178">
         <f>TARGETS!K14</f>
         <v>119782698</v>
       </c>
-      <c r="F60" s="179">
+      <c r="F60" s="178">
         <f t="shared" si="0"/>
         <v>503800007.32355773</v>
       </c>
-      <c r="G60" s="177">
+      <c r="G60" s="176">
         <f>M15</f>
-        <v>257676819.092033</v>
-      </c>
-      <c r="H60" s="177">
+        <v>287597310.91703099</v>
+      </c>
+      <c r="H60" s="176">
         <f t="shared" ref="H60:H64" si="7">N15</f>
-        <v>89431321.466564998</v>
-      </c>
-      <c r="I60" s="177">
+        <v>97263159.896546006</v>
+      </c>
+      <c r="I60" s="176">
         <f t="shared" si="1"/>
-        <v>347108140.55859798</v>
-      </c>
-      <c r="J60" s="178">
+        <v>384860470.813577</v>
+      </c>
+      <c r="J60" s="177">
         <f t="shared" si="2"/>
-        <v>0.68898002285195115</v>
+        <v>0.76391517510718565</v>
       </c>
       <c r="K60" s="165">
         <f t="shared" si="3"/>
-        <v>126340490.23152474</v>
+        <v>96419998.406526744</v>
       </c>
       <c r="L60" s="165">
         <f t="shared" si="4"/>
-        <v>30351376.533435002</v>
+        <v>22519538.103453994</v>
       </c>
       <c r="M60" s="165">
         <f t="shared" si="5"/>
-        <v>156691866.76495975</v>
+        <v>118939536.50998074</v>
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>39172966.691239938</v>
+        <v>39646512.169993579</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="184" t="s">
+      <c r="B61" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="185" t="s">
+      <c r="C61" s="184" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="176">
+      <c r="D61" s="175">
         <f>TARGETS!J15</f>
         <v>611629595.7161876</v>
       </c>
-      <c r="E61" s="176">
+      <c r="E61" s="175">
         <f>TARGETS!K15</f>
         <v>40059909</v>
       </c>
-      <c r="F61" s="176">
+      <c r="F61" s="175">
         <f t="shared" si="0"/>
         <v>651689504.7161876</v>
       </c>
-      <c r="G61" s="177">
+      <c r="G61" s="176">
         <f>M16</f>
-        <v>399179134.232728</v>
-      </c>
-      <c r="H61" s="177">
+        <v>424736895.09258002</v>
+      </c>
+      <c r="H61" s="176">
         <f t="shared" si="7"/>
-        <v>39627430.193971001</v>
-      </c>
-      <c r="I61" s="177">
+        <v>42759954.493941002</v>
+      </c>
+      <c r="I61" s="176">
         <f t="shared" si="1"/>
-        <v>438806564.42669898</v>
-      </c>
-      <c r="J61" s="178">
+        <v>467496849.58652103</v>
+      </c>
+      <c r="J61" s="177">
         <f t="shared" si="2"/>
-        <v>0.67333685942633115</v>
+        <v>0.71736132959532173</v>
       </c>
       <c r="K61" s="165">
         <f t="shared" si="3"/>
-        <v>212450461.48345959</v>
+        <v>186892700.62360758</v>
       </c>
       <c r="L61" s="165">
         <f t="shared" si="4"/>
-        <v>432478.80602899939</v>
+        <v>-2700045.4939410016</v>
       </c>
       <c r="M61" s="165">
         <f t="shared" si="5"/>
-        <v>212882940.28948861</v>
+        <v>184192655.12966657</v>
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>53220735.072372153</v>
+        <v>61397551.709888853</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="186" t="s">
+      <c r="B62" s="185" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="187" t="s">
+      <c r="C62" s="186" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="179">
+      <c r="D62" s="178">
         <f>TARGETS!J16</f>
         <v>366543022.9053762</v>
       </c>
-      <c r="E62" s="179">
+      <c r="E62" s="178">
         <f>TARGETS!K16</f>
         <v>45082463</v>
       </c>
-      <c r="F62" s="179">
+      <c r="F62" s="178">
         <f t="shared" si="0"/>
         <v>411625485.9053762</v>
       </c>
-      <c r="G62" s="177">
+      <c r="G62" s="176">
         <f>M17</f>
-        <v>258387613.393603</v>
-      </c>
-      <c r="H62" s="177">
+        <v>274823941.20819598</v>
+      </c>
+      <c r="H62" s="176">
         <f t="shared" si="7"/>
-        <v>22056994.284492001</v>
-      </c>
-      <c r="I62" s="177">
+        <v>23725280.784492001</v>
+      </c>
+      <c r="I62" s="176">
         <f t="shared" si="1"/>
-        <v>280444607.67809498</v>
-      </c>
-      <c r="J62" s="178">
+        <v>298549221.992688</v>
+      </c>
+      <c r="J62" s="177">
         <f t="shared" si="2"/>
-        <v>0.68131011630937532</v>
+        <v>0.7252933363346652</v>
       </c>
       <c r="K62" s="165">
         <f t="shared" si="3"/>
-        <v>108155409.5117732</v>
+        <v>91719081.697180212</v>
       </c>
       <c r="L62" s="165">
         <f t="shared" si="4"/>
-        <v>23025468.715507999</v>
+        <v>21357182.215507999</v>
       </c>
       <c r="M62" s="165">
         <f t="shared" si="5"/>
-        <v>131180878.22728121</v>
+        <v>113076263.9126882</v>
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>32795219.556820303</v>
+        <v>37692087.970896065</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="184" t="s">
+      <c r="B63" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="C63" s="185" t="s">
+      <c r="C63" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="176">
+      <c r="D63" s="175">
         <f>TARGETS!J17</f>
         <v>563350942.09827971</v>
       </c>
-      <c r="E63" s="176">
+      <c r="E63" s="175">
         <f>TARGETS!K17</f>
         <v>311125253</v>
       </c>
-      <c r="F63" s="176">
+      <c r="F63" s="175">
         <f t="shared" si="0"/>
         <v>874476195.09827971</v>
       </c>
-      <c r="G63" s="177">
+      <c r="G63" s="176">
         <f>M18</f>
-        <v>573634588.45515394</v>
-      </c>
-      <c r="H63" s="177">
+        <v>620725908.03147495</v>
+      </c>
+      <c r="H63" s="176">
         <f t="shared" si="7"/>
-        <v>156779562.95306599</v>
-      </c>
-      <c r="I63" s="177">
+        <v>183075645.13976899</v>
+      </c>
+      <c r="I63" s="176">
         <f t="shared" si="1"/>
-        <v>730414151.40821993</v>
-      </c>
-      <c r="J63" s="178">
+        <v>803801553.17124391</v>
+      </c>
+      <c r="J63" s="177">
         <f t="shared" si="2"/>
-        <v>0.83525904478867019</v>
+        <v>0.91918059939974361</v>
       </c>
       <c r="K63" s="165">
         <f t="shared" si="3"/>
-        <v>-10283646.356874228</v>
+        <v>-57374965.933195233</v>
       </c>
       <c r="L63" s="165">
         <f t="shared" si="4"/>
-        <v>154345690.04693401</v>
+        <v>128049607.86023101</v>
       </c>
       <c r="M63" s="165">
         <f t="shared" si="5"/>
-        <v>144062043.69005978</v>
+        <v>70674641.927035809</v>
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>36015510.922514945</v>
+        <v>23558213.975678604</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="186" t="s">
+      <c r="B64" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="187" t="s">
+      <c r="C64" s="186" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="179">
+      <c r="D64" s="178">
         <f>TARGETS!J18</f>
         <v>239525689.01344877</v>
       </c>
-      <c r="E64" s="179">
+      <c r="E64" s="178">
         <f>TARGETS!K18</f>
         <v>239288340</v>
       </c>
-      <c r="F64" s="179">
+      <c r="F64" s="178">
         <f t="shared" si="0"/>
         <v>478814029.01344877</v>
       </c>
-      <c r="G64" s="177">
+      <c r="G64" s="176">
         <f>M19</f>
-        <v>142906117.71240199</v>
-      </c>
-      <c r="H64" s="177">
+        <v>153408407.40240198</v>
+      </c>
+      <c r="H64" s="176">
         <f t="shared" si="7"/>
-        <v>115588826.743251</v>
-      </c>
-      <c r="I64" s="177">
+        <v>145578146.22700301</v>
+      </c>
+      <c r="I64" s="176">
         <f t="shared" si="1"/>
-        <v>258494944.45565298</v>
-      </c>
-      <c r="J64" s="178">
+        <v>298986553.62940502</v>
+      </c>
+      <c r="J64" s="177">
         <f t="shared" si="2"/>
-        <v>0.53986501813294296</v>
+        <v>0.62443148177057106</v>
       </c>
       <c r="K64" s="165">
         <f t="shared" si="3"/>
-        <v>96619571.301046789</v>
+        <v>86117281.611046791</v>
       </c>
       <c r="L64" s="165">
         <f t="shared" si="4"/>
-        <v>123699513.256749</v>
+        <v>93710193.772996992</v>
       </c>
       <c r="M64" s="165">
         <f t="shared" si="5"/>
-        <v>220319084.55779579</v>
+        <v>179827475.38404375</v>
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>55079771.139448948</v>
+        <v>59942491.794681251</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="190" t="s">
+      <c r="B65" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="191"/>
-      <c r="D65" s="181">
+      <c r="C65" s="190"/>
+      <c r="D65" s="180">
         <f>SUM(D51:D64)</f>
         <v>6619279333.0648613</v>
       </c>
-      <c r="E65" s="181">
+      <c r="E65" s="180">
         <f t="shared" ref="E65" si="8">SUM(E51:E52,E54:E58,E60:E64)</f>
         <v>1269766212</v>
       </c>
-      <c r="F65" s="181">
+      <c r="F65" s="180">
         <f>SUM(F51:F64)</f>
         <v>7889045545.0648613</v>
       </c>
-      <c r="G65" s="182">
+      <c r="G65" s="181">
         <f>SUM(G51:G64)</f>
-        <v>4823621595.2908421</v>
-      </c>
-      <c r="H65" s="182">
+        <v>5035768370.6038408</v>
+      </c>
+      <c r="H65" s="181">
         <f>SUM(H51:H64)</f>
-        <v>780402036.31597483</v>
-      </c>
-      <c r="I65" s="182">
+        <v>860111212.53987396</v>
+      </c>
+      <c r="I65" s="181">
         <f>SUM(I51:I64)</f>
-        <v>5604023631.6068172</v>
-      </c>
-      <c r="J65" s="183">
+        <v>5895879583.1437149</v>
+      </c>
+      <c r="J65" s="182">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.71035508663180658</v>
+        <v>0.74735017683248028</v>
       </c>
       <c r="K65" s="166">
         <f>SUM(K51:K64)</f>
-        <v>1795657737.7740185</v>
+        <v>1583510962.4610195</v>
       </c>
       <c r="L65" s="166">
         <f>SUM(L51:L64)</f>
-        <v>489364175.68402505</v>
+        <v>409654999.46012604</v>
       </c>
       <c r="M65" s="166">
         <f>SUM(M51:M64)</f>
-        <v>2285021913.4580436</v>
+        <v>1993165961.9211457</v>
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>571255478.36451089</v>
+        <v>664388653.97371519</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21127,10 +21115,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21141,8 +21129,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -21151,191 +21139,191 @@
       <c r="I69"/>
     </row>
     <row r="70" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="184" t="s">
+      <c r="B70" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="185" t="s">
+      <c r="C70" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="192">
+      <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>15143387.159992</v>
+        <v>17064107.859992001</v>
       </c>
     </row>
     <row r="71" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="186" t="s">
+      <c r="B71" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="C71" s="187" t="s">
+      <c r="C71" s="186" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="193">
+      <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>78450088.760000005</v>
+        <v>80702340.960000008</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="186" t="s">
+      <c r="B72" s="185" t="s">
         <v>177</v>
       </c>
-      <c r="C72" s="187" t="s">
+      <c r="C72" s="186" t="s">
         <v>178</v>
       </c>
-      <c r="D72" s="193">
+      <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
-        <v>8372972.8399999999</v>
+        <v>12315315.119999999</v>
       </c>
     </row>
     <row r="73" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="184" t="s">
+      <c r="B73" s="183" t="s">
         <v>71</v>
       </c>
-      <c r="C73" s="185" t="s">
+      <c r="C73" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="192">
+      <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>57386179.549984999</v>
+        <v>61073566.889985003</v>
       </c>
     </row>
     <row r="74" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="186" t="s">
+      <c r="B74" s="185" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="187" t="s">
+      <c r="C74" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="193">
+      <c r="D74" s="192">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="184" t="s">
+      <c r="B75" s="183" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="185" t="s">
+      <c r="C75" s="184" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="192">
+      <c r="D75" s="191">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="186" t="s">
+      <c r="B76" s="185" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="187" t="s">
+      <c r="C76" s="186" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="193">
+      <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
         <v>90842339.400000006</v>
       </c>
     </row>
     <row r="77" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="184" t="s">
+      <c r="B77" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="C77" s="185" t="s">
+      <c r="C77" s="184" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="192">
+      <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>19583477.219994999</v>
+        <v>21835729.439994998</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="186" t="s">
+      <c r="B78" s="185" t="s">
         <v>177</v>
       </c>
-      <c r="C78" s="187" t="s">
+      <c r="C78" s="186" t="s">
         <v>179</v>
       </c>
-      <c r="D78" s="193">
+      <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
-        <v>15680179.92</v>
+        <v>17121621.32</v>
       </c>
     </row>
     <row r="79" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="186" t="s">
+      <c r="B79" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="187" t="s">
+      <c r="C79" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="193">
+      <c r="D79" s="192">
         <f>IF(E11="",0,E11)</f>
         <v>34053355</v>
       </c>
     </row>
     <row r="80" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="184" t="s">
+      <c r="B80" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="185" t="s">
+      <c r="C80" s="184" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="192">
+      <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>64357660.099909998</v>
+        <v>88375679.199880004</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="186" t="s">
+      <c r="B81" s="185" t="s">
         <v>84</v>
       </c>
-      <c r="C81" s="187" t="s">
+      <c r="C81" s="186" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="193">
+      <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>51908683.359980002</v>
+        <v>56364538.979979999</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="184" t="s">
+      <c r="B82" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="C82" s="185" t="s">
+      <c r="C82" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="192">
+      <c r="D82" s="191">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="186" t="s">
+      <c r="B83" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="187" t="s">
+      <c r="C83" s="186" t="s">
         <v>89</v>
       </c>
-      <c r="D83" s="193">
+      <c r="D83" s="192">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="190" t="s">
+      <c r="B84" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="C84" s="191"/>
-      <c r="D84" s="194">
+      <c r="C84" s="190"/>
+      <c r="D84" s="193">
         <f>SUM(D70:D83)</f>
-        <v>435778323.30986202</v>
+        <v>479748594.16983199</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="221" t="s">
+      <c r="B87" s="220" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="222"/>
-      <c r="D87" s="222"/>
-      <c r="E87" s="222"/>
-      <c r="F87" s="223"/>
+      <c r="C87" s="221"/>
+      <c r="D87" s="221"/>
+      <c r="E87" s="221"/>
+      <c r="F87" s="222"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21365,108 +21353,108 @@
       <c r="I88" s="168"/>
     </row>
     <row r="89" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="184" t="s">
+      <c r="B89" s="183" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="185" t="s">
+      <c r="C89" s="184" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="195">
+      <c r="D89" s="194">
         <f>TARGETS!G22</f>
         <v>279391895.3166402</v>
       </c>
-      <c r="E89" s="177">
+      <c r="E89" s="176">
         <f>IFERROR(C32,0)</f>
-        <v>174072142.48878601</v>
-      </c>
-      <c r="F89" s="178">
+        <v>177330791.25874501</v>
+      </c>
+      <c r="F89" s="177">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
-        <v>0.62303934153675689</v>
+        <v>0.63470270337574619</v>
       </c>
       <c r="G89" s="171">
         <f>D89-E89</f>
-        <v>105319752.82785419</v>
+        <v>102061104.05789518</v>
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>26329938.206963547</v>
+        <v>34020368.019298397</v>
       </c>
       <c r="I89" s="168"/>
     </row>
     <row r="90" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="186" t="s">
+      <c r="B90" s="185" t="s">
         <v>94</v>
       </c>
-      <c r="C90" s="187" t="s">
+      <c r="C90" s="186" t="s">
         <v>95</v>
       </c>
-      <c r="D90" s="196">
+      <c r="D90" s="195">
         <f>TARGETS!G23</f>
         <v>419611959.16831887</v>
       </c>
-      <c r="E90" s="177">
+      <c r="E90" s="176">
         <f>IFERROR(C33,0)</f>
-        <v>445809428.55673301</v>
-      </c>
-      <c r="F90" s="178">
+        <v>448679644.76670098</v>
+      </c>
+      <c r="F90" s="177">
         <f t="shared" si="9"/>
-        <v>1.0624326090236755</v>
+        <v>1.0692727768197907</v>
       </c>
       <c r="G90" s="172">
         <f>D90-E90</f>
-        <v>-26197469.388414145</v>
+        <v>-29067685.598382115</v>
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-6549367.3471035361</v>
+        <v>-9689228.5327940378</v>
       </c>
       <c r="I90" s="168"/>
     </row>
     <row r="91" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="184" t="s">
+      <c r="B91" s="183" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="185" t="s">
+      <c r="C91" s="184" t="s">
         <v>97</v>
       </c>
-      <c r="D91" s="195">
+      <c r="D91" s="194">
         <f>TARGETS!G24</f>
         <v>1092485507.2171693</v>
       </c>
-      <c r="E91" s="177">
+      <c r="E91" s="176">
         <f>M21+M7</f>
-        <v>747738503.38492</v>
-      </c>
-      <c r="F91" s="178">
+        <v>767572450.50459599</v>
+      </c>
+      <c r="F91" s="177">
         <f t="shared" si="9"/>
-        <v>0.68443791560182332</v>
+        <v>0.70259279911162653</v>
       </c>
       <c r="G91" s="171">
         <f>D91-E91</f>
-        <v>344747003.83224928</v>
+        <v>324913056.71257329</v>
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>86186750.958062321</v>
+        <v>108304352.23752443</v>
       </c>
       <c r="I91" s="168"/>
     </row>
     <row r="92" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="186" t="s">
+      <c r="B92" s="185" t="s">
         <v>98</v>
       </c>
-      <c r="C92" s="187" t="s">
+      <c r="C92" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="D92" s="196">
+      <c r="D92" s="195">
         <f>TARGETS!G25</f>
         <v>0</v>
       </c>
-      <c r="E92" s="177">
+      <c r="E92" s="176">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F92" s="178">
+      <c r="F92" s="177">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21481,21 +21469,21 @@
       <c r="I92" s="168"/>
     </row>
     <row r="93" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="184" t="s">
+      <c r="B93" s="183" t="s">
         <v>100</v>
       </c>
-      <c r="C93" s="197" t="s">
+      <c r="C93" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="D93" s="195">
+      <c r="D93" s="194">
         <f>TARGETS!G26</f>
         <v>0</v>
       </c>
-      <c r="E93" s="177">
+      <c r="E93" s="176">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F93" s="178">
+      <c r="F93" s="177">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21510,29 +21498,29 @@
       <c r="I93" s="168"/>
     </row>
     <row r="94" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="190" t="s">
+      <c r="B94" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="C94" s="191"/>
-      <c r="D94" s="198">
+      <c r="C94" s="190"/>
+      <c r="D94" s="197">
         <f>SUM(D89:D93)</f>
         <v>1791489361.7021284</v>
       </c>
-      <c r="E94" s="198">
+      <c r="E94" s="197">
         <f>SUM(E89:E93)</f>
-        <v>1367620074.430439</v>
-      </c>
-      <c r="F94" s="175">
+        <v>1393582886.5300419</v>
+      </c>
+      <c r="F94" s="174">
         <f t="shared" si="9"/>
-        <v>0.76339837883884332</v>
+        <v>0.77789068488018931</v>
       </c>
       <c r="G94" s="173">
         <f>SUM(G89:G93)</f>
-        <v>423869287.2716893</v>
+        <v>397906475.17208636</v>
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>105967321.81792232</v>
+        <v>132635491.72402878</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21568,7 +21556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -21618,7 +21606,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22151,11 +22139,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>159</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22279,10 +22267,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -22311,40 +22299,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22352,13 +22340,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22377,7 +22365,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22387,7 +22375,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -23180,10 +23168,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23191,8 +23179,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -23386,13 +23374,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23595,6 +23583,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23602,11 +23595,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23625,7 +23613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23675,7 +23663,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -24208,11 +24196,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>161</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24336,10 +24324,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24368,40 +24356,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24409,13 +24397,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24434,7 +24422,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24444,7 +24432,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25237,10 +25225,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25248,8 +25236,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -25443,13 +25431,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25652,6 +25640,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25659,11 +25652,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25682,7 +25670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -25732,7 +25720,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -26265,11 +26253,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
+      <c r="B41" s="216" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="218"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26393,10 +26381,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="213" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="214"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26425,40 +26413,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="220" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="221"/>
+      <c r="F48" s="221"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="221"/>
+      <c r="I48" s="221"/>
+      <c r="J48" s="222"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="235"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="212"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26466,13 +26454,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="236" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="215"/>
+      <c r="C50" s="215"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26491,7 +26479,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="215"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26501,7 +26489,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="236"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27294,10 +27282,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="215" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27305,8 +27293,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="215"/>
+      <c r="C69" s="215"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -27500,13 +27488,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="231"/>
+      <c r="D87" s="231"/>
+      <c r="E87" s="231"/>
+      <c r="F87" s="232"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27709,6 +27697,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27716,11 +27709,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PENCAPAIAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA9E0FF-447E-4DA2-AAA5-263D8BFC4121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7455" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -28,8 +27,18 @@
     <sheet name="NOV" sheetId="13" r:id="rId13"/>
     <sheet name="DES" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -38,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -593,16 +602,16 @@
     <t>DATA PENCAPAIAN — GLOBAL — DESEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 28 APRIL 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 29 APRIL 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.#0"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0.#0"/>
   </numFmts>
   <fonts count="43" x14ac:knownFonts="1">
     <font>
@@ -1215,7 +1224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1253,7 +1262,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1540,7 +1549,7 @@
     <xf numFmtId="9" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1549,53 +1558,53 @@
     <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="24" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="33" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1646,19 +1655,19 @@
     <xf numFmtId="3" fontId="10" fillId="26" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1673,11 +1682,11 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="37" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="37" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1686,7 +1695,7 @@
     <xf numFmtId="0" fontId="37" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="37" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1701,47 +1710,50 @@
     <xf numFmtId="3" fontId="35" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="40" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1771,25 +1783,25 @@
     <xf numFmtId="0" fontId="41" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2654,7 +2666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:C18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2664,16 +2676,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="198" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="198"/>
+      <c r="B1" s="199" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="199"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="200" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="199"/>
+      <c r="C3" s="200"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2724,10 +2736,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="200" t="s">
+      <c r="B11" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="200"/>
+      <c r="C11" s="201"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -2797,7 +2809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2847,7 +2859,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -3380,11 +3392,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3508,10 +3520,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3540,40 +3552,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3581,13 +3593,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3606,7 +3618,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3616,7 +3628,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4409,10 +4421,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4420,8 +4432,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -4615,13 +4627,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4854,7 +4866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4904,7 +4916,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -5437,11 +5449,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5565,10 +5577,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5597,40 +5609,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5638,13 +5650,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5663,7 +5675,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5673,7 +5685,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6466,10 +6478,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6477,8 +6489,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -6672,13 +6684,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6911,7 +6923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6961,7 +6973,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -7494,11 +7506,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7622,10 +7634,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7654,40 +7666,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7695,13 +7707,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7720,7 +7732,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7730,7 +7742,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8523,10 +8535,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8534,8 +8546,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -8729,13 +8741,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8968,7 +8980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9018,7 +9030,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9551,11 +9563,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9679,10 +9691,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9711,40 +9723,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9752,13 +9764,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9777,7 +9789,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9787,7 +9799,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10580,10 +10592,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10591,8 +10603,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -10786,13 +10798,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11025,7 +11037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11075,7 +11087,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11608,11 +11620,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11735,10 +11747,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11767,40 +11779,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11808,13 +11820,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11833,7 +11845,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11843,7 +11855,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12622,10 +12634,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12633,8 +12645,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -12828,13 +12840,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13067,7 +13079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:AA29"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13125,10 +13137,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="199"/>
+      <c r="C3" s="200"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14597,13 +14609,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="201" t="s">
+      <c r="B29" s="202" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="201"/>
-      <c r="D29" s="201"/>
-      <c r="E29" s="201"/>
-      <c r="F29" s="201"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="202"/>
+      <c r="F29" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14616,7 +14628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15133,10 +15145,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="203" t="s">
+      <c r="B44" s="204" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="204"/>
+      <c r="C44" s="205"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15176,23 +15188,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="205" t="s">
+      <c r="B47" s="206" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="205" t="s">
+      <c r="C47" s="206" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="206" t="s">
+      <c r="D47" s="207" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="207"/>
-      <c r="F47" s="208"/>
+      <c r="E47" s="208"/>
+      <c r="F47" s="209"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="205" t="s">
+      <c r="J47" s="206" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15200,13 +15212,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="202" t="s">
+      <c r="N47" s="203" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
+      <c r="B48" s="206"/>
+      <c r="C48" s="206"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15225,7 +15237,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="205"/>
+      <c r="J48" s="206"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15235,7 +15247,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="202"/>
+      <c r="N48" s="203"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16150,7 +16162,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16666,10 +16678,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="203" t="s">
+      <c r="B44" s="204" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="204"/>
+      <c r="C44" s="205"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16709,23 +16721,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="205" t="s">
+      <c r="B47" s="206" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="205" t="s">
+      <c r="C47" s="206" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="206" t="s">
+      <c r="D47" s="207" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="207"/>
-      <c r="F47" s="208"/>
+      <c r="E47" s="208"/>
+      <c r="F47" s="209"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="205" t="s">
+      <c r="J47" s="206" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16733,13 +16745,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="202" t="s">
+      <c r="N47" s="203" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
+      <c r="B48" s="206"/>
+      <c r="C48" s="206"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16758,7 +16770,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="205"/>
+      <c r="J48" s="206"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16768,7 +16780,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="202"/>
+      <c r="N48" s="203"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -17683,7 +17695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18351,10 +18363,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="213" t="s">
+      <c r="B44" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="214"/>
+      <c r="C44" s="215"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18419,23 +18431,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="215" t="s">
+      <c r="B47" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="215" t="s">
+      <c r="C47" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="210" t="s">
+      <c r="D47" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="211"/>
-      <c r="F47" s="212"/>
+      <c r="E47" s="212"/>
+      <c r="F47" s="213"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="215" t="s">
+      <c r="J47" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18443,13 +18455,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="209" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="215"/>
-      <c r="C48" s="215"/>
+      <c r="B48" s="216"/>
+      <c r="C48" s="216"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18468,7 +18480,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="215"/>
+      <c r="J48" s="216"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18478,7 +18490,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="209"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -19457,7 +19469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:R94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19503,7 +19515,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19568,11 +19580,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>270907512.30340701</v>
+        <v>291683670.26340503</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>40589006.213964999</v>
+        <v>44627609.843964003</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -19591,55 +19603,55 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>458942487.08149302</v>
+        <v>484491472.12148905</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>105394829.648726</v>
+        <v>113473009.55866</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="15">
-        <v>274823941.20819598</v>
-      </c>
-      <c r="D10" s="15">
-        <v>23725280.784492001</v>
-      </c>
-      <c r="E10" s="15">
-        <v>56364538.979979999</v>
-      </c>
-      <c r="F10" s="15">
-        <v>332353291.03807497</v>
+      <c r="C10" s="174">
+        <v>295360934.069879</v>
+      </c>
+      <c r="D10" s="174">
+        <v>26245280.784492001</v>
+      </c>
+      <c r="E10" s="174">
+        <v>60112286.639980003</v>
+      </c>
+      <c r="F10" s="174">
+        <v>381718501.49435103</v>
       </c>
       <c r="G10"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>486268153.912296</v>
+        <v>507340228.22389603</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>20953488.849736001</v>
+        <v>21205741.099730998</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="15">
-        <v>287597310.91703099</v>
-      </c>
-      <c r="D11" s="15">
-        <v>97263159.896546006</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="C11" s="174">
+        <v>293790333.37101603</v>
+      </c>
+      <c r="D11" s="174">
+        <v>117629853.266325</v>
+      </c>
+      <c r="E11" s="174">
         <v>34053355</v>
       </c>
-      <c r="F11" s="15">
-        <v>381161495.55859798</v>
+      <c r="F11" s="174">
+        <v>445473541.63734102</v>
       </c>
       <c r="G11"/>
       <c r="J11" s="116"/>
@@ -19649,57 +19661,57 @@
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>38549567.509999998</v>
+        <v>40333351.310000002</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="15">
-        <v>231715164.48392701</v>
-      </c>
-      <c r="D12" s="15">
-        <v>73395613.988894999</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="C12" s="174">
+        <v>252158338.70392501</v>
+      </c>
+      <c r="D12" s="174">
+        <v>74194812.198893994</v>
+      </c>
+      <c r="E12" s="174">
         <v>71143242</v>
       </c>
-      <c r="F12" s="15">
-        <v>369002289.78782201</v>
+      <c r="F12" s="174">
+        <v>397496392.90281898</v>
       </c>
       <c r="G12"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>409371656.25402802</v>
+        <v>419579054.27561802</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>50736809.865864001</v>
+        <v>58766854.885816</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="15">
-        <v>227227322.59756601</v>
-      </c>
-      <c r="D13" s="15">
-        <v>31999215.659830999</v>
-      </c>
-      <c r="E13" s="15">
+      <c r="C13" s="174">
+        <v>232333133.417564</v>
+      </c>
+      <c r="D13" s="174">
+        <v>39278197.359765999</v>
+      </c>
+      <c r="E13" s="174">
         <v>9559098.9600000009</v>
       </c>
-      <c r="F13" s="15">
-        <v>263672748.10739699</v>
+      <c r="F13" s="174">
+        <v>281170429.73733002</v>
       </c>
       <c r="G13"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>879165470.53308499</v>
+        <v>929286104.73370302</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -19710,27 +19722,27 @@
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="15">
-        <v>486268153.912296</v>
-      </c>
-      <c r="D14" s="15">
-        <v>20953488.849736001</v>
-      </c>
-      <c r="E14" s="15">
-        <v>61073566.889985003</v>
-      </c>
-      <c r="F14" s="15">
-        <v>541535276.31951904</v>
+      <c r="C14" s="174">
+        <v>507340228.22389603</v>
+      </c>
+      <c r="D14" s="174">
+        <v>21205741.099730998</v>
+      </c>
+      <c r="E14" s="174">
+        <v>61773566.889985003</v>
+      </c>
+      <c r="F14" s="174">
+        <v>590319536.21361196</v>
       </c>
       <c r="G14"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>347510889.51785499</v>
+        <v>363728557.02905202</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>58038788.109973997</v>
+        <v>58553288.109973997</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -19747,136 +19759,136 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>287597310.91703099</v>
+        <v>293790333.37101603</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>97263159.896546006</v>
+        <v>117629853.266325</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="15">
-        <v>409371656.25402802</v>
-      </c>
-      <c r="D16" s="15">
-        <v>50736809.865864001</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="F16" s="15">
-        <v>450753622.934201</v>
+      <c r="C16" s="174">
+        <v>419579054.27561802</v>
+      </c>
+      <c r="D16" s="174">
+        <v>58766854.885816</v>
+      </c>
+      <c r="E16" s="174">
+        <v>2883783.76</v>
+      </c>
+      <c r="F16" s="174">
+        <v>481229692.92143399</v>
       </c>
       <c r="G16"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>424736895.09258002</v>
+        <v>449679124.99856597</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>42759954.493941002</v>
+        <v>54263754.493941002</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="174">
         <v>292382877.82999301</v>
       </c>
-      <c r="D17" s="15">
-        <v>38549567.509999998</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="D17" s="174">
+        <v>40333351.310000002</v>
+      </c>
+      <c r="E17" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="F17" s="15">
-        <v>328283796.69999301</v>
+      <c r="F17" s="174">
+        <v>332716229.13999301</v>
       </c>
       <c r="G17"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>274823941.20819598</v>
+        <v>295360934.069879</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>23725280.784492001</v>
+        <v>26245280.784492001</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="15">
-        <v>1249137395.119791</v>
-      </c>
-      <c r="D18" s="15">
-        <v>8989432.7548970003</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="C18" s="174">
+        <v>1264403971.559751</v>
+      </c>
+      <c r="D18" s="174">
+        <v>9226432.7548970003</v>
+      </c>
+      <c r="E18" s="174">
         <v>1835135.12</v>
       </c>
-      <c r="F18" s="15">
-        <v>1257880342.8046911</v>
+      <c r="F18" s="174">
+        <v>1275465539.434648</v>
       </c>
       <c r="G18"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>620725908.03147495</v>
+        <v>627615097.431445</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>183075645.13976899</v>
+        <v>183295880.72976899</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="15">
-        <v>879165470.53308499</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="174">
+        <v>929286104.73370302</v>
+      </c>
+      <c r="D19" s="174">
         <v>53446535.799857996</v>
       </c>
-      <c r="E19" s="15">
-        <v>90842339.400000006</v>
-      </c>
-      <c r="F19" s="15">
-        <v>988051717.25167799</v>
+      <c r="E19" s="174">
+        <v>202463983.40000001</v>
+      </c>
+      <c r="F19" s="174">
+        <v>1185196623.9335611</v>
       </c>
       <c r="G19"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>153408407.40240198</v>
+        <v>160849546.587598</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>145578146.22700301</v>
+        <v>152708112.726924</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="15">
-        <v>97888417.982401997</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="174">
+        <v>103489607.16759799</v>
+      </c>
+      <c r="D20" s="174">
         <v>16467727.799813</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="F20" s="15">
-        <v>109624380.192215</v>
+      <c r="F20" s="174">
+        <v>119957334.967411</v>
       </c>
       <c r="G20"/>
       <c r="J20" s="116"/>
@@ -19892,23 +19904,23 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="15">
-        <v>55519989.420000002</v>
-      </c>
-      <c r="D21" s="15">
-        <v>129110418.42719001</v>
-      </c>
-      <c r="E21" s="15" t="s">
+      <c r="C21" s="174">
+        <v>57359939.420000002</v>
+      </c>
+      <c r="D21" s="174">
+        <v>136240384.927111</v>
+      </c>
+      <c r="E21" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="15">
-        <v>148870564.26343799</v>
+      <c r="F21" s="174">
+        <v>193600324.34711099</v>
       </c>
       <c r="G21"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>767572450.50459599</v>
+        <v>794555516.424474</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -19918,17 +19930,17 @@
       <c r="B22" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="15">
-        <v>32665978</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="C22" s="174">
+        <v>38884328.600000001</v>
+      </c>
+      <c r="D22" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="174">
         <v>12315315.119999999</v>
       </c>
-      <c r="F22" s="15">
-        <v>55148621.039999999</v>
+      <c r="F22" s="174">
+        <v>51199643.719999999</v>
       </c>
       <c r="G22"/>
       <c r="J22" s="116"/>
@@ -19939,17 +19951,17 @@
       <c r="B23" s="74" t="s">
         <v>175</v>
       </c>
-      <c r="C23" s="15">
-        <v>97260882.519999996</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="C23" s="174">
+        <v>99451782.519999996</v>
+      </c>
+      <c r="D23" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="174">
         <v>17121621.32</v>
       </c>
-      <c r="F23" s="15">
-        <v>112960693.34</v>
+      <c r="F23" s="174">
+        <v>116573403.84</v>
       </c>
       <c r="G23"/>
       <c r="J23" s="116"/>
@@ -19960,17 +19972,17 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="15">
-        <v>270907512.30340701</v>
-      </c>
-      <c r="D24" s="15">
-        <v>40589006.213964999</v>
-      </c>
-      <c r="E24" s="15">
-        <v>17064107.859992001</v>
-      </c>
-      <c r="F24" s="15">
-        <v>315874956.068088</v>
+      <c r="C24" s="174">
+        <v>291683670.26340503</v>
+      </c>
+      <c r="D24" s="174">
+        <v>44627609.843964003</v>
+      </c>
+      <c r="E24" s="174">
+        <v>23604648.279991999</v>
+      </c>
+      <c r="F24" s="174">
+        <v>359915928.38736099</v>
       </c>
       <c r="G24"/>
       <c r="J24" s="116"/>
@@ -19979,17 +19991,17 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="15">
-        <v>347510889.51785499</v>
-      </c>
-      <c r="D25" s="15">
-        <v>58038788.109973997</v>
-      </c>
-      <c r="E25" s="15">
-        <v>21835729.439994998</v>
-      </c>
-      <c r="F25" s="15">
-        <v>408930126.380826</v>
+      <c r="C25" s="174">
+        <v>363728557.02905202</v>
+      </c>
+      <c r="D25" s="174">
+        <v>58553288.109973997</v>
+      </c>
+      <c r="E25" s="174">
+        <v>23605098.779995002</v>
+      </c>
+      <c r="F25" s="174">
+        <v>445886943.91902101</v>
       </c>
       <c r="G25"/>
       <c r="J25" s="116"/>
@@ -19998,17 +20010,17 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="15">
-        <v>424736895.09258002</v>
-      </c>
-      <c r="D26" s="15">
-        <v>42759954.493941002</v>
-      </c>
-      <c r="E26" s="15">
-        <v>88375679.199880004</v>
-      </c>
-      <c r="F26" s="15">
-        <v>503164224.526609</v>
+      <c r="C26" s="174">
+        <v>449679124.99856597</v>
+      </c>
+      <c r="D26" s="174">
+        <v>54263754.493941002</v>
+      </c>
+      <c r="E26" s="174">
+        <v>90460363.869880006</v>
+      </c>
+      <c r="F26" s="174">
+        <v>594403243.36238694</v>
       </c>
       <c r="G26"/>
       <c r="J26" s="116"/>
@@ -20017,17 +20029,17 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="15">
-        <v>620725908.03147495</v>
-      </c>
-      <c r="D27" s="15">
-        <v>183075645.13976899</v>
-      </c>
-      <c r="E27" s="15" t="s">
+      <c r="C27" s="174">
+        <v>627615097.431445</v>
+      </c>
+      <c r="D27" s="174">
+        <v>183295880.72976899</v>
+      </c>
+      <c r="E27" s="174" t="s">
         <v>170</v>
       </c>
-      <c r="F27" s="15">
-        <v>730414151.40822005</v>
+      <c r="F27" s="174">
+        <v>810910978.16121399</v>
       </c>
       <c r="G27"/>
       <c r="J27" s="116"/>
@@ -20048,45 +20060,45 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="76"/>
-      <c r="C31" s="15"/>
+      <c r="C31" s="174"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="15">
-        <v>177330791.25874501</v>
+      <c r="C32" s="174">
+        <v>203076300.00860801</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="15">
-        <v>448679644.76670098</v>
+      <c r="C33" s="174">
+        <v>452153563.80664498</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="15">
-        <v>287246364.51619601</v>
+      <c r="C34" s="174">
+        <v>308523578.99607402</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="15">
-        <v>169035280.78842399</v>
+      <c r="C35" s="174">
+        <v>174741132.22842401</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="174">
         <v>311290805.19997603</v>
       </c>
     </row>
@@ -20099,17 +20111,17 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.93333333333333335</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20150,19 +20162,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5035768370.6038408</v>
+        <v>5254123112.0556602</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.76077290551087495</v>
+        <v>0.79376059653655595</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1583510962.4610205</v>
+        <v>1365156221.009201</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>527836987.48700684</v>
+        <v>682578110.50460052</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20178,19 +20190,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>860111212.53987396</v>
+        <v>924549272.60945392</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.67737761834528476</v>
+        <v>0.72812559026374057</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>409654999.46012604</v>
+        <v>345216939.39054608</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>136551666.48670867</v>
+        <v>172608469.69527304</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20206,82 +20218,82 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1393582886.5300419</v>
+        <v>1449785380.239727</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.77789068488018931</v>
+        <v>0.80926262317419406</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>397906475.17208648</v>
+        <v>341703981.46240139</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>132635491.72402883</v>
+        <v>170851990.7312007</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>7289462469.6737566</v>
+        <v>7628457764.9048414</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.75300203344943251</v>
+        <v>0.78802027350496051</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2391072437.0932331</v>
+        <v>2052077141.8621485</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>797024145.69774437</v>
+        <v>1026038570.9310743</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="227"/>
-      <c r="L48" s="228"/>
-      <c r="M48" s="228"/>
-      <c r="N48" s="229"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="228"/>
+      <c r="L48" s="229"/>
+      <c r="M48" s="229"/>
+      <c r="N48" s="230"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="226" t="s">
+      <c r="B49" s="227" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="226" t="s">
+      <c r="C49" s="227" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="223" t="s">
+      <c r="D49" s="224" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="224"/>
-      <c r="F49" s="225"/>
+      <c r="E49" s="225"/>
+      <c r="F49" s="226"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="226" t="s">
+      <c r="J49" s="227" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20289,13 +20301,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="219" t="s">
+      <c r="N49" s="220" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="226"/>
-      <c r="C50" s="226"/>
+      <c r="B50" s="227"/>
+      <c r="C50" s="227"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20314,7 +20326,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="226"/>
+      <c r="J50" s="227"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20324,150 +20336,150 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="219"/>
+      <c r="N50" s="220"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="183" t="s">
+      <c r="B51" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="184" t="s">
+      <c r="C51" s="185" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="175">
+      <c r="D51" s="176">
         <f>TARGETS!J5</f>
         <v>396683478.3262167</v>
       </c>
-      <c r="E51" s="175">
+      <c r="E51" s="176">
         <f>TARGETS!K5</f>
         <v>49588709</v>
       </c>
-      <c r="F51" s="175">
+      <c r="F51" s="176">
         <f t="shared" ref="F51:F64" si="0">D51+E51</f>
         <v>446272187.3262167</v>
       </c>
-      <c r="G51" s="176">
+      <c r="G51" s="177">
         <f>M8</f>
-        <v>270907512.30340701</v>
-      </c>
-      <c r="H51" s="176">
+        <v>291683670.26340503</v>
+      </c>
+      <c r="H51" s="177">
         <f>N8</f>
-        <v>40589006.213964999</v>
-      </c>
-      <c r="I51" s="176">
+        <v>44627609.843964003</v>
+      </c>
+      <c r="I51" s="177">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>311496518.51737201</v>
-      </c>
-      <c r="J51" s="177">
+        <v>336311280.10736901</v>
+      </c>
+      <c r="J51" s="178">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.69799670999813801</v>
+        <v>0.75360125425322932</v>
       </c>
       <c r="K51" s="164">
         <f t="shared" ref="K51:K64" si="3">D51-G51</f>
-        <v>125775966.02280968</v>
+        <v>104999808.06281167</v>
       </c>
       <c r="L51" s="164">
         <f t="shared" ref="L51:L64" si="4">E51-H51</f>
-        <v>8999702.7860350013</v>
+        <v>4961099.156035997</v>
       </c>
       <c r="M51" s="164">
         <f t="shared" ref="M51:M64" si="5">F51-I51</f>
-        <v>134775668.80884469</v>
+        <v>109960907.21884769</v>
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>44925222.936281562</v>
+        <v>54980453.609423846</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="185" t="s">
+      <c r="B52" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="186" t="s">
+      <c r="C52" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="178">
+      <c r="D52" s="179">
         <f>TARGETS!J6</f>
         <v>535182371</v>
       </c>
-      <c r="E52" s="178">
+      <c r="E52" s="179">
         <f>TARGETS!K6</f>
         <v>172865092</v>
       </c>
-      <c r="F52" s="178">
+      <c r="F52" s="179">
         <f t="shared" si="0"/>
         <v>708047463</v>
       </c>
-      <c r="G52" s="176">
+      <c r="G52" s="177">
         <f>M9</f>
-        <v>458942487.08149302</v>
-      </c>
-      <c r="H52" s="176">
+        <v>484491472.12148905</v>
+      </c>
+      <c r="H52" s="177">
         <f>N9</f>
-        <v>105394829.648726</v>
-      </c>
-      <c r="I52" s="176">
+        <v>113473009.55866</v>
+      </c>
+      <c r="I52" s="177">
         <f t="shared" si="1"/>
-        <v>564337316.73021901</v>
-      </c>
-      <c r="J52" s="177">
+        <v>597964481.68014908</v>
+      </c>
+      <c r="J52" s="178">
         <f t="shared" si="2"/>
-        <v>0.79703317393317041</v>
+        <v>0.84452598579560068</v>
       </c>
       <c r="K52" s="165">
         <f t="shared" si="3"/>
-        <v>76239883.91850698</v>
+        <v>50690898.878510952</v>
       </c>
       <c r="L52" s="165">
         <f t="shared" si="4"/>
-        <v>67470262.351273999</v>
+        <v>59392082.441339999</v>
       </c>
       <c r="M52" s="165">
         <f t="shared" si="5"/>
-        <v>143710146.26978099</v>
+        <v>110082981.31985092</v>
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>47903382.089926995</v>
+        <v>55041490.659925461</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="187" t="s">
+      <c r="B53" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="C53" s="188" t="s">
+      <c r="C53" s="189" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="179">
+      <c r="D53" s="180">
         <f>TARGETS!J7</f>
         <v>241473268</v>
       </c>
-      <c r="E53" s="179">
+      <c r="E53" s="180">
         <f>TARGETS!K7</f>
         <v>0</v>
       </c>
-      <c r="F53" s="179">
+      <c r="F53" s="180">
         <f>D53+E53</f>
         <v>241473268</v>
       </c>
-      <c r="G53" s="176">
+      <c r="G53" s="177">
         <f>C22</f>
-        <v>32665978</v>
-      </c>
-      <c r="H53" s="176">
+        <v>38884328.600000001</v>
+      </c>
+      <c r="H53" s="177">
         <f>IF(D22="",0,D22)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="176">
+      <c r="I53" s="177">
         <f>G53+H53</f>
-        <v>32665978</v>
-      </c>
-      <c r="J53" s="177">
+        <v>38884328.600000001</v>
+      </c>
+      <c r="J53" s="178">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.13527782296796514</v>
+        <v>0.1610295372322538</v>
       </c>
       <c r="K53" s="165">
         <f>D53-G53</f>
-        <v>208807290</v>
+        <v>202588939.40000001</v>
       </c>
       <c r="L53" s="165">
         <f>E53-H53</f>
@@ -20475,99 +20487,99 @@
       </c>
       <c r="M53" s="165">
         <f>F53-I53</f>
-        <v>208807290</v>
+        <v>202588939.40000001</v>
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>69602430</v>
+        <v>101294469.7</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="185" t="s">
+      <c r="B54" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="186" t="s">
+      <c r="C54" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="178">
+      <c r="D54" s="179">
         <f>TARGETS!J8</f>
         <v>590712471.92289722</v>
       </c>
-      <c r="E54" s="178">
+      <c r="E54" s="179">
         <f>TARGETS!K8</f>
         <v>28200135</v>
       </c>
-      <c r="F54" s="178">
+      <c r="F54" s="179">
         <f t="shared" si="0"/>
         <v>618912606.92289722</v>
       </c>
-      <c r="G54" s="176">
+      <c r="G54" s="177">
         <f>M10</f>
-        <v>486268153.912296</v>
-      </c>
-      <c r="H54" s="176">
+        <v>507340228.22389603</v>
+      </c>
+      <c r="H54" s="177">
         <f t="shared" ref="H54:H58" si="6">N10</f>
-        <v>20953488.849736001</v>
-      </c>
-      <c r="I54" s="176">
+        <v>21205741.099730998</v>
+      </c>
+      <c r="I54" s="177">
         <f t="shared" si="1"/>
-        <v>507221642.76203197</v>
-      </c>
-      <c r="J54" s="177">
+        <v>528545969.323627</v>
+      </c>
+      <c r="J54" s="178">
         <f t="shared" si="2"/>
-        <v>0.81953677641796774</v>
+        <v>0.85399127988593726</v>
       </c>
       <c r="K54" s="165">
         <f>D54-G54</f>
-        <v>104444318.01060122</v>
+        <v>83372243.699001193</v>
       </c>
       <c r="L54" s="165">
         <f t="shared" si="4"/>
-        <v>7246646.1502639987</v>
+        <v>6994393.9002690017</v>
       </c>
       <c r="M54" s="165">
         <f t="shared" si="5"/>
-        <v>111690964.16086525</v>
+        <v>90366637.599270225</v>
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>37230321.386955082</v>
+        <v>45183318.799635112</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="183" t="s">
+      <c r="B55" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="184" t="s">
+      <c r="C55" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="175">
+      <c r="D55" s="176">
         <f>TARGETS!J9</f>
         <v>395063284.19152415</v>
       </c>
-      <c r="E55" s="175">
+      <c r="E55" s="176">
         <f>TARGETS!K9</f>
         <v>73528469</v>
       </c>
-      <c r="F55" s="175">
+      <c r="F55" s="176">
         <f t="shared" si="0"/>
         <v>468591753.19152415</v>
       </c>
-      <c r="G55" s="176">
+      <c r="G55" s="177">
         <f>M11</f>
         <v>292382877.82999301</v>
       </c>
-      <c r="H55" s="176">
+      <c r="H55" s="177">
         <f t="shared" si="6"/>
-        <v>38549567.509999998</v>
-      </c>
-      <c r="I55" s="176">
+        <v>40333351.310000002</v>
+      </c>
+      <c r="I55" s="177">
         <f t="shared" si="1"/>
-        <v>330932445.339993</v>
-      </c>
-      <c r="J55" s="177">
+        <v>332716229.13999301</v>
+      </c>
+      <c r="J55" s="178">
         <f t="shared" si="2"/>
-        <v>0.70622763436626967</v>
+        <v>0.71003432491908214</v>
       </c>
       <c r="K55" s="165">
         <f t="shared" si="3"/>
@@ -20575,107 +20587,107 @@
       </c>
       <c r="L55" s="165">
         <f t="shared" si="4"/>
-        <v>34978901.490000002</v>
+        <v>33195117.689999998</v>
       </c>
       <c r="M55" s="165">
         <f t="shared" si="5"/>
-        <v>137659307.85153115</v>
+        <v>135875524.05153114</v>
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>45886435.950510383</v>
+        <v>67937762.025765568</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="185" t="s">
+      <c r="B56" s="186" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="186" t="s">
+      <c r="C56" s="187" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="178">
+      <c r="D56" s="179">
         <f>TARGETS!J10</f>
         <v>463918832.1226536</v>
       </c>
-      <c r="E56" s="178">
+      <c r="E56" s="179">
         <f>TARGETS!K10</f>
         <v>71898548</v>
       </c>
-      <c r="F56" s="178">
+      <c r="F56" s="179">
         <f t="shared" si="0"/>
         <v>535817380.1226536</v>
       </c>
-      <c r="G56" s="176">
+      <c r="G56" s="177">
         <f>M12</f>
-        <v>409371656.25402802</v>
-      </c>
-      <c r="H56" s="176">
+        <v>419579054.27561802</v>
+      </c>
+      <c r="H56" s="177">
         <f t="shared" si="6"/>
-        <v>50736809.865864001</v>
-      </c>
-      <c r="I56" s="176">
+        <v>58766854.885816</v>
+      </c>
+      <c r="I56" s="177">
         <f t="shared" si="1"/>
-        <v>460108466.119892</v>
-      </c>
-      <c r="J56" s="177">
+        <v>478345909.16143399</v>
+      </c>
+      <c r="J56" s="178">
         <f t="shared" si="2"/>
-        <v>0.85870388529496533</v>
+        <v>0.89274056218918496</v>
       </c>
       <c r="K56" s="165">
         <f t="shared" si="3"/>
-        <v>54547175.868625581</v>
+        <v>44339777.847035587</v>
       </c>
       <c r="L56" s="165">
         <f t="shared" si="4"/>
-        <v>21161738.134135999</v>
+        <v>13131693.114184</v>
       </c>
       <c r="M56" s="165">
         <f t="shared" si="5"/>
-        <v>75708914.002761602</v>
+        <v>57471470.961219609</v>
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>25236304.667587202</v>
+        <v>28735735.480609804</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="183" t="s">
+      <c r="B57" s="184" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="184" t="s">
+      <c r="C57" s="185" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="175">
+      <c r="D57" s="176">
         <f>TARGETS!J11</f>
         <v>941758345.44471872</v>
       </c>
-      <c r="E57" s="175">
+      <c r="E57" s="176">
         <f>TARGETS!K11</f>
         <v>73246884</v>
       </c>
-      <c r="F57" s="175">
+      <c r="F57" s="176">
         <f t="shared" si="0"/>
         <v>1015005229.4447187</v>
       </c>
-      <c r="G57" s="176">
+      <c r="G57" s="177">
         <f>M13</f>
-        <v>879165470.53308499</v>
-      </c>
-      <c r="H57" s="176">
+        <v>929286104.73370302</v>
+      </c>
+      <c r="H57" s="177">
         <f t="shared" si="6"/>
         <v>53446535.799857996</v>
       </c>
-      <c r="I57" s="176">
+      <c r="I57" s="177">
         <f t="shared" si="1"/>
-        <v>932612006.33294296</v>
-      </c>
-      <c r="J57" s="177">
+        <v>982732640.53356099</v>
+      </c>
+      <c r="J57" s="178">
         <f t="shared" si="2"/>
-        <v>0.9188248289549692</v>
+        <v>0.96820450971586303</v>
       </c>
       <c r="K57" s="165">
         <f t="shared" si="3"/>
-        <v>62592874.91163373</v>
+        <v>12472240.711015701</v>
       </c>
       <c r="L57" s="165">
         <f t="shared" si="4"/>
@@ -20683,103 +20695,103 @@
       </c>
       <c r="M57" s="165">
         <f t="shared" si="5"/>
-        <v>82393223.111775756</v>
+        <v>32272588.911157727</v>
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>27464407.703925252</v>
+        <v>16136294.455578864</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="185" t="s">
+      <c r="B58" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="C58" s="186" t="s">
+      <c r="C58" s="187" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="178">
+      <c r="D58" s="179">
         <f>TARGETS!J12</f>
         <v>485287059</v>
       </c>
-      <c r="E58" s="178">
+      <c r="E58" s="179">
         <f>TARGETS!K12</f>
         <v>45099712</v>
       </c>
-      <c r="F58" s="178">
+      <c r="F58" s="179">
         <f t="shared" si="0"/>
         <v>530386771</v>
       </c>
-      <c r="G58" s="176">
+      <c r="G58" s="177">
         <f>M14</f>
-        <v>347510889.51785499</v>
-      </c>
-      <c r="H58" s="176">
+        <v>363728557.02905202</v>
+      </c>
+      <c r="H58" s="177">
         <f t="shared" si="6"/>
-        <v>58038788.109973997</v>
-      </c>
-      <c r="I58" s="176">
+        <v>58553288.109973997</v>
+      </c>
+      <c r="I58" s="177">
         <f>G58+H58</f>
-        <v>405549677.62782896</v>
-      </c>
-      <c r="J58" s="177">
+        <v>422281845.13902605</v>
+      </c>
+      <c r="J58" s="178">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.76463007714766129</v>
+        <v>0.79617718281858518</v>
       </c>
       <c r="K58" s="165">
         <f t="shared" si="3"/>
-        <v>137776169.48214501</v>
+        <v>121558501.97094798</v>
       </c>
       <c r="L58" s="165">
         <f t="shared" si="4"/>
-        <v>-12939076.109973997</v>
+        <v>-13453576.109973997</v>
       </c>
       <c r="M58" s="165">
         <f t="shared" si="5"/>
-        <v>124837093.37217104</v>
+        <v>108104925.86097395</v>
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>41612364.457390346</v>
+        <v>54052462.930486977</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="187" t="s">
+      <c r="B59" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="C59" s="188" t="s">
+      <c r="C59" s="189" t="s">
         <v>179</v>
       </c>
-      <c r="D59" s="179">
+      <c r="D59" s="180">
         <f>TARGETS!J13</f>
         <v>404133664</v>
       </c>
-      <c r="E59" s="179">
+      <c r="E59" s="180">
         <f>TARGETS!K13</f>
         <v>0</v>
       </c>
-      <c r="F59" s="179">
+      <c r="F59" s="180">
         <f>D59+E59</f>
         <v>404133664</v>
       </c>
-      <c r="G59" s="176">
+      <c r="G59" s="177">
         <f>C23</f>
-        <v>97260882.519999996</v>
-      </c>
-      <c r="H59" s="176">
+        <v>99451782.519999996</v>
+      </c>
+      <c r="H59" s="177">
         <f>IF(D23="",0,D23)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="176">
+      <c r="I59" s="177">
         <f>G59+H59</f>
-        <v>97260882.519999996</v>
-      </c>
-      <c r="J59" s="177">
+        <v>99451782.519999996</v>
+      </c>
+      <c r="J59" s="178">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.24066513429576605</v>
+        <v>0.24608636047701285</v>
       </c>
       <c r="K59" s="165">
         <f>D59-G59</f>
-        <v>306872781.48000002</v>
+        <v>304681881.48000002</v>
       </c>
       <c r="L59" s="165">
         <f>E59-H59</f>
@@ -20787,321 +20799,321 @@
       </c>
       <c r="M59" s="165">
         <f>F59-I59</f>
-        <v>306872781.48000002</v>
+        <v>304681881.48000002</v>
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>102290927.16000001</v>
+        <v>152340940.74000001</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="185" t="s">
+      <c r="B60" s="186" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="186" t="s">
+      <c r="C60" s="187" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="178">
+      <c r="D60" s="179">
         <f>TARGETS!J14</f>
         <v>384017309.32355773</v>
       </c>
-      <c r="E60" s="178">
+      <c r="E60" s="179">
         <f>TARGETS!K14</f>
         <v>119782698</v>
       </c>
-      <c r="F60" s="178">
+      <c r="F60" s="179">
         <f t="shared" si="0"/>
         <v>503800007.32355773</v>
       </c>
-      <c r="G60" s="176">
+      <c r="G60" s="177">
         <f>M15</f>
-        <v>287597310.91703099</v>
-      </c>
-      <c r="H60" s="176">
+        <v>293790333.37101603</v>
+      </c>
+      <c r="H60" s="177">
         <f t="shared" ref="H60:H64" si="7">N15</f>
-        <v>97263159.896546006</v>
-      </c>
-      <c r="I60" s="176">
+        <v>117629853.266325</v>
+      </c>
+      <c r="I60" s="177">
         <f t="shared" si="1"/>
-        <v>384860470.813577</v>
-      </c>
-      <c r="J60" s="177">
+        <v>411420186.63734102</v>
+      </c>
+      <c r="J60" s="178">
         <f t="shared" si="2"/>
-        <v>0.76391517510718565</v>
+        <v>0.81663394334393646</v>
       </c>
       <c r="K60" s="165">
         <f t="shared" si="3"/>
-        <v>96419998.406526744</v>
+        <v>90226975.952541709</v>
       </c>
       <c r="L60" s="165">
         <f t="shared" si="4"/>
-        <v>22519538.103453994</v>
+        <v>2152844.7336750031</v>
       </c>
       <c r="M60" s="165">
         <f t="shared" si="5"/>
-        <v>118939536.50998074</v>
+        <v>92379820.686216712</v>
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>39646512.169993579</v>
+        <v>46189910.343108356</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="183" t="s">
+      <c r="B61" s="184" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="184" t="s">
+      <c r="C61" s="185" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="175">
+      <c r="D61" s="176">
         <f>TARGETS!J15</f>
         <v>611629595.7161876</v>
       </c>
-      <c r="E61" s="175">
+      <c r="E61" s="176">
         <f>TARGETS!K15</f>
         <v>40059909</v>
       </c>
-      <c r="F61" s="175">
+      <c r="F61" s="176">
         <f t="shared" si="0"/>
         <v>651689504.7161876</v>
       </c>
-      <c r="G61" s="176">
+      <c r="G61" s="177">
         <f>M16</f>
-        <v>424736895.09258002</v>
-      </c>
-      <c r="H61" s="176">
+        <v>449679124.99856597</v>
+      </c>
+      <c r="H61" s="177">
         <f t="shared" si="7"/>
-        <v>42759954.493941002</v>
-      </c>
-      <c r="I61" s="176">
+        <v>54263754.493941002</v>
+      </c>
+      <c r="I61" s="177">
         <f t="shared" si="1"/>
-        <v>467496849.58652103</v>
-      </c>
-      <c r="J61" s="177">
+        <v>503942879.49250698</v>
+      </c>
+      <c r="J61" s="178">
         <f t="shared" si="2"/>
-        <v>0.71736132959532173</v>
+        <v>0.77328678127473505</v>
       </c>
       <c r="K61" s="165">
         <f t="shared" si="3"/>
-        <v>186892700.62360758</v>
+        <v>161950470.71762162</v>
       </c>
       <c r="L61" s="165">
         <f t="shared" si="4"/>
-        <v>-2700045.4939410016</v>
+        <v>-14203845.493941002</v>
       </c>
       <c r="M61" s="165">
         <f t="shared" si="5"/>
-        <v>184192655.12966657</v>
+        <v>147746625.22368062</v>
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>61397551.709888853</v>
+        <v>73873312.611840308</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="185" t="s">
+      <c r="B62" s="186" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="186" t="s">
+      <c r="C62" s="187" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="178">
+      <c r="D62" s="179">
         <f>TARGETS!J16</f>
         <v>366543022.9053762</v>
       </c>
-      <c r="E62" s="178">
+      <c r="E62" s="179">
         <f>TARGETS!K16</f>
         <v>45082463</v>
       </c>
-      <c r="F62" s="178">
+      <c r="F62" s="179">
         <f t="shared" si="0"/>
         <v>411625485.9053762</v>
       </c>
-      <c r="G62" s="176">
+      <c r="G62" s="177">
         <f>M17</f>
-        <v>274823941.20819598</v>
-      </c>
-      <c r="H62" s="176">
+        <v>295360934.069879</v>
+      </c>
+      <c r="H62" s="177">
         <f t="shared" si="7"/>
-        <v>23725280.784492001</v>
-      </c>
-      <c r="I62" s="176">
+        <v>26245280.784492001</v>
+      </c>
+      <c r="I62" s="177">
         <f t="shared" si="1"/>
-        <v>298549221.992688</v>
-      </c>
-      <c r="J62" s="177">
+        <v>321606214.85437101</v>
+      </c>
+      <c r="J62" s="178">
         <f t="shared" si="2"/>
-        <v>0.7252933363346652</v>
+        <v>0.78130782924432751</v>
       </c>
       <c r="K62" s="165">
         <f t="shared" si="3"/>
-        <v>91719081.697180212</v>
+        <v>71182088.8354972</v>
       </c>
       <c r="L62" s="165">
         <f t="shared" si="4"/>
-        <v>21357182.215507999</v>
+        <v>18837182.215507999</v>
       </c>
       <c r="M62" s="165">
         <f t="shared" si="5"/>
-        <v>113076263.9126882</v>
+        <v>90019271.051005185</v>
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>37692087.970896065</v>
+        <v>45009635.525502592</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="183" t="s">
+      <c r="B63" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="C63" s="184" t="s">
+      <c r="C63" s="185" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="175">
+      <c r="D63" s="176">
         <f>TARGETS!J17</f>
         <v>563350942.09827971</v>
       </c>
-      <c r="E63" s="175">
+      <c r="E63" s="176">
         <f>TARGETS!K17</f>
         <v>311125253</v>
       </c>
-      <c r="F63" s="175">
+      <c r="F63" s="176">
         <f t="shared" si="0"/>
         <v>874476195.09827971</v>
       </c>
-      <c r="G63" s="176">
+      <c r="G63" s="177">
         <f>M18</f>
-        <v>620725908.03147495</v>
-      </c>
-      <c r="H63" s="176">
+        <v>627615097.431445</v>
+      </c>
+      <c r="H63" s="177">
         <f t="shared" si="7"/>
-        <v>183075645.13976899</v>
-      </c>
-      <c r="I63" s="176">
+        <v>183295880.72976899</v>
+      </c>
+      <c r="I63" s="177">
         <f t="shared" si="1"/>
-        <v>803801553.17124391</v>
-      </c>
-      <c r="J63" s="177">
+        <v>810910978.16121399</v>
+      </c>
+      <c r="J63" s="178">
         <f t="shared" si="2"/>
-        <v>0.91918059939974361</v>
+        <v>0.92731052338146058</v>
       </c>
       <c r="K63" s="165">
         <f t="shared" si="3"/>
-        <v>-57374965.933195233</v>
+        <v>-64264155.333165288</v>
       </c>
       <c r="L63" s="165">
         <f t="shared" si="4"/>
-        <v>128049607.86023101</v>
+        <v>127829372.27023101</v>
       </c>
       <c r="M63" s="165">
         <f t="shared" si="5"/>
-        <v>70674641.927035809</v>
+        <v>63565216.937065721</v>
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>23558213.975678604</v>
+        <v>31782608.46853286</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="185" t="s">
+      <c r="B64" s="186" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="186" t="s">
+      <c r="C64" s="187" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="178">
+      <c r="D64" s="179">
         <f>TARGETS!J18</f>
         <v>239525689.01344877</v>
       </c>
-      <c r="E64" s="178">
+      <c r="E64" s="179">
         <f>TARGETS!K18</f>
         <v>239288340</v>
       </c>
-      <c r="F64" s="178">
+      <c r="F64" s="179">
         <f t="shared" si="0"/>
         <v>478814029.01344877</v>
       </c>
-      <c r="G64" s="176">
+      <c r="G64" s="177">
         <f>M19</f>
-        <v>153408407.40240198</v>
-      </c>
-      <c r="H64" s="176">
+        <v>160849546.587598</v>
+      </c>
+      <c r="H64" s="177">
         <f t="shared" si="7"/>
-        <v>145578146.22700301</v>
-      </c>
-      <c r="I64" s="176">
+        <v>152708112.726924</v>
+      </c>
+      <c r="I64" s="177">
         <f t="shared" si="1"/>
-        <v>298986553.62940502</v>
-      </c>
-      <c r="J64" s="177">
+        <v>313557659.31452203</v>
+      </c>
+      <c r="J64" s="178">
         <f t="shared" si="2"/>
-        <v>0.62443148177057106</v>
+        <v>0.65486314166812964</v>
       </c>
       <c r="K64" s="165">
         <f t="shared" si="3"/>
-        <v>86117281.611046791</v>
+        <v>78676142.425850779</v>
       </c>
       <c r="L64" s="165">
         <f t="shared" si="4"/>
-        <v>93710193.772996992</v>
+        <v>86580227.273075998</v>
       </c>
       <c r="M64" s="165">
         <f t="shared" si="5"/>
-        <v>179827475.38404375</v>
+        <v>165256369.69892675</v>
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>59942491.794681251</v>
+        <v>82628184.849463373</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="189" t="s">
+      <c r="B65" s="190" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="190"/>
-      <c r="D65" s="180">
+      <c r="C65" s="191"/>
+      <c r="D65" s="181">
         <f>SUM(D51:D64)</f>
         <v>6619279333.0648613</v>
       </c>
-      <c r="E65" s="180">
+      <c r="E65" s="181">
         <f t="shared" ref="E65" si="8">SUM(E51:E52,E54:E58,E60:E64)</f>
         <v>1269766212</v>
       </c>
-      <c r="F65" s="180">
+      <c r="F65" s="181">
         <f>SUM(F51:F64)</f>
         <v>7889045545.0648613</v>
       </c>
-      <c r="G65" s="181">
+      <c r="G65" s="182">
         <f>SUM(G51:G64)</f>
-        <v>5035768370.6038408</v>
-      </c>
-      <c r="H65" s="181">
+        <v>5254123112.0556602</v>
+      </c>
+      <c r="H65" s="182">
         <f>SUM(H51:H64)</f>
-        <v>860111212.53987396</v>
-      </c>
-      <c r="I65" s="181">
+        <v>924549272.60945392</v>
+      </c>
+      <c r="I65" s="182">
         <f>SUM(I51:I64)</f>
-        <v>5895879583.1437149</v>
-      </c>
-      <c r="J65" s="182">
+        <v>6178672384.6651134</v>
+      </c>
+      <c r="J65" s="183">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.74735017683248028</v>
+        <v>0.78319643984439868</v>
       </c>
       <c r="K65" s="166">
         <f>SUM(K51:K64)</f>
-        <v>1583510962.4610195</v>
+        <v>1365156221.0092006</v>
       </c>
       <c r="L65" s="166">
         <f>SUM(L51:L64)</f>
-        <v>409654999.46012604</v>
+        <v>345216939.39054596</v>
       </c>
       <c r="M65" s="166">
         <f>SUM(M51:M64)</f>
-        <v>1993165961.9211457</v>
+        <v>1710373160.3997462</v>
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>664388653.97371519</v>
+        <v>855186580.19987309</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21115,10 +21127,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21129,8 +21141,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -21139,191 +21151,190 @@
       <c r="I69"/>
     </row>
     <row r="70" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="183" t="s">
+      <c r="B70" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="184" t="s">
+      <c r="C70" s="185" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="191">
+      <c r="D70" s="192">
         <f>IF(E24="",0,E24)</f>
-        <v>17064107.859992001</v>
+        <v>23604648.279991999</v>
       </c>
     </row>
     <row r="71" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="185" t="s">
+      <c r="B71" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="C71" s="186" t="s">
+      <c r="C71" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="192">
+      <c r="D71" s="193">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
         <v>80702340.960000008</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="185" t="s">
+      <c r="B72" s="186" t="s">
         <v>177</v>
       </c>
-      <c r="C72" s="186" t="s">
+      <c r="C72" s="187" t="s">
         <v>178</v>
       </c>
-      <c r="D72" s="192">
+      <c r="D72" s="193">
         <f>IF(E22="",0,E22)</f>
         <v>12315315.119999999</v>
       </c>
     </row>
     <row r="73" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="183" t="s">
+      <c r="B73" s="184" t="s">
         <v>71</v>
       </c>
-      <c r="C73" s="184" t="s">
+      <c r="C73" s="185" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="191">
+      <c r="D73" s="192">
         <f>IF(E14="",0,E14)</f>
-        <v>61073566.889985003</v>
+        <v>61773566.889985003</v>
       </c>
     </row>
     <row r="74" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="185" t="s">
+      <c r="B74" s="186" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="186" t="s">
+      <c r="C74" s="187" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="192">
+      <c r="D74" s="193">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="183" t="s">
+      <c r="B75" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="184" t="s">
+      <c r="C75" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="191">
-        <f>0</f>
-        <v>0</v>
+      <c r="D75" s="192">
+        <v>2883783.76</v>
       </c>
     </row>
     <row r="76" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="185" t="s">
+      <c r="B76" s="186" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="186" t="s">
+      <c r="C76" s="187" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="192">
+      <c r="D76" s="193">
         <f>IF(E19="",0,E19)</f>
-        <v>90842339.400000006</v>
+        <v>202463983.40000001</v>
       </c>
     </row>
     <row r="77" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="183" t="s">
+      <c r="B77" s="184" t="s">
         <v>78</v>
       </c>
-      <c r="C77" s="184" t="s">
+      <c r="C77" s="185" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="191">
+      <c r="D77" s="192">
         <f>IF(E25="",0,E25)</f>
-        <v>21835729.439994998</v>
+        <v>23605098.779995002</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="185" t="s">
+      <c r="B78" s="186" t="s">
         <v>177</v>
       </c>
-      <c r="C78" s="186" t="s">
+      <c r="C78" s="187" t="s">
         <v>179</v>
       </c>
-      <c r="D78" s="192">
+      <c r="D78" s="193">
         <f>IF(E23="",0,E23)</f>
         <v>17121621.32</v>
       </c>
     </row>
     <row r="79" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="185" t="s">
+      <c r="B79" s="186" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="186" t="s">
+      <c r="C79" s="187" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="192">
+      <c r="D79" s="193">
         <f>IF(E11="",0,E11)</f>
         <v>34053355</v>
       </c>
     </row>
     <row r="80" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="183" t="s">
+      <c r="B80" s="184" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="184" t="s">
+      <c r="C80" s="185" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="191">
+      <c r="D80" s="192">
         <f>IF(E26="",0,E26)</f>
-        <v>88375679.199880004</v>
+        <v>90460363.869880006</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="185" t="s">
+      <c r="B81" s="186" t="s">
         <v>84</v>
       </c>
-      <c r="C81" s="186" t="s">
+      <c r="C81" s="187" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="192">
+      <c r="D81" s="193">
         <f>IF(E10="",0,E10)</f>
-        <v>56364538.979979999</v>
+        <v>60112286.639980003</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="183" t="s">
+      <c r="B82" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="C82" s="184" t="s">
+      <c r="C82" s="185" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="191">
+      <c r="D82" s="192">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="185" t="s">
+      <c r="B83" s="186" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="187" t="s">
         <v>89</v>
       </c>
-      <c r="D83" s="192">
+      <c r="D83" s="193">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="189" t="s">
+      <c r="B84" s="190" t="s">
         <v>152</v>
       </c>
-      <c r="C84" s="190"/>
-      <c r="D84" s="193">
+      <c r="C84" s="191"/>
+      <c r="D84" s="194">
         <f>SUM(D70:D83)</f>
-        <v>479748594.16983199</v>
+        <v>609096364.01983202</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="220" t="s">
+      <c r="B87" s="221" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="221"/>
-      <c r="D87" s="221"/>
-      <c r="E87" s="221"/>
-      <c r="F87" s="222"/>
+      <c r="C87" s="222"/>
+      <c r="D87" s="222"/>
+      <c r="E87" s="222"/>
+      <c r="F87" s="223"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21353,108 +21364,108 @@
       <c r="I88" s="168"/>
     </row>
     <row r="89" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="183" t="s">
+      <c r="B89" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="184" t="s">
+      <c r="C89" s="185" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="194">
+      <c r="D89" s="195">
         <f>TARGETS!G22</f>
         <v>279391895.3166402</v>
       </c>
-      <c r="E89" s="176">
+      <c r="E89" s="177">
         <f>IFERROR(C32,0)</f>
-        <v>177330791.25874501</v>
-      </c>
-      <c r="F89" s="177">
+        <v>203076300.00860801</v>
+      </c>
+      <c r="F89" s="178">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
-        <v>0.63470270337574619</v>
+        <v>0.7268510769736457</v>
       </c>
       <c r="G89" s="171">
         <f>D89-E89</f>
-        <v>102061104.05789518</v>
+        <v>76315595.308032185</v>
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>34020368.019298397</v>
+        <v>38157797.654016092</v>
       </c>
       <c r="I89" s="168"/>
     </row>
     <row r="90" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="185" t="s">
+      <c r="B90" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="C90" s="186" t="s">
+      <c r="C90" s="187" t="s">
         <v>95</v>
       </c>
-      <c r="D90" s="195">
+      <c r="D90" s="196">
         <f>TARGETS!G23</f>
         <v>419611959.16831887</v>
       </c>
-      <c r="E90" s="176">
+      <c r="E90" s="177">
         <f>IFERROR(C33,0)</f>
-        <v>448679644.76670098</v>
-      </c>
-      <c r="F90" s="177">
+        <v>452153563.80664498</v>
+      </c>
+      <c r="F90" s="178">
         <f t="shared" si="9"/>
-        <v>1.0692727768197907</v>
+        <v>1.0775516615465974</v>
       </c>
       <c r="G90" s="172">
         <f>D90-E90</f>
-        <v>-29067685.598382115</v>
+        <v>-32541604.638326108</v>
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-9689228.5327940378</v>
+        <v>-16270802.319163054</v>
       </c>
       <c r="I90" s="168"/>
     </row>
     <row r="91" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="183" t="s">
+      <c r="B91" s="184" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="184" t="s">
+      <c r="C91" s="185" t="s">
         <v>97</v>
       </c>
-      <c r="D91" s="194">
+      <c r="D91" s="195">
         <f>TARGETS!G24</f>
         <v>1092485507.2171693</v>
       </c>
-      <c r="E91" s="176">
+      <c r="E91" s="177">
         <f>M21+M7</f>
-        <v>767572450.50459599</v>
-      </c>
-      <c r="F91" s="177">
+        <v>794555516.424474</v>
+      </c>
+      <c r="F91" s="178">
         <f t="shared" si="9"/>
-        <v>0.70259279911162653</v>
+        <v>0.72729158526633764</v>
       </c>
       <c r="G91" s="171">
         <f>D91-E91</f>
-        <v>324913056.71257329</v>
+        <v>297929990.79269528</v>
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>108304352.23752443</v>
+        <v>148964995.39634764</v>
       </c>
       <c r="I91" s="168"/>
     </row>
     <row r="92" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="185" t="s">
+      <c r="B92" s="186" t="s">
         <v>98</v>
       </c>
-      <c r="C92" s="186" t="s">
+      <c r="C92" s="187" t="s">
         <v>99</v>
       </c>
-      <c r="D92" s="195">
+      <c r="D92" s="196">
         <f>TARGETS!G25</f>
         <v>0</v>
       </c>
-      <c r="E92" s="176">
+      <c r="E92" s="177">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F92" s="177">
+      <c r="F92" s="178">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21469,21 +21480,21 @@
       <c r="I92" s="168"/>
     </row>
     <row r="93" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="183" t="s">
+      <c r="B93" s="184" t="s">
         <v>100</v>
       </c>
-      <c r="C93" s="196" t="s">
+      <c r="C93" s="197" t="s">
         <v>101</v>
       </c>
-      <c r="D93" s="194">
+      <c r="D93" s="195">
         <f>TARGETS!G26</f>
         <v>0</v>
       </c>
-      <c r="E93" s="176">
+      <c r="E93" s="177">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F93" s="177">
+      <c r="F93" s="178">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21498,29 +21509,29 @@
       <c r="I93" s="168"/>
     </row>
     <row r="94" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="189" t="s">
+      <c r="B94" s="190" t="s">
         <v>152</v>
       </c>
-      <c r="C94" s="190"/>
-      <c r="D94" s="197">
+      <c r="C94" s="191"/>
+      <c r="D94" s="198">
         <f>SUM(D89:D93)</f>
         <v>1791489361.7021284</v>
       </c>
-      <c r="E94" s="197">
+      <c r="E94" s="198">
         <f>SUM(E89:E93)</f>
-        <v>1393582886.5300419</v>
-      </c>
-      <c r="F94" s="174">
+        <v>1449785380.239727</v>
+      </c>
+      <c r="F94" s="175">
         <f t="shared" si="9"/>
-        <v>0.77789068488018931</v>
+        <v>0.80926262317419406</v>
       </c>
       <c r="G94" s="173">
         <f>SUM(G89:G93)</f>
-        <v>397906475.17208636</v>
+        <v>341703981.46240139</v>
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>132635491.72402878</v>
+        <v>170851990.7312007</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21556,7 +21567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -21606,7 +21617,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -22139,11 +22150,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>159</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -22267,10 +22278,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -22299,40 +22310,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22340,13 +22351,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22365,7 +22376,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22375,7 +22386,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -23168,10 +23179,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23179,8 +23190,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -23374,13 +23385,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23613,7 +23624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23663,7 +23674,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -24196,11 +24207,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>161</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24324,10 +24335,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24356,40 +24367,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24397,13 +24408,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24422,7 +24433,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24432,7 +24443,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25225,10 +25236,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25236,8 +25247,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -25431,13 +25442,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25670,7 +25681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -25720,7 +25731,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -26253,11 +26264,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="217" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="217"/>
-      <c r="D41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="219"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26381,10 +26392,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="214"/>
+      <c r="C46" s="215"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26413,40 +26424,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="220" t="s">
+      <c r="B48" s="221" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="221"/>
-      <c r="D48" s="221"/>
-      <c r="E48" s="221"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="221"/>
-      <c r="J48" s="222"/>
-      <c r="K48" s="233"/>
-      <c r="L48" s="234"/>
-      <c r="M48" s="234"/>
-      <c r="N48" s="235"/>
+      <c r="C48" s="222"/>
+      <c r="D48" s="222"/>
+      <c r="E48" s="222"/>
+      <c r="F48" s="222"/>
+      <c r="G48" s="222"/>
+      <c r="H48" s="222"/>
+      <c r="I48" s="222"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="210" t="s">
+      <c r="D49" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="211"/>
-      <c r="F49" s="212"/>
+      <c r="E49" s="212"/>
+      <c r="F49" s="213"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="216" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26454,13 +26465,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="236" t="s">
+      <c r="N49" s="237" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="215"/>
-      <c r="C50" s="215"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="216"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26479,7 +26490,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="215"/>
+      <c r="J50" s="216"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26489,7 +26500,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="236"/>
+      <c r="N50" s="237"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27282,10 +27293,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="216" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="215" t="s">
+      <c r="C68" s="216" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27293,8 +27304,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="215"/>
-      <c r="C69" s="215"/>
+      <c r="B69" s="216"/>
+      <c r="C69" s="216"/>
       <c r="D69" s="71" t="s">
         <v>173</v>
       </c>
@@ -27488,13 +27499,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="230" t="s">
+      <c r="B87" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="231"/>
-      <c r="D87" s="231"/>
-      <c r="E87" s="231"/>
-      <c r="F87" s="232"/>
+      <c r="C87" s="232"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="233"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — DESEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 29 APRIL 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
 </sst>
 </file>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -4836,11 +4836,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4848,6 +4843,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -6893,11 +6893,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6905,6 +6900,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -8950,11 +8950,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8962,6 +8957,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11007,11 +11007,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11019,6 +11014,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -13049,11 +13049,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13061,6 +13056,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19580,11 +19580,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>291683670.26340503</v>
+        <v>299770568.60838997</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>44627609.843964003</v>
+        <v>45375105.343964003</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -19603,11 +19603,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>484491472.12148905</v>
+        <v>491669786.60148901</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>113473009.55866</v>
+        <v>120248212.43861198</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -19615,22 +19615,22 @@
         <v>113</v>
       </c>
       <c r="C10" s="174">
-        <v>295360934.069879</v>
+        <v>303439555.68576801</v>
       </c>
       <c r="D10" s="174">
-        <v>26245280.784492001</v>
+        <v>28364314.698472001</v>
       </c>
       <c r="E10" s="174">
-        <v>60112286.639980003</v>
+        <v>61031205.54998</v>
       </c>
       <c r="F10" s="174">
-        <v>381718501.49435103</v>
+        <v>392835075.93422002</v>
       </c>
       <c r="G10"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>507340228.22389603</v>
+        <v>537997275.46389103</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -19642,26 +19642,26 @@
         <v>114</v>
       </c>
       <c r="C11" s="174">
-        <v>293790333.37101603</v>
+        <v>304137742.30899602</v>
       </c>
       <c r="D11" s="174">
-        <v>117629853.266325</v>
+        <v>119707150.766315</v>
       </c>
       <c r="E11" s="174">
         <v>34053355</v>
       </c>
       <c r="F11" s="174">
-        <v>445473541.63734102</v>
+        <v>457898248.07531101</v>
       </c>
       <c r="G11"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>292382877.82999301</v>
+        <v>355626119.92999297</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>40333351.310000002</v>
+        <v>44657675.509999998</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -19669,26 +19669,26 @@
         <v>70</v>
       </c>
       <c r="C12" s="174">
-        <v>252158338.70392501</v>
+        <v>255272238.70392501</v>
       </c>
       <c r="D12" s="174">
-        <v>74194812.198893994</v>
+        <v>80101515.078845993</v>
       </c>
       <c r="E12" s="174">
         <v>71143242</v>
       </c>
       <c r="F12" s="174">
-        <v>397496392.90281898</v>
+        <v>406516995.78277099</v>
       </c>
       <c r="G12"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>419579054.27561802</v>
+        <v>449682614.319305</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>58766854.885816</v>
+        <v>60505589.095815003</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -19696,26 +19696,26 @@
         <v>115</v>
       </c>
       <c r="C13" s="174">
-        <v>232333133.417564</v>
+        <v>236397547.89756399</v>
       </c>
       <c r="D13" s="174">
-        <v>39278197.359765999</v>
+        <v>40146697.359765999</v>
       </c>
       <c r="E13" s="174">
-        <v>9559098.9600000009</v>
+        <v>10759098.960000001</v>
       </c>
       <c r="F13" s="174">
-        <v>281170429.73733002</v>
+        <v>287303344.21732998</v>
       </c>
       <c r="G13"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>929286104.73370302</v>
+        <v>1030915377.322188</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>53446535.799857996</v>
+        <v>59498535.799857996</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -19723,26 +19723,26 @@
         <v>116</v>
       </c>
       <c r="C14" s="174">
-        <v>507340228.22389603</v>
+        <v>537997275.46389103</v>
       </c>
       <c r="D14" s="174">
         <v>21205741.099730998</v>
       </c>
       <c r="E14" s="174">
-        <v>61773566.889985003</v>
+        <v>66130323.599985003</v>
       </c>
       <c r="F14" s="174">
-        <v>590319536.21361196</v>
+        <v>625333340.163607</v>
       </c>
       <c r="G14"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>363728557.02905202</v>
+        <v>378754537.60554802</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>58553288.109973997</v>
+        <v>62284984.519973002</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -19759,11 +19759,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>293790333.37101603</v>
+        <v>304137742.30899602</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>117629853.266325</v>
+        <v>119707150.766315</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -19771,26 +19771,26 @@
         <v>74</v>
       </c>
       <c r="C16" s="174">
-        <v>419579054.27561802</v>
+        <v>449682614.319305</v>
       </c>
       <c r="D16" s="174">
-        <v>58766854.885816</v>
+        <v>60505589.095815003</v>
       </c>
       <c r="E16" s="174">
         <v>2883783.76</v>
       </c>
       <c r="F16" s="174">
-        <v>481229692.92143399</v>
+        <v>513071987.17512</v>
       </c>
       <c r="G16"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>449679124.99856597</v>
+        <v>479291727.990435</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>54263754.493941002</v>
+        <v>61629599.543938003</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -19798,26 +19798,26 @@
         <v>118</v>
       </c>
       <c r="C17" s="174">
-        <v>292382877.82999301</v>
+        <v>355626119.92999297</v>
       </c>
       <c r="D17" s="174">
-        <v>40333351.310000002</v>
+        <v>44657675.509999998</v>
       </c>
       <c r="E17" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F17" s="174">
-        <v>332716229.13999301</v>
+        <v>400283795.43999302</v>
       </c>
       <c r="G17"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>295360934.069879</v>
+        <v>303439555.68576801</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>26245280.784492001</v>
+        <v>28364314.698472001</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
@@ -19825,26 +19825,26 @@
         <v>119</v>
       </c>
       <c r="C18" s="174">
-        <v>1264403971.559751</v>
+        <v>1267577083.8097451</v>
       </c>
       <c r="D18" s="174">
-        <v>9226432.7548970003</v>
+        <v>9652531.8548969999</v>
       </c>
       <c r="E18" s="174">
-        <v>1835135.12</v>
+        <v>3932432.4</v>
       </c>
       <c r="F18" s="174">
-        <v>1275465539.434648</v>
+        <v>1281162048.064642</v>
       </c>
       <c r="G18"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>627615097.431445</v>
+        <v>663559823.79009497</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>183295880.72976899</v>
+        <v>200253231.98958299</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
@@ -19852,22 +19852,22 @@
         <v>121</v>
       </c>
       <c r="C19" s="174">
-        <v>929286104.73370302</v>
+        <v>1030915377.322188</v>
       </c>
       <c r="D19" s="174">
-        <v>53446535.799857996</v>
+        <v>59498535.799857996</v>
       </c>
       <c r="E19" s="174">
-        <v>202463983.40000001</v>
+        <v>287203621.35000002</v>
       </c>
       <c r="F19" s="174">
-        <v>1185196623.9335611</v>
+        <v>1377617534.4720459</v>
       </c>
       <c r="G19"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>160849546.587598</v>
+        <v>162674997.04759601</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
@@ -19879,7 +19879,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="174">
-        <v>103489607.16759799</v>
+        <v>105315057.62759601</v>
       </c>
       <c r="D20" s="174">
         <v>16467727.799813</v>
@@ -19888,7 +19888,7 @@
         <v>170</v>
       </c>
       <c r="F20" s="174">
-        <v>119957334.967411</v>
+        <v>121782785.42740899</v>
       </c>
       <c r="G20"/>
       <c r="J20" s="116"/>
@@ -19920,7 +19920,7 @@
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>794555516.424474</v>
+        <v>897130483.57328391</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -19952,16 +19952,16 @@
         <v>175</v>
       </c>
       <c r="C23" s="174">
-        <v>99451782.519999996</v>
+        <v>120550492.72</v>
       </c>
       <c r="D23" s="174" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="174">
-        <v>17121621.32</v>
+        <v>17151621.32</v>
       </c>
       <c r="F23" s="174">
-        <v>116573403.84</v>
+        <v>137702114.03999999</v>
       </c>
       <c r="G23"/>
       <c r="J23" s="116"/>
@@ -19973,16 +19973,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="174">
-        <v>291683670.26340503</v>
+        <v>299770568.60838997</v>
       </c>
       <c r="D24" s="174">
-        <v>44627609.843964003</v>
+        <v>45375105.343964003</v>
       </c>
       <c r="E24" s="174">
-        <v>23604648.279991999</v>
+        <v>24325368.979991999</v>
       </c>
       <c r="F24" s="174">
-        <v>359915928.38736099</v>
+        <v>369471042.93234599</v>
       </c>
       <c r="G24"/>
       <c r="J24" s="116"/>
@@ -19992,16 +19992,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="174">
-        <v>363728557.02905202</v>
+        <v>378754537.60554802</v>
       </c>
       <c r="D25" s="174">
-        <v>58553288.109973997</v>
+        <v>62284984.519973002</v>
       </c>
       <c r="E25" s="174">
-        <v>23605098.779995002</v>
+        <v>26407801.439994998</v>
       </c>
       <c r="F25" s="174">
-        <v>445886943.91902101</v>
+        <v>467447323.565516</v>
       </c>
       <c r="G25"/>
       <c r="J25" s="116"/>
@@ -20011,16 +20011,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="174">
-        <v>449679124.99856597</v>
+        <v>479291727.990435</v>
       </c>
       <c r="D26" s="174">
-        <v>54263754.493941002</v>
+        <v>61629599.543938003</v>
       </c>
       <c r="E26" s="174">
-        <v>90460363.869880006</v>
+        <v>112736039.39988001</v>
       </c>
       <c r="F26" s="174">
-        <v>594403243.36238694</v>
+        <v>653657366.93425298</v>
       </c>
       <c r="G26"/>
       <c r="J26" s="116"/>
@@ -20030,16 +20030,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="174">
-        <v>627615097.431445</v>
+        <v>663559823.79009497</v>
       </c>
       <c r="D27" s="174">
-        <v>183295880.72976899</v>
+        <v>200253231.98958299</v>
       </c>
       <c r="E27" s="174" t="s">
         <v>170</v>
       </c>
       <c r="F27" s="174">
-        <v>810910978.16121399</v>
+        <v>863813055.77967799</v>
       </c>
       <c r="G27"/>
       <c r="J27" s="116"/>
@@ -20067,7 +20067,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="174">
-        <v>203076300.00860801</v>
+        <v>240237597.65824801</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
@@ -20075,7 +20075,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="174">
-        <v>452153563.80664498</v>
+        <v>449933743.924721</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
@@ -20083,7 +20083,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="174">
-        <v>308523578.99607402</v>
+        <v>318278585.086043</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
@@ -20091,7 +20091,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="174">
-        <v>174741132.22842401</v>
+        <v>267561093.287265</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.96666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20162,19 +20162,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>5254123112.0556602</v>
+        <v>5616954947.9936943</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.79376059653655595</v>
+        <v>0.84857499817777438</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>1365156221.009201</v>
+        <v>1002324385.071167</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>682578110.50460052</v>
+        <v>1002324385.071167</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20190,19 +20190,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>924549272.60945392</v>
+        <v>976438253.53318501</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.72812559026374057</v>
+        <v>0.76899057819092842</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>345216939.39054608</v>
+        <v>293327958.46681499</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>172608469.69527304</v>
+        <v>293327958.46681499</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20218,19 +20218,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>1449785380.239727</v>
+        <v>1587301825.1562529</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.80926262317419406</v>
+        <v>0.88602358411334747</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>341703981.46240139</v>
+        <v>204187536.54587555</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>170851990.7312007</v>
+        <v>204187536.54587555</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20244,19 +20244,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>7628457764.9048414</v>
+        <v>8180695026.6831322</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.78802027350496051</v>
+        <v>0.84506642509646601</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>2052077141.8621485</v>
+        <v>1499839880.0838575</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>1026038570.9310743</v>
+        <v>1499839880.0838575</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20359,35 +20359,35 @@
       </c>
       <c r="G51" s="177">
         <f>M8</f>
-        <v>291683670.26340503</v>
+        <v>299770568.60838997</v>
       </c>
       <c r="H51" s="177">
         <f>N8</f>
-        <v>44627609.843964003</v>
+        <v>45375105.343964003</v>
       </c>
       <c r="I51" s="177">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>336311280.10736901</v>
+        <v>345145673.95235395</v>
       </c>
       <c r="J51" s="178">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.75360125425322932</v>
+        <v>0.77339723100435753</v>
       </c>
       <c r="K51" s="164">
         <f t="shared" ref="K51:K64" si="3">D51-G51</f>
-        <v>104999808.06281167</v>
+        <v>96912909.717826724</v>
       </c>
       <c r="L51" s="164">
         <f t="shared" ref="L51:L64" si="4">E51-H51</f>
-        <v>4961099.156035997</v>
+        <v>4213603.656035997</v>
       </c>
       <c r="M51" s="164">
         <f t="shared" ref="M51:M64" si="5">F51-I51</f>
-        <v>109960907.21884769</v>
+        <v>101126513.37386274</v>
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>54980453.609423846</v>
+        <v>101126513.37386274</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20411,35 +20411,35 @@
       </c>
       <c r="G52" s="177">
         <f>M9</f>
-        <v>484491472.12148905</v>
+        <v>491669786.60148901</v>
       </c>
       <c r="H52" s="177">
         <f>N9</f>
-        <v>113473009.55866</v>
+        <v>120248212.43861198</v>
       </c>
       <c r="I52" s="177">
         <f t="shared" si="1"/>
-        <v>597964481.68014908</v>
+        <v>611917999.04010105</v>
       </c>
       <c r="J52" s="178">
         <f t="shared" si="2"/>
-        <v>0.84452598579560068</v>
+        <v>0.86423302252563972</v>
       </c>
       <c r="K52" s="165">
         <f t="shared" si="3"/>
-        <v>50690898.878510952</v>
+        <v>43512584.398510993</v>
       </c>
       <c r="L52" s="165">
         <f t="shared" si="4"/>
-        <v>59392082.441339999</v>
+        <v>52616879.561388016</v>
       </c>
       <c r="M52" s="165">
         <f t="shared" si="5"/>
-        <v>110082981.31985092</v>
+        <v>96129463.959898949</v>
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>55041490.659925461</v>
+        <v>96129463.959898949</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>101294469.7</v>
+        <v>202588939.40000001</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20515,7 +20515,7 @@
       </c>
       <c r="G54" s="177">
         <f>M10</f>
-        <v>507340228.22389603</v>
+        <v>537997275.46389103</v>
       </c>
       <c r="H54" s="177">
         <f t="shared" ref="H54:H58" si="6">N10</f>
@@ -20523,15 +20523,15 @@
       </c>
       <c r="I54" s="177">
         <f t="shared" si="1"/>
-        <v>528545969.323627</v>
+        <v>559203016.563622</v>
       </c>
       <c r="J54" s="178">
         <f t="shared" si="2"/>
-        <v>0.85399127988593726</v>
+        <v>0.90352500548318337</v>
       </c>
       <c r="K54" s="165">
         <f>D54-G54</f>
-        <v>83372243.699001193</v>
+        <v>52715196.45900619</v>
       </c>
       <c r="L54" s="165">
         <f t="shared" si="4"/>
@@ -20539,11 +20539,11 @@
       </c>
       <c r="M54" s="165">
         <f t="shared" si="5"/>
-        <v>90366637.599270225</v>
+        <v>59709590.359275222</v>
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>45183318.799635112</v>
+        <v>59709590.359275222</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20567,35 +20567,35 @@
       </c>
       <c r="G55" s="177">
         <f>M11</f>
-        <v>292382877.82999301</v>
+        <v>355626119.92999297</v>
       </c>
       <c r="H55" s="177">
         <f t="shared" si="6"/>
-        <v>40333351.310000002</v>
+        <v>44657675.509999998</v>
       </c>
       <c r="I55" s="177">
         <f t="shared" si="1"/>
-        <v>332716229.13999301</v>
+        <v>400283795.43999296</v>
       </c>
       <c r="J55" s="178">
         <f t="shared" si="2"/>
-        <v>0.71003432491908214</v>
+        <v>0.85422714487334961</v>
       </c>
       <c r="K55" s="165">
         <f t="shared" si="3"/>
-        <v>102680406.36153114</v>
+        <v>39437164.261531174</v>
       </c>
       <c r="L55" s="165">
         <f t="shared" si="4"/>
-        <v>33195117.689999998</v>
+        <v>28870793.490000002</v>
       </c>
       <c r="M55" s="165">
         <f t="shared" si="5"/>
-        <v>135875524.05153114</v>
+        <v>68307957.751531184</v>
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>67937762.025765568</v>
+        <v>68307957.751531184</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20619,35 +20619,35 @@
       </c>
       <c r="G56" s="177">
         <f>M12</f>
-        <v>419579054.27561802</v>
+        <v>449682614.319305</v>
       </c>
       <c r="H56" s="177">
         <f t="shared" si="6"/>
-        <v>58766854.885816</v>
+        <v>60505589.095815003</v>
       </c>
       <c r="I56" s="177">
         <f t="shared" si="1"/>
-        <v>478345909.16143399</v>
+        <v>510188203.41512001</v>
       </c>
       <c r="J56" s="178">
         <f t="shared" si="2"/>
-        <v>0.89274056218918496</v>
+        <v>0.95216807506007584</v>
       </c>
       <c r="K56" s="165">
         <f t="shared" si="3"/>
-        <v>44339777.847035587</v>
+        <v>14236217.803348601</v>
       </c>
       <c r="L56" s="165">
         <f t="shared" si="4"/>
-        <v>13131693.114184</v>
+        <v>11392958.904184997</v>
       </c>
       <c r="M56" s="165">
         <f t="shared" si="5"/>
-        <v>57471470.961219609</v>
+        <v>25629176.707533598</v>
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>28735735.480609804</v>
+        <v>25629176.707533598</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20671,35 +20671,35 @@
       </c>
       <c r="G57" s="177">
         <f>M13</f>
-        <v>929286104.73370302</v>
+        <v>1030915377.322188</v>
       </c>
       <c r="H57" s="177">
         <f t="shared" si="6"/>
-        <v>53446535.799857996</v>
+        <v>59498535.799857996</v>
       </c>
       <c r="I57" s="177">
         <f t="shared" si="1"/>
-        <v>982732640.53356099</v>
+        <v>1090413913.122046</v>
       </c>
       <c r="J57" s="178">
         <f t="shared" si="2"/>
-        <v>0.96820450971586303</v>
+        <v>1.0742938868586729</v>
       </c>
       <c r="K57" s="165">
         <f t="shared" si="3"/>
-        <v>12472240.711015701</v>
+        <v>-89157031.877469301</v>
       </c>
       <c r="L57" s="165">
         <f t="shared" si="4"/>
-        <v>19800348.200142004</v>
+        <v>13748348.200142004</v>
       </c>
       <c r="M57" s="165">
         <f t="shared" si="5"/>
-        <v>32272588.911157727</v>
+        <v>-75408683.677327275</v>
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>16136294.455578864</v>
+        <v>-75408683.677327275</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20723,35 +20723,35 @@
       </c>
       <c r="G58" s="177">
         <f>M14</f>
-        <v>363728557.02905202</v>
+        <v>378754537.60554802</v>
       </c>
       <c r="H58" s="177">
         <f t="shared" si="6"/>
-        <v>58553288.109973997</v>
+        <v>62284984.519973002</v>
       </c>
       <c r="I58" s="177">
         <f>G58+H58</f>
-        <v>422281845.13902605</v>
+        <v>441039522.125521</v>
       </c>
       <c r="J58" s="178">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.79617718281858518</v>
+        <v>0.83154321759190519</v>
       </c>
       <c r="K58" s="165">
         <f t="shared" si="3"/>
-        <v>121558501.97094798</v>
+        <v>106532521.39445198</v>
       </c>
       <c r="L58" s="165">
         <f t="shared" si="4"/>
-        <v>-13453576.109973997</v>
+        <v>-17185272.519973002</v>
       </c>
       <c r="M58" s="165">
         <f t="shared" si="5"/>
-        <v>108104925.86097395</v>
+        <v>89347248.874478996</v>
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>54052462.930486977</v>
+        <v>89347248.874478996</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="G59" s="177">
         <f>C23</f>
-        <v>99451782.519999996</v>
+        <v>120550492.72</v>
       </c>
       <c r="H59" s="177">
         <f>IF(D23="",0,D23)</f>
@@ -20783,15 +20783,15 @@
       </c>
       <c r="I59" s="177">
         <f>G59+H59</f>
-        <v>99451782.519999996</v>
+        <v>120550492.72</v>
       </c>
       <c r="J59" s="178">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.24608636047701285</v>
+        <v>0.29829361782640307</v>
       </c>
       <c r="K59" s="165">
         <f>D59-G59</f>
-        <v>304681881.48000002</v>
+        <v>283583171.27999997</v>
       </c>
       <c r="L59" s="165">
         <f>E59-H59</f>
@@ -20799,11 +20799,11 @@
       </c>
       <c r="M59" s="165">
         <f>F59-I59</f>
-        <v>304681881.48000002</v>
+        <v>283583171.27999997</v>
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>152340940.74000001</v>
+        <v>283583171.27999997</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20827,35 +20827,35 @@
       </c>
       <c r="G60" s="177">
         <f>M15</f>
-        <v>293790333.37101603</v>
+        <v>304137742.30899602</v>
       </c>
       <c r="H60" s="177">
         <f t="shared" ref="H60:H64" si="7">N15</f>
-        <v>117629853.266325</v>
+        <v>119707150.766315</v>
       </c>
       <c r="I60" s="177">
         <f t="shared" si="1"/>
-        <v>411420186.63734102</v>
+        <v>423844893.07531101</v>
       </c>
       <c r="J60" s="178">
         <f t="shared" si="2"/>
-        <v>0.81663394334393646</v>
+        <v>0.84129592479958659</v>
       </c>
       <c r="K60" s="165">
         <f t="shared" si="3"/>
-        <v>90226975.952541709</v>
+        <v>79879567.014561713</v>
       </c>
       <c r="L60" s="165">
         <f t="shared" si="4"/>
-        <v>2152844.7336750031</v>
+        <v>75547.233685001731</v>
       </c>
       <c r="M60" s="165">
         <f t="shared" si="5"/>
-        <v>92379820.686216712</v>
+        <v>79955114.248246729</v>
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>46189910.343108356</v>
+        <v>79955114.248246729</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20879,35 +20879,35 @@
       </c>
       <c r="G61" s="177">
         <f>M16</f>
-        <v>449679124.99856597</v>
+        <v>479291727.990435</v>
       </c>
       <c r="H61" s="177">
         <f t="shared" si="7"/>
-        <v>54263754.493941002</v>
+        <v>61629599.543938003</v>
       </c>
       <c r="I61" s="177">
         <f t="shared" si="1"/>
-        <v>503942879.49250698</v>
+        <v>540921327.53437304</v>
       </c>
       <c r="J61" s="178">
         <f t="shared" si="2"/>
-        <v>0.77328678127473505</v>
+        <v>0.8300292142497302</v>
       </c>
       <c r="K61" s="165">
         <f t="shared" si="3"/>
-        <v>161950470.71762162</v>
+        <v>132337867.72575259</v>
       </c>
       <c r="L61" s="165">
         <f t="shared" si="4"/>
-        <v>-14203845.493941002</v>
+        <v>-21569690.543938003</v>
       </c>
       <c r="M61" s="165">
         <f t="shared" si="5"/>
-        <v>147746625.22368062</v>
+        <v>110768177.18181455</v>
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>73873312.611840308</v>
+        <v>110768177.18181455</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20931,35 +20931,35 @@
       </c>
       <c r="G62" s="177">
         <f>M17</f>
-        <v>295360934.069879</v>
+        <v>303439555.68576801</v>
       </c>
       <c r="H62" s="177">
         <f t="shared" si="7"/>
-        <v>26245280.784492001</v>
+        <v>28364314.698472001</v>
       </c>
       <c r="I62" s="177">
         <f t="shared" si="1"/>
-        <v>321606214.85437101</v>
+        <v>331803870.38424003</v>
       </c>
       <c r="J62" s="178">
         <f t="shared" si="2"/>
-        <v>0.78130782924432751</v>
+        <v>0.80608194036973346</v>
       </c>
       <c r="K62" s="165">
         <f t="shared" si="3"/>
-        <v>71182088.8354972</v>
+        <v>63103467.219608188</v>
       </c>
       <c r="L62" s="165">
         <f t="shared" si="4"/>
-        <v>18837182.215507999</v>
+        <v>16718148.301527999</v>
       </c>
       <c r="M62" s="165">
         <f t="shared" si="5"/>
-        <v>90019271.051005185</v>
+        <v>79821615.521136165</v>
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>45009635.525502592</v>
+        <v>79821615.521136165</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20983,35 +20983,35 @@
       </c>
       <c r="G63" s="177">
         <f>M18</f>
-        <v>627615097.431445</v>
+        <v>663559823.79009497</v>
       </c>
       <c r="H63" s="177">
         <f t="shared" si="7"/>
-        <v>183295880.72976899</v>
+        <v>200253231.98958299</v>
       </c>
       <c r="I63" s="177">
         <f t="shared" si="1"/>
-        <v>810910978.16121399</v>
+        <v>863813055.77967799</v>
       </c>
       <c r="J63" s="178">
         <f t="shared" si="2"/>
-        <v>0.92731052338146058</v>
+        <v>0.98780625547227918</v>
       </c>
       <c r="K63" s="165">
         <f t="shared" si="3"/>
-        <v>-64264155.333165288</v>
+        <v>-100208881.69181526</v>
       </c>
       <c r="L63" s="165">
         <f t="shared" si="4"/>
-        <v>127829372.27023101</v>
+        <v>110872021.01041701</v>
       </c>
       <c r="M63" s="165">
         <f t="shared" si="5"/>
-        <v>63565216.937065721</v>
+        <v>10663139.318601727</v>
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>31782608.46853286</v>
+        <v>10663139.318601727</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="G64" s="177">
         <f>M19</f>
-        <v>160849546.587598</v>
+        <v>162674997.04759601</v>
       </c>
       <c r="H64" s="177">
         <f t="shared" si="7"/>
@@ -21043,15 +21043,15 @@
       </c>
       <c r="I64" s="177">
         <f t="shared" si="1"/>
-        <v>313557659.31452203</v>
+        <v>315383109.77452004</v>
       </c>
       <c r="J64" s="178">
         <f t="shared" si="2"/>
-        <v>0.65486314166812964</v>
+        <v>0.65867558313681251</v>
       </c>
       <c r="K64" s="165">
         <f t="shared" si="3"/>
-        <v>78676142.425850779</v>
+        <v>76850691.965852767</v>
       </c>
       <c r="L64" s="165">
         <f t="shared" si="4"/>
@@ -21059,11 +21059,11 @@
       </c>
       <c r="M64" s="165">
         <f t="shared" si="5"/>
-        <v>165256369.69892675</v>
+        <v>163430919.23892874</v>
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>82628184.849463373</v>
+        <v>163430919.23892874</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21085,35 +21085,35 @@
       </c>
       <c r="G65" s="182">
         <f>SUM(G51:G64)</f>
-        <v>5254123112.0556602</v>
+        <v>5616954947.9936943</v>
       </c>
       <c r="H65" s="182">
         <f>SUM(H51:H64)</f>
-        <v>924549272.60945392</v>
+        <v>976438253.53318501</v>
       </c>
       <c r="I65" s="182">
         <f>SUM(I51:I64)</f>
-        <v>6178672384.6651134</v>
+        <v>6593393201.5268793</v>
       </c>
       <c r="J65" s="183">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.78319643984439868</v>
+        <v>0.83576564032533673</v>
       </c>
       <c r="K65" s="166">
         <f>SUM(K51:K64)</f>
-        <v>1365156221.0092006</v>
+        <v>1002324385.0711663</v>
       </c>
       <c r="L65" s="166">
         <f>SUM(L51:L64)</f>
-        <v>345216939.39054596</v>
+        <v>293327958.46681499</v>
       </c>
       <c r="M65" s="166">
         <f>SUM(M51:M64)</f>
-        <v>1710373160.3997462</v>
+        <v>1295652343.537981</v>
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>855186580.19987309</v>
+        <v>1295652343.537981</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="D70" s="192">
         <f>IF(E24="",0,E24)</f>
-        <v>23604648.279991999</v>
+        <v>24325368.979991999</v>
       </c>
     </row>
     <row r="71" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="D71" s="193">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>80702340.960000008</v>
+        <v>81902340.960000008</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21195,7 +21195,7 @@
       </c>
       <c r="D73" s="192">
         <f>IF(E14="",0,E14)</f>
-        <v>61773566.889985003</v>
+        <v>66130323.599985003</v>
       </c>
     </row>
     <row r="74" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="D76" s="193">
         <f>IF(E19="",0,E19)</f>
-        <v>202463983.40000001</v>
+        <v>287203621.35000002</v>
       </c>
     </row>
     <row r="77" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="D77" s="192">
         <f>IF(E25="",0,E25)</f>
-        <v>23605098.779995002</v>
+        <v>26407801.439994998</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21254,7 +21254,7 @@
       </c>
       <c r="D78" s="193">
         <f>IF(E23="",0,E23)</f>
-        <v>17121621.32</v>
+        <v>17151621.32</v>
       </c>
     </row>
     <row r="79" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21278,7 +21278,7 @@
       </c>
       <c r="D80" s="192">
         <f>IF(E26="",0,E26)</f>
-        <v>90460363.869880006</v>
+        <v>112736039.39988001</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="D81" s="193">
         <f>IF(E10="",0,E10)</f>
-        <v>60112286.639980003</v>
+        <v>61031205.54998</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21324,7 +21324,7 @@
       <c r="C84" s="191"/>
       <c r="D84" s="194">
         <f>SUM(D70:D83)</f>
-        <v>609096364.01983202</v>
+        <v>726140776.47983217</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21376,19 +21376,19 @@
       </c>
       <c r="E89" s="177">
         <f>IFERROR(C32,0)</f>
-        <v>203076300.00860801</v>
+        <v>240237597.65824801</v>
       </c>
       <c r="F89" s="178">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
-        <v>0.7268510769736457</v>
+        <v>0.85985886378694742</v>
       </c>
       <c r="G89" s="171">
         <f>D89-E89</f>
-        <v>76315595.308032185</v>
+        <v>39154297.658392191</v>
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>38157797.654016092</v>
+        <v>39154297.658392191</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21405,19 +21405,19 @@
       </c>
       <c r="E90" s="177">
         <f>IFERROR(C33,0)</f>
-        <v>452153563.80664498</v>
+        <v>449933743.924721</v>
       </c>
       <c r="F90" s="178">
         <f t="shared" si="9"/>
-        <v>1.0775516615465974</v>
+        <v>1.0722614884868884</v>
       </c>
       <c r="G90" s="172">
         <f>D90-E90</f>
-        <v>-32541604.638326108</v>
+        <v>-30321784.756402135</v>
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-16270802.319163054</v>
+        <v>-30321784.756402135</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21434,19 +21434,19 @@
       </c>
       <c r="E91" s="177">
         <f>M21+M7</f>
-        <v>794555516.424474</v>
+        <v>897130483.57328391</v>
       </c>
       <c r="F91" s="178">
         <f t="shared" si="9"/>
-        <v>0.72729158526633764</v>
+        <v>0.82118296091496634</v>
       </c>
       <c r="G91" s="171">
         <f>D91-E91</f>
-        <v>297929990.79269528</v>
+        <v>195355023.64388537</v>
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>148964995.39634764</v>
+        <v>195355023.64388537</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21519,19 +21519,19 @@
       </c>
       <c r="E94" s="198">
         <f>SUM(E89:E93)</f>
-        <v>1449785380.239727</v>
+        <v>1587301825.1562529</v>
       </c>
       <c r="F94" s="175">
         <f t="shared" si="9"/>
-        <v>0.80926262317419406</v>
+        <v>0.88602358411334747</v>
       </c>
       <c r="G94" s="173">
         <f>SUM(G89:G93)</f>
-        <v>341703981.46240139</v>
+        <v>204187536.54587543</v>
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>170851990.7312007</v>
+        <v>204187536.54587543</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -23594,11 +23594,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23606,6 +23601,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -25651,11 +25651,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25663,6 +25658,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -27708,11 +27708,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27720,6 +27715,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7455" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -527,9 +526,6 @@
     <t>DATA PENCAPAIAN — MEI 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — MEI 2026</t>
-  </si>
-  <si>
     <t>DATA PENCAPAIAN — JUNI 2026</t>
   </si>
   <si>
@@ -603,6 +599,9 @@
   </si>
   <si>
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
+  </si>
+  <si>
+    <t>DATA PENCAPAIAN — GLOBAL — 02 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -927,7 +926,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1108,6 +1107,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFAFAFA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1224,7 +1229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1729,9 +1734,6 @@
     <xf numFmtId="41" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1803,6 +1805,30 @@
     </xf>
     <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="39" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="26" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1900,6 +1926,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1920,6 +1955,9 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2676,16 +2714,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="199" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="199"/>
+      <c r="B1" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="206"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="200"/>
+      <c r="C3" s="207"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2736,10 +2774,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="201" t="s">
+      <c r="B11" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="201"/>
+      <c r="C11" s="208"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -2833,7 +2871,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -2859,14 +2897,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),4))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -2931,7 +2969,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -3210,7 +3248,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -3222,7 +3260,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -3392,11 +3430,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>164</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3520,10 +3558,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3552,40 +3590,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3593,13 +3631,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3618,7 +3656,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3628,7 +3666,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -3736,10 +3774,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!R7</f>
@@ -4048,10 +4086,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!R13</f>
@@ -4415,16 +4453,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4432,10 +4470,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -4464,10 +4502,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -4536,10 +4574,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -4627,13 +4665,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4890,7 +4928,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -4916,14 +4954,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),5))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -4988,7 +5026,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -5267,7 +5305,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -5279,7 +5317,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -5449,11 +5487,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>166</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>165</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5577,10 +5615,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5609,40 +5647,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5650,13 +5688,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5675,7 +5713,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5685,7 +5723,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -5793,10 +5831,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!T7</f>
@@ -6105,10 +6143,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!T13</f>
@@ -6472,16 +6510,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6489,10 +6527,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -6521,10 +6559,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -6593,10 +6631,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -6684,13 +6722,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6947,7 +6985,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -6973,14 +7011,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),6))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -7045,7 +7083,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -7324,7 +7362,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -7336,7 +7374,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -7506,11 +7544,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>168</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7634,10 +7672,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7666,40 +7704,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7707,13 +7745,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7732,7 +7770,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7742,7 +7780,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -7850,10 +7888,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!V7</f>
@@ -8162,10 +8200,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!V13</f>
@@ -8529,16 +8567,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8546,10 +8584,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -8578,10 +8616,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -8650,10 +8688,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -8741,13 +8779,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -9004,7 +9042,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -9030,14 +9068,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),7))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -9102,7 +9140,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -9381,7 +9419,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -9393,7 +9431,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -9563,11 +9601,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>181</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9691,10 +9729,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9723,40 +9761,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9764,13 +9802,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9789,7 +9827,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9799,7 +9837,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -9907,10 +9945,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!X7</f>
@@ -10219,10 +10257,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!X13</f>
@@ -10586,16 +10624,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10603,10 +10641,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -10635,10 +10673,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -10707,10 +10745,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -10798,13 +10836,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11061,7 +11099,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -11087,7 +11125,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11159,7 +11197,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -11438,7 +11476,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -11450,7 +11488,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -11620,11 +11658,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>183</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>182</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11747,10 +11785,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11779,40 +11817,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11820,13 +11858,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11845,7 +11883,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11855,7 +11893,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -11961,10 +11999,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!Z7</f>
@@ -12267,10 +12305,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!Z13</f>
@@ -12628,16 +12666,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12645,10 +12683,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -12677,10 +12715,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -12749,10 +12787,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -12840,13 +12878,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13137,10 +13175,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="200"/>
+      <c r="C3" s="207"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -13302,10 +13340,10 @@
         <v>49588709</v>
       </c>
       <c r="L5" s="7">
-        <v>0</v>
+        <v>416683478</v>
       </c>
       <c r="M5" s="7">
-        <v>0</v>
+        <v>68270401.220654309</v>
       </c>
       <c r="N5" s="7">
         <v>0</v>
@@ -13382,10 +13420,10 @@
         <v>172865092</v>
       </c>
       <c r="L6" s="7">
-        <v>0</v>
+        <v>555182371</v>
       </c>
       <c r="M6" s="7">
-        <v>0</v>
+        <v>191546784</v>
       </c>
       <c r="N6" s="7">
         <v>0</v>
@@ -13432,10 +13470,10 @@
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="145" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="146" t="s">
         <v>177</v>
-      </c>
-      <c r="C7" s="146" t="s">
-        <v>178</v>
       </c>
       <c r="D7" s="147">
         <v>241473268</v>
@@ -13461,7 +13499,9 @@
       <c r="K7" s="147">
         <v>0</v>
       </c>
-      <c r="L7" s="138"/>
+      <c r="L7" s="138">
+        <v>241473268</v>
+      </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -13510,10 +13550,10 @@
         <v>28200135</v>
       </c>
       <c r="L8" s="7">
-        <v>0</v>
+        <v>610712472</v>
       </c>
       <c r="M8" s="7">
-        <v>0</v>
+        <v>46881826.81733489</v>
       </c>
       <c r="N8" s="7">
         <v>0</v>
@@ -13590,10 +13630,10 @@
         <v>73528469</v>
       </c>
       <c r="L9" s="7">
-        <v>0</v>
+        <v>405063284</v>
       </c>
       <c r="M9" s="7">
-        <v>0</v>
+        <v>82869315.191524148</v>
       </c>
       <c r="N9" s="7">
         <v>0</v>
@@ -13670,10 +13710,10 @@
         <v>71898548</v>
       </c>
       <c r="L10" s="7">
-        <v>0</v>
+        <v>473918832</v>
       </c>
       <c r="M10" s="7">
-        <v>0</v>
+        <v>81239394.122653604</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
@@ -13750,10 +13790,10 @@
         <v>73246884</v>
       </c>
       <c r="L11" s="7">
-        <v>0</v>
+        <v>961758345</v>
       </c>
       <c r="M11" s="7">
-        <v>0</v>
+        <v>91928576.339156389</v>
       </c>
       <c r="N11" s="7">
         <v>0</v>
@@ -13830,10 +13870,10 @@
         <v>45099712</v>
       </c>
       <c r="L12" s="7">
-        <v>0</v>
+        <v>505287059</v>
       </c>
       <c r="M12" s="7">
-        <v>0</v>
+        <v>63781404</v>
       </c>
       <c r="N12" s="7">
         <v>0</v>
@@ -13880,10 +13920,10 @@
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="145" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="146" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D13" s="147">
         <v>404133664</v>
@@ -13909,7 +13949,9 @@
       <c r="K13" s="147">
         <v>0</v>
       </c>
-      <c r="L13" s="138"/>
+      <c r="L13" s="138">
+        <v>404133664</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -13958,10 +14000,10 @@
         <v>119782698</v>
       </c>
       <c r="L14" s="7">
-        <v>0</v>
+        <v>404017309</v>
       </c>
       <c r="M14" s="7">
-        <v>0</v>
+        <v>138464390.21799541</v>
       </c>
       <c r="N14" s="7">
         <v>0</v>
@@ -14038,10 +14080,10 @@
         <v>40059909</v>
       </c>
       <c r="L15" s="7">
-        <v>0</v>
+        <v>631629596</v>
       </c>
       <c r="M15" s="7">
-        <v>0</v>
+        <v>58741600.610625267</v>
       </c>
       <c r="N15" s="7">
         <v>0</v>
@@ -14118,10 +14160,10 @@
         <v>45082463</v>
       </c>
       <c r="L16" s="7">
-        <v>0</v>
+        <v>386543023</v>
       </c>
       <c r="M16" s="7">
-        <v>0</v>
+        <v>63764154.799813807</v>
       </c>
       <c r="N16" s="7">
         <v>0</v>
@@ -14198,10 +14240,10 @@
         <v>311125253</v>
       </c>
       <c r="L17" s="7">
-        <v>0</v>
+        <v>583350942</v>
       </c>
       <c r="M17" s="7">
-        <v>0</v>
+        <v>329806944.99271739</v>
       </c>
       <c r="N17" s="7">
         <v>0</v>
@@ -14278,10 +14320,10 @@
         <v>239288340</v>
       </c>
       <c r="L18" s="7">
-        <v>0</v>
+        <v>259525689</v>
       </c>
       <c r="M18" s="7">
-        <v>0</v>
+        <v>257970031.90788639</v>
       </c>
       <c r="N18" s="7">
         <v>0</v>
@@ -14408,7 +14450,7 @@
         <v>279391895.3166402</v>
       </c>
       <c r="H22" s="7">
-        <v>0</v>
+        <v>278064617.90420955</v>
       </c>
       <c r="I22" s="7">
         <v>0</v>
@@ -14452,7 +14494,7 @@
         <v>419611959.16831887</v>
       </c>
       <c r="H23" s="7">
-        <v>0</v>
+        <v>417618553.18652159</v>
       </c>
       <c r="I23" s="7">
         <v>0</v>
@@ -14496,7 +14538,7 @@
         <v>1092485507.2171693</v>
       </c>
       <c r="H24" s="7">
-        <v>0</v>
+        <v>1087295552.3135247</v>
       </c>
       <c r="I24" s="7">
         <v>0</v>
@@ -14609,13 +14651,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="202" t="s">
+      <c r="B29" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="202"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="202"/>
-      <c r="F29" s="202"/>
+      <c r="C29" s="209"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="209"/>
+      <c r="F29" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14649,7 +14691,7 @@
   <sheetData>
     <row r="1" spans="2:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -15145,10 +15187,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="204" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="205"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15188,23 +15230,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="206" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="206" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="207" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="208"/>
-      <c r="F47" s="209"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="206" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15212,13 +15254,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="203" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="206"/>
-      <c r="C48" s="206"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15237,7 +15279,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="206"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15247,7 +15289,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="203"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16182,7 +16224,7 @@
   <sheetData>
     <row r="1" spans="2:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -16678,10 +16720,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="204" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="205"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16721,23 +16763,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="206" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="206" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="207" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="208"/>
-      <c r="F47" s="209"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="206" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16745,13 +16787,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="203" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="206"/>
-      <c r="C48" s="206"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16770,7 +16812,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="206"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16780,7 +16822,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="203"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -17801,7 +17843,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C9" s="15">
         <v>188107.92</v>
@@ -17939,7 +17981,7 @@
         <v>282161.88</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E15" s="15">
         <v>282161.88</v>
@@ -18155,7 +18197,7 @@
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C29" s="15">
         <v>3087270.2699850001</v>
@@ -18363,10 +18405,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="214" t="s">
+      <c r="B44" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="215"/>
+      <c r="C44" s="222"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18431,23 +18473,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="216" t="s">
+      <c r="B47" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="216" t="s">
+      <c r="C47" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="211" t="s">
+      <c r="D47" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="212"/>
-      <c r="F47" s="213"/>
+      <c r="E47" s="219"/>
+      <c r="F47" s="220"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="216" t="s">
+      <c r="J47" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18455,13 +18497,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="217" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="216"/>
-      <c r="C48" s="216"/>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18480,7 +18522,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="216"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18490,7 +18532,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="217"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -19515,7 +19557,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -19571,7 +19613,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -19614,16 +19656,16 @@
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="174">
+      <c r="C10" s="15">
         <v>303439555.68576801</v>
       </c>
-      <c r="D10" s="174">
+      <c r="D10" s="15">
         <v>28364314.698472001</v>
       </c>
-      <c r="E10" s="174">
+      <c r="E10" s="15">
         <v>61031205.54998</v>
       </c>
-      <c r="F10" s="174">
+      <c r="F10" s="15">
         <v>392835075.93422002</v>
       </c>
       <c r="G10"/>
@@ -19641,16 +19683,16 @@
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="174">
+      <c r="C11" s="15">
         <v>304137742.30899602</v>
       </c>
-      <c r="D11" s="174">
+      <c r="D11" s="15">
         <v>119707150.766315</v>
       </c>
-      <c r="E11" s="174">
+      <c r="E11" s="15">
         <v>34053355</v>
       </c>
-      <c r="F11" s="174">
+      <c r="F11" s="15">
         <v>457898248.07531101</v>
       </c>
       <c r="G11"/>
@@ -19668,16 +19710,16 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="174">
+      <c r="C12" s="15">
         <v>255272238.70392501</v>
       </c>
-      <c r="D12" s="174">
+      <c r="D12" s="15">
         <v>80101515.078845993</v>
       </c>
-      <c r="E12" s="174">
+      <c r="E12" s="15">
         <v>71143242</v>
       </c>
-      <c r="F12" s="174">
+      <c r="F12" s="15">
         <v>406516995.78277099</v>
       </c>
       <c r="G12"/>
@@ -19695,16 +19737,16 @@
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="174">
+      <c r="C13" s="15">
         <v>236397547.89756399</v>
       </c>
-      <c r="D13" s="174">
+      <c r="D13" s="15">
         <v>40146697.359765999</v>
       </c>
-      <c r="E13" s="174">
+      <c r="E13" s="15">
         <v>10759098.960000001</v>
       </c>
-      <c r="F13" s="174">
+      <c r="F13" s="15">
         <v>287303344.21732998</v>
       </c>
       <c r="G13"/>
@@ -19722,16 +19764,16 @@
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="174">
+      <c r="C14" s="15">
         <v>537997275.46389103</v>
       </c>
-      <c r="D14" s="174">
+      <c r="D14" s="15">
         <v>21205741.099730998</v>
       </c>
-      <c r="E14" s="174">
+      <c r="E14" s="15">
         <v>66130323.599985003</v>
       </c>
-      <c r="F14" s="174">
+      <c r="F14" s="15">
         <v>625333340.163607</v>
       </c>
       <c r="G14"/>
@@ -19751,7 +19793,7 @@
       </c>
       <c r="C15" s="150"/>
       <c r="D15" s="150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E15" s="150"/>
       <c r="F15" s="150"/>
@@ -19770,16 +19812,16 @@
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="174">
+      <c r="C16" s="15">
         <v>449682614.319305</v>
       </c>
-      <c r="D16" s="174">
+      <c r="D16" s="15">
         <v>60505589.095815003</v>
       </c>
-      <c r="E16" s="174">
+      <c r="E16" s="15">
         <v>2883783.76</v>
       </c>
-      <c r="F16" s="174">
+      <c r="F16" s="15">
         <v>513071987.17512</v>
       </c>
       <c r="G16"/>
@@ -19797,16 +19839,16 @@
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="174">
+      <c r="C17" s="15">
         <v>355626119.92999297</v>
       </c>
-      <c r="D17" s="174">
+      <c r="D17" s="15">
         <v>44657675.509999998</v>
       </c>
-      <c r="E17" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="F17" s="174">
+      <c r="E17" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" s="15">
         <v>400283795.43999302</v>
       </c>
       <c r="G17"/>
@@ -19824,16 +19866,16 @@
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="174">
+      <c r="C18" s="15">
         <v>1267577083.8097451</v>
       </c>
-      <c r="D18" s="174">
+      <c r="D18" s="15">
         <v>9652531.8548969999</v>
       </c>
-      <c r="E18" s="174">
+      <c r="E18" s="15">
         <v>3932432.4</v>
       </c>
-      <c r="F18" s="174">
+      <c r="F18" s="15">
         <v>1281162048.064642</v>
       </c>
       <c r="G18"/>
@@ -19851,16 +19893,16 @@
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="174">
+      <c r="C19" s="15">
         <v>1030915377.322188</v>
       </c>
-      <c r="D19" s="174">
+      <c r="D19" s="15">
         <v>59498535.799857996</v>
       </c>
-      <c r="E19" s="174">
+      <c r="E19" s="15">
         <v>287203621.35000002</v>
       </c>
-      <c r="F19" s="174">
+      <c r="F19" s="15">
         <v>1377617534.4720459</v>
       </c>
       <c r="G19"/>
@@ -19878,16 +19920,16 @@
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="174">
+      <c r="C20" s="15">
         <v>105315057.62759601</v>
       </c>
-      <c r="D20" s="174">
+      <c r="D20" s="15">
         <v>16467727.799813</v>
       </c>
-      <c r="E20" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="174">
+      <c r="E20" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="15">
         <v>121782785.42740899</v>
       </c>
       <c r="G20"/>
@@ -19904,16 +19946,16 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="174">
+      <c r="C21" s="15">
         <v>57359939.420000002</v>
       </c>
-      <c r="D21" s="174">
+      <c r="D21" s="15">
         <v>136240384.927111</v>
       </c>
-      <c r="E21" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="174">
+      <c r="E21" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="15">
         <v>193600324.34711099</v>
       </c>
       <c r="G21"/>
@@ -19928,18 +19970,18 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="174">
+        <v>173</v>
+      </c>
+      <c r="C22" s="15">
         <v>38884328.600000001</v>
       </c>
-      <c r="D22" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="E22" s="174">
+      <c r="D22" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="15">
         <v>12315315.119999999</v>
       </c>
-      <c r="F22" s="174">
+      <c r="F22" s="15">
         <v>51199643.719999999</v>
       </c>
       <c r="G22"/>
@@ -19949,18 +19991,18 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="174">
+        <v>174</v>
+      </c>
+      <c r="C23" s="15">
         <v>120550492.72</v>
       </c>
-      <c r="D23" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="174">
+      <c r="D23" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="15">
         <v>17151621.32</v>
       </c>
-      <c r="F23" s="174">
+      <c r="F23" s="15">
         <v>137702114.03999999</v>
       </c>
       <c r="G23"/>
@@ -19972,16 +20014,16 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="174">
+      <c r="C24" s="15">
         <v>299770568.60838997</v>
       </c>
-      <c r="D24" s="174">
+      <c r="D24" s="15">
         <v>45375105.343964003</v>
       </c>
-      <c r="E24" s="174">
+      <c r="E24" s="15">
         <v>24325368.979991999</v>
       </c>
-      <c r="F24" s="174">
+      <c r="F24" s="15">
         <v>369471042.93234599</v>
       </c>
       <c r="G24"/>
@@ -19991,16 +20033,16 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="174">
+      <c r="C25" s="15">
         <v>378754537.60554802</v>
       </c>
-      <c r="D25" s="174">
+      <c r="D25" s="15">
         <v>62284984.519973002</v>
       </c>
-      <c r="E25" s="174">
+      <c r="E25" s="15">
         <v>26407801.439994998</v>
       </c>
-      <c r="F25" s="174">
+      <c r="F25" s="15">
         <v>467447323.565516</v>
       </c>
       <c r="G25"/>
@@ -20010,16 +20052,16 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="174">
+      <c r="C26" s="15">
         <v>479291727.990435</v>
       </c>
-      <c r="D26" s="174">
+      <c r="D26" s="15">
         <v>61629599.543938003</v>
       </c>
-      <c r="E26" s="174">
+      <c r="E26" s="15">
         <v>112736039.39988001</v>
       </c>
-      <c r="F26" s="174">
+      <c r="F26" s="15">
         <v>653657366.93425298</v>
       </c>
       <c r="G26"/>
@@ -20029,16 +20071,16 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="174">
+      <c r="C27" s="15">
         <v>663559823.79009497</v>
       </c>
-      <c r="D27" s="174">
+      <c r="D27" s="15">
         <v>200253231.98958299</v>
       </c>
-      <c r="E27" s="174" t="s">
-        <v>170</v>
-      </c>
-      <c r="F27" s="174">
+      <c r="E27" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="15">
         <v>863813055.77967799</v>
       </c>
       <c r="G27"/>
@@ -20060,13 +20102,13 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="76"/>
-      <c r="C31" s="174"/>
+      <c r="C31" s="15"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="174">
+      <c r="C32" s="15">
         <v>240237597.65824801</v>
       </c>
     </row>
@@ -20074,7 +20116,7 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="174">
+      <c r="C33" s="15">
         <v>449933743.924721</v>
       </c>
     </row>
@@ -20082,7 +20124,7 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="174">
+      <c r="C34" s="15">
         <v>318278585.086043</v>
       </c>
     </row>
@@ -20090,7 +20132,7 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="174">
+      <c r="C35" s="15">
         <v>267561093.287265</v>
       </c>
     </row>
@@ -20098,7 +20140,7 @@
       <c r="B36" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="174">
+      <c r="C36" s="15">
         <v>311290805.19997603</v>
       </c>
     </row>
@@ -20111,17 +20153,17 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>184</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>183</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>1</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20174,7 +20216,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>1002324385.071167</v>
+        <v>40092975.402846679</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20202,7 +20244,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>293327958.46681499</v>
+        <v>11733118.338672601</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20230,14 +20272,14 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>204187536.54587555</v>
+        <v>8167501.4618350221</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20256,44 +20298,44 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>1499839880.0838575</v>
+        <v>59993595.203354299</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="228"/>
-      <c r="L48" s="229"/>
-      <c r="M48" s="229"/>
-      <c r="N48" s="230"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="236"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="237"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="227" t="s">
+      <c r="B49" s="234" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="227" t="s">
+      <c r="C49" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="224" t="s">
+      <c r="D49" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="225"/>
-      <c r="F49" s="226"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="233"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="227" t="s">
+      <c r="J49" s="234" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20301,13 +20343,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="220" t="s">
+      <c r="N49" s="227" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="234"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20326,7 +20368,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="227"/>
+      <c r="J50" s="234"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20336,40 +20378,40 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="220"/>
+      <c r="N50" s="227"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="184" t="s">
+      <c r="B51" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="185" t="s">
+      <c r="C51" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="176">
+      <c r="D51" s="175">
         <f>TARGETS!J5</f>
         <v>396683478.3262167</v>
       </c>
-      <c r="E51" s="176">
+      <c r="E51" s="175">
         <f>TARGETS!K5</f>
         <v>49588709</v>
       </c>
-      <c r="F51" s="176">
+      <c r="F51" s="175">
         <f t="shared" ref="F51:F64" si="0">D51+E51</f>
         <v>446272187.3262167</v>
       </c>
-      <c r="G51" s="177">
+      <c r="G51" s="176">
         <f>M8</f>
         <v>299770568.60838997</v>
       </c>
-      <c r="H51" s="177">
+      <c r="H51" s="176">
         <f>N8</f>
         <v>45375105.343964003</v>
       </c>
-      <c r="I51" s="177">
+      <c r="I51" s="176">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
         <v>345145673.95235395</v>
       </c>
-      <c r="J51" s="178">
+      <c r="J51" s="177">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
         <v>0.77339723100435753</v>
       </c>
@@ -20387,41 +20429,41 @@
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>101126513.37386274</v>
+        <v>4045060.5349545097</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="186" t="s">
+      <c r="B52" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="187" t="s">
+      <c r="C52" s="186" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="179">
+      <c r="D52" s="178">
         <f>TARGETS!J6</f>
         <v>535182371</v>
       </c>
-      <c r="E52" s="179">
+      <c r="E52" s="178">
         <f>TARGETS!K6</f>
         <v>172865092</v>
       </c>
-      <c r="F52" s="179">
+      <c r="F52" s="178">
         <f t="shared" si="0"/>
         <v>708047463</v>
       </c>
-      <c r="G52" s="177">
+      <c r="G52" s="176">
         <f>M9</f>
         <v>491669786.60148901</v>
       </c>
-      <c r="H52" s="177">
+      <c r="H52" s="176">
         <f>N9</f>
         <v>120248212.43861198</v>
       </c>
-      <c r="I52" s="177">
+      <c r="I52" s="176">
         <f t="shared" si="1"/>
         <v>611917999.04010105</v>
       </c>
-      <c r="J52" s="178">
+      <c r="J52" s="177">
         <f t="shared" si="2"/>
         <v>0.86423302252563972</v>
       </c>
@@ -20439,41 +20481,41 @@
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>96129463.959898949</v>
+        <v>3845178.558395958</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="188" t="s">
+      <c r="B53" s="187" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="C53" s="189" t="s">
-        <v>178</v>
-      </c>
-      <c r="D53" s="180">
+      <c r="D53" s="179">
         <f>TARGETS!J7</f>
         <v>241473268</v>
       </c>
-      <c r="E53" s="180">
+      <c r="E53" s="179">
         <f>TARGETS!K7</f>
         <v>0</v>
       </c>
-      <c r="F53" s="180">
+      <c r="F53" s="179">
         <f>D53+E53</f>
         <v>241473268</v>
       </c>
-      <c r="G53" s="177">
+      <c r="G53" s="176">
         <f>C22</f>
         <v>38884328.600000001</v>
       </c>
-      <c r="H53" s="177">
+      <c r="H53" s="176">
         <f>IF(D22="",0,D22)</f>
         <v>0</v>
       </c>
-      <c r="I53" s="177">
+      <c r="I53" s="176">
         <f>G53+H53</f>
         <v>38884328.600000001</v>
       </c>
-      <c r="J53" s="178">
+      <c r="J53" s="177">
         <f>IFERROR(I53/F53,0)</f>
         <v>0.1610295372322538</v>
       </c>
@@ -20491,41 +20533,41 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>202588939.40000001</v>
+        <v>8103557.5760000004</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="186" t="s">
+      <c r="B54" s="185" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="187" t="s">
+      <c r="C54" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="179">
+      <c r="D54" s="178">
         <f>TARGETS!J8</f>
         <v>590712471.92289722</v>
       </c>
-      <c r="E54" s="179">
+      <c r="E54" s="178">
         <f>TARGETS!K8</f>
         <v>28200135</v>
       </c>
-      <c r="F54" s="179">
+      <c r="F54" s="178">
         <f t="shared" si="0"/>
         <v>618912606.92289722</v>
       </c>
-      <c r="G54" s="177">
+      <c r="G54" s="176">
         <f>M10</f>
         <v>537997275.46389103</v>
       </c>
-      <c r="H54" s="177">
+      <c r="H54" s="176">
         <f t="shared" ref="H54:H58" si="6">N10</f>
         <v>21205741.099730998</v>
       </c>
-      <c r="I54" s="177">
+      <c r="I54" s="176">
         <f t="shared" si="1"/>
         <v>559203016.563622</v>
       </c>
-      <c r="J54" s="178">
+      <c r="J54" s="177">
         <f t="shared" si="2"/>
         <v>0.90352500548318337</v>
       </c>
@@ -20543,41 +20585,41 @@
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>59709590.359275222</v>
+        <v>2388383.6143710087</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="184" t="s">
+      <c r="B55" s="183" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="185" t="s">
+      <c r="C55" s="184" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="176">
+      <c r="D55" s="175">
         <f>TARGETS!J9</f>
         <v>395063284.19152415</v>
       </c>
-      <c r="E55" s="176">
+      <c r="E55" s="175">
         <f>TARGETS!K9</f>
         <v>73528469</v>
       </c>
-      <c r="F55" s="176">
+      <c r="F55" s="175">
         <f t="shared" si="0"/>
         <v>468591753.19152415</v>
       </c>
-      <c r="G55" s="177">
+      <c r="G55" s="176">
         <f>M11</f>
         <v>355626119.92999297</v>
       </c>
-      <c r="H55" s="177">
+      <c r="H55" s="176">
         <f t="shared" si="6"/>
         <v>44657675.509999998</v>
       </c>
-      <c r="I55" s="177">
+      <c r="I55" s="176">
         <f t="shared" si="1"/>
         <v>400283795.43999296</v>
       </c>
-      <c r="J55" s="178">
+      <c r="J55" s="177">
         <f t="shared" si="2"/>
         <v>0.85422714487334961</v>
       </c>
@@ -20595,41 +20637,41 @@
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>68307957.751531184</v>
+        <v>2732318.3100612476</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="186" t="s">
+      <c r="B56" s="185" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="187" t="s">
+      <c r="C56" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="179">
+      <c r="D56" s="178">
         <f>TARGETS!J10</f>
         <v>463918832.1226536</v>
       </c>
-      <c r="E56" s="179">
+      <c r="E56" s="178">
         <f>TARGETS!K10</f>
         <v>71898548</v>
       </c>
-      <c r="F56" s="179">
+      <c r="F56" s="178">
         <f t="shared" si="0"/>
         <v>535817380.1226536</v>
       </c>
-      <c r="G56" s="177">
+      <c r="G56" s="176">
         <f>M12</f>
         <v>449682614.319305</v>
       </c>
-      <c r="H56" s="177">
+      <c r="H56" s="176">
         <f t="shared" si="6"/>
         <v>60505589.095815003</v>
       </c>
-      <c r="I56" s="177">
+      <c r="I56" s="176">
         <f t="shared" si="1"/>
         <v>510188203.41512001</v>
       </c>
-      <c r="J56" s="178">
+      <c r="J56" s="177">
         <f t="shared" si="2"/>
         <v>0.95216807506007584</v>
       </c>
@@ -20647,41 +20689,41 @@
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>25629176.707533598</v>
+        <v>1025167.0683013439</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="184" t="s">
+      <c r="B57" s="183" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="185" t="s">
+      <c r="C57" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="176">
+      <c r="D57" s="175">
         <f>TARGETS!J11</f>
         <v>941758345.44471872</v>
       </c>
-      <c r="E57" s="176">
+      <c r="E57" s="175">
         <f>TARGETS!K11</f>
         <v>73246884</v>
       </c>
-      <c r="F57" s="176">
+      <c r="F57" s="175">
         <f t="shared" si="0"/>
         <v>1015005229.4447187</v>
       </c>
-      <c r="G57" s="177">
+      <c r="G57" s="176">
         <f>M13</f>
         <v>1030915377.322188</v>
       </c>
-      <c r="H57" s="177">
+      <c r="H57" s="176">
         <f t="shared" si="6"/>
         <v>59498535.799857996</v>
       </c>
-      <c r="I57" s="177">
+      <c r="I57" s="176">
         <f t="shared" si="1"/>
         <v>1090413913.122046</v>
       </c>
-      <c r="J57" s="178">
+      <c r="J57" s="177">
         <f t="shared" si="2"/>
         <v>1.0742938868586729</v>
       </c>
@@ -20699,41 +20741,41 @@
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-75408683.677327275</v>
+        <v>-3016347.3470930909</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="186" t="s">
+      <c r="B58" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="C58" s="187" t="s">
+      <c r="C58" s="186" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="179">
+      <c r="D58" s="178">
         <f>TARGETS!J12</f>
         <v>485287059</v>
       </c>
-      <c r="E58" s="179">
+      <c r="E58" s="178">
         <f>TARGETS!K12</f>
         <v>45099712</v>
       </c>
-      <c r="F58" s="179">
+      <c r="F58" s="178">
         <f t="shared" si="0"/>
         <v>530386771</v>
       </c>
-      <c r="G58" s="177">
+      <c r="G58" s="176">
         <f>M14</f>
         <v>378754537.60554802</v>
       </c>
-      <c r="H58" s="177">
+      <c r="H58" s="176">
         <f t="shared" si="6"/>
         <v>62284984.519973002</v>
       </c>
-      <c r="I58" s="177">
+      <c r="I58" s="176">
         <f>G58+H58</f>
         <v>441039522.125521</v>
       </c>
-      <c r="J58" s="178">
+      <c r="J58" s="177">
         <f>IFERROR(I58/F58,0)</f>
         <v>0.83154321759190519</v>
       </c>
@@ -20751,41 +20793,41 @@
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>89347248.874478996</v>
+        <v>3573889.9549791599</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="188" t="s">
-        <v>177</v>
-      </c>
-      <c r="C59" s="189" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" s="180">
+      <c r="B59" s="187" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="188" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" s="179">
         <f>TARGETS!J13</f>
         <v>404133664</v>
       </c>
-      <c r="E59" s="180">
+      <c r="E59" s="179">
         <f>TARGETS!K13</f>
         <v>0</v>
       </c>
-      <c r="F59" s="180">
+      <c r="F59" s="179">
         <f>D59+E59</f>
         <v>404133664</v>
       </c>
-      <c r="G59" s="177">
+      <c r="G59" s="176">
         <f>C23</f>
         <v>120550492.72</v>
       </c>
-      <c r="H59" s="177">
+      <c r="H59" s="176">
         <f>IF(D23="",0,D23)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="177">
+      <c r="I59" s="176">
         <f>G59+H59</f>
         <v>120550492.72</v>
       </c>
-      <c r="J59" s="178">
+      <c r="J59" s="177">
         <f>IFERROR(I59/F59,0)</f>
         <v>0.29829361782640307</v>
       </c>
@@ -20803,41 +20845,41 @@
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>283583171.27999997</v>
+        <v>11343326.851199999</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="186" t="s">
+      <c r="B60" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="187" t="s">
+      <c r="C60" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="179">
+      <c r="D60" s="178">
         <f>TARGETS!J14</f>
         <v>384017309.32355773</v>
       </c>
-      <c r="E60" s="179">
+      <c r="E60" s="178">
         <f>TARGETS!K14</f>
         <v>119782698</v>
       </c>
-      <c r="F60" s="179">
+      <c r="F60" s="178">
         <f t="shared" si="0"/>
         <v>503800007.32355773</v>
       </c>
-      <c r="G60" s="177">
+      <c r="G60" s="176">
         <f>M15</f>
         <v>304137742.30899602</v>
       </c>
-      <c r="H60" s="177">
+      <c r="H60" s="176">
         <f t="shared" ref="H60:H64" si="7">N15</f>
         <v>119707150.766315</v>
       </c>
-      <c r="I60" s="177">
+      <c r="I60" s="176">
         <f t="shared" si="1"/>
         <v>423844893.07531101</v>
       </c>
-      <c r="J60" s="178">
+      <c r="J60" s="177">
         <f t="shared" si="2"/>
         <v>0.84129592479958659</v>
       </c>
@@ -20855,41 +20897,41 @@
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>79955114.248246729</v>
+        <v>3198204.5699298694</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="184" t="s">
+      <c r="B61" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="185" t="s">
+      <c r="C61" s="184" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="176">
+      <c r="D61" s="175">
         <f>TARGETS!J15</f>
         <v>611629595.7161876</v>
       </c>
-      <c r="E61" s="176">
+      <c r="E61" s="175">
         <f>TARGETS!K15</f>
         <v>40059909</v>
       </c>
-      <c r="F61" s="176">
+      <c r="F61" s="175">
         <f t="shared" si="0"/>
         <v>651689504.7161876</v>
       </c>
-      <c r="G61" s="177">
+      <c r="G61" s="176">
         <f>M16</f>
         <v>479291727.990435</v>
       </c>
-      <c r="H61" s="177">
+      <c r="H61" s="176">
         <f t="shared" si="7"/>
         <v>61629599.543938003</v>
       </c>
-      <c r="I61" s="177">
+      <c r="I61" s="176">
         <f t="shared" si="1"/>
         <v>540921327.53437304</v>
       </c>
-      <c r="J61" s="178">
+      <c r="J61" s="177">
         <f t="shared" si="2"/>
         <v>0.8300292142497302</v>
       </c>
@@ -20907,41 +20949,41 @@
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>110768177.18181455</v>
+        <v>4430727.0872725816</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="186" t="s">
+      <c r="B62" s="185" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="187" t="s">
+      <c r="C62" s="186" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="179">
+      <c r="D62" s="178">
         <f>TARGETS!J16</f>
         <v>366543022.9053762</v>
       </c>
-      <c r="E62" s="179">
+      <c r="E62" s="178">
         <f>TARGETS!K16</f>
         <v>45082463</v>
       </c>
-      <c r="F62" s="179">
+      <c r="F62" s="178">
         <f t="shared" si="0"/>
         <v>411625485.9053762</v>
       </c>
-      <c r="G62" s="177">
+      <c r="G62" s="176">
         <f>M17</f>
         <v>303439555.68576801</v>
       </c>
-      <c r="H62" s="177">
+      <c r="H62" s="176">
         <f t="shared" si="7"/>
         <v>28364314.698472001</v>
       </c>
-      <c r="I62" s="177">
+      <c r="I62" s="176">
         <f t="shared" si="1"/>
         <v>331803870.38424003</v>
       </c>
-      <c r="J62" s="178">
+      <c r="J62" s="177">
         <f t="shared" si="2"/>
         <v>0.80608194036973346</v>
       </c>
@@ -20959,41 +21001,41 @@
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>79821615.521136165</v>
+        <v>3192864.6208454464</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="184" t="s">
+      <c r="B63" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="C63" s="185" t="s">
+      <c r="C63" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="176">
+      <c r="D63" s="175">
         <f>TARGETS!J17</f>
         <v>563350942.09827971</v>
       </c>
-      <c r="E63" s="176">
+      <c r="E63" s="175">
         <f>TARGETS!K17</f>
         <v>311125253</v>
       </c>
-      <c r="F63" s="176">
+      <c r="F63" s="175">
         <f t="shared" si="0"/>
         <v>874476195.09827971</v>
       </c>
-      <c r="G63" s="177">
+      <c r="G63" s="176">
         <f>M18</f>
         <v>663559823.79009497</v>
       </c>
-      <c r="H63" s="177">
+      <c r="H63" s="176">
         <f t="shared" si="7"/>
         <v>200253231.98958299</v>
       </c>
-      <c r="I63" s="177">
+      <c r="I63" s="176">
         <f t="shared" si="1"/>
         <v>863813055.77967799</v>
       </c>
-      <c r="J63" s="178">
+      <c r="J63" s="177">
         <f t="shared" si="2"/>
         <v>0.98780625547227918</v>
       </c>
@@ -21011,41 +21053,41 @@
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>10663139.318601727</v>
+        <v>426525.5727440691</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="186" t="s">
+      <c r="B64" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="187" t="s">
+      <c r="C64" s="186" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="179">
+      <c r="D64" s="178">
         <f>TARGETS!J18</f>
         <v>239525689.01344877</v>
       </c>
-      <c r="E64" s="179">
+      <c r="E64" s="178">
         <f>TARGETS!K18</f>
         <v>239288340</v>
       </c>
-      <c r="F64" s="179">
+      <c r="F64" s="178">
         <f t="shared" si="0"/>
         <v>478814029.01344877</v>
       </c>
-      <c r="G64" s="177">
+      <c r="G64" s="176">
         <f>M19</f>
         <v>162674997.04759601</v>
       </c>
-      <c r="H64" s="177">
+      <c r="H64" s="176">
         <f t="shared" si="7"/>
         <v>152708112.726924</v>
       </c>
-      <c r="I64" s="177">
+      <c r="I64" s="176">
         <f t="shared" si="1"/>
         <v>315383109.77452004</v>
       </c>
-      <c r="J64" s="178">
+      <c r="J64" s="177">
         <f t="shared" si="2"/>
         <v>0.65867558313681251</v>
       </c>
@@ -21063,39 +21105,39 @@
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>163430919.23892874</v>
+        <v>6537236.7695571491</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="190" t="s">
+      <c r="B65" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="191"/>
-      <c r="D65" s="181">
+      <c r="C65" s="190"/>
+      <c r="D65" s="180">
         <f>SUM(D51:D64)</f>
         <v>6619279333.0648613</v>
       </c>
-      <c r="E65" s="181">
+      <c r="E65" s="180">
         <f t="shared" ref="E65" si="8">SUM(E51:E52,E54:E58,E60:E64)</f>
         <v>1269766212</v>
       </c>
-      <c r="F65" s="181">
+      <c r="F65" s="180">
         <f>SUM(F51:F64)</f>
         <v>7889045545.0648613</v>
       </c>
-      <c r="G65" s="182">
+      <c r="G65" s="181">
         <f>SUM(G51:G64)</f>
         <v>5616954947.9936943</v>
       </c>
-      <c r="H65" s="182">
+      <c r="H65" s="181">
         <f>SUM(H51:H64)</f>
         <v>976438253.53318501</v>
       </c>
-      <c r="I65" s="182">
+      <c r="I65" s="181">
         <f>SUM(I51:I64)</f>
         <v>6593393201.5268793</v>
       </c>
-      <c r="J65" s="183">
+      <c r="J65" s="182">
         <f>IFERROR(I65/F65,0)</f>
         <v>0.83576564032533673</v>
       </c>
@@ -21113,12 +21155,12 @@
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>1295652343.537981</v>
+        <v>51826093.741519243</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
@@ -21127,10 +21169,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21141,200 +21183,200 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
       <c r="I69"/>
     </row>
     <row r="70" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="184" t="s">
+      <c r="B70" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="185" t="s">
+      <c r="C70" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="192">
+      <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
         <v>24325368.979991999</v>
       </c>
     </row>
     <row r="71" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="186" t="s">
+      <c r="B71" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="C71" s="187" t="s">
+      <c r="C71" s="186" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="193">
+      <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
         <v>81902340.960000008</v>
       </c>
     </row>
     <row r="72" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="186" t="s">
+      <c r="B72" s="185" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="186" t="s">
         <v>177</v>
       </c>
-      <c r="C72" s="187" t="s">
-        <v>178</v>
-      </c>
-      <c r="D72" s="193">
+      <c r="D72" s="192">
         <f>IF(E22="",0,E22)</f>
         <v>12315315.119999999</v>
       </c>
     </row>
     <row r="73" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="184" t="s">
+      <c r="B73" s="183" t="s">
         <v>71</v>
       </c>
-      <c r="C73" s="185" t="s">
+      <c r="C73" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="192">
+      <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
         <v>66130323.599985003</v>
       </c>
     </row>
     <row r="74" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="186" t="s">
+      <c r="B74" s="185" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="187" t="s">
+      <c r="C74" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="193">
+      <c r="D74" s="192">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="184" t="s">
+      <c r="B75" s="183" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="185" t="s">
+      <c r="C75" s="184" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="192">
+      <c r="D75" s="191">
         <v>2883783.76</v>
       </c>
     </row>
     <row r="76" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="186" t="s">
+      <c r="B76" s="185" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="187" t="s">
+      <c r="C76" s="186" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="193">
+      <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
         <v>287203621.35000002</v>
       </c>
     </row>
     <row r="77" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="184" t="s">
+      <c r="B77" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="C77" s="185" t="s">
+      <c r="C77" s="184" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="192">
+      <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
         <v>26407801.439994998</v>
       </c>
     </row>
     <row r="78" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="186" t="s">
-        <v>177</v>
-      </c>
-      <c r="C78" s="187" t="s">
-        <v>179</v>
-      </c>
-      <c r="D78" s="193">
+      <c r="B78" s="185" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="186" t="s">
+        <v>178</v>
+      </c>
+      <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
         <v>17151621.32</v>
       </c>
     </row>
     <row r="79" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="186" t="s">
+      <c r="B79" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="187" t="s">
+      <c r="C79" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="193">
+      <c r="D79" s="192">
         <f>IF(E11="",0,E11)</f>
         <v>34053355</v>
       </c>
     </row>
     <row r="80" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="184" t="s">
+      <c r="B80" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="185" t="s">
+      <c r="C80" s="184" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="192">
+      <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
         <v>112736039.39988001</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="186" t="s">
+      <c r="B81" s="185" t="s">
         <v>84</v>
       </c>
-      <c r="C81" s="187" t="s">
+      <c r="C81" s="186" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="193">
+      <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
         <v>61031205.54998</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="184" t="s">
+      <c r="B82" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="C82" s="185" t="s">
+      <c r="C82" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="192">
+      <c r="D82" s="191">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="186" t="s">
+      <c r="B83" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="187" t="s">
+      <c r="C83" s="186" t="s">
         <v>89</v>
       </c>
-      <c r="D83" s="193">
+      <c r="D83" s="192">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="190" t="s">
+      <c r="B84" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="C84" s="191"/>
-      <c r="D84" s="194">
+      <c r="C84" s="190"/>
+      <c r="D84" s="193">
         <f>SUM(D70:D83)</f>
         <v>726140776.47983217</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="221" t="s">
+      <c r="B87" s="228" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="222"/>
-      <c r="D87" s="222"/>
-      <c r="E87" s="222"/>
-      <c r="F87" s="223"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="230"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21364,21 +21406,21 @@
       <c r="I88" s="168"/>
     </row>
     <row r="89" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="184" t="s">
+      <c r="B89" s="183" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="185" t="s">
+      <c r="C89" s="184" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="195">
+      <c r="D89" s="194">
         <f>TARGETS!G22</f>
         <v>279391895.3166402</v>
       </c>
-      <c r="E89" s="177">
+      <c r="E89" s="176">
         <f>IFERROR(C32,0)</f>
         <v>240237597.65824801</v>
       </c>
-      <c r="F89" s="178">
+      <c r="F89" s="177">
         <f t="shared" ref="F89:F94" si="9">IFERROR(E89/D89,0)</f>
         <v>0.85985886378694742</v>
       </c>
@@ -21388,26 +21430,26 @@
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>39154297.658392191</v>
+        <v>1566171.9063356877</v>
       </c>
       <c r="I89" s="168"/>
     </row>
     <row r="90" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="186" t="s">
+      <c r="B90" s="198" t="s">
         <v>94</v>
       </c>
-      <c r="C90" s="187" t="s">
+      <c r="C90" s="199" t="s">
         <v>95</v>
       </c>
-      <c r="D90" s="196">
+      <c r="D90" s="200">
         <f>TARGETS!G23</f>
         <v>419611959.16831887</v>
       </c>
-      <c r="E90" s="177">
+      <c r="E90" s="176">
         <f>IFERROR(C33,0)</f>
         <v>449933743.924721</v>
       </c>
-      <c r="F90" s="178">
+      <c r="F90" s="177">
         <f t="shared" si="9"/>
         <v>1.0722614884868884</v>
       </c>
@@ -21417,26 +21459,26 @@
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-30321784.756402135</v>
+        <v>-1212871.3902560854</v>
       </c>
       <c r="I90" s="168"/>
     </row>
     <row r="91" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="184" t="s">
+      <c r="B91" s="183" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="185" t="s">
+      <c r="C91" s="184" t="s">
         <v>97</v>
       </c>
-      <c r="D91" s="195">
+      <c r="D91" s="194">
         <f>TARGETS!G24</f>
         <v>1092485507.2171693</v>
       </c>
-      <c r="E91" s="177">
+      <c r="E91" s="176">
         <f>M21+M7</f>
         <v>897130483.57328391</v>
       </c>
-      <c r="F91" s="178">
+      <c r="F91" s="177">
         <f t="shared" si="9"/>
         <v>0.82118296091496634</v>
       </c>
@@ -21446,26 +21488,26 @@
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>195355023.64388537</v>
+        <v>7814200.9457554147</v>
       </c>
       <c r="I91" s="168"/>
     </row>
     <row r="92" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="186" t="s">
+      <c r="B92" s="185" t="s">
         <v>98</v>
       </c>
-      <c r="C92" s="187" t="s">
+      <c r="C92" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="D92" s="196">
+      <c r="D92" s="195">
         <f>TARGETS!G25</f>
         <v>0</v>
       </c>
-      <c r="E92" s="177">
+      <c r="E92" s="176">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F92" s="178">
+      <c r="F92" s="177">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21480,21 +21522,21 @@
       <c r="I92" s="168"/>
     </row>
     <row r="93" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="184" t="s">
+      <c r="B93" s="183" t="s">
         <v>100</v>
       </c>
-      <c r="C93" s="197" t="s">
+      <c r="C93" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="D93" s="195">
+      <c r="D93" s="194">
         <f>TARGETS!G26</f>
         <v>0</v>
       </c>
-      <c r="E93" s="177">
+      <c r="E93" s="176">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="F93" s="178">
+      <c r="F93" s="177">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21509,19 +21551,19 @@
       <c r="I93" s="168"/>
     </row>
     <row r="94" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="190" t="s">
+      <c r="B94" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="C94" s="191"/>
-      <c r="D94" s="198">
+      <c r="C94" s="190"/>
+      <c r="D94" s="197">
         <f>SUM(D89:D93)</f>
         <v>1791489361.7021284</v>
       </c>
-      <c r="E94" s="198">
+      <c r="E94" s="197">
         <f>SUM(E89:E93)</f>
         <v>1587301825.1562529</v>
       </c>
-      <c r="F94" s="175">
+      <c r="F94" s="174">
         <f t="shared" si="9"/>
         <v>0.88602358411334747</v>
       </c>
@@ -21531,7 +21573,7 @@
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>204187536.54587543</v>
+        <v>8167501.4618350174</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21572,15 +21614,15 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -21617,14 +21659,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),1))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -21689,7 +21731,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -21699,11 +21741,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>0</v>
+        <v>9988474.3199879993</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>0</v>
+        <v>1081081.079988</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21721,47 +21763,63 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>0</v>
+        <v>12944544.679975001</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>0</v>
+        <v>1618261.26</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="C10" s="248">
+        <v>6943190.0841720002</v>
+      </c>
+      <c r="D10" s="248">
+        <v>0</v>
+      </c>
+      <c r="E10" s="248">
+        <v>5322522.1399999997</v>
+      </c>
+      <c r="F10" s="248">
+        <v>12265712.224172</v>
+      </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>0</v>
+        <v>24141948.2852</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>0</v>
+        <v>3542756.7799820001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="C11" s="248">
+        <v>43918836.375333004</v>
+      </c>
+      <c r="D11" s="248">
+        <v>2932657.6799639999</v>
+      </c>
+      <c r="E11" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="248">
+        <v>46851494.055297002</v>
+      </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>0</v>
+        <v>18738738.399999999</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -21772,60 +21830,84 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="C12" s="248">
+        <v>3396558.56</v>
+      </c>
+      <c r="D12" s="248">
+        <v>380261.26</v>
+      </c>
+      <c r="E12" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12" s="248">
+        <v>3776819.82</v>
+      </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>0</v>
+        <v>7485797.7924610004</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>0</v>
+        <v>3747243.2399639999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="C13" s="248">
+        <v>9547986.1199750006</v>
+      </c>
+      <c r="D13" s="248">
+        <v>1238000</v>
+      </c>
+      <c r="E13" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13" s="248">
+        <v>10785986.119975001</v>
+      </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>0</v>
+        <v>20101498.149969999</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>0</v>
+        <v>812196.4</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="C14" s="248">
+        <v>24141948.2852</v>
+      </c>
+      <c r="D14" s="248">
+        <v>3542756.7799820001</v>
+      </c>
+      <c r="E14" s="248">
+        <v>1531531.5</v>
+      </c>
+      <c r="F14" s="248">
+        <v>29216236.565182</v>
+      </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>0</v>
+        <v>8809071.3864999991</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>0</v>
+        <v>1512000</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21841,47 +21923,63 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>0</v>
+        <v>43918836.375333004</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>0</v>
+        <v>2932657.6799639999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="C16" s="248">
+        <v>7485797.7924610004</v>
+      </c>
+      <c r="D16" s="248">
+        <v>3747243.2399639999</v>
+      </c>
+      <c r="E16" s="248">
+        <v>3932432.4</v>
+      </c>
+      <c r="F16" s="248">
+        <v>15165473.432425</v>
+      </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>0</v>
+        <v>16085162.183885001</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>0</v>
+        <v>2520000</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="248">
+        <v>18738738.399999999</v>
+      </c>
+      <c r="D17" s="248">
+        <v>0</v>
+      </c>
+      <c r="E17" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" s="248">
+        <v>18738738.399999999</v>
+      </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>0</v>
+        <v>6943190.0841720002</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
@@ -21892,16 +21990,24 @@
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
+      <c r="C18" s="248">
+        <v>29666896.059999999</v>
+      </c>
+      <c r="D18" s="248">
+        <v>474000</v>
+      </c>
+      <c r="E18" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="248">
+        <v>30140896.059999999</v>
+      </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>0</v>
+        <v>3954954.9199979999</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -21912,30 +22018,46 @@
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
+      <c r="C19" s="248">
+        <v>20101498.149969999</v>
+      </c>
+      <c r="D19" s="248">
+        <v>812196.4</v>
+      </c>
+      <c r="E19" s="248">
+        <v>32291891</v>
+      </c>
+      <c r="F19" s="248">
+        <v>53205585.549970001</v>
+      </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>0</v>
+        <v>5099867.3999969997</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>0</v>
+        <v>1855936.93</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="C20" s="248">
+        <v>2782567.3999970001</v>
+      </c>
+      <c r="D20" s="248">
+        <v>1855936.93</v>
+      </c>
+      <c r="E20" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="248">
+        <v>4638504.3299970003</v>
+      </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
@@ -21951,16 +22073,24 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="C21" s="248">
+        <v>2317300</v>
+      </c>
+      <c r="D21" s="248">
+        <v>0</v>
+      </c>
+      <c r="E21" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="248">
+        <v>2317300</v>
+      </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>0</v>
+        <v>24129738.547830999</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -21968,24 +22098,32 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+        <v>173</v>
+      </c>
+      <c r="C22" s="248"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="248"/>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
       <c r="J22" s="116"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+        <v>174</v>
+      </c>
+      <c r="C23" s="248">
+        <v>10757199.1</v>
+      </c>
+      <c r="D23" s="248"/>
+      <c r="E23" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="248">
+        <v>10757199.1</v>
+      </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
       <c r="J23" s="116"/>
@@ -21994,10 +22132,18 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+      <c r="C24" s="248">
+        <v>9988474.3199879993</v>
+      </c>
+      <c r="D24" s="248">
+        <v>1081081.079988</v>
+      </c>
+      <c r="E24" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="248">
+        <v>11069555.399976</v>
+      </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
       <c r="J24" s="116"/>
@@ -22006,10 +22152,18 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
+      <c r="C25" s="248">
+        <v>8809071.3864999991</v>
+      </c>
+      <c r="D25" s="248">
+        <v>1512000</v>
+      </c>
+      <c r="E25" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="248">
+        <v>10321071.386499999</v>
+      </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
       <c r="J25" s="116"/>
@@ -22018,10 +22172,18 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="C26" s="248">
+        <v>16085162.183885001</v>
+      </c>
+      <c r="D26" s="248">
+        <v>2520000</v>
+      </c>
+      <c r="E26" s="248">
+        <v>4932432.4000000004</v>
+      </c>
+      <c r="F26" s="248">
+        <v>23537594.583884999</v>
+      </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
       <c r="J26" s="116"/>
@@ -22030,15 +22192,27 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+      <c r="C27" s="248">
+        <v>3954954.9199979999</v>
+      </c>
+      <c r="D27" s="248">
+        <v>0</v>
+      </c>
+      <c r="E27" s="248" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="248">
+        <v>3954954.9199979999</v>
+      </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
       <c r="J27" s="116"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="116"/>
       <c r="H28" s="116"/>
       <c r="I28" s="116"/>
@@ -22074,8 +22248,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="15">
-        <v>0</v>
+      <c r="C32" s="248">
+        <v>5093180.1099570002</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22085,8 +22259,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="15">
-        <v>0</v>
+      <c r="C33" s="248">
+        <v>5997054.3339799996</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22096,8 +22270,8 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="15">
-        <v>0</v>
+      <c r="C34" s="248">
+        <v>21275684.467831001</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22107,8 +22281,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="15">
-        <v>0</v>
+      <c r="C35" s="248">
+        <v>2854054.08</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22149,24 +22323,24 @@
       <c r="H40" s="116"/>
       <c r="I40" s="116"/>
     </row>
-    <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+    <row r="41" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="238" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
       <c r="I41" s="116"/>
     </row>
-    <row r="42" spans="2:14" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="69" t="s">
         <v>137</v>
       </c>
@@ -22190,7 +22364,7 @@
       </c>
       <c r="I42" s="116"/>
     </row>
-    <row r="43" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="114" t="s">
         <v>143</v>
       </c>
@@ -22199,27 +22373,27 @@
       </c>
       <c r="D43" s="45">
         <f>SUM(TARGETS!L5:L7,TARGETS!L8:L13,TARGETS!L14:L18)</f>
-        <v>0</v>
+        <v>6839279332</v>
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>0</v>
+        <v>188969283.077479</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0</v>
+        <v>2.7629999288568172E-2</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>0</v>
+        <v>6650310048.9225206</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>0</v>
+        <v>130398236.25338276</v>
       </c>
       <c r="I43" s="116"/>
     </row>
-    <row r="44" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="114" t="s">
         <v>111</v>
       </c>
@@ -22228,27 +22402,27 @@
       </c>
       <c r="D44" s="45">
         <f>SUM(TARGETS!M5:M6,TARGETS!M8:M12,TARGETS!M14:M18)</f>
-        <v>0</v>
+        <v>1475264824.2203617</v>
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>0</v>
+        <v>19622133.369897999</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0</v>
+        <v>1.3300753225962515E-2</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>0</v>
+        <v>1455642690.8504636</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>0</v>
+        <v>28542013.546087522</v>
       </c>
       <c r="I44" s="116"/>
     </row>
-    <row r="45" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="114" t="s">
         <v>145</v>
       </c>
@@ -22257,50 +22431,50 @@
       </c>
       <c r="D45" s="45">
         <f>SUM(TARGETS!H22:H26)</f>
-        <v>0</v>
+        <v>1782978723.4042559</v>
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>0</v>
+        <v>35219972.991768003</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0</v>
+        <v>1.975344547270997E-2</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>0</v>
+        <v>1747758750.412488</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>0</v>
+        <v>34269779.419852704</v>
       </c>
       <c r="I45" s="116"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+    <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
-        <v>0</v>
+        <v>10097522879.624619</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>0</v>
+        <v>243811389.439145</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0</v>
+        <v>2.4145663480606924E-2</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>0</v>
+        <v>9853711490.1854725</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>0</v>
+        <v>193210029.21932298</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22310,40 +22484,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
-    </row>
-    <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
+    </row>
+    <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22351,13 +22525,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+    <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22376,7 +22550,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22386,122 +22560,122 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B51" s="50" t="s">
+      <c r="N50" s="247"/>
+    </row>
+    <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="55" t="s">
+      <c r="C51" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="127">
+      <c r="D51" s="205">
         <f>TARGETS!L5</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="127">
+        <v>416683478</v>
+      </c>
+      <c r="E51" s="205">
         <f>TARGETS!M5</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="127">
+        <v>68270401.220654309</v>
+      </c>
+      <c r="F51" s="205">
         <f t="shared" ref="F51:F64" si="0">D51+E51</f>
-        <v>0</v>
+        <v>484953879.22065431</v>
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>0</v>
+        <v>9988474.3199879993</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>0</v>
+        <v>1081081.079988</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>0</v>
+        <v>11069555.399976</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0</v>
+        <v>2.2825996191153976E-2</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>0</v>
+        <v>406695003.68001199</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>67189320.140666306</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>473884323.82067829</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B52" s="53" t="s">
+        <v>9291849.4866799656</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="201" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="128">
+      <c r="D52" s="205">
         <f>TARGETS!L6</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="128">
+        <v>555182371</v>
+      </c>
+      <c r="E52" s="205">
         <f>TARGETS!M6</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="128">
+        <v>191546784</v>
+      </c>
+      <c r="F52" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>746729155</v>
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>0</v>
+        <v>12944544.679975001</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>0</v>
+        <v>1618261.26</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14562805.939975001</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.950212582763693E-2</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>542237826.32002497</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>189928522.74000001</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>732166349.06002498</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>14356202.922745587</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!L7</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="E53" s="157">
         <f>TARGETS!M7</f>
@@ -22509,7 +22683,7 @@
       </c>
       <c r="F53" s="157">
         <f>D53+E53</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="G53" s="122">
         <f>C22</f>
@@ -22529,7 +22703,7 @@
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22537,87 +22711,87 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>0</v>
+        <v>241473268</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B54" s="53" t="s">
+        <v>4734769.9607843133</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="201" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="56" t="s">
+      <c r="C54" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="128">
+      <c r="D54" s="205">
         <f>TARGETS!L8</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="128">
+        <v>610712472</v>
+      </c>
+      <c r="E54" s="205">
         <f>TARGETS!M8</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="128">
+        <v>46881826.81733489</v>
+      </c>
+      <c r="F54" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>657594298.81733489</v>
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>0</v>
+        <v>24141948.2852</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>0</v>
+        <v>3542756.7799820001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>27684705.065182</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.2099977318800018E-2</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>0</v>
+        <v>586570523.7148</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>43339070.03735289</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>629909593.75215292</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B55" s="50" t="s">
+        <v>12351168.504944175</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="201" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="55" t="s">
+      <c r="C55" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="127">
+      <c r="D55" s="205">
         <f>TARGETS!L9</f>
-        <v>0</v>
-      </c>
-      <c r="E55" s="127">
+        <v>405063284</v>
+      </c>
+      <c r="E55" s="205">
         <f>TARGETS!M9</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="127">
+        <v>82869315.191524148</v>
+      </c>
+      <c r="F55" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>487932599.19152415</v>
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>0</v>
+        <v>18738738.399999999</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -22625,195 +22799,195 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18738738.399999999</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.8404358370498291E-2</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>386324545.60000002</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>82869315.191524148</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>469193860.79152417</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B56" s="53" t="s">
+        <v>9199879.6233632192</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="56" t="s">
+      <c r="C56" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="128">
+      <c r="D56" s="205">
         <f>TARGETS!L10</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="128">
+        <v>473918832</v>
+      </c>
+      <c r="E56" s="205">
         <f>TARGETS!M10</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="128">
+        <v>81239394.122653604</v>
+      </c>
+      <c r="F56" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>555158226.1226536</v>
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>0</v>
+        <v>7485797.7924610004</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3747243.2399639999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11233041.032425001</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0233945033795168E-2</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>466433034.20753902</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>77492150.88268961</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>543925185.09022856</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B57" s="50" t="s">
+        <v>10665199.707651541</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="201" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="55" t="s">
+      <c r="C57" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="127">
+      <c r="D57" s="205">
         <f>TARGETS!L11</f>
-        <v>0</v>
-      </c>
-      <c r="E57" s="127">
+        <v>961758345</v>
+      </c>
+      <c r="E57" s="205">
         <f>TARGETS!M11</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="127">
+        <v>91928576.339156389</v>
+      </c>
+      <c r="F57" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1053686921.3391564</v>
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>0</v>
+        <v>20101498.149969999</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>812196.4</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20913694.549969997</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9848110597586496E-2</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>941656846.85002995</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>91116379.939156383</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1032773226.7891864</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B58" s="53" t="s">
+        <v>20250455.427238949</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="201" t="s">
         <v>78</v>
       </c>
-      <c r="C58" s="56" t="s">
+      <c r="C58" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="128">
+      <c r="D58" s="205">
         <f>TARGETS!L12</f>
-        <v>0</v>
-      </c>
-      <c r="E58" s="128">
+        <v>505287059</v>
+      </c>
+      <c r="E58" s="205">
         <f>TARGETS!M12</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="128">
+        <v>63781404</v>
+      </c>
+      <c r="F58" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>569068463</v>
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>0</v>
+        <v>8809071.3864999991</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1512000</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>0</v>
+        <v>10321071.386499999</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0</v>
+        <v>1.813678328278754E-2</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>496477987.6135</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>62269404</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>558747391.6135</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+        <v>10955831.208107844</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!L13</f>
-        <v>0</v>
+        <v>404133664</v>
       </c>
       <c r="E59" s="157">
         <f>TARGETS!M13</f>
@@ -22821,11 +22995,11 @@
       </c>
       <c r="F59" s="157">
         <f>D59+E59</f>
-        <v>0</v>
+        <v>404133664</v>
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>0</v>
+        <v>10757199.1</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -22833,15 +23007,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>0</v>
+        <v>10757199.1</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0</v>
+        <v>2.6617923865901949E-2</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>0</v>
+        <v>393376464.89999998</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -22849,139 +23023,139 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>0</v>
+        <v>393376464.89999998</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B60" s="53" t="s">
+        <v>7713264.0176470587</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="56" t="s">
+      <c r="C60" s="202" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="128">
+      <c r="D60" s="205">
         <f>TARGETS!L14</f>
-        <v>0</v>
-      </c>
-      <c r="E60" s="128">
+        <v>404017309</v>
+      </c>
+      <c r="E60" s="205">
         <f>TARGETS!M14</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="128">
+        <v>138464390.21799541</v>
+      </c>
+      <c r="F60" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>542481699.21799541</v>
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>0</v>
+        <v>43918836.375333004</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>0</v>
+        <v>2932657.6799639999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46851494.055297002</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.6365114478211741E-2</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>360098472.62466699</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>135531732.5380314</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>495630205.16269839</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B61" s="50" t="s">
+        <v>9718239.3169156555</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="201" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="55" t="s">
+      <c r="C61" s="202" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="127">
+      <c r="D61" s="205">
         <f>TARGETS!L15</f>
-        <v>0</v>
-      </c>
-      <c r="E61" s="127">
+        <v>631629596</v>
+      </c>
+      <c r="E61" s="205">
         <f>TARGETS!M15</f>
-        <v>0</v>
-      </c>
-      <c r="F61" s="127">
+        <v>58741600.610625267</v>
+      </c>
+      <c r="F61" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>690371196.61062527</v>
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>0</v>
+        <v>16085162.183885001</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2520000</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18605162.183885001</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.6949505244753796E-2</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>615544433.81611502</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>56221600.610625267</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>671766034.42674029</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B62" s="53" t="s">
+        <v>13171883.0279753</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="201" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="56" t="s">
+      <c r="C62" s="202" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="128">
+      <c r="D62" s="205">
         <f>TARGETS!L16</f>
-        <v>0</v>
-      </c>
-      <c r="E62" s="128">
+        <v>386543023</v>
+      </c>
+      <c r="E62" s="205">
         <f>TARGETS!M16</f>
-        <v>0</v>
-      </c>
-      <c r="F62" s="128">
+        <v>63764154.799813807</v>
+      </c>
+      <c r="F62" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>450307177.79981381</v>
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>0</v>
+        <v>6943190.0841720002</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
@@ -22989,51 +23163,51 @@
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6943190.0841720002</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5418786167469506E-2</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>379599832.91582799</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>63764154.799813807</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>443363987.7156418</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B63" s="50" t="s">
+        <v>8693411.5238361135</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="201" t="s">
         <v>86</v>
       </c>
-      <c r="C63" s="55" t="s">
+      <c r="C63" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="127">
+      <c r="D63" s="205">
         <f>TARGETS!L17</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="127">
+        <v>583350942</v>
+      </c>
+      <c r="E63" s="205">
         <f>TARGETS!M17</f>
-        <v>0</v>
-      </c>
-      <c r="F63" s="127">
+        <v>329806944.99271739</v>
+      </c>
+      <c r="F63" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>913157886.99271739</v>
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>0</v>
+        <v>3954954.9199979999</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
@@ -23041,129 +23215,129 @@
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3954954.9199979999</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.331074588889294E-3</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>579395987.08000195</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>329806944.99271739</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>909202932.07271934</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B64" s="53" t="s">
+        <v>17827508.472014103</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="201" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="56" t="s">
+      <c r="C64" s="202" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="128">
+      <c r="D64" s="205">
         <f>TARGETS!L18</f>
-        <v>0</v>
-      </c>
-      <c r="E64" s="128">
+        <v>259525689</v>
+      </c>
+      <c r="E64" s="205">
         <f>TARGETS!M18</f>
-        <v>0</v>
-      </c>
-      <c r="F64" s="128">
+        <v>257970031.90788639</v>
+      </c>
+      <c r="F64" s="205">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>517495720.90788639</v>
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>0</v>
+        <v>5099867.3999969997</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1855936.93</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6955804.3299969994</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.3441278930372304E-2</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>254425821.600003</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>256114094.97788638</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>510539916.57788938</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+        <v>10010586.599566458</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="57" t="s">
         <v>152</v>
       </c>
       <c r="C65" s="58"/>
       <c r="D65" s="151">
         <f>SUM(D51:D64)</f>
-        <v>0</v>
+        <v>6839279332</v>
       </c>
       <c r="E65" s="151">
         <f t="shared" ref="E65" si="6">SUM(E51:E52,E54:E58,E60:E64)</f>
-        <v>0</v>
+        <v>1475264824.2203617</v>
       </c>
       <c r="F65" s="151">
         <f>SUM(F51:F64)</f>
-        <v>0</v>
+        <v>8314544156.2203627</v>
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>0</v>
+        <v>188969283.077479</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>0</v>
+        <v>19622133.369897999</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>0</v>
+        <v>208591416.447377</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0</v>
+        <v>2.5087534870005281E-2</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>0</v>
+        <v>6650310048.9225216</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>0</v>
+        <v>1455642690.8504636</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>0</v>
+        <v>8105952739.7729855</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>0</v>
+        <v>158940249.79947031</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23173,205 +23347,204 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
-    <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+    <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+    <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B70" s="50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="55" t="s">
+      <c r="C70" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="148">
+      <c r="D70" s="204">
         <f>IF(E24="",0,E24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B71" s="53" t="s">
+    <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="201" t="s">
         <v>69</v>
       </c>
-      <c r="C71" s="56" t="s">
+      <c r="C71" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="149">
+      <c r="D71" s="204">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B72" s="53" t="s">
+    <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="202" t="s">
         <v>177</v>
       </c>
-      <c r="C72" s="56" t="s">
+      <c r="D72" s="204">
+        <f>IF(E22="",0,E22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="201" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" s="202" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73" s="204">
+        <f>IF(E14="",0,E14)</f>
+        <v>1531531.5</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="201" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="202" t="s">
+        <v>74</v>
+      </c>
+      <c r="D74" s="204">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="201" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="202" t="s">
+        <v>74</v>
+      </c>
+      <c r="D75" s="204">
+        <v>3932432.4</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="201" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" s="202" t="s">
+        <v>77</v>
+      </c>
+      <c r="D76" s="204">
+        <f>IF(E19="",0,E19)</f>
+        <v>32291891</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="201" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="202" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="204">
+        <f>IF(E25="",0,E25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="201" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="202" t="s">
         <v>178</v>
       </c>
-      <c r="D72" s="149">
-        <f>IF(E22="",0,E22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B73" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="D73" s="148">
-        <f>IF(E14="",0,E14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B74" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="C74" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="D74" s="149">
+      <c r="D78" s="204">
+        <f>IF(E23="",0,E23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="201" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="202" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="204">
+        <f>IF(E11="",0,E11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="201" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="202" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80" s="204">
+        <f>IF(E26="",0,E26)</f>
+        <v>4932432.4000000004</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="201" t="s">
+        <v>84</v>
+      </c>
+      <c r="C81" s="202" t="s">
+        <v>85</v>
+      </c>
+      <c r="D81" s="204">
+        <f>IF(E10="",0,E10)</f>
+        <v>5322522.1399999997</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="201" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" s="202" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="204">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B75" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C75" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D75" s="148">
+    <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="202" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83" s="204">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B76" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C76" s="56" t="s">
-        <v>77</v>
-      </c>
-      <c r="D76" s="149">
-        <f>IF(E19="",0,E19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B77" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="D77" s="148">
-        <f>IF(E25="",0,E25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B78" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="C78" s="56" t="s">
-        <v>179</v>
-      </c>
-      <c r="D78" s="149">
-        <f>IF(E23="",0,E23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B79" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D79" s="149">
-        <f>IF(E11="",0,E11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B80" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="D80" s="148">
-        <f>IF(E26="",0,E26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B81" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="D81" s="149">
-        <f>IF(E10="",0,E10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B82" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="D82" s="148">
-        <f>0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B83" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="149">
-        <f>0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="57" t="s">
         <v>152</v>
       </c>
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>0</v>
+        <v>48010809.439999998</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23385,18 +23558,18 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
     </row>
-    <row r="88" spans="2:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="75" t="s">
         <v>153</v>
       </c>
@@ -23420,94 +23593,94 @@
       </c>
       <c r="I88" s="116"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B89" s="50" t="s">
+    <row r="89" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="201" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="55" t="s">
+      <c r="C89" s="202" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="125">
+      <c r="D89" s="203">
         <f>TARGETS!H22</f>
-        <v>0</v>
+        <v>278064617.90420955</v>
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>0</v>
+        <v>5093180.1099570002</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0</v>
+        <v>1.8316534294598924E-2</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>0</v>
+        <v>272971437.79425257</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>0</v>
+        <v>5352381.1332206391</v>
       </c>
       <c r="I89" s="116"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" s="53" t="s">
+    <row r="90" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="201" t="s">
         <v>94</v>
       </c>
-      <c r="C90" s="56" t="s">
+      <c r="C90" s="202" t="s">
         <v>95</v>
       </c>
-      <c r="D90" s="126">
+      <c r="D90" s="203">
         <f>TARGETS!H23</f>
-        <v>0</v>
+        <v>417618553.18652159</v>
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>0</v>
+        <v>5997054.3339799996</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.4360124300563645E-2</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>0</v>
+        <v>411621498.85254157</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>0</v>
+        <v>8071009.7814223841</v>
       </c>
       <c r="I90" s="116"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B91" s="50" t="s">
+    <row r="91" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="201" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="55" t="s">
+      <c r="C91" s="202" t="s">
         <v>97</v>
       </c>
-      <c r="D91" s="125">
+      <c r="D91" s="203">
         <f>TARGETS!H24</f>
-        <v>0</v>
+        <v>1087295552.3135247</v>
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>0</v>
+        <v>24129738.547830999</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.2192437462370047E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>0</v>
+        <v>1063165813.7656937</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>0</v>
+        <v>20846388.505209681</v>
       </c>
       <c r="I91" s="116"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="53" t="s">
         <v>98</v>
       </c>
@@ -23536,7 +23709,7 @@
       </c>
       <c r="I92" s="116"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="50" t="s">
         <v>100</v>
       </c>
@@ -23565,30 +23738,30 @@
       </c>
       <c r="I93" s="116"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="57" t="s">
         <v>152</v>
       </c>
       <c r="C94" s="58"/>
       <c r="D94" s="123">
         <f>SUM(D89:D93)</f>
-        <v>0</v>
+        <v>1782978723.4042559</v>
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>0</v>
+        <v>35219972.991768003</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.975344547270997E-2</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>0</v>
+        <v>1747758750.4124877</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>0</v>
+        <v>34269779.419852704</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -23648,7 +23821,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -23674,14 +23847,14 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
         <f ca="1">DAY(EOMONTH(TODAY(),2))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -23746,7 +23919,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -24025,7 +24198,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -24037,7 +24210,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -24207,11 +24380,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>161</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24335,10 +24508,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24367,40 +24540,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24408,13 +24581,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24433,7 +24606,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24443,7 +24616,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -24551,10 +24724,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!N7</f>
@@ -24863,10 +25036,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!N13</f>
@@ -25230,16 +25403,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25247,10 +25420,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -25279,10 +25452,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -25351,10 +25524,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -25442,13 +25615,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25705,7 +25878,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -25731,7 +25904,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -25803,7 +25976,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="83" t="s">
         <v>112</v>
@@ -26082,7 +26255,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -26094,7 +26267,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -26264,11 +26437,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="217" t="s">
-        <v>180</v>
-      </c>
-      <c r="C41" s="218"/>
-      <c r="D41" s="219"/>
+      <c r="B41" s="224" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26392,10 +26565,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="214" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26424,40 +26597,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="221" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="222"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="222"/>
-      <c r="F48" s="222"/>
-      <c r="G48" s="222"/>
-      <c r="H48" s="222"/>
-      <c r="I48" s="222"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="211" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="212"/>
-      <c r="F49" s="213"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="216" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26465,13 +26638,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="237" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="216"/>
-      <c r="C50" s="216"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26490,7 +26663,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="216"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26500,7 +26673,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="237"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -26608,10 +26781,10 @@
     </row>
     <row r="53" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" s="156" t="s">
-        <v>178</v>
       </c>
       <c r="D53" s="157">
         <f>TARGETS!P7</f>
@@ -26920,10 +27093,10 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="155" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="157">
         <f>TARGETS!P13</f>
@@ -27287,16 +27460,16 @@
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" s="136"/>
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="216" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="216" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27304,10 +27477,10 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="216"/>
-      <c r="C69" s="216"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
@@ -27336,10 +27509,10 @@
     </row>
     <row r="72" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="56" t="s">
         <v>177</v>
-      </c>
-      <c r="C72" s="56" t="s">
-        <v>178</v>
       </c>
       <c r="D72" s="149">
         <f>IF(E22="",0,E22)</f>
@@ -27408,10 +27581,10 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="149">
         <f>IF(E23="",0,E23)</f>
@@ -27499,13 +27672,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="231" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="232"/>
-      <c r="D87" s="232"/>
-      <c r="E87" s="232"/>
-      <c r="F87" s="233"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -601,7 +601,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 02 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 04 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1830,6 +1830,9 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1926,15 +1929,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1956,8 +1950,14 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2714,16 +2714,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="206" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="206"/>
+      <c r="B1" s="207" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="207"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="208"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2774,10 +2774,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="208"/>
+      <c r="C11" s="209"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -3430,11 +3430,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3558,10 +3558,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3590,40 +3590,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3631,13 +3631,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3656,7 +3656,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3666,7 +3666,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4459,10 +4459,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4470,8 +4470,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -4665,13 +4665,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4874,6 +4874,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4881,11 +4886,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -5487,11 +5487,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5615,10 +5615,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5647,40 +5647,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5688,13 +5688,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5713,7 +5713,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5723,7 +5723,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6516,10 +6516,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6527,8 +6527,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -6722,13 +6722,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6931,6 +6931,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6938,11 +6943,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -7544,11 +7544,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>167</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7672,10 +7672,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7704,40 +7704,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7745,13 +7745,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7770,7 +7770,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7780,7 +7780,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8573,10 +8573,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8584,8 +8584,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -8779,13 +8779,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8988,6 +8988,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8995,11 +9000,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9601,11 +9601,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9729,10 +9729,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9761,40 +9761,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9802,13 +9802,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9827,7 +9827,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9837,7 +9837,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10630,10 +10630,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10641,8 +10641,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -10836,13 +10836,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11045,6 +11045,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11052,11 +11057,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11658,11 +11658,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11785,10 +11785,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11817,40 +11817,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11858,13 +11858,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11883,7 +11883,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11893,7 +11893,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12672,10 +12672,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12683,8 +12683,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -12878,13 +12878,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13087,6 +13087,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13094,11 +13099,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13175,10 +13175,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="208" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="208"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14651,13 +14651,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="209" t="s">
+      <c r="B29" s="210" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="209"/>
-      <c r="F29" s="209"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
+      <c r="E29" s="210"/>
+      <c r="F29" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15187,10 +15187,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="212" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="213"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15230,23 +15230,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="215" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="217"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="214" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15254,13 +15254,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="211" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="214"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15279,7 +15279,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="214"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15289,7 +15289,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16720,10 +16720,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="212" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="213"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16763,23 +16763,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="215" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="217"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="214" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16787,13 +16787,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="211" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="214"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16812,7 +16812,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="214"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16822,7 +16822,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="211"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18405,10 +18405,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="221" t="s">
+      <c r="B44" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="222"/>
+      <c r="C44" s="223"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18473,23 +18473,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="223" t="s">
+      <c r="B47" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="223" t="s">
+      <c r="C47" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="218" t="s">
+      <c r="D47" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="219"/>
-      <c r="F47" s="220"/>
+      <c r="E47" s="220"/>
+      <c r="F47" s="221"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="223" t="s">
+      <c r="J47" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18497,13 +18497,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="217" t="s">
+      <c r="N47" s="218" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="223"/>
-      <c r="C48" s="223"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18522,7 +18522,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="223"/>
+      <c r="J48" s="224"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18532,7 +18532,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="217"/>
+      <c r="N48" s="218"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -20153,17 +20153,17 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>6.4516129032258063E-2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>40092975.402846679</v>
+        <v>41763516.044631958</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>11733118.338672601</v>
+        <v>12221998.269450625</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>8167501.4618350221</v>
+        <v>8507814.0227448139</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20298,44 +20298,44 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>59993595.203354299</v>
+        <v>62493328.336827397</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="235"/>
-      <c r="L48" s="236"/>
-      <c r="M48" s="236"/>
-      <c r="N48" s="237"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="236"/>
+      <c r="L48" s="237"/>
+      <c r="M48" s="237"/>
+      <c r="N48" s="238"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="234" t="s">
+      <c r="B49" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="234" t="s">
+      <c r="C49" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="231" t="s">
+      <c r="D49" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="232"/>
-      <c r="F49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="234"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="234" t="s">
+      <c r="J49" s="235" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20343,13 +20343,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="227" t="s">
+      <c r="N49" s="228" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="234"/>
-      <c r="C50" s="234"/>
+      <c r="B50" s="235"/>
+      <c r="C50" s="235"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20368,7 +20368,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="234"/>
+      <c r="J50" s="235"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20378,7 +20378,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="227"/>
+      <c r="N50" s="228"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>4045060.5349545097</v>
+        <v>4213604.7239109473</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>3845178.558395958</v>
+        <v>4005394.331662456</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>8103557.5760000004</v>
+        <v>8441205.8083333336</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20585,7 +20585,7 @@
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>2388383.6143710087</v>
+        <v>2487899.5983031341</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>2732318.3100612476</v>
+        <v>2846164.9063137993</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>1025167.0683013439</v>
+        <v>1067882.3628139</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-3016347.3470930909</v>
+        <v>-3142028.486555303</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>3573889.9549791599</v>
+        <v>3722802.0364366248</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>11343326.851199999</v>
+        <v>11815965.469999999</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3198204.5699298694</v>
+        <v>3331463.0936769471</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>4430727.0872725816</v>
+        <v>4615340.71590894</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>3192864.6208454464</v>
+        <v>3325900.646714007</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>426525.5727440691</v>
+        <v>444297.47160840529</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>6537236.7695571491</v>
+        <v>6809621.6349553643</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21155,7 +21155,7 @@
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>51826093.741519243</v>
+        <v>53985514.314082541</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21169,10 +21169,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21183,8 +21183,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -21370,13 +21370,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="228" t="s">
+      <c r="B87" s="229" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="229"/>
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="230"/>
+      <c r="C87" s="230"/>
+      <c r="D87" s="230"/>
+      <c r="E87" s="230"/>
+      <c r="F87" s="231"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>1566171.9063356877</v>
+        <v>1631429.0690996747</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1212871.3902560854</v>
+        <v>-1263407.6981834222</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>7814200.9457554147</v>
+        <v>8139792.6518285573</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>8167501.4618350174</v>
+        <v>8507814.0227448102</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21741,11 +21741,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>9988474.3199879993</v>
+        <v>17591498.039963</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>1081081.079988</v>
+        <v>2234414.409986</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21763,56 +21763,56 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>12944544.679975001</v>
+        <v>36531306.759904005</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>1618261.26</v>
+        <v>4824309.4452999998</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="248">
-        <v>6943190.0841720002</v>
-      </c>
-      <c r="D10" s="248">
-        <v>0</v>
-      </c>
-      <c r="E10" s="248">
-        <v>5322522.1399999997</v>
-      </c>
-      <c r="F10" s="248">
-        <v>12265712.224172</v>
+      <c r="C10" s="206">
+        <v>11647973.840856001</v>
+      </c>
+      <c r="D10" s="206">
+        <v>1694257.366497</v>
+      </c>
+      <c r="E10" s="206">
+        <v>13660359.880000001</v>
+      </c>
+      <c r="F10" s="206">
+        <v>27002591.087352999</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>24141948.2852</v>
+        <v>42927190.625198998</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>3542756.7799820001</v>
+        <v>6103601.8199669998</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="248">
-        <v>43918836.375333004</v>
-      </c>
-      <c r="D11" s="248">
-        <v>2932657.6799639999</v>
-      </c>
-      <c r="E11" s="248" t="s">
+      <c r="C11" s="206">
+        <v>59343656.966316</v>
+      </c>
+      <c r="D11" s="206">
+        <v>4597378.3994570002</v>
+      </c>
+      <c r="E11" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="248">
-        <v>46851494.055297002</v>
+      <c r="F11" s="206">
+        <v>63941035.365773</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21830,84 +21830,84 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="248">
-        <v>3396558.56</v>
-      </c>
-      <c r="D12" s="248">
-        <v>380261.26</v>
-      </c>
-      <c r="E12" s="248" t="s">
+      <c r="C12" s="206">
+        <v>14869279.899979001</v>
+      </c>
+      <c r="D12" s="206">
+        <v>1783917.5453000001</v>
+      </c>
+      <c r="E12" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="248">
-        <v>3776819.82</v>
+      <c r="F12" s="206">
+        <v>16653197.445279</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>7485797.7924610004</v>
+        <v>22279494.140058</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>3747243.2399639999</v>
+        <v>13462378.069882</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="248">
-        <v>9547986.1199750006</v>
-      </c>
-      <c r="D13" s="248">
-        <v>1238000</v>
-      </c>
-      <c r="E13" s="248" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" s="248">
-        <v>10785986.119975001</v>
+      <c r="C13" s="206">
+        <v>21662026.859925002</v>
+      </c>
+      <c r="D13" s="206">
+        <v>3040391.9</v>
+      </c>
+      <c r="E13" s="206">
+        <v>2252252.2000000002</v>
+      </c>
+      <c r="F13" s="206">
+        <v>26954670.959925</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>20101498.149969999</v>
+        <v>58541628.168898001</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>812196.4</v>
+        <v>11919388.989965999</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="248">
-        <v>24141948.2852</v>
-      </c>
-      <c r="D14" s="248">
-        <v>3542756.7799820001</v>
-      </c>
-      <c r="E14" s="248">
-        <v>1531531.5</v>
-      </c>
-      <c r="F14" s="248">
-        <v>29216236.565182</v>
+      <c r="C14" s="206">
+        <v>42927190.625198998</v>
+      </c>
+      <c r="D14" s="206">
+        <v>6103601.8199669998</v>
+      </c>
+      <c r="E14" s="206">
+        <v>3936936.9</v>
+      </c>
+      <c r="F14" s="206">
+        <v>52967729.345165998</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>8809071.3864999991</v>
+        <v>35047789.896495</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>1512000</v>
+        <v>8846417.9699939992</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21923,55 +21923,55 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>43918836.375333004</v>
+        <v>59343656.966316</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>2932657.6799639999</v>
+        <v>4597378.3994570002</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="248">
-        <v>7485797.7924610004</v>
-      </c>
-      <c r="D16" s="248">
-        <v>3747243.2399639999</v>
-      </c>
-      <c r="E16" s="248">
+      <c r="C16" s="206">
+        <v>22279494.140058</v>
+      </c>
+      <c r="D16" s="206">
+        <v>13462378.069882</v>
+      </c>
+      <c r="E16" s="206">
         <v>3932432.4</v>
       </c>
-      <c r="F16" s="248">
-        <v>15165473.432425</v>
+      <c r="F16" s="206">
+        <v>39674304.60994</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>16085162.183885001</v>
+        <v>29309860.628509</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>2520000</v>
+        <v>4394439.6500000004</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="248">
+      <c r="C17" s="206">
         <v>18738738.399999999</v>
       </c>
-      <c r="D17" s="248">
-        <v>0</v>
-      </c>
-      <c r="E17" s="248" t="s">
+      <c r="D17" s="206">
+        <v>0</v>
+      </c>
+      <c r="E17" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="248">
+      <c r="F17" s="206">
         <v>18738738.399999999</v>
       </c>
       <c r="H17" s="116"/>
@@ -21979,35 +21979,35 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>6943190.0841720002</v>
+        <v>11647973.840856001</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>0</v>
+        <v>1694257.366497</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="248">
-        <v>29666896.059999999</v>
-      </c>
-      <c r="D18" s="248">
+      <c r="C18" s="206">
+        <v>33045812.219997998</v>
+      </c>
+      <c r="D18" s="206">
         <v>474000</v>
       </c>
-      <c r="E18" s="248" t="s">
+      <c r="E18" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F18" s="248">
-        <v>30140896.059999999</v>
+      <c r="F18" s="206">
+        <v>33519812.219997998</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>3954954.9199979999</v>
+        <v>28789378.789965</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
@@ -22018,45 +22018,45 @@
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="248">
-        <v>20101498.149969999</v>
-      </c>
-      <c r="D19" s="248">
-        <v>812196.4</v>
-      </c>
-      <c r="E19" s="248">
-        <v>32291891</v>
-      </c>
-      <c r="F19" s="248">
-        <v>53205585.549970001</v>
+      <c r="C19" s="206">
+        <v>58541628.168898001</v>
+      </c>
+      <c r="D19" s="206">
+        <v>11919388.989965999</v>
+      </c>
+      <c r="E19" s="206">
+        <v>145055877.39998001</v>
+      </c>
+      <c r="F19" s="206">
+        <v>215516894.558844</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>5099867.3999969997</v>
+        <v>23545355.999937002</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>1855936.93</v>
+        <v>3740334.9659799999</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="248">
-        <v>2782567.3999970001</v>
-      </c>
-      <c r="D20" s="248">
+      <c r="C20" s="206">
+        <v>20673375.999937002</v>
+      </c>
+      <c r="D20" s="206">
         <v>1855936.93</v>
       </c>
-      <c r="E20" s="248" t="s">
+      <c r="E20" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="248">
-        <v>4638504.3299970003</v>
+      <c r="F20" s="206">
+        <v>22529312.929937001</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22073,24 +22073,24 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="248">
-        <v>2317300</v>
-      </c>
-      <c r="D21" s="248">
-        <v>0</v>
-      </c>
-      <c r="E21" s="248" t="s">
-        <v>169</v>
-      </c>
-      <c r="F21" s="248">
-        <v>2317300</v>
+      <c r="C21" s="206">
+        <v>2871980</v>
+      </c>
+      <c r="D21" s="206">
+        <v>1884398.0359799999</v>
+      </c>
+      <c r="E21" s="206">
+        <v>12518919.199999999</v>
+      </c>
+      <c r="F21" s="206">
+        <v>17275297.23598</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>24129738.547830999</v>
+        <v>41768477.379684001</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22100,12 +22100,18 @@
       <c r="B22" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="248"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248" t="s">
+      <c r="C22" s="206">
+        <v>26538800</v>
+      </c>
+      <c r="D22" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F22" s="248"/>
+      <c r="E22" s="206" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="206">
+        <v>26538800</v>
+      </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
       <c r="J22" s="116"/>
@@ -22114,15 +22120,17 @@
       <c r="B23" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="248">
-        <v>10757199.1</v>
-      </c>
-      <c r="D23" s="248"/>
-      <c r="E23" s="248" t="s">
+      <c r="C23" s="206">
+        <v>32932953.699999999</v>
+      </c>
+      <c r="D23" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="248">
-        <v>10757199.1</v>
+      <c r="E23" s="206">
+        <v>1441441.4</v>
+      </c>
+      <c r="F23" s="206">
+        <v>34374395.100000001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22132,17 +22140,17 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="248">
-        <v>9988474.3199879993</v>
-      </c>
-      <c r="D24" s="248">
-        <v>1081081.079988</v>
-      </c>
-      <c r="E24" s="248" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="248">
-        <v>11069555.399976</v>
+      <c r="C24" s="206">
+        <v>17591498.039963</v>
+      </c>
+      <c r="D24" s="206">
+        <v>2234414.409986</v>
+      </c>
+      <c r="E24" s="206">
+        <v>2526126.0800000001</v>
+      </c>
+      <c r="F24" s="206">
+        <v>22352038.529948998</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22152,17 +22160,17 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="248">
-        <v>8809071.3864999991</v>
-      </c>
-      <c r="D25" s="248">
-        <v>1512000</v>
-      </c>
-      <c r="E25" s="248" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="248">
-        <v>10321071.386499999</v>
+      <c r="C25" s="206">
+        <v>35047789.896495</v>
+      </c>
+      <c r="D25" s="206">
+        <v>8846417.9699939992</v>
+      </c>
+      <c r="E25" s="206">
+        <v>1945945.92</v>
+      </c>
+      <c r="F25" s="206">
+        <v>45840153.786489002</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22172,17 +22180,17 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="248">
-        <v>16085162.183885001</v>
-      </c>
-      <c r="D26" s="248">
-        <v>2520000</v>
-      </c>
-      <c r="E26" s="248">
-        <v>4932432.4000000004</v>
-      </c>
-      <c r="F26" s="248">
-        <v>23537594.583884999</v>
+      <c r="C26" s="206">
+        <v>29309860.628509</v>
+      </c>
+      <c r="D26" s="206">
+        <v>4394439.6500000004</v>
+      </c>
+      <c r="E26" s="206">
+        <v>13705405.279999999</v>
+      </c>
+      <c r="F26" s="206">
+        <v>47409705.558509</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22192,17 +22200,17 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="248">
-        <v>3954954.9199979999</v>
-      </c>
-      <c r="D27" s="248">
-        <v>0</v>
-      </c>
-      <c r="E27" s="248" t="s">
+      <c r="C27" s="206">
+        <v>28789378.789965</v>
+      </c>
+      <c r="D27" s="206">
+        <v>0</v>
+      </c>
+      <c r="E27" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="F27" s="248">
-        <v>3954954.9199979999</v>
+      <c r="F27" s="206">
+        <v>28789378.789965</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22248,8 +22256,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="248">
-        <v>5093180.1099570002</v>
+      <c r="C32" s="206">
+        <v>57813761.925821997</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22259,8 +22267,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="248">
-        <v>5997054.3339799996</v>
+      <c r="C33" s="206">
+        <v>7874081.4339800002</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22270,8 +22278,8 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="248">
-        <v>21275684.467831001</v>
+      <c r="C34" s="206">
+        <v>33296170.9397</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22281,8 +22289,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="248">
-        <v>2854054.08</v>
+      <c r="C35" s="206">
+        <v>8472306.4399839994</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22324,17 +22332,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="246" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>6.4516129032258063E-2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22377,19 +22385,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>188969283.077479</v>
+        <v>443765625.95609993</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>2.7629999288568172E-2</v>
+        <v>6.4884851811766869E-2</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>6650310048.9225206</v>
+        <v>6395513706.0439005</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>130398236.25338276</v>
+        <v>127910274.12087801</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22406,19 +22414,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>19622133.369897999</v>
+        <v>61816921.087029003</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>1.3300753225962515E-2</v>
+        <v>4.1902253800227093E-2</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1455642690.8504636</v>
+        <v>1413447903.1333327</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>28542013.546087522</v>
+        <v>28268958.062666655</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22435,46 +22443,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>35219972.991768003</v>
+        <v>107456320.73948601</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>1.975344547270997E-2</v>
+        <v>6.0267864853888319E-2</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1747758750.412488</v>
+        <v>1675522402.6647699</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>34269779.419852704</v>
+        <v>33510448.053295396</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>243811389.439145</v>
+        <v>613038867.78261495</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>2.4145663480606924E-2</v>
+        <v>6.0711807746397006E-2</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>9853711490.1854725</v>
+        <v>9484484011.8420029</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>193210029.21932298</v>
+        <v>189689680.23684007</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22484,40 +22492,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22525,13 +22533,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22550,7 +22558,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22560,7 +22568,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22583,35 +22591,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>9988474.3199879993</v>
+        <v>17591498.039963</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>1081081.079988</v>
+        <v>2234414.409986</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>11069555.399976</v>
+        <v>19825912.449949</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>2.2825996191153976E-2</v>
+        <v>4.0882057654245914E-2</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>406695003.68001199</v>
+        <v>399091979.96003699</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>67189320.140666306</v>
+        <v>66035986.810668312</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>473884323.82067829</v>
+        <v>465127966.77070528</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>9291849.4866799656</v>
+        <v>9302559.335414106</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22635,35 +22643,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>12944544.679975001</v>
+        <v>36531306.759904005</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>1618261.26</v>
+        <v>4824309.4452999998</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>14562805.939975001</v>
+        <v>41355616.205204003</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>1.950212582763693E-2</v>
+        <v>5.5382351054987268E-2</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>542237826.32002497</v>
+        <v>518651064.24009597</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>189928522.74000001</v>
+        <v>186722474.55469999</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>732166349.06002498</v>
+        <v>705373538.79479599</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>14356202.922745587</v>
+        <v>14107470.77589592</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22687,7 +22695,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>0</v>
+        <v>26538800</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22695,15 +22703,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>0</v>
+        <v>26538800</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0</v>
+        <v>0.1099036767912546</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>241473268</v>
+        <v>214934468</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22711,11 +22719,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>241473268</v>
+        <v>214934468</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>4734769.9607843133</v>
+        <v>4298689.3600000003</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22739,35 +22747,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>24141948.2852</v>
+        <v>42927190.625198998</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>3542756.7799820001</v>
+        <v>6103601.8199669998</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>27684705.065182</v>
+        <v>49030792.445165999</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>4.2099977318800018E-2</v>
+        <v>7.4560853908475971E-2</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>586570523.7148</v>
+        <v>567785281.37480104</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>43339070.03735289</v>
+        <v>40778224.997367889</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>629909593.75215292</v>
+        <v>608563506.3721689</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>12351168.504944175</v>
+        <v>12171270.127443379</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22819,7 +22827,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>9199879.6233632192</v>
+        <v>9383877.2158304825</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22843,35 +22851,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>7485797.7924610004</v>
+        <v>22279494.140058</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>3747243.2399639999</v>
+        <v>13462378.069882</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>11233041.032425001</v>
+        <v>35741872.209940001</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>2.0233945033795168E-2</v>
+        <v>6.4381415113973994E-2</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>466433034.20753902</v>
+        <v>451639337.85994202</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>77492150.88268961</v>
+        <v>67777016.052771598</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>543925185.09022856</v>
+        <v>519416353.91271359</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>10665199.707651541</v>
+        <v>10388327.078254271</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22895,35 +22903,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>20101498.149969999</v>
+        <v>58541628.168898001</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>812196.4</v>
+        <v>11919388.989965999</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>20913694.549969997</v>
+        <v>70461017.158864006</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>1.9848110597586496E-2</v>
+        <v>6.6870923166924556E-2</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>941656846.85002995</v>
+        <v>903216716.83110201</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>91116379.939156383</v>
+        <v>80009187.349190384</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>1032773226.7891864</v>
+        <v>983225904.18029237</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>20250455.427238949</v>
+        <v>19664518.083605848</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22947,35 +22955,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>8809071.3864999991</v>
+        <v>35047789.896495</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>1512000</v>
+        <v>8846417.9699939992</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>10321071.386499999</v>
+        <v>43894207.866489001</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>1.813678328278754E-2</v>
+        <v>7.7133439507592258E-2</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>496477987.6135</v>
+        <v>470239269.10350502</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>62269404</v>
+        <v>54934986.030005999</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>558747391.6135</v>
+        <v>525174255.13351101</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>10955831.208107844</v>
+        <v>10503485.102670221</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22999,7 +23007,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>10757199.1</v>
+        <v>32932953.699999999</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23007,15 +23015,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>10757199.1</v>
+        <v>32932953.699999999</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>2.6617923865901949E-2</v>
+        <v>8.1490250958158233E-2</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>393376464.89999998</v>
+        <v>371200710.30000001</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23023,11 +23031,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>393376464.89999998</v>
+        <v>371200710.30000001</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>7713264.0176470587</v>
+        <v>7424014.2060000002</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23051,35 +23059,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>43918836.375333004</v>
+        <v>59343656.966316</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>2932657.6799639999</v>
+        <v>4597378.3994570002</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>46851494.055297002</v>
+        <v>63941035.365773</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>8.6365114478211741E-2</v>
+        <v>0.11786763582614129</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>360098472.62466699</v>
+        <v>344673652.03368402</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>135531732.5380314</v>
+        <v>133867011.8185384</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>495630205.16269839</v>
+        <v>478540663.85222238</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>9718239.3169156555</v>
+        <v>9570813.2770444471</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23103,35 +23111,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>16085162.183885001</v>
+        <v>29309860.628509</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>2520000</v>
+        <v>4394439.6500000004</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>18605162.183885001</v>
+        <v>33704300.278508998</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>2.6949505244753796E-2</v>
+        <v>4.8820548197810294E-2</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>615544433.81611502</v>
+        <v>602319735.37149096</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>56221600.610625267</v>
+        <v>54347160.960625269</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>671766034.42674029</v>
+        <v>656666896.33211625</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>13171883.0279753</v>
+        <v>13133337.926642325</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23155,35 +23163,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>6943190.0841720002</v>
+        <v>11647973.840856001</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1694257.366497</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>6943190.0841720002</v>
+        <v>13342231.207353001</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>1.5418786167469506E-2</v>
+        <v>2.9629177293026304E-2</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>379599832.91582799</v>
+        <v>374895049.15914398</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>63764154.799813807</v>
+        <v>62069897.433316804</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>443363987.7156418</v>
+        <v>436964946.59246081</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>8693411.5238361135</v>
+        <v>8739298.931849217</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23207,7 +23215,7 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>3954954.9199979999</v>
+        <v>28789378.789965</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
@@ -23215,15 +23223,15 @@
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>3954954.9199979999</v>
+        <v>28789378.789965</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>4.331074588889294E-3</v>
+        <v>3.1527273870213639E-2</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>579395987.08000195</v>
+        <v>554561563.21003497</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
@@ -23231,11 +23239,11 @@
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>909202932.07271934</v>
+        <v>884368508.20275235</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>17827508.472014103</v>
+        <v>17687370.164055046</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23259,35 +23267,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>5099867.3999969997</v>
+        <v>23545355.999937002</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>1855936.93</v>
+        <v>3740334.9659799999</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>6955804.3299969994</v>
+        <v>27285690.965917002</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>1.3441278930372304E-2</v>
+        <v>5.2726408863917586E-2</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>254425821.600003</v>
+        <v>235980333.000063</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>256114094.97788638</v>
+        <v>254229696.94190639</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>510539916.57788938</v>
+        <v>490210029.94196939</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>10010586.599566458</v>
+        <v>9804200.5988393873</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23309,35 +23317,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>188969283.077479</v>
+        <v>443765625.95609993</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>19622133.369897999</v>
+        <v>61816921.087029003</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>208591416.447377</v>
+        <v>505582547.04312903</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>2.5087534870005281E-2</v>
+        <v>6.0807007280716335E-2</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>6650310048.9225216</v>
+        <v>6395513706.0439005</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1455642690.8504636</v>
+        <v>1413447903.1333327</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>8105952739.7729855</v>
+        <v>7808961609.1772327</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>158940249.79947031</v>
+        <v>156179232.18354467</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23353,10 +23361,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23364,8 +23372,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -23379,7 +23387,7 @@
       </c>
       <c r="D70" s="204">
         <f>IF(E24="",0,E24)</f>
-        <v>0</v>
+        <v>2526126.0800000001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23391,7 +23399,7 @@
       </c>
       <c r="D71" s="204">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>0</v>
+        <v>2252252.2000000002</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23415,7 +23423,7 @@
       </c>
       <c r="D73" s="204">
         <f>IF(E14="",0,E14)</f>
-        <v>1531531.5</v>
+        <v>3936936.9</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23450,7 +23458,7 @@
       </c>
       <c r="D76" s="204">
         <f>IF(E19="",0,E19)</f>
-        <v>32291891</v>
+        <v>145055877.39998001</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23462,7 +23470,7 @@
       </c>
       <c r="D77" s="204">
         <f>IF(E25="",0,E25)</f>
-        <v>0</v>
+        <v>1945945.92</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23474,7 +23482,7 @@
       </c>
       <c r="D78" s="204">
         <f>IF(E23="",0,E23)</f>
-        <v>0</v>
+        <v>1441441.4</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23498,7 +23506,7 @@
       </c>
       <c r="D80" s="204">
         <f>IF(E26="",0,E26)</f>
-        <v>4932432.4000000004</v>
+        <v>13705405.279999999</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23510,7 +23518,7 @@
       </c>
       <c r="D81" s="204">
         <f>IF(E10="",0,E10)</f>
-        <v>5322522.1399999997</v>
+        <v>13660359.880000001</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23533,8 +23541,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="204">
-        <f>0</f>
-        <v>0</v>
+        <v>12518919.199999999</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23544,7 +23551,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>48010809.439999998</v>
+        <v>200975696.65998</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23558,13 +23565,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23606,19 +23613,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>5093180.1099570002</v>
+        <v>57813761.925821997</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>1.8316534294598924E-2</v>
+        <v>0.20791484497944379</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>272971437.79425257</v>
+        <v>220250855.97838756</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>5352381.1332206391</v>
+        <v>4405017.119567751</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23635,19 +23642,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>5997054.3339799996</v>
+        <v>7874081.4339800002</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>1.4360124300563645E-2</v>
+        <v>1.8854721309431832E-2</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>411621498.85254157</v>
+        <v>409744471.7525416</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>8071009.7814223841</v>
+        <v>8194889.4350508321</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23664,19 +23671,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>24129738.547830999</v>
+        <v>41768477.379684001</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>2.2192437462370047E-2</v>
+        <v>3.8415017233179985E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1063165813.7656937</v>
+        <v>1045527074.9338408</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>20846388.505209681</v>
+        <v>20910541.498676814</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23749,24 +23756,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>35219972.991768003</v>
+        <v>107456320.73948601</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>1.975344547270997E-2</v>
+        <v>6.0267864853888319E-2</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1747758750.4124877</v>
+        <v>1675522402.6647699</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>34269779.419852704</v>
+        <v>33510448.053295396</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23774,11 +23786,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23847,7 +23854,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -24380,11 +24387,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24508,10 +24515,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24540,40 +24547,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24581,13 +24588,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24606,7 +24613,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24616,7 +24623,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25409,10 +25416,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25420,8 +25427,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -25615,13 +25622,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25824,6 +25831,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25831,11 +25843,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25904,7 +25911,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -26437,11 +26444,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="225" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="227"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26565,10 +26572,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="223"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26597,40 +26604,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="230"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="230"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="219" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="221"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="224" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26638,13 +26645,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="224"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26663,7 +26670,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="224"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26673,7 +26680,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27466,10 +27473,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="224" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27477,8 +27484,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="224"/>
+      <c r="C69" s="224"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -27672,13 +27679,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27881,6 +27888,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27888,11 +27900,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -601,7 +601,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 04 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 05 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1929,6 +1929,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1948,15 +1957,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -3601,10 +3601,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4665,13 +4665,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4874,11 +4874,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4886,6 +4881,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -5658,10 +5658,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6722,13 +6722,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6931,11 +6931,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6943,6 +6938,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -7715,10 +7715,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8779,13 +8779,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8988,11 +8988,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -9000,6 +8995,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9772,10 +9772,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10836,13 +10836,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11045,11 +11045,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11057,6 +11052,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11828,10 +11828,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11893,7 +11893,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12878,13 +12878,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13087,11 +13087,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13099,6 +13094,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.12903225806451613</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>41763516.044631958</v>
+        <v>43579321.090050742</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>12221998.269450625</v>
+        <v>12753389.498557175</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>8507814.0227448139</v>
+        <v>8877718.9802554585</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>62493328.336827397</v>
+        <v>65210429.56886337</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>4213604.7239109473</v>
+        <v>4396804.9292983804</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>4005394.331662456</v>
+        <v>4179541.9112999542</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>8441205.8083333336</v>
+        <v>8808214.7565217391</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20585,7 +20585,7 @@
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>2487899.5983031341</v>
+        <v>2596069.1460554446</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>2846164.9063137993</v>
+        <v>2969911.2065883125</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>1067882.3628139</v>
+        <v>1114312.0307623304</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-3142028.486555303</v>
+        <v>-3278638.4207533598</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>3722802.0364366248</v>
+        <v>3884662.9945425652</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>11815965.469999999</v>
+        <v>12329703.099130433</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3331463.0936769471</v>
+        <v>3476309.3151411624</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>4615340.71590894</v>
+        <v>4816007.7035571542</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>3325900.646714007</v>
+        <v>3470505.0226580943</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>444297.47160840529</v>
+        <v>463614.75298268383</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>6809621.6349553643</v>
+        <v>7105692.1408229889</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21155,7 +21155,7 @@
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>53985514.314082541</v>
+        <v>56332710.58860787</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>1631429.0690996747</v>
+        <v>1702360.7677561822</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1263407.6981834222</v>
+        <v>-1318338.4676696581</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>8139792.6518285573</v>
+        <v>8493696.6801689286</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>8507814.0227448102</v>
+        <v>8877718.9802554529</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21741,11 +21741,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>17591498.039963</v>
+        <v>25781529.671627</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>2234414.409986</v>
+        <v>5633788.5984819997</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21763,11 +21763,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>36531306.759904005</v>
+        <v>59564857.203666002</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>4824309.4452999998</v>
+        <v>15407258.180297999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21775,27 +21775,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="206">
-        <v>11647973.840856001</v>
+        <v>37405669.322714999</v>
       </c>
       <c r="D10" s="206">
-        <v>1694257.366497</v>
+        <v>2839684.290397</v>
       </c>
       <c r="E10" s="206">
-        <v>13660359.880000001</v>
+        <v>34372071.079999998</v>
       </c>
       <c r="F10" s="206">
-        <v>27002591.087352999</v>
+        <v>74617424.693112001</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>42927190.625198998</v>
+        <v>68059225.285199001</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>6103601.8199669998</v>
+        <v>9412519.1139570009</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21803,27 +21803,27 @@
         <v>114</v>
       </c>
       <c r="C11" s="206">
-        <v>59343656.966316</v>
+        <v>70050112.890311003</v>
       </c>
       <c r="D11" s="206">
-        <v>4597378.3994570002</v>
+        <v>9373502.6594130006</v>
       </c>
       <c r="E11" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F11" s="206">
-        <v>63941035.365773</v>
+        <v>79423615.549723998</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>18738738.399999999</v>
+        <v>21387387.039999999</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>0</v>
+        <v>594594.6</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -21831,27 +21831,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="206">
-        <v>14869279.899979001</v>
+        <v>19598532.899978999</v>
       </c>
       <c r="D12" s="206">
-        <v>1783917.5453000001</v>
+        <v>11278249.160297999</v>
       </c>
       <c r="E12" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F12" s="206">
-        <v>16653197.445279</v>
+        <v>30876782.060277</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>22279494.140058</v>
+        <v>29647735.587652002</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>13462378.069882</v>
+        <v>17914974.499876998</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21859,23 +21859,23 @@
         <v>115</v>
       </c>
       <c r="C13" s="206">
-        <v>21662026.859925002</v>
+        <v>39966324.303686999</v>
       </c>
       <c r="D13" s="206">
-        <v>3040391.9</v>
+        <v>4129009.02</v>
       </c>
       <c r="E13" s="206">
         <v>2252252.2000000002</v>
       </c>
       <c r="F13" s="206">
-        <v>26954670.959925</v>
+        <v>46347585.523686998</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>58541628.168898001</v>
+        <v>89694325.230609998</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
@@ -21887,27 +21887,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="206">
-        <v>42927190.625198998</v>
+        <v>68059225.285199001</v>
       </c>
       <c r="D14" s="206">
-        <v>6103601.8199669998</v>
+        <v>9412519.1139570009</v>
       </c>
       <c r="E14" s="206">
-        <v>3936936.9</v>
+        <v>10646846.74</v>
       </c>
       <c r="F14" s="206">
-        <v>52967729.345165998</v>
+        <v>88118591.139155999</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>35047789.896495</v>
+        <v>61972743.358419999</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>8846417.9699939992</v>
+        <v>19809837.809866</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21923,11 +21923,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>59343656.966316</v>
+        <v>70050112.890311003</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>4597378.3994570002</v>
+        <v>9373502.6594130006</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21935,27 +21935,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="206">
-        <v>22279494.140058</v>
+        <v>29647735.587652002</v>
       </c>
       <c r="D16" s="206">
-        <v>13462378.069882</v>
+        <v>17914974.499876998</v>
       </c>
       <c r="E16" s="206">
         <v>3932432.4</v>
       </c>
       <c r="F16" s="206">
-        <v>39674304.60994</v>
+        <v>51495142.487529002</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>29309860.628509</v>
+        <v>50253462.618390001</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>4394439.6500000004</v>
+        <v>11618043.239971999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21963,27 +21963,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="206">
-        <v>18738738.399999999</v>
+        <v>21387387.039999999</v>
       </c>
       <c r="D17" s="206">
-        <v>0</v>
+        <v>594594.6</v>
       </c>
       <c r="E17" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F17" s="206">
-        <v>18738738.399999999</v>
+        <v>21981981.640000001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>11647973.840856001</v>
+        <v>37405669.322714999</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>1694257.366497</v>
+        <v>2839684.290397</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21991,27 +21991,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="206">
-        <v>33045812.219997998</v>
+        <v>333064390.74396801</v>
       </c>
       <c r="D18" s="206">
-        <v>474000</v>
-      </c>
-      <c r="E18" s="206" t="s">
-        <v>169</v>
+        <v>1185000</v>
+      </c>
+      <c r="E18" s="206">
+        <v>972972.96</v>
       </c>
       <c r="F18" s="206">
-        <v>33519812.219997998</v>
+        <v>335222363.70396799</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>28789378.789965</v>
+        <v>90105944.180085003</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>0</v>
+        <v>16853837.639756002</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22019,27 +22019,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="206">
-        <v>58541628.168898001</v>
+        <v>89694325.230609998</v>
       </c>
       <c r="D19" s="206">
         <v>11919388.989965999</v>
       </c>
       <c r="E19" s="206">
-        <v>145055877.39998001</v>
+        <v>202760383.15997201</v>
       </c>
       <c r="F19" s="206">
-        <v>215516894.558844</v>
+        <v>304374097.380548</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>23545355.999937002</v>
+        <v>29230330.799936999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>3740334.9659799999</v>
+        <v>24403172.497872002</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22047,16 +22047,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="206">
-        <v>20673375.999937002</v>
+        <v>24783330.799936999</v>
       </c>
       <c r="D20" s="206">
-        <v>1855936.93</v>
+        <v>8237791.0899999999</v>
       </c>
       <c r="E20" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F20" s="206">
-        <v>22529312.929937001</v>
+        <v>33021121.889936998</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22074,23 +22074,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="206">
-        <v>2871980</v>
+        <v>4447000</v>
       </c>
       <c r="D21" s="206">
-        <v>1884398.0359799999</v>
+        <v>16165381.407872001</v>
       </c>
       <c r="E21" s="206">
         <v>12518919.199999999</v>
       </c>
       <c r="F21" s="206">
-        <v>17275297.23598</v>
+        <v>33131300.607872002</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>41768477.379684001</v>
+        <v>73114044.800494</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22121,7 +22121,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="206">
-        <v>32932953.699999999</v>
+        <v>34696242</v>
       </c>
       <c r="D23" s="206" t="s">
         <v>169</v>
@@ -22130,7 +22130,7 @@
         <v>1441441.4</v>
       </c>
       <c r="F23" s="206">
-        <v>34374395.100000001</v>
+        <v>36137683.399999999</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22141,16 +22141,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="206">
-        <v>17591498.039963</v>
+        <v>25781529.671627</v>
       </c>
       <c r="D24" s="206">
-        <v>2234414.409986</v>
+        <v>5633788.5984819997</v>
       </c>
       <c r="E24" s="206">
-        <v>2526126.0800000001</v>
+        <v>3409008.94</v>
       </c>
       <c r="F24" s="206">
-        <v>22352038.529948998</v>
+        <v>34824327.210109003</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22161,16 +22161,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="206">
-        <v>35047789.896495</v>
+        <v>61972743.358419999</v>
       </c>
       <c r="D25" s="206">
-        <v>8846417.9699939992</v>
+        <v>19809837.809866</v>
       </c>
       <c r="E25" s="206">
-        <v>1945945.92</v>
+        <v>10536035.92</v>
       </c>
       <c r="F25" s="206">
-        <v>45840153.786489002</v>
+        <v>92318617.088285998</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22181,16 +22181,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="206">
-        <v>29309860.628509</v>
+        <v>50253462.618390001</v>
       </c>
       <c r="D26" s="206">
-        <v>4394439.6500000004</v>
+        <v>11618043.239971999</v>
       </c>
       <c r="E26" s="206">
-        <v>13705405.279999999</v>
+        <v>33927927.649999999</v>
       </c>
       <c r="F26" s="206">
-        <v>47409705.558509</v>
+        <v>95799433.508361995</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22201,16 +22201,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="206">
-        <v>28789378.789965</v>
+        <v>90105944.180085003</v>
       </c>
       <c r="D27" s="206">
-        <v>0</v>
-      </c>
-      <c r="E27" s="206" t="s">
-        <v>169</v>
+        <v>16853837.639756002</v>
+      </c>
+      <c r="E27" s="206">
+        <v>2097297.34</v>
       </c>
       <c r="F27" s="206">
-        <v>28789378.789965</v>
+        <v>109057079.159841</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22257,7 +22257,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="206">
-        <v>57813761.925821997</v>
+        <v>65522982.685794003</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22268,7 +22268,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>7874081.4339800002</v>
+        <v>9055162.4139740001</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22279,7 +22279,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="206">
-        <v>33296170.9397</v>
+        <v>61614711.480541997</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22290,7 +22290,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="206">
-        <v>8472306.4399839994</v>
+        <v>11499333.319952</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22331,24 +22331,24 @@
       <c r="H40" s="116"/>
       <c r="I40" s="116"/>
     </row>
-    <row r="41" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="246" t="s">
+    <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="239" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="247"/>
-      <c r="D41" s="248"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="241"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.12903225806451613</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
       <c r="I41" s="116"/>
     </row>
-    <row r="42" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="69" t="s">
         <v>137</v>
       </c>
@@ -22385,19 +22385,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>443765625.95609993</v>
+        <v>694388365.18861198</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>6.4884851811766869E-2</v>
+        <v>0.10152946406789808</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>6395513706.0439005</v>
+        <v>6144890966.811388</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>127910274.12087801</v>
+        <v>125405938.09819159</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22414,19 +22414,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>61816921.087029003</v>
+        <v>145780602.119856</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>4.1902253800227093E-2</v>
+        <v>9.8816564813640956E-2</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1413447903.1333327</v>
+        <v>1329484222.1005058</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>28268958.062666655</v>
+        <v>27132331.063275628</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22443,19 +22443,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>107456320.73948601</v>
+        <v>147692189.900262</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>6.0267864853888319E-2</v>
+        <v>8.2834521781769824E-2</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1675522402.6647699</v>
+        <v>1635286533.503994</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>33510448.053295396</v>
+        <v>33373194.561306</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22470,19 +22470,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>613038867.78261495</v>
+        <v>987861157.20872998</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>6.0711807746397006E-2</v>
+        <v>9.7832029596297818E-2</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>9484484011.8420029</v>
+        <v>9109661722.4158878</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>189689680.23684007</v>
+        <v>185911463.72277322</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22491,7 +22491,7 @@
       <c r="H47" s="116"/>
       <c r="I47" s="116"/>
     </row>
-    <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="229" t="s">
         <v>147</v>
       </c>
@@ -22503,10 +22503,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22591,35 +22591,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>17591498.039963</v>
+        <v>25781529.671627</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>2234414.409986</v>
+        <v>5633788.5984819997</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>19825912.449949</v>
+        <v>31415318.270108998</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>4.0882057654245914E-2</v>
+        <v>6.4780012319099342E-2</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>399091979.96003699</v>
+        <v>390901948.32837301</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>66035986.810668312</v>
+        <v>62636612.622172311</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>465127966.77070528</v>
+        <v>453538560.95054531</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>9302559.335414106</v>
+        <v>9255888.9989907201</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22643,35 +22643,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>36531306.759904005</v>
+        <v>59564857.203666002</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>4824309.4452999998</v>
+        <v>15407258.180297999</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>41355616.205204003</v>
+        <v>74972115.383964002</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>5.5382351054987268E-2</v>
+        <v>0.10040068059745706</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>518651064.24009597</v>
+        <v>495617513.79633403</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>186722474.55469999</v>
+        <v>176139525.819702</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>705373538.79479599</v>
+        <v>671757039.61603594</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>14107470.77589592</v>
+        <v>13709327.339102775</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>4298689.3600000003</v>
+        <v>4386417.7142857146</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22747,35 +22747,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>42927190.625198998</v>
+        <v>68059225.285199001</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>6103601.8199669998</v>
+        <v>9412519.1139570009</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>49030792.445165999</v>
+        <v>77471744.399156004</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>7.4560853908475971E-2</v>
+        <v>0.11781085167326844</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>567785281.37480104</v>
+        <v>542653246.71480095</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>40778224.997367889</v>
+        <v>37469307.703377888</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>608563506.3721689</v>
+        <v>580122554.41817892</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>12171270.127443379</v>
+        <v>11839235.804452632</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22799,35 +22799,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>18738738.399999999</v>
+        <v>21387387.039999999</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>594594.6</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>18738738.399999999</v>
+        <v>21981981.640000001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>3.8404358370498291E-2</v>
+        <v>4.5051266663516359E-2</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>386324545.60000002</v>
+        <v>383675896.95999998</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>82869315.191524148</v>
+        <v>82274720.591524154</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>469193860.79152417</v>
+        <v>465950617.55152416</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>9383877.2158304825</v>
+        <v>9509196.2765617184</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22851,35 +22851,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>22279494.140058</v>
+        <v>29647735.587652002</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>13462378.069882</v>
+        <v>17914974.499876998</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>35741872.209940001</v>
+        <v>47562710.087529004</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>6.4381415113973994E-2</v>
+        <v>8.5674151709355661E-2</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>451639337.85994202</v>
+        <v>444271096.41234797</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>67777016.052771598</v>
+        <v>63324419.622776605</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>519416353.91271359</v>
+        <v>507595516.0351246</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>10388327.078254271</v>
+        <v>10359092.163982134</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>58541628.168898001</v>
+        <v>89694325.230609998</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
@@ -22911,15 +22911,15 @@
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>70461017.158864006</v>
+        <v>101613714.220576</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>6.6870923166924556E-2</v>
+        <v>9.643634381589615E-2</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>903216716.83110201</v>
+        <v>872064019.76938999</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
@@ -22927,11 +22927,11 @@
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>983225904.18029237</v>
+        <v>952073207.11858034</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>19664518.083605848</v>
+        <v>19430065.451399598</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22955,35 +22955,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>35047789.896495</v>
+        <v>61972743.358419999</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>8846417.9699939992</v>
+        <v>19809837.809866</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>43894207.866489001</v>
+        <v>81782581.168285996</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>7.7133439507592258E-2</v>
+        <v>0.14371307933169722</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>470239269.10350502</v>
+        <v>443314315.64157999</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>54934986.030005999</v>
+        <v>43971566.190134004</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>525174255.13351101</v>
+        <v>487285881.83171403</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>10503485.102670221</v>
+        <v>9944609.8333002869</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23007,7 +23007,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>32932953.699999999</v>
+        <v>34696242</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23015,15 +23015,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>32932953.699999999</v>
+        <v>34696242</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>8.1490250958158233E-2</v>
+        <v>8.5853382409637621E-2</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>371200710.30000001</v>
+        <v>369437422</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23031,11 +23031,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>371200710.30000001</v>
+        <v>369437422</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>7424014.2060000002</v>
+        <v>7539539.224489796</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23059,35 +23059,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>59343656.966316</v>
+        <v>70050112.890311003</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>4597378.3994570002</v>
+        <v>9373502.6594130006</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>63941035.365773</v>
+        <v>79423615.549723998</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.11786763582614129</v>
+        <v>0.14640791691999133</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>344673652.03368402</v>
+        <v>333967196.109689</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>133867011.8185384</v>
+        <v>129090887.55858241</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>478540663.85222238</v>
+        <v>463058083.66827142</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>9570813.2770444471</v>
+        <v>9450164.9728218652</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23111,35 +23111,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>29309860.628509</v>
+        <v>50253462.618390001</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>4394439.6500000004</v>
+        <v>11618043.239971999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>33704300.278508998</v>
+        <v>61871505.858362004</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>4.8820548197810294E-2</v>
+        <v>8.9620636205739637E-2</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>602319735.37149096</v>
+        <v>581376133.38161004</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>54347160.960625269</v>
+        <v>47123557.370653272</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>656666896.33211625</v>
+        <v>628499690.75226331</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>13133337.926642325</v>
+        <v>12826524.301066598</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23163,35 +23163,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>11647973.840856001</v>
+        <v>37405669.322714999</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>1694257.366497</v>
+        <v>2839684.290397</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>13342231.207353001</v>
+        <v>40245353.613112003</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>2.9629177293026304E-2</v>
+        <v>8.9373111505238467E-2</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>374895049.15914398</v>
+        <v>349137353.67728502</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>62069897.433316804</v>
+        <v>60924470.509416804</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>436964946.59246081</v>
+        <v>410061824.18670177</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>8739298.931849217</v>
+        <v>8368608.656871465</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23215,35 +23215,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>28789378.789965</v>
+        <v>90105944.180085003</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16853837.639756002</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>28789378.789965</v>
+        <v>106959781.819841</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>3.1527273870213639E-2</v>
+        <v>0.11713175053668898</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>554561563.21003497</v>
+        <v>493244997.819915</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>329806944.99271739</v>
+        <v>312953107.35296136</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>884368508.20275235</v>
+        <v>806198105.17287636</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>17687370.164055046</v>
+        <v>16453022.554548496</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23267,35 +23267,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>23545355.999937002</v>
+        <v>29230330.799936999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>3740334.9659799999</v>
+        <v>24403172.497872002</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>27285690.965917002</v>
+        <v>53633503.297809005</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>5.2726408863917586E-2</v>
+        <v>0.10364047687914255</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>235980333.000063</v>
+        <v>230295358.20006299</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>254229696.94190639</v>
+        <v>233566859.41001439</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>490210029.94196939</v>
+        <v>463862217.61007738</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>9804200.5988393873</v>
+        <v>9466575.8695934154</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23317,35 +23317,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>443765625.95609993</v>
+        <v>694388365.18861198</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>61816921.087029003</v>
+        <v>145780602.119856</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>505582547.04312903</v>
+        <v>840168967.30846798</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>6.0807007280716335E-2</v>
+        <v>0.10104810937589551</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>6395513706.0439005</v>
+        <v>6144890966.811388</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1413447903.1333327</v>
+        <v>1329484222.1005056</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>7808961609.1772327</v>
+        <v>7474375188.9118938</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>156179232.18354467</v>
+        <v>152538269.16146722</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23387,7 +23387,7 @@
       </c>
       <c r="D70" s="204">
         <f>IF(E24="",0,E24)</f>
-        <v>2526126.0800000001</v>
+        <v>3409008.94</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="D73" s="204">
         <f>IF(E14="",0,E14)</f>
-        <v>3936936.9</v>
+        <v>10646846.74</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="D76" s="204">
         <f>IF(E19="",0,E19)</f>
-        <v>145055877.39998001</v>
+        <v>202760383.15997201</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23470,7 +23470,7 @@
       </c>
       <c r="D77" s="204">
         <f>IF(E25="",0,E25)</f>
-        <v>1945945.92</v>
+        <v>10536035.92</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="D80" s="204">
         <f>IF(E26="",0,E26)</f>
-        <v>13705405.279999999</v>
+        <v>33927927.649999999</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="D81" s="204">
         <f>IF(E10="",0,E10)</f>
-        <v>13660359.880000001</v>
+        <v>34372071.079999998</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23551,7 +23551,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>200975696.65998</v>
+        <v>315797318.68997198</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23565,13 +23565,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23613,19 +23613,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>57813761.925821997</v>
+        <v>65522982.685794003</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.20791484497944379</v>
+        <v>0.2356394106508222</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>220250855.97838756</v>
+        <v>212541635.21841556</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>4405017.119567751</v>
+        <v>4337584.3922125623</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23642,19 +23642,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>7874081.4339800002</v>
+        <v>9055162.4139740001</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>1.8854721309431832E-2</v>
+        <v>2.1682854712466951E-2</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>409744471.7525416</v>
+        <v>408563390.7725476</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>8194889.4350508321</v>
+        <v>8338028.3831132166</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23671,19 +23671,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>41768477.379684001</v>
+        <v>73114044.800494</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>3.8415017233179985E-2</v>
+        <v>6.7243947282708424E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1045527074.9338408</v>
+        <v>1014181507.5130308</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>20910541.498676814</v>
+        <v>20697581.785980221</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23756,29 +23756,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>107456320.73948601</v>
+        <v>147692189.900262</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>6.0267864853888319E-2</v>
+        <v>8.2834521781769824E-2</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1675522402.6647699</v>
+        <v>1635286533.503994</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>33510448.053295396</v>
+        <v>33373194.561306</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23786,6 +23781,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -24558,10 +24558,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24623,7 +24623,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25622,13 +25622,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25831,11 +25831,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25843,6 +25838,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -26615,10 +26615,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26680,7 +26680,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27679,13 +27679,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27888,11 +27888,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27900,6 +27895,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -601,7 +601,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 05 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 06 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1929,15 +1929,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1959,6 +1950,16 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2897,7 +2898,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -3601,10 +3602,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3631,7 +3632,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3666,7 +3667,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4665,13 +4666,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4874,6 +4875,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4881,11 +4887,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4954,7 +4955,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -5658,10 +5659,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5688,7 +5689,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5723,7 +5724,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6722,13 +6723,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6931,6 +6932,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6938,11 +6944,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7011,7 +7012,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -7715,10 +7716,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7745,7 +7746,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7780,7 +7781,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8779,13 +8780,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8988,6 +8989,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8995,11 +9001,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9068,7 +9069,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -9772,10 +9773,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9802,7 +9803,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9837,7 +9838,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10836,13 +10837,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11045,6 +11046,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11052,11 +11058,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11125,7 +11126,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -11828,10 +11829,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11858,7 +11859,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11893,7 +11894,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12878,13 +12879,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13087,6 +13088,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13094,11 +13100,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -19557,7 +19558,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -20163,7 +20164,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.16129032258064516</v>
+        <v>0.19354838709677419</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20216,7 +20217,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>43579321.090050742</v>
+        <v>45560199.321416683</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20244,7 +20245,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>12753389.498557175</v>
+        <v>13333089.021218864</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20272,7 +20273,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>8877718.9802554585</v>
+        <v>9281251.6611761618</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20298,7 +20299,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>65210429.56886337</v>
+        <v>68174540.003811702</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20429,7 +20430,7 @@
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>4396804.9292983804</v>
+        <v>4596659.6988119427</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20481,7 +20482,7 @@
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>4179541.9112999542</v>
+        <v>4369521.0890863156</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20533,7 +20534,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>8808214.7565217391</v>
+        <v>9208588.1545454543</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20585,7 +20586,7 @@
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>2596069.1460554446</v>
+        <v>2714072.2890579645</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20637,7 +20638,7 @@
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>2969911.2065883125</v>
+        <v>3104907.1705241445</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20689,7 +20690,7 @@
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>1114312.0307623304</v>
+        <v>1164962.5776151635</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20741,7 +20742,7 @@
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-3278638.4207533598</v>
+        <v>-3427667.4398785126</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20793,7 +20794,7 @@
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>3884662.9945425652</v>
+        <v>4061238.5852035908</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20845,7 +20846,7 @@
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>12329703.099130433</v>
+        <v>12890144.149090908</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20897,7 +20898,7 @@
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3476309.3151411624</v>
+        <v>3634323.3749203058</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20949,7 +20950,7 @@
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>4816007.7035571542</v>
+        <v>5034917.1446279343</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21001,7 +21002,7 @@
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>3470505.0226580943</v>
+        <v>3628255.2509607347</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21053,7 +21054,7 @@
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>463614.75298268383</v>
+        <v>484688.15084553306</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21105,7 +21106,7 @@
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>7105692.1408229889</v>
+        <v>7428678.1472240333</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21155,7 +21156,7 @@
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>56332710.58860787</v>
+        <v>58893288.342635505</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21430,7 +21431,7 @@
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>1702360.7677561822</v>
+        <v>1779740.8026541905</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21459,7 +21460,7 @@
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1318338.4676696581</v>
+        <v>-1378262.9434728243</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21488,7 +21489,7 @@
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>8493696.6801689286</v>
+        <v>8879773.8019947894</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21573,7 +21574,7 @@
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>8877718.9802554529</v>
+        <v>9281251.6611761563</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21659,7 +21660,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21741,11 +21742,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>25781529.671627</v>
+        <v>32709858.660574999</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>5633788.5984819997</v>
+        <v>9597998.5084819999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21763,11 +21764,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>59564857.203666002</v>
+        <v>81423428.073637992</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>15407258.180297999</v>
+        <v>17193208.630292002</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21775,27 +21776,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="206">
-        <v>37405669.322714999</v>
+        <v>47271367.069149002</v>
       </c>
       <c r="D10" s="206">
-        <v>2839684.290397</v>
+        <v>3968008.6203959999</v>
       </c>
       <c r="E10" s="206">
-        <v>34372071.079999998</v>
+        <v>39231530.520000003</v>
       </c>
       <c r="F10" s="206">
-        <v>74617424.693112001</v>
+        <v>90470906.209545001</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>68059225.285199001</v>
+        <v>93242063.585198998</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>9412519.1139570009</v>
+        <v>9773879.4739570003</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21803,16 +21804,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="206">
-        <v>70050112.890311003</v>
+        <v>78951925.710300997</v>
       </c>
       <c r="D11" s="206">
-        <v>9373502.6594130006</v>
+        <v>14526745.840333</v>
       </c>
       <c r="E11" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F11" s="206">
-        <v>79423615.549723998</v>
+        <v>93478671.550633997</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21831,27 +21832,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="206">
-        <v>19598532.899978999</v>
+        <v>34317464.039976001</v>
       </c>
       <c r="D12" s="206">
-        <v>11278249.160297999</v>
+        <v>11865672.590298001</v>
       </c>
       <c r="E12" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F12" s="206">
-        <v>30876782.060277</v>
+        <v>46183136.630273998</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>29647735.587652002</v>
+        <v>48103144.068025999</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>17914974.499876998</v>
+        <v>18718384.409876999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21859,27 +21860,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="206">
-        <v>39966324.303686999</v>
+        <v>47105964.033661999</v>
       </c>
       <c r="D13" s="206">
-        <v>4129009.02</v>
+        <v>5327536.0399940005</v>
       </c>
       <c r="E13" s="206">
-        <v>2252252.2000000002</v>
+        <v>7495495.4000000004</v>
       </c>
       <c r="F13" s="206">
-        <v>46347585.523686998</v>
+        <v>59928995.473655999</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>89694325.230609998</v>
+        <v>117065779.879189</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>11919388.989965999</v>
+        <v>14545481.789966</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21887,27 +21888,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="206">
-        <v>68059225.285199001</v>
+        <v>93242063.585198998</v>
       </c>
       <c r="D14" s="206">
-        <v>9412519.1139570009</v>
+        <v>9773879.4739570003</v>
       </c>
       <c r="E14" s="206">
-        <v>10646846.74</v>
+        <v>13097297.140000001</v>
       </c>
       <c r="F14" s="206">
-        <v>88118591.139155999</v>
+        <v>116113240.199156</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>61972743.358419999</v>
+        <v>78677946.036803007</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>19809837.809866</v>
+        <v>20233135.109866001</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21923,11 +21924,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>70050112.890311003</v>
+        <v>78951925.710300997</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>9373502.6594130006</v>
+        <v>14526745.840333</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21935,27 +21936,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="206">
-        <v>29647735.587652002</v>
+        <v>48103144.068025999</v>
       </c>
       <c r="D16" s="206">
-        <v>17914974.499876998</v>
+        <v>18718384.409876999</v>
       </c>
       <c r="E16" s="206">
         <v>3932432.4</v>
       </c>
       <c r="F16" s="206">
-        <v>51495142.487529002</v>
+        <v>70753960.877903</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>50253462.618390001</v>
+        <v>68670310.1743</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>11618043.239971999</v>
+        <v>14865583.799972</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21979,11 +21980,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>37405669.322714999</v>
+        <v>47271367.069149002</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>2839684.290397</v>
+        <v>3968008.6203959999</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21991,27 +21992,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="206">
-        <v>333064390.74396801</v>
+        <v>380995257.12396801</v>
       </c>
       <c r="D18" s="206">
-        <v>1185000</v>
+        <v>1368617.12</v>
       </c>
       <c r="E18" s="206">
         <v>972972.96</v>
       </c>
       <c r="F18" s="206">
-        <v>335222363.70396799</v>
+        <v>383336847.20396799</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>90105944.180085003</v>
+        <v>106086123.63008501</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>16853837.639756002</v>
+        <v>84961944.838635996</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22019,27 +22020,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="206">
-        <v>89694325.230609998</v>
+        <v>117065779.879189</v>
       </c>
       <c r="D19" s="206">
-        <v>11919388.989965999</v>
+        <v>14545481.789966</v>
       </c>
       <c r="E19" s="206">
-        <v>202760383.15997201</v>
+        <v>229879300.729956</v>
       </c>
       <c r="F19" s="206">
-        <v>304374097.380548</v>
+        <v>361490562.39911097</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>29230330.799936999</v>
+        <v>38070114.355120003</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>24403172.497872002</v>
+        <v>32251926.952272002</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22047,7 +22048,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="206">
-        <v>24783330.799936999</v>
+        <v>28613114.355119999</v>
       </c>
       <c r="D20" s="206">
         <v>8237791.0899999999</v>
@@ -22056,7 +22057,7 @@
         <v>169</v>
       </c>
       <c r="F20" s="206">
-        <v>33021121.889936998</v>
+        <v>36850905.445119999</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22074,23 +22075,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="206">
-        <v>4447000</v>
+        <v>9457000</v>
       </c>
       <c r="D21" s="206">
-        <v>16165381.407872001</v>
+        <v>24014135.862272002</v>
       </c>
       <c r="E21" s="206">
         <v>12518919.199999999</v>
       </c>
       <c r="F21" s="206">
-        <v>33131300.607872002</v>
+        <v>45990055.062271997</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>73114044.800494</v>
+        <v>94960806.617712989</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22101,16 +22102,16 @@
         <v>173</v>
       </c>
       <c r="C22" s="206">
-        <v>26538800</v>
+        <v>32194810</v>
       </c>
       <c r="D22" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="206" t="s">
-        <v>169</v>
+      <c r="E22" s="206">
+        <v>4036035.92</v>
       </c>
       <c r="F22" s="206">
-        <v>26538800</v>
+        <v>36230845.920000002</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22121,7 +22122,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="206">
-        <v>34696242</v>
+        <v>38412458.249975003</v>
       </c>
       <c r="D23" s="206" t="s">
         <v>169</v>
@@ -22130,7 +22131,7 @@
         <v>1441441.4</v>
       </c>
       <c r="F23" s="206">
-        <v>36137683.399999999</v>
+        <v>39853899.649975002</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22141,16 +22142,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="206">
-        <v>25781529.671627</v>
+        <v>32709858.660574999</v>
       </c>
       <c r="D24" s="206">
-        <v>5633788.5984819997</v>
+        <v>9597998.5084819999</v>
       </c>
       <c r="E24" s="206">
-        <v>3409008.94</v>
+        <v>8219819.6200000001</v>
       </c>
       <c r="F24" s="206">
-        <v>34824327.210109003</v>
+        <v>50527676.789057001</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22161,16 +22162,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="206">
-        <v>61972743.358419999</v>
+        <v>78677946.036803007</v>
       </c>
       <c r="D25" s="206">
-        <v>19809837.809866</v>
+        <v>20233135.109866001</v>
       </c>
       <c r="E25" s="206">
         <v>10536035.92</v>
       </c>
       <c r="F25" s="206">
-        <v>92318617.088285998</v>
+        <v>109447117.066669</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22181,16 +22182,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="206">
-        <v>50253462.618390001</v>
+        <v>68670310.1743</v>
       </c>
       <c r="D26" s="206">
-        <v>11618043.239971999</v>
+        <v>14865583.799972</v>
       </c>
       <c r="E26" s="206">
-        <v>33927927.649999999</v>
+        <v>40603603.649999999</v>
       </c>
       <c r="F26" s="206">
-        <v>95799433.508361995</v>
+        <v>124139497.624272</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22201,16 +22202,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="206">
-        <v>90105944.180085003</v>
+        <v>106086123.63008501</v>
       </c>
       <c r="D27" s="206">
-        <v>16853837.639756002</v>
+        <v>84961944.838635996</v>
       </c>
       <c r="E27" s="206">
-        <v>2097297.34</v>
+        <v>4259459.54</v>
       </c>
       <c r="F27" s="206">
-        <v>109057079.159841</v>
+        <v>195307528.00872099</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22256,8 +22257,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="206">
-        <v>65522982.685794003</v>
+      <c r="C32" s="249">
+        <v>87095406.395739004</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22268,7 +22269,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>9055162.4139740001</v>
+        <v>13891811.213934001</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22279,7 +22280,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="206">
-        <v>61614711.480541997</v>
+        <v>83461473.297760993</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22332,17 +22333,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="246" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.16129032258064516</v>
+        <v>0.19354838709677419</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22385,19 +22386,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>694388365.18861198</v>
+        <v>882266716.53236008</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.10152946406789808</v>
+        <v>0.12899995360686053</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>6144890966.811388</v>
+        <v>5957012615.4676399</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>125405938.09819159</v>
+        <v>124104429.48890917</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22414,19 +22415,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>145780602.119856</v>
+        <v>241230892.574049</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>9.8816564813640956E-2</v>
+        <v>0.16351700970131455</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1329484222.1005058</v>
+        <v>1234033931.6463127</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>27132331.063275628</v>
+        <v>25709040.242631514</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22443,19 +22444,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>147692189.900262</v>
+        <v>195948024.227386</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>8.2834521781769824E-2</v>
+        <v>0.10989924986500166</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1635286533.503994</v>
+        <v>1587030699.1768699</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>33373194.561306</v>
+        <v>33063139.566184789</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22470,19 +22471,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>987861157.20872998</v>
+        <v>1319445633.3337951</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>9.7832029596297818E-2</v>
+        <v>0.13067022962594627</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>9109661722.4158878</v>
+        <v>8778077246.290823</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>185911463.72277322</v>
+        <v>182876609.29772547</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22503,10 +22504,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22533,7 +22534,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22568,7 +22569,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22591,35 +22592,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>25781529.671627</v>
+        <v>32709858.660574999</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>5633788.5984819997</v>
+        <v>9597998.5084819999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>31415318.270108998</v>
+        <v>42307857.169056997</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>6.4780012319099342E-2</v>
+        <v>8.7240991322819997E-2</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>390901948.32837301</v>
+        <v>383973619.33942503</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>62636612.622172311</v>
+        <v>58672402.712172307</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>453538560.95054531</v>
+        <v>442646022.0515973</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>9255888.9989907201</v>
+        <v>9221792.1260749437</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22643,35 +22644,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>59564857.203666002</v>
+        <v>81423428.073637992</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>15407258.180297999</v>
+        <v>17193208.630292002</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>74972115.383964002</v>
+        <v>98616636.703929991</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.10040068059745706</v>
+        <v>0.13206480026071835</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>495617513.79633403</v>
+        <v>473758942.92636204</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>176139525.819702</v>
+        <v>174353575.369708</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>671757039.61603594</v>
+        <v>648112518.29606998</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>13709327.339102775</v>
+        <v>13502344.131168125</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22695,7 +22696,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>26538800</v>
+        <v>32194810</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22703,15 +22704,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>26538800</v>
+        <v>32194810</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.1099036767912546</v>
+        <v>0.1333266007730512</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>214934468</v>
+        <v>209278458</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22719,11 +22720,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>214934468</v>
+        <v>209278458</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>4386417.7142857146</v>
+        <v>4359967.875</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22747,35 +22748,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>68059225.285199001</v>
+        <v>93242063.585198998</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>9412519.1139570009</v>
+        <v>9773879.4739570003</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>77471744.399156004</v>
+        <v>103015943.059156</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.11781085167326844</v>
+        <v>0.15665577278335185</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>542653246.71480095</v>
+        <v>517470408.414801</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>37469307.703377888</v>
+        <v>37107947.343377888</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>580122554.41817892</v>
+        <v>554578355.75817895</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>11839235.804452632</v>
+        <v>11553715.744962061</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22827,7 +22828,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>9509196.2765617184</v>
+        <v>9707304.53232342</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22851,35 +22852,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>29647735.587652002</v>
+        <v>48103144.068025999</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>17914974.499876998</v>
+        <v>18718384.409876999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>47562710.087529004</v>
+        <v>66821528.477902994</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>8.5674151709355661E-2</v>
+        <v>0.12036483534540982</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>444271096.41234797</v>
+        <v>425815687.93197399</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>63324419.622776605</v>
+        <v>62521009.712776601</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>507595516.0351246</v>
+        <v>488336697.6447506</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>10359092.163982134</v>
+        <v>10173681.200932303</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22903,35 +22904,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>89694325.230609998</v>
+        <v>117065779.879189</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>11919388.989965999</v>
+        <v>14545481.789966</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>101613714.220576</v>
+        <v>131611261.669155</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>9.643634381589615E-2</v>
+        <v>0.12490547144866052</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>872064019.76938999</v>
+        <v>844692565.12081099</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>80009187.349190384</v>
+        <v>77383094.549190387</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>952073207.11858034</v>
+        <v>922075659.67000139</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>19430065.451399598</v>
+        <v>19209909.576458361</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22955,35 +22956,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>61972743.358419999</v>
+        <v>78677946.036803007</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>19809837.809866</v>
+        <v>20233135.109866001</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>81782581.168285996</v>
+        <v>98911081.146669</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.14371307933169722</v>
+        <v>0.17381226966124988</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>443314315.64157999</v>
+        <v>426609112.96319699</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>43971566.190134004</v>
+        <v>43548268.890133999</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>487285881.83171403</v>
+        <v>470157381.85333097</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>9944609.8333002869</v>
+        <v>9794945.4552777279</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23007,7 +23008,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>34696242</v>
+        <v>38412458.249975003</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23015,15 +23016,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>34696242</v>
+        <v>38412458.249975003</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>8.5853382409637621E-2</v>
+        <v>9.5048895134791353E-2</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>369437422</v>
+        <v>365721205.75002497</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23031,11 +23032,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>369437422</v>
+        <v>365721205.75002497</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>7539539.224489796</v>
+        <v>7619191.7864588536</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23059,35 +23060,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>70050112.890311003</v>
+        <v>78951925.710300997</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>9373502.6594130006</v>
+        <v>14526745.840333</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>79423615.549723998</v>
+        <v>93478671.550633997</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.14640791691999133</v>
+        <v>0.17231672826085465</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>333967196.109689</v>
+        <v>325065383.28969902</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>129090887.55858241</v>
+        <v>123937644.37766241</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>463058083.66827142</v>
+        <v>449003027.66736138</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>9450164.9728218652</v>
+        <v>9354229.7430700287</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23111,35 +23112,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>50253462.618390001</v>
+        <v>68670310.1743</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>11618043.239971999</v>
+        <v>14865583.799972</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>61871505.858362004</v>
+        <v>83535893.974271998</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>8.9620636205739637E-2</v>
+        <v>0.12100141834478488</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>581376133.38161004</v>
+        <v>562959285.82570004</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>47123557.370653272</v>
+        <v>43876016.810653269</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>628499690.75226331</v>
+        <v>606835302.63635325</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>12826524.301066598</v>
+        <v>12642402.13825736</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23163,35 +23164,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>37405669.322714999</v>
+        <v>47271367.069149002</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>2839684.290397</v>
+        <v>3968008.6203959999</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>40245353.613112003</v>
+        <v>51239375.689545006</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>8.9373111505238467E-2</v>
+        <v>0.11378760591802894</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>349137353.67728502</v>
+        <v>339271655.93085098</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>60924470.509416804</v>
+        <v>59796146.179417804</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>410061824.18670177</v>
+        <v>399067802.11026883</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>8368608.656871465</v>
+        <v>8313912.5439639343</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23215,35 +23216,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>90105944.180085003</v>
+        <v>106086123.63008501</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>16853837.639756002</v>
+        <v>84961944.838635996</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>106959781.819841</v>
+        <v>191048068.468721</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.11713175053668898</v>
+        <v>0.20921690672562154</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>493244997.819915</v>
+        <v>477264818.36991501</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>312953107.35296136</v>
+        <v>244845000.1540814</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>806198105.17287636</v>
+        <v>722109818.52399635</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>16453022.554548496</v>
+        <v>15043954.552583257</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23267,35 +23268,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>29230330.799936999</v>
+        <v>38070114.355120003</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>24403172.497872002</v>
+        <v>32251926.952272002</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>53633503.297809005</v>
+        <v>70322041.307392001</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.10364047687914255</v>
+        <v>0.13588912616324655</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>230295358.20006299</v>
+        <v>221455574.64488</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>233566859.41001439</v>
+        <v>225718104.95561439</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>463862217.61007738</v>
+        <v>447173679.60049438</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>9466575.8695934154</v>
+        <v>9316118.3250102997</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23317,35 +23318,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>694388365.18861198</v>
+        <v>882266716.53236008</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>145780602.119856</v>
+        <v>241230892.574049</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>840168967.30846798</v>
+        <v>1123497609.1064091</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.10104810937589551</v>
+        <v>0.13512437819767742</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>6144890966.811388</v>
+        <v>5957012615.4676399</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1329484222.1005056</v>
+        <v>1234033931.6463125</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>7474375188.9118938</v>
+        <v>7191046547.1139526</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>152538269.16146722</v>
+        <v>149813469.73154068</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23386,8 +23387,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="204">
-        <f>IF(E24="",0,E24)</f>
-        <v>3409008.94</v>
+        <v>8219819.6200000001</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23398,8 +23398,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="204">
-        <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>2252252.2000000002</v>
+        <v>7495495.4000000004</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23410,8 +23409,7 @@
         <v>177</v>
       </c>
       <c r="D72" s="204">
-        <f>IF(E22="",0,E22)</f>
-        <v>0</v>
+        <v>4036035.92</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23422,8 +23420,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="204">
-        <f>IF(E14="",0,E14)</f>
-        <v>10646846.74</v>
+        <v>13097297.140000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23457,8 +23454,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="204">
-        <f>IF(E19="",0,E19)</f>
-        <v>202760383.15997201</v>
+        <v>229879300.729956</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23469,7 +23465,6 @@
         <v>79</v>
       </c>
       <c r="D77" s="204">
-        <f>IF(E25="",0,E25)</f>
         <v>10536035.92</v>
       </c>
     </row>
@@ -23481,7 +23476,6 @@
         <v>178</v>
       </c>
       <c r="D78" s="204">
-        <f>IF(E23="",0,E23)</f>
         <v>1441441.4</v>
       </c>
     </row>
@@ -23505,8 +23499,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="204">
-        <f>IF(E26="",0,E26)</f>
-        <v>33927927.649999999</v>
+        <v>40603603.649999999</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23517,8 +23510,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="204">
-        <f>IF(E10="",0,E10)</f>
-        <v>34372071.079999998</v>
+        <v>39231530.520000003</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23529,8 +23521,7 @@
         <v>87</v>
       </c>
       <c r="D82" s="204">
-        <f>0</f>
-        <v>0</v>
+        <v>4259459.54</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23551,7 +23542,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>315797318.68997198</v>
+        <v>375251371.43995595</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23565,13 +23556,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23613,19 +23604,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>65522982.685794003</v>
+        <v>87095406.395739004</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.2356394106508222</v>
+        <v>0.31322002436765434</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>212541635.21841556</v>
+        <v>190969211.50847054</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>4337584.3922125623</v>
+        <v>3978525.2397598028</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23642,19 +23633,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>9055162.4139740001</v>
+        <v>13891811.213934001</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>2.1682854712466951E-2</v>
+        <v>3.3264353578011371E-2</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>408563390.7725476</v>
+        <v>403726741.97258759</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>8338028.3831132166</v>
+        <v>8410973.7910955753</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23671,19 +23662,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>73114044.800494</v>
+        <v>94960806.617712989</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>6.7243947282708424E-2</v>
+        <v>8.7336701061323546E-2</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>1014181507.5130308</v>
+        <v>992334745.69581175</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>20697581.785980221</v>
+        <v>20673640.535329413</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23756,24 +23747,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>147692189.900262</v>
+        <v>195948024.227386</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>8.2834521781769824E-2</v>
+        <v>0.10989924986500166</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1635286533.503994</v>
+        <v>1587030699.1768699</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>33373194.561306</v>
+        <v>33063139.566184789</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23781,11 +23777,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23854,7 +23845,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -24558,10 +24549,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24588,7 +24579,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24623,7 +24614,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25622,13 +25613,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25831,6 +25822,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25838,11 +25834,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25911,7 +25902,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -26615,10 +26606,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="K48" s="242"/>
+      <c r="L48" s="243"/>
+      <c r="M48" s="243"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26645,7 +26636,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="245" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26680,7 +26671,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="245"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27679,13 +27670,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="240"/>
+      <c r="D87" s="240"/>
+      <c r="E87" s="240"/>
+      <c r="F87" s="241"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27888,6 +27879,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27895,11 +27891,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -601,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 06 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 07 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1929,6 +1930,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1948,15 +1958,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2897,15 +2898,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),4),11)</f>
-        <v>127</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),8,1)),EOMONTH(DATE(YEAR(TODAY()),8,1),0),11))</f>
+        <v>26</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),4))</f>
-        <v>30</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),8,1),0))</f>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -3602,10 +3603,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -3632,7 +3633,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3667,7 +3668,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4666,13 +4667,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4875,11 +4876,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4887,6 +4883,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -4954,15 +4955,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),5),11)</f>
-        <v>154</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11))</f>
+        <v>26</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),5))</f>
-        <v>31</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),9,1),0))</f>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -5659,10 +5660,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -5689,7 +5690,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5724,7 +5725,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6723,13 +6724,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6932,11 +6933,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6944,6 +6940,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7011,15 +7012,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),6),11)</f>
-        <v>179</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),10,1)),EOMONTH(DATE(YEAR(TODAY()),10,1),0),11))</f>
+        <v>27</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),6))</f>
-        <v>30</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),10,1),0))</f>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -7716,10 +7717,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -7746,7 +7747,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7781,7 +7782,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8780,13 +8781,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8989,11 +8990,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -9001,6 +8997,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9068,15 +9069,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),7),11)</f>
-        <v>206</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),11,1)),EOMONTH(DATE(YEAR(TODAY()),11,1),0),11))</f>
+        <v>25</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),7))</f>
-        <v>31</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),11,1),0))</f>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -9773,10 +9774,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -9803,7 +9804,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9838,7 +9839,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10837,13 +10838,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11046,11 +11047,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11058,6 +11054,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11125,14 +11126,14 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),8),11)</f>
-        <v>232</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),12,1)),EOMONTH(DATE(YEAR(TODAY()),12,1),0),11))</f>
+        <v>27</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),8))</f>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),12,1),0))</f>
         <v>31</v>
       </c>
       <c r="G3" s="116"/>
@@ -11829,10 +11830,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -11859,7 +11860,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11894,7 +11895,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12879,13 +12880,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13088,11 +13089,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13100,6 +13096,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13130,8 +13131,7 @@
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -14712,13 +14712,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),1,1)),EOMONTH(DATE(YEAR(TODAY()),1,1),0),11))</f>
         <v>0</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <v>30</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),1,1),0))</f>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
@@ -15127,7 +15129,7 @@
         <v>7715107456</v>
       </c>
       <c r="H41" s="42">
-        <f>IFERROR(G41/C3,0)</f>
+        <f ca="1">IFERROR(G41/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15155,7 +15157,7 @@
         <v>1276773007</v>
       </c>
       <c r="H42" s="42">
-        <f>IFERROR(G42/C3,0)</f>
+        <f ca="1">IFERROR(G42/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15183,7 +15185,7 @@
         <v>1667021276</v>
       </c>
       <c r="H43" s="42">
-        <f>IFERROR(G43/C3,0)</f>
+        <f ca="1">IFERROR(G43/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15209,7 +15211,7 @@
         <v>10658901739</v>
       </c>
       <c r="H44" s="65">
-        <f>IFERROR(G44/C3,0)</f>
+        <f ca="1">IFERROR(G44/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15340,7 +15342,7 @@
         <v>392047577</v>
       </c>
       <c r="N49" s="26">
-        <f>IFERROR(M49/C3,0)</f>
+        <f ca="1">IFERROR(M49/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15392,7 +15394,7 @@
         <v>1232863608</v>
       </c>
       <c r="N50" s="28">
-        <f>IFERROR(M50/C3,0)</f>
+        <f ca="1">IFERROR(M50/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15444,7 +15446,7 @@
         <v>520034697</v>
       </c>
       <c r="N51" s="26">
-        <f>IFERROR(M51/C3,0)</f>
+        <f ca="1">IFERROR(M51/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15496,7 +15498,7 @@
         <v>549321255</v>
       </c>
       <c r="N52" s="28">
-        <f>IFERROR(M52/C3,0)</f>
+        <f ca="1">IFERROR(M52/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15548,7 +15550,7 @@
         <v>591552008</v>
       </c>
       <c r="N53" s="26">
-        <f>IFERROR(M53/C3,0)</f>
+        <f ca="1">IFERROR(M53/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15600,7 +15602,7 @@
         <v>993303944</v>
       </c>
       <c r="N54" s="28">
-        <f>IFERROR(M54/C3,0)</f>
+        <f ca="1">IFERROR(M54/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15652,7 +15654,7 @@
         <v>1033670335</v>
       </c>
       <c r="N55" s="26">
-        <f>IFERROR(M55/C3,0)</f>
+        <f ca="1">IFERROR(M55/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15704,7 +15706,7 @@
         <v>600197669</v>
       </c>
       <c r="N56" s="28">
-        <f>IFERROR(M56/C3,0)</f>
+        <f ca="1">IFERROR(M56/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15756,7 +15758,7 @@
         <v>604625323</v>
       </c>
       <c r="N57" s="26">
-        <f>IFERROR(M57/C3,0)</f>
+        <f ca="1">IFERROR(M57/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15808,7 +15810,7 @@
         <v>410707083</v>
       </c>
       <c r="N58" s="28">
-        <f>IFERROR(M58/C3,0)</f>
+        <f ca="1">IFERROR(M58/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15860,7 +15862,7 @@
         <v>845099507</v>
       </c>
       <c r="N59" s="26">
-        <f>IFERROR(M59/C3,0)</f>
+        <f ca="1">IFERROR(M59/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15912,7 +15914,7 @@
         <v>572850525</v>
       </c>
       <c r="N60" s="28">
-        <f>IFERROR(M60/C3,0)</f>
+        <f ca="1">IFERROR(M60/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15962,7 +15964,7 @@
         <v>8346273531</v>
       </c>
       <c r="N61" s="66">
-        <f>IFERROR(M61/C3,0)</f>
+        <f ca="1">IFERROR(M61/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16024,7 +16026,7 @@
         <v>333545989</v>
       </c>
       <c r="H65" s="26">
-        <f>IFERROR(G65/C3,0)</f>
+        <f ca="1">IFERROR(G65/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16052,7 +16054,7 @@
         <v>439764978</v>
       </c>
       <c r="H66" s="28">
-        <f>IFERROR(G66/C3,0)</f>
+        <f ca="1">IFERROR(G66/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16080,7 +16082,7 @@
         <v>403437384</v>
       </c>
       <c r="H67" s="26">
-        <f>IFERROR(G67/C3,0)</f>
+        <f ca="1">IFERROR(G67/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16108,7 +16110,7 @@
         <v>490272925</v>
       </c>
       <c r="H68" s="28">
-        <f>IFERROR(G68/C3,0)</f>
+        <f ca="1">IFERROR(G68/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16136,7 +16138,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="26">
-        <f>IFERROR(G69/C3,0)</f>
+        <f ca="1">IFERROR(G69/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16162,7 +16164,7 @@
         <v>1667021276</v>
       </c>
       <c r="H70" s="32">
-        <f>IFERROR(G70/C3,0)</f>
+        <f ca="1">IFERROR(G70/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16245,13 +16247,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),2,1)),EOMONTH(DATE(YEAR(TODAY()),2,1),0),11))</f>
         <v>0</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <v>30</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),2,1),0))</f>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
@@ -16660,7 +16664,7 @@
         <v>6785121897</v>
       </c>
       <c r="H41" s="42">
-        <f>IFERROR(G41/C3,0)</f>
+        <f ca="1">IFERROR(G41/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16688,7 +16692,7 @@
         <v>1174575386</v>
       </c>
       <c r="H42" s="42">
-        <f>IFERROR(G42/C3,0)</f>
+        <f ca="1">IFERROR(G42/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16716,7 +16720,7 @@
         <v>1816737288</v>
       </c>
       <c r="H43" s="42">
-        <f>IFERROR(G43/C3,0)</f>
+        <f ca="1">IFERROR(G43/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16742,7 +16746,7 @@
         <v>9776434571</v>
       </c>
       <c r="H44" s="65">
-        <f>IFERROR(G44/C3,0)</f>
+        <f ca="1">IFERROR(G44/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16873,7 +16877,7 @@
         <v>364434988</v>
       </c>
       <c r="N49" s="26">
-        <f>IFERROR(M49/C3,0)</f>
+        <f ca="1">IFERROR(M49/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16925,7 +16929,7 @@
         <v>1177638430</v>
       </c>
       <c r="N50" s="28">
-        <f>IFERROR(M50/C3,0)</f>
+        <f ca="1">IFERROR(M50/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16977,7 +16981,7 @@
         <v>492422108</v>
       </c>
       <c r="N51" s="26">
-        <f>IFERROR(M51/C3,0)</f>
+        <f ca="1">IFERROR(M51/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17029,7 +17033,7 @@
         <v>521708666</v>
       </c>
       <c r="N52" s="28">
-        <f>IFERROR(M52/C3,0)</f>
+        <f ca="1">IFERROR(M52/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17081,7 +17085,7 @@
         <v>563939419</v>
       </c>
       <c r="N53" s="26">
-        <f>IFERROR(M53/C3,0)</f>
+        <f ca="1">IFERROR(M53/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17133,7 +17137,7 @@
         <v>965691355</v>
       </c>
       <c r="N54" s="28">
-        <f>IFERROR(M54/C3,0)</f>
+        <f ca="1">IFERROR(M54/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17185,7 +17189,7 @@
         <v>1006057745</v>
       </c>
       <c r="N55" s="26">
-        <f>IFERROR(M55/C3,0)</f>
+        <f ca="1">IFERROR(M55/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17237,7 +17241,7 @@
         <v>572585080</v>
       </c>
       <c r="N56" s="28">
-        <f>IFERROR(M56/C3,0)</f>
+        <f ca="1">IFERROR(M56/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17289,7 +17293,7 @@
         <v>577012733</v>
       </c>
       <c r="N57" s="26">
-        <f>IFERROR(M57/C3,0)</f>
+        <f ca="1">IFERROR(M57/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17341,7 +17345,7 @@
         <v>383094494</v>
       </c>
       <c r="N58" s="28">
-        <f>IFERROR(M58/C3,0)</f>
+        <f ca="1">IFERROR(M58/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17393,7 +17397,7 @@
         <v>817486918</v>
       </c>
       <c r="N59" s="26">
-        <f>IFERROR(M59/C3,0)</f>
+        <f ca="1">IFERROR(M59/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17445,7 +17449,7 @@
         <v>517625347</v>
       </c>
       <c r="N60" s="28">
-        <f>IFERROR(M60/C3,0)</f>
+        <f ca="1">IFERROR(M60/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17495,7 +17499,7 @@
         <v>7959697283</v>
       </c>
       <c r="N61" s="66">
-        <f>IFERROR(M61/C3,0)</f>
+        <f ca="1">IFERROR(M61/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17557,7 +17561,7 @@
         <v>332600635</v>
       </c>
       <c r="H65" s="26">
-        <f>IFERROR(G65/C3,0)</f>
+        <f ca="1">IFERROR(G65/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17585,7 +17589,7 @@
         <v>467649702</v>
       </c>
       <c r="H66" s="28">
-        <f>IFERROR(G66/C3,0)</f>
+        <f ca="1">IFERROR(G66/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17613,7 +17617,7 @@
         <v>1016486951</v>
       </c>
       <c r="H67" s="26">
-        <f>IFERROR(G67/C3,0)</f>
+        <f ca="1">IFERROR(G67/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17641,7 +17645,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="28">
-        <f>IFERROR(G68/C3,0)</f>
+        <f ca="1">IFERROR(G68/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17669,7 +17673,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="26">
-        <f>IFERROR(G69/C3,0)</f>
+        <f ca="1">IFERROR(G69/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17695,7 +17699,7 @@
         <v>1816737288</v>
       </c>
       <c r="H70" s="32">
-        <f>IFERROR(G70/C3,0)</f>
+        <f ca="1">IFERROR(G70/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17781,12 +17785,14 @@
         <v>103</v>
       </c>
       <c r="C3" s="8">
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),3,1)),EOMONTH(DATE(YEAR(TODAY()),3,1),0),11))</f>
         <v>0</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="9">
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),3,1),0))</f>
         <v>31</v>
       </c>
     </row>
@@ -18327,7 +18333,7 @@
         <v>2160198393.6843271</v>
       </c>
       <c r="H41" s="42">
-        <f>IFERROR(G41/C3,0)</f>
+        <f ca="1">IFERROR(G41/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I41" s="24"/>
@@ -18361,7 +18367,7 @@
         <v>419268186.81712699</v>
       </c>
       <c r="H42" s="42">
-        <f>IFERROR(G42/C3,0)</f>
+        <f ca="1">IFERROR(G42/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I42" s="24"/>
@@ -18395,7 +18401,7 @@
         <v>597508817.9278388</v>
       </c>
       <c r="H43" s="42">
-        <f>IFERROR(G43/C3,0)</f>
+        <f ca="1">IFERROR(G43/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I43" s="24"/>
@@ -18427,7 +18433,7 @@
         <v>3176975398.4292932</v>
       </c>
       <c r="H44" s="65">
-        <f>IFERROR(G44/C3,0)</f>
+        <f ca="1">IFERROR(G44/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I44" s="24"/>
@@ -18583,7 +18589,7 @@
         <v>77615907.003009021</v>
       </c>
       <c r="N49" s="26">
-        <f>IFERROR(M49/C3,0)</f>
+        <f ca="1">IFERROR(M49/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18635,7 +18641,7 @@
         <v>684335423.10337496</v>
       </c>
       <c r="N50" s="28">
-        <f>IFERROR(M50/C3,0)</f>
+        <f ca="1">IFERROR(M50/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18687,7 +18693,7 @@
         <v>20662365.196989</v>
       </c>
       <c r="N51" s="26">
-        <f>IFERROR(M51/C3,0)</f>
+        <f ca="1">IFERROR(M51/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18739,7 +18745,7 @@
         <v>185160790.04000199</v>
       </c>
       <c r="N52" s="28">
-        <f>IFERROR(M52/C3,0)</f>
+        <f ca="1">IFERROR(M52/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18791,7 +18797,7 @@
         <v>169846907.78680599</v>
       </c>
       <c r="N53" s="26">
-        <f>IFERROR(M53/C3,0)</f>
+        <f ca="1">IFERROR(M53/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18843,7 +18849,7 @@
         <v>176949096.18189609</v>
       </c>
       <c r="N54" s="28">
-        <f>IFERROR(M54/C3,0)</f>
+        <f ca="1">IFERROR(M54/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18895,7 +18901,7 @@
         <v>492166660.31492698</v>
       </c>
       <c r="N55" s="26">
-        <f>IFERROR(M55/C3,0)</f>
+        <f ca="1">IFERROR(M55/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18947,7 +18953,7 @@
         <v>232272626.848355</v>
       </c>
       <c r="N56" s="28">
-        <f>IFERROR(M56/C3,0)</f>
+        <f ca="1">IFERROR(M56/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18999,7 +19005,7 @@
         <v>140717151.254839</v>
       </c>
       <c r="N57" s="26">
-        <f>IFERROR(M57/C3,0)</f>
+        <f ca="1">IFERROR(M57/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19051,7 +19057,7 @@
         <v>116836803.45176297</v>
       </c>
       <c r="N58" s="28">
-        <f>IFERROR(M58/C3,0)</f>
+        <f ca="1">IFERROR(M58/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19103,7 +19109,7 @@
         <v>92269289.556923032</v>
       </c>
       <c r="N59" s="26">
-        <f>IFERROR(M59/C3,0)</f>
+        <f ca="1">IFERROR(M59/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19155,7 +19161,7 @@
         <v>190633559.76257002</v>
       </c>
       <c r="N60" s="28">
-        <f>IFERROR(M60/C3,0)</f>
+        <f ca="1">IFERROR(M60/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19205,7 +19211,7 @@
         <v>2579466580.5014544</v>
       </c>
       <c r="N61" s="66">
-        <f>IFERROR(M61/C3,0)</f>
+        <f ca="1">IFERROR(M61/C3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19294,7 +19300,7 @@
         <v>149659577.66111699</v>
       </c>
       <c r="H65" s="26">
-        <f>IFERROR(G65/C3,0)</f>
+        <f ca="1">IFERROR(G65/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I65" s="24"/>
@@ -19328,7 +19334,7 @@
         <v>145600270.063281</v>
       </c>
       <c r="H66" s="28">
-        <f>IFERROR(G66/C3,0)</f>
+        <f ca="1">IFERROR(G66/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I66" s="24"/>
@@ -19362,7 +19368,7 @@
         <v>302248970.20344102</v>
       </c>
       <c r="H67" s="26">
-        <f>IFERROR(G67/C3,0)</f>
+        <f ca="1">IFERROR(G67/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I67" s="24"/>
@@ -19396,7 +19402,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="28">
-        <f>IFERROR(G68/C3,0)</f>
+        <f ca="1">IFERROR(G68/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I68" s="24"/>
@@ -19430,7 +19436,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="26">
-        <f>IFERROR(G69/C3,0)</f>
+        <f ca="1">IFERROR(G69/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I69" s="24"/>
@@ -19462,7 +19468,7 @@
         <v>597508817.92783904</v>
       </c>
       <c r="H70" s="32">
-        <f>IFERROR(G70/C3,0)</f>
+        <f ca="1">IFERROR(G70/C3,0)</f>
         <v>0</v>
       </c>
       <c r="I70" s="24"/>
@@ -19557,13 +19563,14 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>22</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),4,1)),EOMONTH(DATE(YEAR(TODAY()),4,1),0),11))</f>
+        <v>0</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),4,1),0))</f>
         <v>30</v>
       </c>
     </row>
@@ -20163,8 +20170,7 @@
         <v>138</v>
       </c>
       <c r="F41" s="73">
-        <f ca="1">DAY(TODAY())/DAY(EOMONTH(TODAY(),0))</f>
-        <v>0.19354838709677419</v>
+        <v>1</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -20217,7 +20223,7 @@
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>45560199.321416683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20245,7 +20251,7 @@
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>13333089.021218864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20273,7 +20279,7 @@
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>9281251.6611761618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20299,7 +20305,7 @@
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>68174540.003811702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20430,7 +20436,7 @@
       </c>
       <c r="N51" s="164">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>4596659.6988119427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20482,7 +20488,7 @@
       </c>
       <c r="N52" s="165">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>4369521.0890863156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20534,7 +20540,7 @@
       </c>
       <c r="N53" s="165">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9208588.1545454543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20586,7 +20592,7 @@
       </c>
       <c r="N54" s="165">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>2714072.2890579645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20638,7 +20644,7 @@
       </c>
       <c r="N55" s="165">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>3104907.1705241445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20690,7 +20696,7 @@
       </c>
       <c r="N56" s="165">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>1164962.5776151635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20742,7 +20748,7 @@
       </c>
       <c r="N57" s="165">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>-3427667.4398785126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20794,7 +20800,7 @@
       </c>
       <c r="N58" s="165">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>4061238.5852035908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20846,7 +20852,7 @@
       </c>
       <c r="N59" s="165">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>12890144.149090908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20898,7 +20904,7 @@
       </c>
       <c r="N60" s="165">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>3634323.3749203058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20950,7 +20956,7 @@
       </c>
       <c r="N61" s="165">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>5034917.1446279343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21002,7 +21008,7 @@
       </c>
       <c r="N62" s="165">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>3628255.2509607347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21054,7 +21060,7 @@
       </c>
       <c r="N63" s="165">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>484688.15084553306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21106,7 +21112,7 @@
       </c>
       <c r="N64" s="165">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>7428678.1472240333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21156,7 +21162,7 @@
       </c>
       <c r="N65" s="166">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>58893288.342635505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21431,7 +21437,7 @@
       </c>
       <c r="H89" s="171">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>1779740.8026541905</v>
+        <v>0</v>
       </c>
       <c r="I89" s="168"/>
     </row>
@@ -21460,7 +21466,7 @@
       </c>
       <c r="H90" s="172">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>-1378262.9434728243</v>
+        <v>0</v>
       </c>
       <c r="I90" s="168"/>
     </row>
@@ -21489,7 +21495,7 @@
       </c>
       <c r="H91" s="171">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>8879773.8019947894</v>
+        <v>0</v>
       </c>
       <c r="I91" s="168"/>
     </row>
@@ -21574,7 +21580,7 @@
       </c>
       <c r="H94" s="173">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>9281251.6611761563</v>
+        <v>0</v>
       </c>
       <c r="I94" s="168"/>
     </row>
@@ -21622,12 +21628,11 @@
     <col min="6" max="6" width="15.140625" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
   </cols>
@@ -21659,15 +21664,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),1),11)</f>
-        <v>48</v>
+        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
+        <v>21</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),1))</f>
-        <v>30</v>
+        <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
+        <v>31</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -21742,11 +21747,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>32709858.660574999</v>
+        <v>42873985.280547</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>9597998.5084819999</v>
+        <v>14041957.978482001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21764,11 +21769,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>81423428.073637992</v>
+        <v>99060006.837617993</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>17193208.630292002</v>
+        <v>18273402.330292001</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21776,27 +21781,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="206">
-        <v>47271367.069149002</v>
+        <v>54174339.979146004</v>
       </c>
       <c r="D10" s="206">
-        <v>3968008.6203959999</v>
+        <v>5380116.9003720004</v>
       </c>
       <c r="E10" s="206">
-        <v>39231530.520000003</v>
+        <v>40139638.439999998</v>
       </c>
       <c r="F10" s="206">
-        <v>90470906.209545001</v>
+        <v>99694095.319518</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>93242063.585198998</v>
+        <v>117467040.76519699</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>9773879.4739570003</v>
+        <v>10240095.673957</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21804,16 +21809,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="206">
-        <v>78951925.710300997</v>
+        <v>86706793.804280996</v>
       </c>
       <c r="D11" s="206">
-        <v>14526745.840333</v>
-      </c>
-      <c r="E11" s="206" t="s">
-        <v>169</v>
+        <v>23834171.600310002</v>
+      </c>
+      <c r="E11" s="206">
+        <v>2972973</v>
       </c>
       <c r="F11" s="206">
-        <v>93478671.550633997</v>
+        <v>113513938.40459099</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21832,27 +21837,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="206">
-        <v>34317464.039976001</v>
+        <v>46067556.383975998</v>
       </c>
       <c r="D12" s="206">
-        <v>11865672.590298001</v>
+        <v>12945866.290298</v>
       </c>
       <c r="E12" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F12" s="206">
-        <v>46183136.630273998</v>
+        <v>59013422.674273998</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>48103144.068025999</v>
+        <v>56191655.338026002</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>18718384.409876999</v>
+        <v>19878088.459867999</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21860,27 +21865,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="206">
-        <v>47105964.033661999</v>
+        <v>52992450.453642003</v>
       </c>
       <c r="D13" s="206">
         <v>5327536.0399940005</v>
       </c>
       <c r="E13" s="206">
-        <v>7495495.4000000004</v>
+        <v>9592792.6799999997</v>
       </c>
       <c r="F13" s="206">
-        <v>59928995.473655999</v>
+        <v>67912779.173636004</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>117065779.879189</v>
+        <v>152304041.79159999</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>14545481.789966</v>
+        <v>17140076.309966002</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21888,27 +21893,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="206">
-        <v>93242063.585198998</v>
+        <v>117467040.76519699</v>
       </c>
       <c r="D14" s="206">
-        <v>9773879.4739570003</v>
+        <v>10240095.673957</v>
       </c>
       <c r="E14" s="206">
-        <v>13097297.140000001</v>
+        <v>15773873.699999999</v>
       </c>
       <c r="F14" s="206">
-        <v>116113240.199156</v>
+        <v>143481010.13915399</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>78677946.036803007</v>
+        <v>98086123.531784996</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>20233135.109866001</v>
+        <v>20422324.289864</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21924,11 +21929,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>78951925.710300997</v>
+        <v>86706793.804280996</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>14526745.840333</v>
+        <v>23834171.600310002</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21936,27 +21941,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="206">
-        <v>48103144.068025999</v>
+        <v>56191655.338026002</v>
       </c>
       <c r="D16" s="206">
-        <v>18718384.409876999</v>
+        <v>19878088.459867999</v>
       </c>
       <c r="E16" s="206">
-        <v>3932432.4</v>
+        <v>7175675.5999999996</v>
       </c>
       <c r="F16" s="206">
-        <v>70753960.877903</v>
+        <v>83245419.397893995</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>68670310.1743</v>
+        <v>79658589.395199001</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>14865583.799972</v>
+        <v>16881583.799972001</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21980,11 +21985,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>47271367.069149002</v>
+        <v>54174339.979146004</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>3968008.6203959999</v>
+        <v>5380116.9003720004</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21992,27 +21997,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="206">
-        <v>380995257.12396801</v>
+        <v>391192036.163966</v>
       </c>
       <c r="D18" s="206">
-        <v>1368617.12</v>
+        <v>3422346.9499789998</v>
       </c>
       <c r="E18" s="206">
-        <v>972972.96</v>
+        <v>1135135.1200000001</v>
       </c>
       <c r="F18" s="206">
-        <v>383336847.20396799</v>
+        <v>395749518.23394501</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>106086123.63008501</v>
+        <v>169536385.769223</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>84961944.838635996</v>
+        <v>85651530.428636</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22020,27 +22025,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="206">
-        <v>117065779.879189</v>
+        <v>152304041.79159999</v>
       </c>
       <c r="D19" s="206">
-        <v>14545481.789966</v>
+        <v>17140076.309966002</v>
       </c>
       <c r="E19" s="206">
-        <v>229879300.729956</v>
+        <v>235554977.329956</v>
       </c>
       <c r="F19" s="206">
-        <v>361490562.39911097</v>
+        <v>404999095.43152201</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>38070114.355120003</v>
+        <v>40531555.855117999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>32251926.952272002</v>
+        <v>38541853.192187995</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22048,16 +22053,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="206">
-        <v>28613114.355119999</v>
+        <v>30864555.855117999</v>
       </c>
       <c r="D20" s="206">
-        <v>8237791.0899999999</v>
+        <v>13102655.88992</v>
       </c>
       <c r="E20" s="206" t="s">
         <v>169</v>
       </c>
       <c r="F20" s="206">
-        <v>36850905.445119999</v>
+        <v>43967211.745038003</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22075,23 +22080,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="206">
-        <v>9457000</v>
+        <v>9667000</v>
       </c>
       <c r="D21" s="206">
-        <v>24014135.862272002</v>
+        <v>25439197.302267998</v>
       </c>
       <c r="E21" s="206">
-        <v>12518919.199999999</v>
+        <v>21881081.52</v>
       </c>
       <c r="F21" s="206">
-        <v>45990055.062271997</v>
+        <v>56987278.822268002</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>94960806.617712989</v>
+        <v>123951644.45549099</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22122,7 +22127,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="206">
-        <v>38412458.249975003</v>
+        <v>68042438.249974996</v>
       </c>
       <c r="D23" s="206" t="s">
         <v>169</v>
@@ -22131,7 +22136,7 @@
         <v>1441441.4</v>
       </c>
       <c r="F23" s="206">
-        <v>39853899.649975002</v>
+        <v>69483879.649975002</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22142,16 +22147,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="206">
-        <v>32709858.660574999</v>
+        <v>42873985.280547</v>
       </c>
       <c r="D24" s="206">
-        <v>9597998.5084819999</v>
+        <v>14041957.978482001</v>
       </c>
       <c r="E24" s="206">
-        <v>8219819.6200000001</v>
+        <v>8419819.6199999992</v>
       </c>
       <c r="F24" s="206">
-        <v>50527676.789057001</v>
+        <v>65335762.879028998</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22162,16 +22167,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="206">
-        <v>78677946.036803007</v>
+        <v>98086123.531784996</v>
       </c>
       <c r="D25" s="206">
-        <v>20233135.109866001</v>
+        <v>20422324.289864</v>
       </c>
       <c r="E25" s="206">
-        <v>10536035.92</v>
+        <v>12157657.52</v>
       </c>
       <c r="F25" s="206">
-        <v>109447117.066669</v>
+        <v>130666105.341649</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22182,16 +22187,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="206">
-        <v>68670310.1743</v>
+        <v>79658589.395199001</v>
       </c>
       <c r="D26" s="206">
-        <v>14865583.799972</v>
+        <v>16881583.799972001</v>
       </c>
       <c r="E26" s="206">
-        <v>40603603.649999999</v>
+        <v>61576576.450000003</v>
       </c>
       <c r="F26" s="206">
-        <v>124139497.624272</v>
+        <v>158116749.64517099</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22202,16 +22207,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="206">
-        <v>106086123.63008501</v>
+        <v>169536385.769223</v>
       </c>
       <c r="D27" s="206">
-        <v>84961944.838635996</v>
+        <v>85651530.428636</v>
       </c>
       <c r="E27" s="206">
         <v>4259459.54</v>
       </c>
       <c r="F27" s="206">
-        <v>195307528.00872099</v>
+        <v>259447375.73785901</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22258,7 +22263,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="249">
-        <v>87095406.395739004</v>
+        <v>100116365.515632</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22269,7 +22274,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="206">
-        <v>13891811.213934001</v>
+        <v>42117487.793516003</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22280,7 +22285,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="206">
-        <v>83461473.297760993</v>
+        <v>112452311.135539</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22333,17 +22338,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="246" t="s">
+      <c r="B41" s="239" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="247"/>
-      <c r="D41" s="248"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="241"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.19354838709677419</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22386,19 +22391,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>882266716.53236008</v>
+        <v>1118215153.6377149</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.12899995360686053</v>
+        <v>0.16349897399361182</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5957012615.4676399</v>
+        <v>5721064178.3622856</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>124104429.48890917</v>
+        <v>272431627.54106122</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22415,19 +22420,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>241230892.574049</v>
+        <v>270879795.56390703</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.16351700970131455</v>
+        <v>0.18361435256687544</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1234033931.6463127</v>
+        <v>1204385028.6564546</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>25709040.242631514</v>
+        <v>57351668.031259738</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22444,19 +22449,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>195948024.227386</v>
+        <v>266185497.76463902</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.10989924986500166</v>
+        <v>0.14929258227849679</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1587030699.1768699</v>
+        <v>1516793225.639617</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>33063139.566184789</v>
+        <v>72228248.839981765</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22471,19 +22476,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>1319445633.3337951</v>
+        <v>1655280446.9662609</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.13067022962594627</v>
+        <v>0.1639293583881235</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>8778077246.290823</v>
+        <v>8442242432.6583567</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>182876609.29772547</v>
+        <v>402011544.41230267</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22504,10 +22509,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -22534,7 +22539,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22569,7 +22574,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22592,35 +22597,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>32709858.660574999</v>
+        <v>42873985.280547</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>9597998.5084819999</v>
+        <v>14041957.978482001</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>42307857.169056997</v>
+        <v>56915943.259029001</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>8.7240991322819997E-2</v>
+        <v>0.11736362094988462</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>383973619.33942503</v>
+        <v>373809492.71945298</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>58672402.712172307</v>
+        <v>54228443.242172308</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>442646022.0515973</v>
+        <v>428037935.96162534</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>9221792.1260749437</v>
+        <v>20382758.855315492</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22644,35 +22649,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>81423428.073637992</v>
+        <v>99060006.837617993</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>17193208.630292002</v>
+        <v>18273402.330292001</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>98616636.703929991</v>
+        <v>117333409.16790999</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.13206480026071835</v>
+        <v>0.15712980855543265</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>473758942.92636204</v>
+        <v>456122364.16238201</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>174353575.369708</v>
+        <v>173273381.66970801</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>648112518.29606998</v>
+        <v>629395745.83209002</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>13502344.131168125</v>
+        <v>29971225.992004286</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22724,7 +22729,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>4359967.875</v>
+        <v>9965640.8571428563</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22748,35 +22753,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>93242063.585198998</v>
+        <v>117467040.76519699</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>9773879.4739570003</v>
+        <v>10240095.673957</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>103015943.059156</v>
+        <v>127707136.439154</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.15665577278335185</v>
+        <v>0.19420353349904607</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>517470408.414801</v>
+        <v>493245431.23480302</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>37107947.343377888</v>
+        <v>36641731.143377893</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>554578355.75817895</v>
+        <v>529887162.37818086</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>11553715.744962061</v>
+        <v>25232722.018008612</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22828,7 +22833,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>9707304.53232342</v>
+        <v>22188124.645310674</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22852,35 +22857,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>48103144.068025999</v>
+        <v>56191655.338026002</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>18718384.409876999</v>
+        <v>19878088.459867999</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>66821528.477902994</v>
+        <v>76069743.797894001</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.12036483534540982</v>
+        <v>0.13702353710793716</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>425815687.93197399</v>
+        <v>417727176.66197401</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>62521009.712776601</v>
+        <v>61361305.662785605</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>488336697.6447506</v>
+        <v>479088482.3247596</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>10173681.200932303</v>
+        <v>22813737.253559981</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22904,35 +22909,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>117065779.879189</v>
+        <v>152304041.79159999</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>14545481.789966</v>
+        <v>17140076.309966002</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>131611261.669155</v>
+        <v>169444118.10156599</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.12490547144866052</v>
+        <v>0.16081068737781742</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>844692565.12081099</v>
+        <v>809454303.20840001</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>77383094.549190387</v>
+        <v>74788500.029190391</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>922075659.67000139</v>
+        <v>884242803.23759043</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>19209909.576458361</v>
+        <v>42106800.154170975</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22956,35 +22961,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>78677946.036803007</v>
+        <v>98086123.531784996</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>20233135.109866001</v>
+        <v>20422324.289864</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>98911081.146669</v>
+        <v>118508447.821649</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.17381226966124988</v>
+        <v>0.20824989527077167</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>426609112.96319699</v>
+        <v>407200935.46821499</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>43548268.890133999</v>
+        <v>43359079.710135996</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>470157381.85333097</v>
+        <v>450560015.17835099</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>9794945.4552777279</v>
+        <v>21455238.818016715</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23008,7 +23013,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>38412458.249975003</v>
+        <v>68042438.249974996</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23016,15 +23021,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>38412458.249975003</v>
+        <v>68042438.249974996</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>9.5048895134791353E-2</v>
+        <v>0.16836617265810105</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>365721205.75002497</v>
+        <v>336091225.75002503</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23032,11 +23037,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>365721205.75002497</v>
+        <v>336091225.75002503</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>7619191.7864588536</v>
+        <v>16004344.083334526</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23060,35 +23065,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>78951925.710300997</v>
+        <v>86706793.804280996</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>14526745.840333</v>
+        <v>23834171.600310002</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>93478671.550633997</v>
+        <v>110540965.40459099</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.17231672826085465</v>
+        <v>0.20376902218810203</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>325065383.28969902</v>
+        <v>317310515.195719</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>123937644.37766241</v>
+        <v>114630218.61768541</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>449003027.66736138</v>
+        <v>431940733.81340444</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>9354229.7430700287</v>
+        <v>20568606.372066878</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23112,35 +23117,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>68670310.1743</v>
+        <v>79658589.395199001</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>14865583.799972</v>
+        <v>16881583.799972001</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>83535893.974271998</v>
+        <v>96540173.195170999</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.12100141834478488</v>
+        <v>0.13983806634624185</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>562959285.82570004</v>
+        <v>551971006.60480094</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>43876016.810653269</v>
+        <v>41860016.810653269</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>606835302.63635325</v>
+        <v>593831023.41545427</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>12642402.13825736</v>
+        <v>28277667.781688299</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23164,35 +23169,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>47271367.069149002</v>
+        <v>54174339.979146004</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>3968008.6203959999</v>
+        <v>5380116.9003720004</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>51239375.689545006</v>
+        <v>59554456.879518002</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.11378760591802894</v>
+        <v>0.13225295934765938</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>339271655.93085098</v>
+        <v>332368683.020854</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>59796146.179417804</v>
+        <v>58384037.899441808</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>399067802.11026883</v>
+        <v>390752720.92029583</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>8313912.5439639343</v>
+        <v>18607272.424775992</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23216,35 +23221,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>106086123.63008501</v>
+        <v>169536385.769223</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>84961944.838635996</v>
+        <v>85651530.428636</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>191048068.468721</v>
+        <v>255187916.19785899</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.20921690672562154</v>
+        <v>0.27945651002179228</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>477264818.36991501</v>
+        <v>413814556.23077703</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>244845000.1540814</v>
+        <v>244155414.56408137</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>722109818.52399635</v>
+        <v>657969970.79485846</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>15043954.552583257</v>
+        <v>31331903.371183734</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23268,35 +23273,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>38070114.355120003</v>
+        <v>40531555.855117999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>32251926.952272002</v>
+        <v>38541853.192187995</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>70322041.307392001</v>
+        <v>79073409.047306001</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.13588912616324655</v>
+        <v>0.15280012153256234</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>221455574.64488</v>
+        <v>218994133.14488199</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>225718104.95561439</v>
+        <v>219428178.71569839</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>447173679.60049438</v>
+        <v>438422311.86058038</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>9316118.3250102997</v>
+        <v>20877252.945741922</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23318,35 +23323,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>882266716.53236008</v>
+        <v>1118215153.6377149</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>241230892.574049</v>
+        <v>270879795.56390703</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>1123497609.1064091</v>
+        <v>1389094949.201622</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.13512437819767742</v>
+        <v>0.16706808251928015</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5957012615.4676399</v>
+        <v>5721064178.3622847</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1234033931.6463125</v>
+        <v>1204385028.6564546</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>7191046547.1139526</v>
+        <v>6925449207.0187397</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>149813469.73154068</v>
+        <v>329783295.57232094</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23387,7 +23392,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="204">
-        <v>8219819.6200000001</v>
+        <v>8419819.6199999992</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23398,7 +23403,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="204">
-        <v>7495495.4000000004</v>
+        <v>9592792.6799999997</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23420,7 +23425,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="204">
-        <v>13097297.140000001</v>
+        <v>15773873.699999999</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23443,7 +23448,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="204">
-        <v>3932432.4</v>
+        <v>7175675.5999999996</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23454,7 +23459,7 @@
         <v>77</v>
       </c>
       <c r="D76" s="204">
-        <v>229879300.729956</v>
+        <v>235554977.329956</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23465,7 +23470,7 @@
         <v>79</v>
       </c>
       <c r="D77" s="204">
-        <v>10536035.92</v>
+        <v>12157657.52</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23487,8 +23492,7 @@
         <v>81</v>
       </c>
       <c r="D79" s="204">
-        <f>IF(E11="",0,E11)</f>
-        <v>0</v>
+        <v>2972973</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23499,7 +23503,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="204">
-        <v>40603603.649999999</v>
+        <v>61576576.450000003</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23510,7 +23514,7 @@
         <v>85</v>
       </c>
       <c r="D81" s="204">
-        <v>39231530.520000003</v>
+        <v>40139638.439999998</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23532,7 +23536,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="204">
-        <v>12518919.199999999</v>
+        <v>21881081.52</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23542,7 +23546,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>375251371.43995595</v>
+        <v>424982002.71995592</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23556,13 +23560,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23604,19 +23608,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>87095406.395739004</v>
+        <v>100116365.515632</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.31322002436765434</v>
+        <v>0.36004712239268455</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>190969211.50847054</v>
+        <v>177948252.38857755</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>3978525.2397598028</v>
+        <v>8473726.3042179793</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23633,19 +23637,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>13891811.213934001</v>
+        <v>42117487.793516003</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>3.3264353578011371E-2</v>
+        <v>0.10085157249875584</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>403726741.97258759</v>
+        <v>375501065.39300561</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>8410973.7910955753</v>
+        <v>17881003.113952648</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23662,19 +23666,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>94960806.617712989</v>
+        <v>123951644.45549099</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>8.7336701061323546E-2</v>
+        <v>0.11399995538632461</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>992334745.69581175</v>
+        <v>963343907.85803378</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>20673640.535329413</v>
+        <v>45873519.421811134</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23747,29 +23751,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>195948024.227386</v>
+        <v>266185497.76463902</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.10989924986500166</v>
+        <v>0.14929258227849679</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1587030699.1768699</v>
+        <v>1516793225.639617</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>33063139.566184789</v>
+        <v>72228248.839981765</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23777,6 +23776,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -23844,15 +23848,15 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),2),11)</f>
-        <v>75</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),6,1)),EOMONTH(DATE(YEAR(TODAY()),6,1),0),11))</f>
+        <v>26</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),2))</f>
-        <v>31</v>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),6,1),0))</f>
+        <v>30</v>
       </c>
       <c r="G3" s="116"/>
       <c r="H3" s="116"/>
@@ -24549,10 +24553,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -24579,7 +24583,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24614,7 +24618,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25613,13 +25617,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25822,11 +25826,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25834,6 +25833,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -25901,14 +25905,14 @@
         <v>103</v>
       </c>
       <c r="C3" s="78">
-        <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),3),11)</f>
-        <v>101</v>
+        <f ca="1">MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),7,1)),EOMONTH(DATE(YEAR(TODAY()),7,1),0),11))</f>
+        <v>27</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="80">
-        <f ca="1">DAY(EOMONTH(TODAY(),3))</f>
+        <f ca="1">DAY(EOMONTH(DATE(YEAR(TODAY()),7,1),0))</f>
         <v>31</v>
       </c>
       <c r="G3" s="116"/>
@@ -26606,10 +26610,10 @@
       <c r="H48" s="230"/>
       <c r="I48" s="230"/>
       <c r="J48" s="231"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="244"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="247"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="224" t="s">
@@ -26636,7 +26640,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="245" t="s">
+      <c r="N49" s="248" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26671,7 +26675,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="245"/>
+      <c r="N50" s="248"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27670,13 +27674,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="239" t="s">
+      <c r="B87" s="242" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="240"/>
-      <c r="D87" s="240"/>
-      <c r="E87" s="240"/>
-      <c r="F87" s="241"/>
+      <c r="C87" s="243"/>
+      <c r="D87" s="243"/>
+      <c r="E87" s="243"/>
+      <c r="F87" s="244"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27879,11 +27883,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27891,6 +27890,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 07 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 08 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1825,14 +1825,8 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1930,15 +1924,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1960,7 +1945,18 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2716,16 +2712,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="207" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="207"/>
+      <c r="B1" s="205" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="205"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="206"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2776,10 +2772,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="209" t="s">
+      <c r="B11" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="209"/>
+      <c r="C11" s="207"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3432,11 +3428,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3560,10 +3556,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3592,40 +3588,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3633,13 +3629,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3658,7 +3654,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3668,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4461,10 +4457,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4472,8 +4468,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -4667,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4876,6 +4872,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4883,11 +4884,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5489,11 +5485,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5617,10 +5613,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5649,40 +5645,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5690,13 +5686,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5715,7 +5711,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5725,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6518,10 +6514,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6529,8 +6525,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -6724,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6933,6 +6929,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6940,11 +6941,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7546,11 +7542,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>167</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7674,10 +7670,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7706,40 +7702,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7747,13 +7743,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7772,7 +7768,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7782,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8575,10 +8571,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8586,8 +8582,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -8781,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8990,6 +8986,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8997,11 +8998,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9603,11 +9599,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9731,10 +9727,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9763,40 +9759,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9804,13 +9800,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9829,7 +9825,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9839,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10632,10 +10628,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10643,8 +10639,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -10838,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11047,6 +11043,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11054,11 +11055,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11660,11 +11656,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11787,10 +11783,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11819,40 +11815,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11860,13 +11856,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11885,7 +11881,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11895,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12674,10 +12670,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12685,8 +12681,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -12880,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13089,6 +13085,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13096,11 +13097,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -13176,10 +13172,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="206" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="208"/>
+      <c r="C3" s="206"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14652,13 +14648,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="208" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
+      <c r="C29" s="208"/>
+      <c r="D29" s="208"/>
+      <c r="E29" s="208"/>
+      <c r="F29" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15190,10 +15186,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="210" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="211"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15233,23 +15229,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="212" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="212" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="213" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="214"/>
+      <c r="F47" s="215"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="212" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15257,13 +15253,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="209" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="212"/>
+      <c r="C48" s="212"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15282,7 +15278,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="212"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15292,7 +15288,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="209"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16725,10 +16721,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="210" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="213"/>
+      <c r="C44" s="211"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16768,23 +16764,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="214" t="s">
+      <c r="B47" s="212" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="214" t="s">
+      <c r="C47" s="212" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="213" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="216"/>
-      <c r="F47" s="217"/>
+      <c r="E47" s="214"/>
+      <c r="F47" s="215"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="214" t="s">
+      <c r="J47" s="212" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16792,13 +16788,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="211" t="s">
+      <c r="N47" s="209" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="214"/>
-      <c r="C48" s="214"/>
+      <c r="B48" s="212"/>
+      <c r="C48" s="212"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16817,7 +16813,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="214"/>
+      <c r="J48" s="212"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16827,7 +16823,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="211"/>
+      <c r="N48" s="209"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18412,10 +18408,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="223"/>
+      <c r="C44" s="221"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18480,23 +18476,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="224" t="s">
+      <c r="B47" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="224" t="s">
+      <c r="C47" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="219" t="s">
+      <c r="D47" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="220"/>
-      <c r="F47" s="221"/>
+      <c r="E47" s="218"/>
+      <c r="F47" s="219"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="224" t="s">
+      <c r="J47" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18504,13 +18500,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="218" t="s">
+      <c r="N47" s="216" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="224"/>
-      <c r="C48" s="224"/>
+      <c r="B48" s="222"/>
+      <c r="C48" s="222"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18529,7 +18525,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="224"/>
+      <c r="J48" s="222"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18539,7 +18535,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="218"/>
+      <c r="N48" s="216"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20161,11 +20157,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20283,10 +20279,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20309,40 +20305,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="236"/>
-      <c r="L48" s="237"/>
-      <c r="M48" s="237"/>
-      <c r="N48" s="238"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="235" t="s">
+      <c r="C49" s="233" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="232" t="s">
+      <c r="D49" s="230" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="233"/>
-      <c r="F49" s="234"/>
+      <c r="E49" s="231"/>
+      <c r="F49" s="232"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="235" t="s">
+      <c r="J49" s="233" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20350,13 +20346,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="228" t="s">
+      <c r="N49" s="226" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="235"/>
-      <c r="C50" s="235"/>
+      <c r="B50" s="233"/>
+      <c r="C50" s="233"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20375,7 +20371,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="235"/>
+      <c r="J50" s="233"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20385,7 +20381,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="228"/>
+      <c r="N50" s="226"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21176,10 +21172,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21190,8 +21186,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -21377,13 +21373,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="229" t="s">
+      <c r="B87" s="227" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="230"/>
-      <c r="D87" s="230"/>
-      <c r="E87" s="230"/>
-      <c r="F87" s="231"/>
+      <c r="C87" s="228"/>
+      <c r="D87" s="228"/>
+      <c r="E87" s="228"/>
+      <c r="F87" s="229"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21665,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21747,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>42873985.280547</v>
+        <v>51183371.799344003</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>14041957.978482001</v>
+        <v>16691291.318482</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21769,35 +21765,35 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>99060006.837617993</v>
+        <v>128778259.167568</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>18273402.330292001</v>
+        <v>21919523.940276001</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="206">
-        <v>54174339.979146004</v>
-      </c>
-      <c r="D10" s="206">
-        <v>5380116.9003720004</v>
-      </c>
-      <c r="E10" s="206">
-        <v>40139638.439999998</v>
-      </c>
-      <c r="F10" s="206">
-        <v>99694095.319518</v>
+      <c r="C10" s="247">
+        <v>61750218.379142001</v>
+      </c>
+      <c r="D10" s="247">
+        <v>5632116.9003720004</v>
+      </c>
+      <c r="E10" s="247">
+        <v>45345043.799999997</v>
+      </c>
+      <c r="F10" s="247">
+        <v>112727379.079514</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>117467040.76519699</v>
+        <v>136066851.64607301</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -21808,24 +21804,24 @@
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="206">
-        <v>86706793.804280996</v>
-      </c>
-      <c r="D11" s="206">
-        <v>23834171.600310002</v>
-      </c>
-      <c r="E11" s="206">
+      <c r="C11" s="247">
+        <v>92488701.064246997</v>
+      </c>
+      <c r="D11" s="247">
+        <v>25701757.190308999</v>
+      </c>
+      <c r="E11" s="247">
         <v>2972973</v>
       </c>
-      <c r="F11" s="206">
-        <v>113513938.40459099</v>
+      <c r="F11" s="247">
+        <v>121163431.254556</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>21387387.039999999</v>
+        <v>44810810.039999999</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -21836,84 +21832,84 @@
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="206">
-        <v>46067556.383975998</v>
-      </c>
-      <c r="D12" s="206">
-        <v>12945866.290298</v>
-      </c>
-      <c r="E12" s="206" t="s">
+      <c r="C12" s="247">
+        <v>67303826.533976004</v>
+      </c>
+      <c r="D12" s="247">
+        <v>14434312.220286001</v>
+      </c>
+      <c r="E12" s="247" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="206">
-        <v>59013422.674273998</v>
+      <c r="F12" s="247">
+        <v>81738138.754262</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>56191655.338026002</v>
+        <v>113507896.122786</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>19878088.459867999</v>
+        <v>23237394.769868001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="206">
-        <v>52992450.453642003</v>
-      </c>
-      <c r="D13" s="206">
-        <v>5327536.0399940005</v>
-      </c>
-      <c r="E13" s="206">
+      <c r="C13" s="247">
+        <v>61474432.633592002</v>
+      </c>
+      <c r="D13" s="247">
+        <v>7485211.7199900001</v>
+      </c>
+      <c r="E13" s="247">
         <v>9592792.6799999997</v>
       </c>
-      <c r="F13" s="206">
-        <v>67912779.173636004</v>
+      <c r="F13" s="247">
+        <v>78552437.033582002</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>152304041.79159999</v>
+        <v>210013135.14625701</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>17140076.309966002</v>
+        <v>18479876.309966002</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="206">
-        <v>117467040.76519699</v>
-      </c>
-      <c r="D14" s="206">
+      <c r="C14" s="247">
+        <v>136066851.64607301</v>
+      </c>
+      <c r="D14" s="247">
         <v>10240095.673957</v>
       </c>
-      <c r="E14" s="206">
-        <v>15773873.699999999</v>
-      </c>
-      <c r="F14" s="206">
-        <v>143481010.13915399</v>
+      <c r="E14" s="247">
+        <v>19841441.25</v>
+      </c>
+      <c r="F14" s="247">
+        <v>166148388.57003</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>98086123.531784996</v>
+        <v>106270829.332285</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>20422324.289864</v>
+        <v>22991702.699864</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21929,140 +21925,140 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>86706793.804280996</v>
+        <v>92488701.064246997</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>23834171.600310002</v>
+        <v>25701757.190308999</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="206">
-        <v>56191655.338026002</v>
-      </c>
-      <c r="D16" s="206">
-        <v>19878088.459867999</v>
-      </c>
-      <c r="E16" s="206">
+      <c r="C16" s="247">
+        <v>113507896.122786</v>
+      </c>
+      <c r="D16" s="247">
+        <v>23237394.769868001</v>
+      </c>
+      <c r="E16" s="247">
         <v>7175675.5999999996</v>
       </c>
-      <c r="F16" s="206">
-        <v>83245419.397893995</v>
+      <c r="F16" s="247">
+        <v>143920966.492654</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>79658589.395199001</v>
+        <v>92197364.187153995</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>16881583.799972001</v>
+        <v>20338068.039972</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="206">
-        <v>21387387.039999999</v>
-      </c>
-      <c r="D17" s="206">
+      <c r="C17" s="247">
+        <v>44810810.039999999</v>
+      </c>
+      <c r="D17" s="247">
         <v>594594.6</v>
       </c>
-      <c r="E17" s="206" t="s">
+      <c r="E17" s="247" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="206">
-        <v>21981981.640000001</v>
+      <c r="F17" s="247">
+        <v>45405404.640000001</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>54174339.979146004</v>
+        <v>61750218.379142001</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>5380116.9003720004</v>
+        <v>5632116.9003720004</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="206">
-        <v>391192036.163966</v>
-      </c>
-      <c r="D18" s="206">
-        <v>3422346.9499789998</v>
-      </c>
-      <c r="E18" s="206">
+      <c r="C18" s="247">
+        <v>397945849.11396599</v>
+      </c>
+      <c r="D18" s="247">
+        <v>4687981.1899769995</v>
+      </c>
+      <c r="E18" s="247">
         <v>1135135.1200000001</v>
       </c>
-      <c r="F18" s="206">
-        <v>395749518.23394501</v>
+      <c r="F18" s="247">
+        <v>403768965.42394298</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>169536385.769223</v>
+        <v>188605800.348975</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>85651530.428636</v>
+        <v>92026249.268583</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="206">
-        <v>152304041.79159999</v>
-      </c>
-      <c r="D19" s="206">
-        <v>17140076.309966002</v>
-      </c>
-      <c r="E19" s="206">
+      <c r="C19" s="247">
+        <v>210013135.14625701</v>
+      </c>
+      <c r="D19" s="247">
+        <v>18479876.309966002</v>
+      </c>
+      <c r="E19" s="247">
         <v>235554977.329956</v>
       </c>
-      <c r="F19" s="206">
-        <v>404999095.43152201</v>
+      <c r="F19" s="247">
+        <v>464047988.78617901</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>40531555.855117999</v>
+        <v>49661701.355117999</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>38541853.192187995</v>
+        <v>39610664.002186999</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="206">
-        <v>30864555.855117999</v>
-      </c>
-      <c r="D20" s="206">
+      <c r="C20" s="247">
+        <v>36829051.355117999</v>
+      </c>
+      <c r="D20" s="247">
         <v>13102655.88992</v>
       </c>
-      <c r="E20" s="206" t="s">
+      <c r="E20" s="247" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="206">
-        <v>43967211.745038003</v>
+      <c r="F20" s="247">
+        <v>49931707.245038003</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22079,24 +22075,24 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="206">
-        <v>9667000</v>
-      </c>
-      <c r="D21" s="206">
-        <v>25439197.302267998</v>
-      </c>
-      <c r="E21" s="206">
+      <c r="C21" s="247">
+        <v>12832650</v>
+      </c>
+      <c r="D21" s="247">
+        <v>26508008.112266999</v>
+      </c>
+      <c r="E21" s="247">
         <v>21881081.52</v>
       </c>
-      <c r="F21" s="206">
-        <v>56987278.822268002</v>
+      <c r="F21" s="247">
+        <v>61221739.632266998</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>123951644.45549099</v>
+        <v>126614910.26897201</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22106,16 +22102,16 @@
       <c r="B22" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="206">
+      <c r="C22" s="247">
         <v>32194810</v>
       </c>
-      <c r="D22" s="206" t="s">
+      <c r="D22" s="247" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="206">
+      <c r="E22" s="247">
         <v>4036035.92</v>
       </c>
-      <c r="F22" s="206">
+      <c r="F22" s="247">
         <v>36230845.920000002</v>
       </c>
       <c r="H22" s="116"/>
@@ -22126,17 +22122,17 @@
       <c r="B23" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="206">
+      <c r="C23" s="247">
         <v>68042438.249974996</v>
       </c>
-      <c r="D23" s="206" t="s">
+      <c r="D23" s="247" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="206">
-        <v>1441441.4</v>
-      </c>
-      <c r="F23" s="206">
-        <v>69483879.649975002</v>
+      <c r="E23" s="247">
+        <v>3207207.12</v>
+      </c>
+      <c r="F23" s="247">
+        <v>71249645.369975001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22146,17 +22142,17 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="206">
-        <v>42873985.280547</v>
-      </c>
-      <c r="D24" s="206">
-        <v>14041957.978482001</v>
-      </c>
-      <c r="E24" s="206">
-        <v>8419819.6199999992</v>
-      </c>
-      <c r="F24" s="206">
-        <v>65335762.879028998</v>
+      <c r="C24" s="247">
+        <v>51183371.799344003</v>
+      </c>
+      <c r="D24" s="247">
+        <v>16691291.318482</v>
+      </c>
+      <c r="E24" s="247">
+        <v>25563062.68</v>
+      </c>
+      <c r="F24" s="247">
+        <v>93437725.797826007</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22166,17 +22162,17 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="206">
-        <v>98086123.531784996</v>
-      </c>
-      <c r="D25" s="206">
-        <v>20422324.289864</v>
-      </c>
-      <c r="E25" s="206">
-        <v>12157657.52</v>
-      </c>
-      <c r="F25" s="206">
-        <v>130666105.341649</v>
+      <c r="C25" s="247">
+        <v>106270829.332285</v>
+      </c>
+      <c r="D25" s="247">
+        <v>22991702.699864</v>
+      </c>
+      <c r="E25" s="247">
+        <v>15952252.08</v>
+      </c>
+      <c r="F25" s="247">
+        <v>145214784.112149</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22186,17 +22182,17 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="206">
-        <v>79658589.395199001</v>
-      </c>
-      <c r="D26" s="206">
-        <v>16881583.799972001</v>
-      </c>
-      <c r="E26" s="206">
-        <v>61576576.450000003</v>
-      </c>
-      <c r="F26" s="206">
-        <v>158116749.64517099</v>
+      <c r="C26" s="247">
+        <v>92197364.187153995</v>
+      </c>
+      <c r="D26" s="247">
+        <v>20338068.039972</v>
+      </c>
+      <c r="E26" s="247">
+        <v>85687387.089980006</v>
+      </c>
+      <c r="F26" s="247">
+        <v>198222819.31710601</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22206,17 +22202,17 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="206">
-        <v>169536385.769223</v>
-      </c>
-      <c r="D27" s="206">
-        <v>85651530.428636</v>
-      </c>
-      <c r="E27" s="206">
+      <c r="C27" s="247">
+        <v>188605800.348975</v>
+      </c>
+      <c r="D27" s="247">
+        <v>92026249.268583</v>
+      </c>
+      <c r="E27" s="247">
         <v>4259459.54</v>
       </c>
-      <c r="F27" s="206">
-        <v>259447375.73785901</v>
+      <c r="F27" s="247">
+        <v>284891509.15755802</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22262,8 +22258,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="249">
-        <v>100116365.515632</v>
+      <c r="C32" s="247">
+        <v>105815824.835517</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22273,8 +22269,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="206">
-        <v>42117487.793516003</v>
+      <c r="C33" s="247">
+        <v>59054515.013503999</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22284,8 +22280,8 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="206">
-        <v>112452311.135539</v>
+      <c r="C34" s="247">
+        <v>113688549.90902001</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22295,8 +22291,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="206">
-        <v>11499333.319952</v>
+      <c r="C35" s="247">
+        <v>12926360.359952001</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22338,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="244" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="240"/>
-      <c r="D41" s="241"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="246"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.22580645161290322</v>
+        <v>0.25806451612903225</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22391,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1118215153.6377149</v>
+        <v>1375572186.8389242</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.16349897399361182</v>
+        <v>0.20112823589509213</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5721064178.3622856</v>
+        <v>5463707145.1610756</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>272431627.54106122</v>
+        <v>273185357.25805378</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22420,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>270879795.56390703</v>
+        <v>297463334.71383601</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.18361435256687544</v>
+        <v>0.20163385571877745</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1204385028.6564546</v>
+        <v>1177801489.5065258</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>57351668.031259738</v>
+        <v>58890074.475326285</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22449,46 +22445,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>266185497.76463902</v>
+        <v>291485250.117993</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.14929258227849679</v>
+        <v>0.1634821808537669</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1516793225.639617</v>
+        <v>1491493473.286263</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>72228248.839981765</v>
+        <v>74574673.664313152</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>1655280446.9662609</v>
+        <v>1964520771.670753</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.1639293583881235</v>
+        <v>0.19455472347924854</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>8442242432.6583567</v>
+        <v>8133002107.9538651</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>402011544.41230267</v>
+        <v>406650105.39769328</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22498,40 +22494,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22539,13 +22535,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22564,7 +22560,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22574,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22583,49 +22579,49 @@
       <c r="C51" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="205">
+      <c r="D51" s="204">
         <f>TARGETS!L5</f>
         <v>416683478</v>
       </c>
-      <c r="E51" s="205">
+      <c r="E51" s="204">
         <f>TARGETS!M5</f>
         <v>68270401.220654309</v>
       </c>
-      <c r="F51" s="205">
+      <c r="F51" s="204">
         <f t="shared" ref="F51:F64" si="0">D51+E51</f>
         <v>484953879.22065431</v>
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>42873985.280547</v>
+        <v>51183371.799344003</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>14041957.978482001</v>
+        <v>16691291.318482</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>56915943.259029001</v>
+        <v>67874663.117826</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.11736362094988462</v>
+        <v>0.13996106851831777</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>373809492.71945298</v>
+        <v>365500106.200656</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>54228443.242172308</v>
+        <v>51579109.902172312</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>428037935.96162534</v>
+        <v>417079216.10282832</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>20382758.855315492</v>
+        <v>20853960.805141415</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22635,49 +22631,49 @@
       <c r="C52" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="205">
+      <c r="D52" s="204">
         <f>TARGETS!L6</f>
         <v>555182371</v>
       </c>
-      <c r="E52" s="205">
+      <c r="E52" s="204">
         <f>TARGETS!M6</f>
         <v>191546784</v>
       </c>
-      <c r="F52" s="205">
+      <c r="F52" s="204">
         <f t="shared" si="0"/>
         <v>746729155</v>
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>99060006.837617993</v>
+        <v>128778259.167568</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>18273402.330292001</v>
+        <v>21919523.940276001</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>117333409.16790999</v>
+        <v>150697783.107844</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.15712980855543265</v>
+        <v>0.20181049862428901</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>456122364.16238201</v>
+        <v>426404111.83243203</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>173273381.66970801</v>
+        <v>169627260.059724</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>629395745.83209002</v>
+        <v>596031371.892156</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>29971225.992004286</v>
+        <v>29801568.5946078</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22729,7 +22725,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>9965640.8571428563</v>
+        <v>10463922.9</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22739,21 +22735,21 @@
       <c r="C54" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="205">
+      <c r="D54" s="204">
         <f>TARGETS!L8</f>
         <v>610712472</v>
       </c>
-      <c r="E54" s="205">
+      <c r="E54" s="204">
         <f>TARGETS!M8</f>
         <v>46881826.81733489</v>
       </c>
-      <c r="F54" s="205">
+      <c r="F54" s="204">
         <f t="shared" si="0"/>
         <v>657594298.81733489</v>
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>117467040.76519699</v>
+        <v>136066851.64607301</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
@@ -22761,15 +22757,15 @@
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>127707136.439154</v>
+        <v>146306947.32003</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.19420353349904607</v>
+        <v>0.22248816266071497</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>493245431.23480302</v>
+        <v>474645620.35392702</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
@@ -22777,11 +22773,11 @@
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>529887162.37818086</v>
+        <v>511287351.49730492</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>25232722.018008612</v>
+        <v>25564367.574865244</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22791,21 +22787,21 @@
       <c r="C55" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="205">
+      <c r="D55" s="204">
         <f>TARGETS!L9</f>
         <v>405063284</v>
       </c>
-      <c r="E55" s="205">
+      <c r="E55" s="204">
         <f>TARGETS!M9</f>
         <v>82869315.191524148</v>
       </c>
-      <c r="F55" s="205">
+      <c r="F55" s="204">
         <f t="shared" si="0"/>
         <v>487932599.19152415</v>
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>21387387.039999999</v>
+        <v>44810810.039999999</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -22813,15 +22809,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>21981981.640000001</v>
+        <v>45405404.640000001</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>4.5051266663516359E-2</v>
+        <v>9.3056714626639225E-2</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>383675896.95999998</v>
+        <v>360252473.95999998</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -22829,11 +22825,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>465950617.55152416</v>
+        <v>442527194.55152416</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>22188124.645310674</v>
+        <v>22126359.727576207</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22843,49 +22839,49 @@
       <c r="C56" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="205">
+      <c r="D56" s="204">
         <f>TARGETS!L10</f>
         <v>473918832</v>
       </c>
-      <c r="E56" s="205">
+      <c r="E56" s="204">
         <f>TARGETS!M10</f>
         <v>81239394.122653604</v>
       </c>
-      <c r="F56" s="205">
+      <c r="F56" s="204">
         <f t="shared" si="0"/>
         <v>555158226.1226536</v>
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>56191655.338026002</v>
+        <v>113507896.122786</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>19878088.459867999</v>
+        <v>23237394.769868001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>76069743.797894001</v>
+        <v>136745290.892654</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.13702353710793716</v>
+        <v>0.24631768828809941</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>417727176.66197401</v>
+        <v>360410935.87721401</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>61361305.662785605</v>
+        <v>58001999.352785602</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>479088482.3247596</v>
+        <v>418412935.2299996</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>22813737.253559981</v>
+        <v>20920646.761499979</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22895,49 +22891,49 @@
       <c r="C57" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="205">
+      <c r="D57" s="204">
         <f>TARGETS!L11</f>
         <v>961758345</v>
       </c>
-      <c r="E57" s="205">
+      <c r="E57" s="204">
         <f>TARGETS!M11</f>
         <v>91928576.339156389</v>
       </c>
-      <c r="F57" s="205">
+      <c r="F57" s="204">
         <f t="shared" si="0"/>
         <v>1053686921.3391564</v>
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>152304041.79159999</v>
+        <v>210013135.14625701</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>17140076.309966002</v>
+        <v>18479876.309966002</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>169444118.10156599</v>
+        <v>228493011.45622301</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.16081068737781742</v>
+        <v>0.21685095148170358</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>809454303.20840001</v>
+        <v>751745209.85374296</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>74788500.029190391</v>
+        <v>73448700.029190391</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>884242803.23759043</v>
+        <v>825193909.88293338</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>42106800.154170975</v>
+        <v>41259695.494146667</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22947,49 +22943,49 @@
       <c r="C58" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="205">
+      <c r="D58" s="204">
         <f>TARGETS!L12</f>
         <v>505287059</v>
       </c>
-      <c r="E58" s="205">
+      <c r="E58" s="204">
         <f>TARGETS!M12</f>
         <v>63781404</v>
       </c>
-      <c r="F58" s="205">
+      <c r="F58" s="204">
         <f t="shared" si="0"/>
         <v>569068463</v>
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>98086123.531784996</v>
+        <v>106270829.332285</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>20422324.289864</v>
+        <v>22991702.699864</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>118508447.821649</v>
+        <v>129262532.032149</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.20824989527077167</v>
+        <v>0.22714759371957852</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>407200935.46821499</v>
+        <v>399016229.66771501</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>43359079.710135996</v>
+        <v>40789701.300136</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>450560015.17835099</v>
+        <v>439805930.96785098</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>21455238.818016715</v>
+        <v>21990296.548392549</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23041,7 +23037,7 @@
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>16004344.083334526</v>
+        <v>16804561.287501253</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23051,49 +23047,49 @@
       <c r="C60" s="202" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="205">
+      <c r="D60" s="204">
         <f>TARGETS!L14</f>
         <v>404017309</v>
       </c>
-      <c r="E60" s="205">
+      <c r="E60" s="204">
         <f>TARGETS!M14</f>
         <v>138464390.21799541</v>
       </c>
-      <c r="F60" s="205">
+      <c r="F60" s="204">
         <f t="shared" si="0"/>
         <v>542481699.21799541</v>
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>86706793.804280996</v>
+        <v>92488701.064246997</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>23834171.600310002</v>
+        <v>25701757.190308999</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>110540965.40459099</v>
+        <v>118190458.254556</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.20376902218810203</v>
+        <v>0.21786994552061628</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>317310515.195719</v>
+        <v>311528607.93575299</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>114630218.61768541</v>
+        <v>112762633.0276864</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>431940733.81340444</v>
+        <v>424291240.9634394</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>20568606.372066878</v>
+        <v>21214562.048171971</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23103,49 +23099,49 @@
       <c r="C61" s="202" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="205">
+      <c r="D61" s="204">
         <f>TARGETS!L15</f>
         <v>631629596</v>
       </c>
-      <c r="E61" s="205">
+      <c r="E61" s="204">
         <f>TARGETS!M15</f>
         <v>58741600.610625267</v>
       </c>
-      <c r="F61" s="205">
+      <c r="F61" s="204">
         <f t="shared" si="0"/>
         <v>690371196.61062527</v>
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>79658589.395199001</v>
+        <v>92197364.187153995</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>16881583.799972001</v>
+        <v>20338068.039972</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>96540173.195170999</v>
+        <v>112535432.227126</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.13983806634624185</v>
+        <v>0.16300713700052707</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>551971006.60480094</v>
+        <v>539432231.81284595</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>41860016.810653269</v>
+        <v>38403532.570653267</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>593831023.41545427</v>
+        <v>577835764.38349926</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>28277667.781688299</v>
+        <v>28891788.219174962</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23155,49 +23151,49 @@
       <c r="C62" s="202" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="205">
+      <c r="D62" s="204">
         <f>TARGETS!L16</f>
         <v>386543023</v>
       </c>
-      <c r="E62" s="205">
+      <c r="E62" s="204">
         <f>TARGETS!M16</f>
         <v>63764154.799813807</v>
       </c>
-      <c r="F62" s="205">
+      <c r="F62" s="204">
         <f t="shared" si="0"/>
         <v>450307177.79981381</v>
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>54174339.979146004</v>
+        <v>61750218.379142001</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>5380116.9003720004</v>
+        <v>5632116.9003720004</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>59554456.879518002</v>
+        <v>67382335.279514</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.13225295934765938</v>
+        <v>0.14963637845779384</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>332368683.020854</v>
+        <v>324792804.62085801</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>58384037.899441808</v>
+        <v>58132037.899441808</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>390752720.92029583</v>
+        <v>382924842.52029979</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>18607272.424775992</v>
+        <v>19146242.126014989</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23207,49 +23203,49 @@
       <c r="C63" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="205">
+      <c r="D63" s="204">
         <f>TARGETS!L17</f>
         <v>583350942</v>
       </c>
-      <c r="E63" s="205">
+      <c r="E63" s="204">
         <f>TARGETS!M17</f>
         <v>329806944.99271739</v>
       </c>
-      <c r="F63" s="205">
+      <c r="F63" s="204">
         <f t="shared" si="0"/>
         <v>913157886.99271739</v>
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>169536385.769223</v>
+        <v>188605800.348975</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>85651530.428636</v>
+        <v>92026249.268583</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>255187916.19785899</v>
+        <v>280632049.617558</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.27945651002179228</v>
+        <v>0.307320402763817</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>413814556.23077703</v>
+        <v>394745141.651025</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>244155414.56408137</v>
+        <v>237780695.72413439</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>657969970.79485846</v>
+        <v>632525837.37515938</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>31331903.371183734</v>
+        <v>31626291.868757971</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23259,49 +23255,49 @@
       <c r="C64" s="202" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="205">
+      <c r="D64" s="204">
         <f>TARGETS!L18</f>
         <v>259525689</v>
       </c>
-      <c r="E64" s="205">
+      <c r="E64" s="204">
         <f>TARGETS!M18</f>
         <v>257970031.90788639</v>
       </c>
-      <c r="F64" s="205">
+      <c r="F64" s="204">
         <f t="shared" si="0"/>
         <v>517495720.90788639</v>
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>40531555.855117999</v>
+        <v>49661701.355117999</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>38541853.192187995</v>
+        <v>39610664.002186999</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>79073409.047306001</v>
+        <v>89272365.35730499</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.15280012153256234</v>
+        <v>0.17250841263129085</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>218994133.14488199</v>
+        <v>209863987.64488199</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>219428178.71569839</v>
+        <v>218359367.90569937</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>438422311.86058038</v>
+        <v>428223355.5505814</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>20877252.945741922</v>
+        <v>21411167.777529068</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23323,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1118215153.6377149</v>
+        <v>1375572186.8389242</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>270879795.56390703</v>
+        <v>297463334.71383601</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>1389094949.201622</v>
+        <v>1673035521.5527599</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.16706808251928015</v>
+        <v>0.20121794894806244</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5721064178.3622847</v>
+        <v>5463707145.1610765</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1204385028.6564546</v>
+        <v>1177801489.5065255</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>6925449207.0187397</v>
+        <v>6641508634.6676016</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>329783295.57232094</v>
+        <v>332075431.73338008</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23367,10 +23363,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23378,8 +23374,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -23391,8 +23387,9 @@
       <c r="C70" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="204">
-        <v>8419819.6199999992</v>
+      <c r="D70" s="191">
+        <f>IF(E24="",0,E24)</f>
+        <v>25563062.68</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23402,7 +23399,8 @@
       <c r="C71" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="204">
+      <c r="D71" s="192">
+        <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
         <v>9592792.6799999997</v>
       </c>
     </row>
@@ -23413,7 +23411,8 @@
       <c r="C72" s="202" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="204">
+      <c r="D72" s="192">
+        <f>IF(E22="",0,E22)</f>
         <v>4036035.92</v>
       </c>
     </row>
@@ -23424,8 +23423,9 @@
       <c r="C73" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="204">
-        <v>15773873.699999999</v>
+      <c r="D73" s="191">
+        <f>IF(E14="",0,E14)</f>
+        <v>19841441.25</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23435,7 +23435,7 @@
       <c r="C74" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="204">
+      <c r="D74" s="192">
         <f>0</f>
         <v>0</v>
       </c>
@@ -23447,7 +23447,8 @@
       <c r="C75" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="204">
+      <c r="D75" s="192">
+        <f>IF(E16="",0,E16)</f>
         <v>7175675.5999999996</v>
       </c>
     </row>
@@ -23458,7 +23459,8 @@
       <c r="C76" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="204">
+      <c r="D76" s="192">
+        <f>IF(E19="",0,E19)</f>
         <v>235554977.329956</v>
       </c>
     </row>
@@ -23469,8 +23471,9 @@
       <c r="C77" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="204">
-        <v>12157657.52</v>
+      <c r="D77" s="191">
+        <f>IF(E25="",0,E25)</f>
+        <v>15952252.08</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23480,8 +23483,9 @@
       <c r="C78" s="202" t="s">
         <v>178</v>
       </c>
-      <c r="D78" s="204">
-        <v>1441441.4</v>
+      <c r="D78" s="192">
+        <f>IF(E23="",0,E23)</f>
+        <v>3207207.12</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23491,7 +23495,8 @@
       <c r="C79" s="202" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="204">
+      <c r="D79" s="192">
+        <f>IF(E11="",0,E11)</f>
         <v>2972973</v>
       </c>
     </row>
@@ -23502,8 +23507,9 @@
       <c r="C80" s="202" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="204">
-        <v>61576576.450000003</v>
+      <c r="D80" s="191">
+        <f>IF(E26="",0,E26)</f>
+        <v>85687387.089980006</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23513,8 +23519,9 @@
       <c r="C81" s="202" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="204">
-        <v>40139638.439999998</v>
+      <c r="D81" s="192">
+        <f>IF(E10="",0,E10)</f>
+        <v>45345043.799999997</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23524,7 +23531,8 @@
       <c r="C82" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="204">
+      <c r="D82" s="192">
+        <f>IF(E27="",0,E27)</f>
         <v>4259459.54</v>
       </c>
     </row>
@@ -23535,7 +23543,8 @@
       <c r="C83" s="202" t="s">
         <v>89</v>
       </c>
-      <c r="D83" s="204">
+      <c r="D83" s="192">
+        <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
         <v>21881081.52</v>
       </c>
     </row>
@@ -23546,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>424982002.71995592</v>
+        <v>481069389.609936</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23560,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23608,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>100116365.515632</v>
+        <v>105815824.835517</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.36004712239268455</v>
+        <v>0.38054401035650454</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>177948252.38857755</v>
+        <v>172248793.06869256</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>8473726.3042179793</v>
+        <v>8612439.6534346286</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23637,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>42117487.793516003</v>
+        <v>59054515.013503999</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.10085157249875584</v>
+        <v>0.14140778603561799</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>375501065.39300561</v>
+        <v>358564038.17301762</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17881003.113952648</v>
+        <v>17928201.908650883</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23666,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>123951644.45549099</v>
+        <v>126614910.26897201</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.11399995538632461</v>
+        <v>0.11644939593431008</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>963343907.85803378</v>
+        <v>960680642.04455268</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>45873519.421811134</v>
+        <v>48034032.102227636</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23751,24 +23760,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>266185497.76463902</v>
+        <v>291485250.117993</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.14929258227849679</v>
+        <v>0.1634821808537669</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1516793225.639617</v>
+        <v>1491493473.286263</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>72228248.839981765</v>
+        <v>74574673.664313152</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23776,11 +23790,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24382,11 +24391,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24510,10 +24519,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24542,40 +24551,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24583,13 +24592,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24608,7 +24617,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24618,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25411,10 +25420,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25422,8 +25431,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -25617,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25826,6 +25835,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25833,11 +25847,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26439,11 +26448,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="225" t="s">
+      <c r="B41" s="223" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="226"/>
-      <c r="D41" s="227"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26567,10 +26576,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="222" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="223"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26599,40 +26608,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="229" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="230"/>
-      <c r="D48" s="230"/>
-      <c r="E48" s="230"/>
-      <c r="F48" s="230"/>
-      <c r="G48" s="230"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="230"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="245"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="247"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="241"/>
+      <c r="M48" s="241"/>
+      <c r="N48" s="242"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="224" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="219" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="220"/>
-      <c r="F49" s="221"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="224" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26640,13 +26649,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="248" t="s">
+      <c r="N49" s="243" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="224"/>
-      <c r="C50" s="224"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26665,7 +26674,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="224"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26675,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="248"/>
+      <c r="N50" s="243"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27468,10 +27477,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="224" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="224" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27479,8 +27488,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -27674,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="242" t="s">
+      <c r="B87" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="243"/>
-      <c r="D87" s="243"/>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="239"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27883,6 +27892,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27890,11 +27904,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 08 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 11 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1828,6 +1828,9 @@
     <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1953,9 +1956,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2712,16 +2712,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="205" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="205"/>
+      <c r="B1" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="206"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="206"/>
+      <c r="C3" s="207"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2772,10 +2772,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="207" t="s">
+      <c r="B11" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="207"/>
+      <c r="C11" s="208"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -3428,11 +3428,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3556,10 +3556,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3588,40 +3588,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3629,13 +3629,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3654,7 +3654,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4457,10 +4457,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4468,8 +4468,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -5485,11 +5485,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5613,10 +5613,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5645,40 +5645,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5686,13 +5686,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5711,7 +5711,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6514,10 +6514,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6525,8 +6525,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -7542,11 +7542,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>167</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7670,10 +7670,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7702,40 +7702,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7743,13 +7743,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7768,7 +7768,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8571,10 +8571,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8582,8 +8582,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -9599,11 +9599,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9727,10 +9727,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9759,40 +9759,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9800,13 +9800,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9825,7 +9825,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10628,10 +10628,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10639,8 +10639,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11656,11 +11656,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11783,10 +11783,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11815,40 +11815,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11856,13 +11856,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11881,7 +11881,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12670,10 +12670,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12681,8 +12681,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13172,10 +13172,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="206"/>
+      <c r="C3" s="207"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14648,13 +14648,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="208" t="s">
+      <c r="B29" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="208"/>
-      <c r="D29" s="208"/>
-      <c r="E29" s="208"/>
-      <c r="F29" s="208"/>
+      <c r="C29" s="209"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="209"/>
+      <c r="F29" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15186,10 +15186,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="210" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="211"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15229,23 +15229,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="212" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="212" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="213" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="214"/>
-      <c r="F47" s="215"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="212" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15253,13 +15253,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="209" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="212"/>
-      <c r="C48" s="212"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15278,7 +15278,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="212"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15288,7 +15288,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="209"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16721,10 +16721,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="210" t="s">
+      <c r="B44" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="211"/>
+      <c r="C44" s="212"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16764,23 +16764,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="212" t="s">
+      <c r="B47" s="213" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="212" t="s">
+      <c r="C47" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="213" t="s">
+      <c r="D47" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="214"/>
-      <c r="F47" s="215"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="216"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="212" t="s">
+      <c r="J47" s="213" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16788,13 +16788,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="209" t="s">
+      <c r="N47" s="210" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="212"/>
-      <c r="C48" s="212"/>
+      <c r="B48" s="213"/>
+      <c r="C48" s="213"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16813,7 +16813,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="212"/>
+      <c r="J48" s="213"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16823,7 +16823,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="209"/>
+      <c r="N48" s="210"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -18408,10 +18408,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="220" t="s">
+      <c r="B44" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="221"/>
+      <c r="C44" s="222"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18476,23 +18476,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="222" t="s">
+      <c r="B47" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="222" t="s">
+      <c r="C47" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="217" t="s">
+      <c r="D47" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="218"/>
-      <c r="F47" s="219"/>
+      <c r="E47" s="219"/>
+      <c r="F47" s="220"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="222" t="s">
+      <c r="J47" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18500,13 +18500,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="216" t="s">
+      <c r="N47" s="217" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="222"/>
-      <c r="C48" s="222"/>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18525,7 +18525,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="222"/>
+      <c r="J48" s="223"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18535,7 +18535,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="216"/>
+      <c r="N48" s="217"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -20157,11 +20157,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20279,10 +20279,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20305,40 +20305,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="234"/>
-      <c r="L48" s="235"/>
-      <c r="M48" s="235"/>
-      <c r="N48" s="236"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="236"/>
+      <c r="M48" s="236"/>
+      <c r="N48" s="237"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="233" t="s">
+      <c r="B49" s="234" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="233" t="s">
+      <c r="C49" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="230" t="s">
+      <c r="D49" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="231"/>
-      <c r="F49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="233"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="233" t="s">
+      <c r="J49" s="234" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20346,13 +20346,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="226" t="s">
+      <c r="N49" s="227" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="233"/>
-      <c r="C50" s="233"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="234"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20371,7 +20371,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="233"/>
+      <c r="J50" s="234"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20381,7 +20381,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="226"/>
+      <c r="N50" s="227"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21172,10 +21172,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21186,8 +21186,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -21373,13 +21373,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="227" t="s">
+      <c r="B87" s="228" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="228"/>
-      <c r="D87" s="228"/>
-      <c r="E87" s="228"/>
-      <c r="F87" s="229"/>
+      <c r="C87" s="229"/>
+      <c r="D87" s="229"/>
+      <c r="E87" s="229"/>
+      <c r="F87" s="230"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>51183371.799344003</v>
+        <v>58368679.429343998</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>16691291.318482</v>
+        <v>20851146.278480999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,151 +21765,151 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>128778259.167568</v>
+        <v>172091721.67948002</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>21919523.940276001</v>
+        <v>21717727.550274</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="247">
-        <v>61750218.379142001</v>
-      </c>
-      <c r="D10" s="247">
-        <v>5632116.9003720004</v>
-      </c>
-      <c r="E10" s="247">
-        <v>45345043.799999997</v>
-      </c>
-      <c r="F10" s="247">
-        <v>112727379.079514</v>
+      <c r="C10" s="205">
+        <v>77944829.396174997</v>
+      </c>
+      <c r="D10" s="205">
+        <v>6970810.6003719997</v>
+      </c>
+      <c r="E10" s="205">
+        <v>58585511.899998002</v>
+      </c>
+      <c r="F10" s="205">
+        <v>143501151.89654499</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>136066851.64607301</v>
+        <v>188725035.55556199</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>10240095.673957</v>
+        <v>11409771.353956001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="247">
-        <v>92488701.064246997</v>
-      </c>
-      <c r="D11" s="247">
-        <v>25701757.190308999</v>
-      </c>
-      <c r="E11" s="247">
-        <v>2972973</v>
-      </c>
-      <c r="F11" s="247">
-        <v>121163431.254556</v>
+      <c r="C11" s="205">
+        <v>108828331.84418499</v>
+      </c>
+      <c r="D11" s="205">
+        <v>32668296.128307998</v>
+      </c>
+      <c r="E11" s="205">
+        <v>26756757</v>
+      </c>
+      <c r="F11" s="205">
+        <v>168253384.97249299</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>44810810.039999999</v>
+        <v>85278629.140000001</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>594594.6</v>
+        <v>2320094.6</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="247">
-        <v>67303826.533976004</v>
-      </c>
-      <c r="D12" s="247">
-        <v>14434312.220286001</v>
-      </c>
-      <c r="E12" s="247" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" s="247">
-        <v>81738138.754262</v>
+      <c r="C12" s="205">
+        <v>83976070.315963</v>
+      </c>
+      <c r="D12" s="205">
+        <v>14825637.450284</v>
+      </c>
+      <c r="E12" s="205">
+        <v>14414414</v>
+      </c>
+      <c r="F12" s="205">
+        <v>113216121.766247</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>113507896.122786</v>
+        <v>133739590.288058</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>23237394.769868001</v>
+        <v>26651421.779856998</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="247">
-        <v>61474432.633592002</v>
-      </c>
-      <c r="D13" s="247">
-        <v>7485211.7199900001</v>
-      </c>
-      <c r="E13" s="247">
-        <v>9592792.6799999997</v>
-      </c>
-      <c r="F13" s="247">
-        <v>78552437.033582002</v>
+      <c r="C13" s="205">
+        <v>88115651.363517001</v>
+      </c>
+      <c r="D13" s="205">
+        <v>6892090.09999</v>
+      </c>
+      <c r="E13" s="205">
+        <v>13628828.68</v>
+      </c>
+      <c r="F13" s="205">
+        <v>108636570.143507</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>210013135.14625701</v>
+        <v>275491593.84094697</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>18479876.309966002</v>
+        <v>22081730.359965999</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="247">
-        <v>136066851.64607301</v>
-      </c>
-      <c r="D14" s="247">
-        <v>10240095.673957</v>
-      </c>
-      <c r="E14" s="247">
-        <v>19841441.25</v>
-      </c>
-      <c r="F14" s="247">
-        <v>166148388.57003</v>
+      <c r="C14" s="205">
+        <v>188725035.55556199</v>
+      </c>
+      <c r="D14" s="205">
+        <v>11409771.353956001</v>
+      </c>
+      <c r="E14" s="205">
+        <v>28486486.239999998</v>
+      </c>
+      <c r="F14" s="205">
+        <v>228621293.14951801</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>106270829.332285</v>
+        <v>142851101.47690901</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>22991702.699864</v>
+        <v>24190801.809859999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,140 +21925,140 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>92488701.064246997</v>
+        <v>108828331.84418499</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>25701757.190308999</v>
+        <v>32668296.128307998</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="247">
-        <v>113507896.122786</v>
-      </c>
-      <c r="D16" s="247">
-        <v>23237394.769868001</v>
-      </c>
-      <c r="E16" s="247">
+      <c r="C16" s="205">
+        <v>133739590.288058</v>
+      </c>
+      <c r="D16" s="205">
+        <v>26651421.779856998</v>
+      </c>
+      <c r="E16" s="205">
         <v>7175675.5999999996</v>
       </c>
-      <c r="F16" s="247">
-        <v>143920966.492654</v>
+      <c r="F16" s="205">
+        <v>167566687.66791499</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>92197364.187153995</v>
+        <v>124610353.397696</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>20338068.039972</v>
+        <v>22722918.039972</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="247">
-        <v>44810810.039999999</v>
-      </c>
-      <c r="D17" s="247">
-        <v>594594.6</v>
-      </c>
-      <c r="E17" s="247" t="s">
+      <c r="C17" s="205">
+        <v>85278629.140000001</v>
+      </c>
+      <c r="D17" s="205">
+        <v>2320094.6</v>
+      </c>
+      <c r="E17" s="205" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="247">
-        <v>45405404.640000001</v>
+      <c r="F17" s="205">
+        <v>87598723.739999995</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>61750218.379142001</v>
+        <v>77944829.396174997</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>5632116.9003720004</v>
+        <v>6970810.6003719997</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="247">
-        <v>397945849.11396599</v>
-      </c>
-      <c r="D18" s="247">
-        <v>4687981.1899769995</v>
-      </c>
-      <c r="E18" s="247">
-        <v>1135135.1200000001</v>
-      </c>
-      <c r="F18" s="247">
-        <v>403768965.42394298</v>
+      <c r="C18" s="205">
+        <v>466344443.26396602</v>
+      </c>
+      <c r="D18" s="205">
+        <v>5313981.1899769995</v>
+      </c>
+      <c r="E18" s="205">
+        <v>2970270.24</v>
+      </c>
+      <c r="F18" s="205">
+        <v>474628694.69394302</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>188605800.348975</v>
+        <v>227942417.85589701</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>92026249.268583</v>
+        <v>95261276.348582998</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="247">
-        <v>210013135.14625701</v>
-      </c>
-      <c r="D19" s="247">
-        <v>18479876.309966002</v>
-      </c>
-      <c r="E19" s="247">
-        <v>235554977.329956</v>
-      </c>
-      <c r="F19" s="247">
-        <v>464047988.78617901</v>
+      <c r="C19" s="205">
+        <v>275491593.84094697</v>
+      </c>
+      <c r="D19" s="205">
+        <v>22081730.359965999</v>
+      </c>
+      <c r="E19" s="205">
+        <v>280222544.21996802</v>
+      </c>
+      <c r="F19" s="205">
+        <v>577795868.42088103</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>49661701.355117999</v>
+        <v>63349366.195118003</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>39610664.002186999</v>
+        <v>62172993.828704998</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="247">
-        <v>36829051.355117999</v>
-      </c>
-      <c r="D20" s="247">
-        <v>13102655.88992</v>
-      </c>
-      <c r="E20" s="247" t="s">
+      <c r="C20" s="205">
+        <v>47471006.195118003</v>
+      </c>
+      <c r="D20" s="205">
+        <v>16417971.229896</v>
+      </c>
+      <c r="E20" s="205" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="247">
-        <v>49931707.245038003</v>
+      <c r="F20" s="205">
+        <v>63888977.425013997</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22075,24 +22075,24 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="247">
-        <v>12832650</v>
-      </c>
-      <c r="D21" s="247">
-        <v>26508008.112266999</v>
-      </c>
-      <c r="E21" s="247">
+      <c r="C21" s="205">
+        <v>15878360</v>
+      </c>
+      <c r="D21" s="205">
+        <v>45755022.598808996</v>
+      </c>
+      <c r="E21" s="205">
         <v>21881081.52</v>
       </c>
-      <c r="F21" s="247">
-        <v>61221739.632266998</v>
+      <c r="F21" s="205">
+        <v>83514464.118809</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>126614910.26897201</v>
+        <v>252290532.04750901</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22102,17 +22102,17 @@
       <c r="B22" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="247">
-        <v>32194810</v>
-      </c>
-      <c r="D22" s="247" t="s">
+      <c r="C22" s="205">
+        <v>25563399.100000001</v>
+      </c>
+      <c r="D22" s="205" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="247">
+      <c r="E22" s="205">
         <v>4036035.92</v>
       </c>
-      <c r="F22" s="247">
-        <v>36230845.920000002</v>
+      <c r="F22" s="205">
+        <v>29599435.02</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22122,17 +22122,17 @@
       <c r="B23" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="247">
-        <v>68042438.249974996</v>
-      </c>
-      <c r="D23" s="247" t="s">
+      <c r="C23" s="205">
+        <v>67930568.249974996</v>
+      </c>
+      <c r="D23" s="205" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="247">
+      <c r="E23" s="205">
         <v>3207207.12</v>
       </c>
-      <c r="F23" s="247">
-        <v>71249645.369975001</v>
+      <c r="F23" s="205">
+        <v>71137775.369975001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22142,17 +22142,17 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="247">
-        <v>51183371.799344003</v>
-      </c>
-      <c r="D24" s="247">
-        <v>16691291.318482</v>
-      </c>
-      <c r="E24" s="247">
-        <v>25563062.68</v>
-      </c>
-      <c r="F24" s="247">
-        <v>93437725.797826007</v>
+      <c r="C24" s="205">
+        <v>58368679.429343998</v>
+      </c>
+      <c r="D24" s="205">
+        <v>20851146.278480999</v>
+      </c>
+      <c r="E24" s="205">
+        <v>34577476.979999997</v>
+      </c>
+      <c r="F24" s="205">
+        <v>113797302.68782499</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22162,17 +22162,17 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="247">
-        <v>106270829.332285</v>
-      </c>
-      <c r="D25" s="247">
-        <v>22991702.699864</v>
-      </c>
-      <c r="E25" s="247">
-        <v>15952252.08</v>
-      </c>
-      <c r="F25" s="247">
-        <v>145214784.112149</v>
+      <c r="C25" s="205">
+        <v>142851101.47690901</v>
+      </c>
+      <c r="D25" s="205">
+        <v>24190801.809859999</v>
+      </c>
+      <c r="E25" s="205">
+        <v>19236936.719999999</v>
+      </c>
+      <c r="F25" s="205">
+        <v>186278840.006769</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22182,17 +22182,17 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="247">
-        <v>92197364.187153995</v>
-      </c>
-      <c r="D26" s="247">
-        <v>20338068.039972</v>
-      </c>
-      <c r="E26" s="247">
-        <v>85687387.089980006</v>
-      </c>
-      <c r="F26" s="247">
-        <v>198222819.31710601</v>
+      <c r="C26" s="205">
+        <v>124610353.397696</v>
+      </c>
+      <c r="D26" s="205">
+        <v>22722918.039972</v>
+      </c>
+      <c r="E26" s="205">
+        <v>100871170.77998</v>
+      </c>
+      <c r="F26" s="205">
+        <v>248204442.217648</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22202,17 +22202,17 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="247">
-        <v>188605800.348975</v>
-      </c>
-      <c r="D27" s="247">
-        <v>92026249.268583</v>
-      </c>
-      <c r="E27" s="247">
+      <c r="C27" s="205">
+        <v>227942417.85589701</v>
+      </c>
+      <c r="D27" s="205">
+        <v>95261276.348582998</v>
+      </c>
+      <c r="E27" s="205">
         <v>4259459.54</v>
       </c>
-      <c r="F27" s="247">
-        <v>284891509.15755802</v>
+      <c r="F27" s="205">
+        <v>327463153.74448001</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22258,8 +22258,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="247">
-        <v>105815824.835517</v>
+      <c r="C32" s="205">
+        <v>116009536.39545999</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22269,8 +22269,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="247">
-        <v>59054515.013503999</v>
+      <c r="C33" s="205">
+        <v>127341080.376175</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22280,8 +22280,8 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="247">
-        <v>113688549.90902001</v>
+      <c r="C34" s="205">
+        <v>118556158.02902</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22291,8 +22291,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="247">
-        <v>12926360.359952001</v>
+      <c r="C35" s="205">
+        <v>133734374.018489</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="244" t="s">
+      <c r="B41" s="245" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="245"/>
-      <c r="D41" s="246"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.25806451612903225</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1375572186.8389242</v>
+        <v>1752715617.4493456</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.20112823589509213</v>
+        <v>0.25627197433633725</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5463707145.1610756</v>
+        <v>5086563714.5506544</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>273185357.25805378</v>
+        <v>282586873.03059191</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>297463334.71383601</v>
+        <v>349018988.678334</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.20163385571877745</v>
+        <v>0.23658056706041322</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1177801489.5065258</v>
+        <v>1126245835.5420277</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>58890074.475326285</v>
+        <v>62569213.085668206</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,46 +22445,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>291485250.117993</v>
+        <v>495641148.81914401</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.1634821808537669</v>
+        <v>0.27798489253579667</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1491493473.286263</v>
+        <v>1287337574.5851119</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>74574673.664313152</v>
+        <v>71518754.143617332</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>1964520771.670753</v>
+        <v>2597375754.9468236</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.19455472347924854</v>
+        <v>0.25722900417368327</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>8133002107.9538651</v>
+        <v>7500147124.6777935</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>406650105.39769328</v>
+        <v>416674840.25987744</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22494,40 +22494,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22535,13 +22535,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22560,7 +22560,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>51183371.799344003</v>
+        <v>58368679.429343998</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>16691291.318482</v>
+        <v>20851146.278480999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>67874663.117826</v>
+        <v>79219825.707825005</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.13996106851831777</v>
+        <v>0.16335538100063313</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>365500106.200656</v>
+        <v>358314798.570656</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>51579109.902172312</v>
+        <v>47419254.94217331</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>417079216.10282832</v>
+        <v>405734053.5128293</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>20853960.805141415</v>
+        <v>22540780.750712737</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>128778259.167568</v>
+        <v>172091721.67948002</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>21919523.940276001</v>
+        <v>21717727.550274</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>150697783.107844</v>
+        <v>193809449.22975403</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.20181049862428901</v>
+        <v>0.25954450543685287</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>426404111.83243203</v>
+        <v>383090649.32051998</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>169627260.059724</v>
+        <v>169829056.44972599</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>596031371.892156</v>
+        <v>552919705.77024603</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>29801568.5946078</v>
+        <v>30717761.431680337</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>32194810</v>
+        <v>25563399.100000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>32194810</v>
+        <v>25563399.100000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.1333266007730512</v>
+        <v>0.10586430254466098</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>209278458</v>
+        <v>215909868.90000001</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>209278458</v>
+        <v>215909868.90000001</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>10463922.9</v>
+        <v>11994992.716666667</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>136066851.64607301</v>
+        <v>188725035.55556199</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>10240095.673957</v>
+        <v>11409771.353956001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>146306947.32003</v>
+        <v>200134806.909518</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.22248816266071497</v>
+        <v>0.30434388994773054</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>474645620.35392702</v>
+        <v>421987436.44443798</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>36641731.143377893</v>
+        <v>35472055.463378891</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>511287351.49730492</v>
+        <v>457459491.90781689</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>25564367.574865244</v>
+        <v>25414416.217100937</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,35 +22801,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>44810810.039999999</v>
+        <v>85278629.140000001</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>594594.6</v>
+        <v>2320094.6</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>45405404.640000001</v>
+        <v>87598723.739999995</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>9.3056714626639225E-2</v>
+        <v>0.17953037752580164</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>360252473.95999998</v>
+        <v>319784654.86000001</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>82274720.591524154</v>
+        <v>80549220.591524154</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>442527194.55152416</v>
+        <v>400333875.45152414</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>22126359.727576207</v>
+        <v>22240770.858418006</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>113507896.122786</v>
+        <v>133739590.288058</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>23237394.769868001</v>
+        <v>26651421.779856998</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>136745290.892654</v>
+        <v>160391012.06791499</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.24631768828809941</v>
+        <v>0.2889104484466003</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>360410935.87721401</v>
+        <v>340179241.71194202</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>58001999.352785602</v>
+        <v>54587972.342796609</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>418412935.2299996</v>
+        <v>394767214.05473864</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>20920646.761499979</v>
+        <v>21931511.891929924</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>210013135.14625701</v>
+        <v>275491593.84094697</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>18479876.309966002</v>
+        <v>22081730.359965999</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>228493011.45622301</v>
+        <v>297573324.20091295</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.21685095148170358</v>
+        <v>0.28241151918514823</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>751745209.85374296</v>
+        <v>686266751.15905309</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>73448700.029190391</v>
+        <v>69846845.979190394</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>825193909.88293338</v>
+        <v>756113597.13824344</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>41259695.494146667</v>
+        <v>42006310.952124633</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>106270829.332285</v>
+        <v>142851101.47690901</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>22991702.699864</v>
+        <v>24190801.809859999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>129262532.032149</v>
+        <v>167041903.286769</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.22714759371957852</v>
+        <v>0.29353568884517328</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>399016229.66771501</v>
+        <v>362435957.52309096</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>40789701.300136</v>
+        <v>39590602.190140001</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>439805930.96785098</v>
+        <v>402026559.71323097</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>21990296.548392549</v>
+        <v>22334808.872957274</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>68042438.249974996</v>
+        <v>67930568.249974996</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>68042438.249974996</v>
+        <v>67930568.249974996</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.16836617265810105</v>
+        <v>0.16808935830194782</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>336091225.75002503</v>
+        <v>336203095.75002503</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>336091225.75002503</v>
+        <v>336203095.75002503</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>16804561.287501253</v>
+        <v>18677949.763890281</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>92488701.064246997</v>
+        <v>108828331.84418499</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>25701757.190308999</v>
+        <v>32668296.128307998</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>118190458.254556</v>
+        <v>141496627.97249299</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.21786994552061628</v>
+        <v>0.26083207631974475</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>311528607.93575299</v>
+        <v>295188977.15581501</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>112762633.0276864</v>
+        <v>105796094.08968741</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>424291240.9634394</v>
+        <v>400985071.24550241</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>21214562.048171971</v>
+        <v>22276948.402527913</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>92197364.187153995</v>
+        <v>124610353.397696</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>20338068.039972</v>
+        <v>22722918.039972</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>112535432.227126</v>
+        <v>147333271.437668</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.16300713700052707</v>
+        <v>0.2134116720990101</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>539432231.81284595</v>
+        <v>507019242.60230398</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>38403532.570653267</v>
+        <v>36018682.570653267</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>577835764.38349926</v>
+        <v>543037925.1729573</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>28891788.219174962</v>
+        <v>30168773.62071985</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>61750218.379142001</v>
+        <v>77944829.396174997</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>5632116.9003720004</v>
+        <v>6970810.6003719997</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>67382335.279514</v>
+        <v>84915639.996546999</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.14963637845779384</v>
+        <v>0.18857269922154482</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>324792804.62085801</v>
+        <v>308598193.60382497</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>58132037.899441808</v>
+        <v>56793344.199441805</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>382924842.52029979</v>
+        <v>365391537.80326682</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>19146242.126014989</v>
+        <v>20299529.877959266</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>188605800.348975</v>
+        <v>227942417.85589701</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>92026249.268583</v>
+        <v>95261276.348582998</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>280632049.617558</v>
+        <v>323203694.20447999</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.307320402763817</v>
+        <v>0.35394064795177926</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>394745141.651025</v>
+        <v>355408524.14410299</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>237780695.72413439</v>
+        <v>234545668.6441344</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>632525837.37515938</v>
+        <v>589954192.78823733</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>31626291.868757971</v>
+        <v>32775232.932679851</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>49661701.355117999</v>
+        <v>63349366.195118003</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>39610664.002186999</v>
+        <v>62172993.828704998</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>89272365.35730499</v>
+        <v>125522360.02382299</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.17250841263129085</v>
+        <v>0.24255729072234361</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>209863987.64488199</v>
+        <v>196176322.80488199</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>218359367.90569937</v>
+        <v>195797038.07918137</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>428223355.5505814</v>
+        <v>391973360.88406336</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>21411167.777529068</v>
+        <v>21776297.826892409</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1375572186.8389242</v>
+        <v>1752715617.4493456</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>297463334.71383601</v>
+        <v>349018988.678334</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>1673035521.5527599</v>
+        <v>2101734606.1276798</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.20121794894806244</v>
+        <v>0.25277809181581029</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5463707145.1610765</v>
+        <v>5086563714.5506544</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1177801489.5065255</v>
+        <v>1126245835.5420277</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>6641508634.6676016</v>
+        <v>6212809550.0926819</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>332075431.73338008</v>
+        <v>345156086.11626011</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23363,10 +23363,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23374,8 +23374,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>25563062.68</v>
+        <v>34577476.979999997</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>9592792.6799999997</v>
+        <v>28043242.68</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>19841441.25</v>
+        <v>28486486.239999998</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>235554977.329956</v>
+        <v>280222544.21996802</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>15952252.08</v>
+        <v>19236936.719999999</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="D79" s="192">
         <f>IF(E11="",0,E11)</f>
-        <v>2972973</v>
+        <v>26756757</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>85687387.089980006</v>
+        <v>100871170.77998</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>45345043.799999997</v>
+        <v>58585511.899998002</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>481069389.609936</v>
+        <v>617339586.21994603</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>105815824.835517</v>
+        <v>116009536.39545999</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.38054401035650454</v>
+        <v>0.41720351646977288</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>172248793.06869256</v>
+        <v>162055081.50874954</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>8612439.6534346286</v>
+        <v>9003060.0838194191</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>59054515.013503999</v>
+        <v>127341080.376175</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.14140778603561799</v>
+        <v>0.30492199018586336</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>358564038.17301762</v>
+        <v>290277472.8103466</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17928201.908650883</v>
+        <v>16126526.267241478</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>126614910.26897201</v>
+        <v>252290532.04750901</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.11644939593431008</v>
+        <v>0.23203491590735426</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>960680642.04455268</v>
+        <v>835005020.26601577</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>48034032.102227636</v>
+        <v>46389167.792556435</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,19 +23760,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>291485250.117993</v>
+        <v>495641148.81914401</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.1634821808537669</v>
+        <v>0.27798489253579667</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1491493473.286263</v>
+        <v>1287337574.5851119</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>74574673.664313152</v>
+        <v>71518754.143617332</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -24391,11 +24391,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24519,10 +24519,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24551,40 +24551,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24592,13 +24592,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24617,7 +24617,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25420,10 +25420,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25431,8 +25431,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -26448,11 +26448,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="223" t="s">
+      <c r="B41" s="224" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="224"/>
-      <c r="D41" s="225"/>
+      <c r="C41" s="225"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26576,10 +26576,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="220" t="s">
+      <c r="B46" s="221" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="221"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26608,40 +26608,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="227" t="s">
+      <c r="B48" s="228" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="228"/>
-      <c r="D48" s="228"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="228"/>
-      <c r="G48" s="228"/>
-      <c r="H48" s="228"/>
-      <c r="I48" s="228"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="240"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="242"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="222" t="s">
+      <c r="B49" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="222" t="s">
+      <c r="C49" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="217" t="s">
+      <c r="D49" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="218"/>
-      <c r="F49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="220"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="222" t="s">
+      <c r="J49" s="223" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26649,13 +26649,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="243" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26674,7 +26674,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="222"/>
+      <c r="J50" s="223"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="243"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27477,10 +27477,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="222" t="s">
+      <c r="B68" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="222" t="s">
+      <c r="C68" s="223" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27488,8 +27488,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="222"/>
-      <c r="C69" s="222"/>
+      <c r="B69" s="223"/>
+      <c r="C69" s="223"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="237" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="238"/>
-      <c r="D87" s="238"/>
-      <c r="E87" s="238"/>
-      <c r="F87" s="239"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 11 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 12 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,6 +1927,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1946,15 +1955,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,11 +4872,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4884,6 +4879,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,11 +6929,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6941,6 +6936,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,11 +8986,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8998,6 +8993,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,11 +11043,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11055,6 +11050,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,11 +13085,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13097,6 +13092,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>58368679.429343998</v>
+        <v>86134461.094157994</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>20851146.278480999</v>
+        <v>22140216.108477</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>172091721.67948002</v>
+        <v>187770500.990475</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>21717727.550274</v>
+        <v>30994065.455272</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>77944829.396174997</v>
+        <v>90330395.193459004</v>
       </c>
       <c r="D10" s="205">
-        <v>6970810.6003719997</v>
+        <v>8137421.2493679998</v>
       </c>
       <c r="E10" s="205">
-        <v>58585511.899998002</v>
+        <v>67988214.499998003</v>
       </c>
       <c r="F10" s="205">
-        <v>143501151.89654499</v>
+        <v>166456030.94282499</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>188725035.55556199</v>
+        <v>249048066.50765699</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>11409771.353956001</v>
+        <v>12242861.503951</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,27 +21805,27 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>108828331.84418499</v>
+        <v>127666059.844179</v>
       </c>
       <c r="D11" s="205">
-        <v>32668296.128307998</v>
+        <v>40837106.988243997</v>
       </c>
       <c r="E11" s="205">
         <v>26756757</v>
       </c>
       <c r="F11" s="205">
-        <v>168253384.97249299</v>
+        <v>195259923.832423</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>85278629.140000001</v>
+        <v>89427277.780000001</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>2320094.6</v>
+        <v>7082418.9199999999</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>83976070.315963</v>
+        <v>93939827.095957994</v>
       </c>
       <c r="D12" s="205">
-        <v>14825637.450284</v>
+        <v>23649853.735282</v>
       </c>
       <c r="E12" s="205">
         <v>14414414</v>
       </c>
       <c r="F12" s="205">
-        <v>113216121.766247</v>
+        <v>132004094.83124</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>133739590.288058</v>
+        <v>146645254.30481699</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>26651421.779856998</v>
+        <v>27700232.589857001</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>88115651.363517001</v>
+        <v>93830673.894517004</v>
       </c>
       <c r="D13" s="205">
-        <v>6892090.09999</v>
+        <v>7344211.7199900001</v>
       </c>
       <c r="E13" s="205">
         <v>13628828.68</v>
       </c>
       <c r="F13" s="205">
-        <v>108636570.143507</v>
+        <v>114803714.294507</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>275491593.84094697</v>
+        <v>319031714.35037303</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>22081730.359965999</v>
+        <v>24841130.359965999</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>188725035.55556199</v>
+        <v>249048066.50765699</v>
       </c>
       <c r="D14" s="205">
-        <v>11409771.353956001</v>
+        <v>12242861.503951</v>
       </c>
       <c r="E14" s="205">
-        <v>28486486.239999998</v>
+        <v>33718918.590000004</v>
       </c>
       <c r="F14" s="205">
-        <v>228621293.14951801</v>
+        <v>255109846.60160801</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>142851101.47690901</v>
+        <v>168120864.63430399</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>24190801.809859999</v>
+        <v>30287594.56986</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>108828331.84418499</v>
+        <v>127666059.844179</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>32668296.128307998</v>
+        <v>40837106.988243997</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>133739590.288058</v>
+        <v>146645254.30481699</v>
       </c>
       <c r="D16" s="205">
-        <v>26651421.779856998</v>
+        <v>27700232.589857001</v>
       </c>
       <c r="E16" s="205">
         <v>7175675.5999999996</v>
       </c>
       <c r="F16" s="205">
-        <v>167566687.66791499</v>
+        <v>181521162.494674</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>124610353.397696</v>
+        <v>153920681.22660801</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>22722918.039972</v>
+        <v>26441026.139972001</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21965,27 +21965,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>85278629.140000001</v>
+        <v>89427277.780000001</v>
       </c>
       <c r="D17" s="205">
-        <v>2320094.6</v>
+        <v>7082418.9199999999</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>87598723.739999995</v>
+        <v>96509696.700000003</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>77944829.396174997</v>
+        <v>90330395.193459004</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>6970810.6003719997</v>
+        <v>8137421.2493679998</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>466344443.26396602</v>
+        <v>478548075.04396403</v>
       </c>
       <c r="D18" s="205">
         <v>5313981.1899769995</v>
       </c>
       <c r="E18" s="205">
-        <v>2970270.24</v>
+        <v>4043243.2</v>
       </c>
       <c r="F18" s="205">
-        <v>474628694.69394302</v>
+        <v>487905299.43394101</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>227942417.85589701</v>
+        <v>253962994.37583601</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>95261276.348582998</v>
+        <v>112968670.74834301</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>275491593.84094697</v>
+        <v>319031714.35037303</v>
       </c>
       <c r="D19" s="205">
-        <v>22081730.359965999</v>
+        <v>24841130.359965999</v>
       </c>
       <c r="E19" s="205">
-        <v>280222544.21996802</v>
+        <v>338000021.619968</v>
       </c>
       <c r="F19" s="205">
-        <v>577795868.42088103</v>
+        <v>681872866.33030701</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>63349366.195118003</v>
+        <v>99455498.264208004</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>62172993.828704998</v>
+        <v>66649448.201086998</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,16 +22049,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>47471006.195118003</v>
+        <v>75798478.264208004</v>
       </c>
       <c r="D20" s="205">
-        <v>16417971.229896</v>
+        <v>16789142.409896001</v>
       </c>
       <c r="E20" s="205" t="s">
         <v>169</v>
       </c>
       <c r="F20" s="205">
-        <v>63888977.425013997</v>
+        <v>92587620.674104005</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>15878360</v>
+        <v>23657020</v>
       </c>
       <c r="D21" s="205">
-        <v>45755022.598808996</v>
+        <v>49860305.791190997</v>
       </c>
       <c r="E21" s="205">
-        <v>21881081.52</v>
+        <v>24237838.32</v>
       </c>
       <c r="F21" s="205">
-        <v>83514464.118809</v>
+        <v>97755164.111191005</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>252290532.04750901</v>
+        <v>263561198.787453</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22103,7 +22103,7 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>25563399.100000001</v>
+        <v>26153399.100000001</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
@@ -22112,7 +22112,7 @@
         <v>4036035.92</v>
       </c>
       <c r="F22" s="205">
-        <v>29599435.02</v>
+        <v>30189435.02</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22123,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>67930568.249974996</v>
+        <v>93771608.249974996</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22132,7 +22132,7 @@
         <v>3207207.12</v>
       </c>
       <c r="F23" s="205">
-        <v>71137775.369975001</v>
+        <v>96978815.369975001</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>58368679.429343998</v>
+        <v>86134461.094157994</v>
       </c>
       <c r="D24" s="205">
-        <v>20851146.278480999</v>
+        <v>22140216.108477</v>
       </c>
       <c r="E24" s="205">
-        <v>34577476.979999997</v>
+        <v>45358738.119999997</v>
       </c>
       <c r="F24" s="205">
-        <v>113797302.68782499</v>
+        <v>153633415.32263499</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>142851101.47690901</v>
+        <v>168120864.63430399</v>
       </c>
       <c r="D25" s="205">
-        <v>24190801.809859999</v>
+        <v>30287594.56986</v>
       </c>
       <c r="E25" s="205">
-        <v>19236936.719999999</v>
+        <v>72822521.819999993</v>
       </c>
       <c r="F25" s="205">
-        <v>186278840.006769</v>
+        <v>271230981.02416402</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>124610353.397696</v>
+        <v>153920681.22660801</v>
       </c>
       <c r="D26" s="205">
-        <v>22722918.039972</v>
+        <v>26441026.139972001</v>
       </c>
       <c r="E26" s="205">
-        <v>100871170.77998</v>
+        <v>124450449.88998</v>
       </c>
       <c r="F26" s="205">
-        <v>248204442.217648</v>
+        <v>304812157.25656003</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>227942417.85589701</v>
+        <v>253962994.37583601</v>
       </c>
       <c r="D27" s="205">
-        <v>95261276.348582998</v>
+        <v>112968670.74834301</v>
       </c>
       <c r="E27" s="205">
         <v>4259459.54</v>
       </c>
       <c r="F27" s="205">
-        <v>327463153.74448001</v>
+        <v>371191124.66417903</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>116009536.39545999</v>
+        <v>119496802.195455</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>127341080.376175</v>
+        <v>135847296.89607501</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>118556158.02902</v>
+        <v>126972770.68896399</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>133734374.018489</v>
+        <v>136588428.09848899</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.35483870967741937</v>
+        <v>0.38709677419354838</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>1752715617.4493456</v>
+        <v>2091438775.9160492</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.25627197433633725</v>
+        <v>0.30579812205220358</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>5086563714.5506544</v>
+        <v>4747840556.083951</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>282586873.03059191</v>
+        <v>279284738.59317356</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>349018988.678334</v>
+        <v>410322192.83439702</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.23658056706041322</v>
+        <v>0.2781346007156657</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1126245835.5420277</v>
+        <v>1064942631.3859646</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>62569213.085668206</v>
+        <v>62643684.199174389</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>495641148.81914401</v>
+        <v>518905297.87898302</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.27798489253579667</v>
+        <v>0.29103280429966821</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1287337574.5851119</v>
+        <v>1264073425.5252728</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>71518754.143617332</v>
+        <v>74357260.325016052</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>2597375754.9468236</v>
+        <v>3020666266.6294293</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.25722900417368327</v>
+        <v>0.29914923715842318</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>7500147124.6777935</v>
+        <v>7076856612.9951878</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>416674840.25987744</v>
+        <v>416285683.11736399</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>58368679.429343998</v>
+        <v>86134461.094157994</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>20851146.278480999</v>
+        <v>22140216.108477</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>79219825.707825005</v>
+        <v>108274677.20263499</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.16335538100063313</v>
+        <v>0.2232679886521125</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>358314798.570656</v>
+        <v>330549016.90584201</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>47419254.94217331</v>
+        <v>46130185.112177312</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>405734053.5128293</v>
+        <v>376679202.01801932</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>22540780.750712737</v>
+        <v>22157600.11870702</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>172091721.67948002</v>
+        <v>187770500.990475</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>21717727.550274</v>
+        <v>30994065.455272</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>193809449.22975403</v>
+        <v>218764566.44574699</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.25954450543685287</v>
+        <v>0.2929637405757205</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>383090649.32051998</v>
+        <v>367411870.009525</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>169829056.44972599</v>
+        <v>160552718.54472801</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>552919705.77024603</v>
+        <v>527964588.55425298</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>30717761.431680337</v>
+        <v>31056740.503191352</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>25563399.100000001</v>
+        <v>26153399.100000001</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>25563399.100000001</v>
+        <v>26153399.100000001</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.10586430254466098</v>
+        <v>0.10830763718325956</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>215909868.90000001</v>
+        <v>215319868.90000001</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>215909868.90000001</v>
+        <v>215319868.90000001</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>11994992.716666667</v>
+        <v>12665874.641176471</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>188725035.55556199</v>
+        <v>249048066.50765699</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>11409771.353956001</v>
+        <v>12242861.503951</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>200134806.909518</v>
+        <v>261290928.011608</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.30434388994773054</v>
+        <v>0.39734366383883268</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>421987436.44443798</v>
+        <v>361664405.49234301</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>35472055.463378891</v>
+        <v>34638965.313383892</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>457459491.90781689</v>
+        <v>396303370.80572689</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>25414416.217100937</v>
+        <v>23311962.988572169</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,35 +22801,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>85278629.140000001</v>
+        <v>89427277.780000001</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>2320094.6</v>
+        <v>7082418.9199999999</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>87598723.739999995</v>
+        <v>96509696.700000003</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.17953037752580164</v>
+        <v>0.19779309039795853</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>319784654.86000001</v>
+        <v>315636006.22000003</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>80549220.591524154</v>
+        <v>75786896.271524146</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>400333875.45152414</v>
+        <v>391422902.49152416</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>22240770.858418006</v>
+        <v>23024876.617148481</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>133739590.288058</v>
+        <v>146645254.30481699</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>26651421.779856998</v>
+        <v>27700232.589857001</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>160391012.06791499</v>
+        <v>174345486.894674</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.2889104484466003</v>
+        <v>0.31404648024823661</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>340179241.71194202</v>
+        <v>327273577.69518304</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>54587972.342796609</v>
+        <v>53539161.532796606</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>394767214.05473864</v>
+        <v>380812739.2279796</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>21931511.891929924</v>
+        <v>22400749.366351742</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>275491593.84094697</v>
+        <v>319031714.35037303</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>22081730.359965999</v>
+        <v>24841130.359965999</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>297573324.20091295</v>
+        <v>343872844.71033901</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.28241151918514823</v>
+        <v>0.32635201001954417</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>686266751.15905309</v>
+        <v>642726630.64962697</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>69846845.979190394</v>
+        <v>67087445.979190394</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>756113597.13824344</v>
+        <v>709814076.62881732</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>42006310.952124633</v>
+        <v>41753769.213459842</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>142851101.47690901</v>
+        <v>168120864.63430399</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>24190801.809859999</v>
+        <v>30287594.56986</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>167041903.286769</v>
+        <v>198408459.204164</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.29353568884517328</v>
+        <v>0.34865481414696492</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>362435957.52309096</v>
+        <v>337166194.36569601</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>39590602.190140001</v>
+        <v>33493809.43014</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>402026559.71323097</v>
+        <v>370660003.79583597</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>22334808.872957274</v>
+        <v>21803529.635049175</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>67930568.249974996</v>
+        <v>93771608.249974996</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>67930568.249974996</v>
+        <v>93771608.249974996</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.16808935830194782</v>
+        <v>0.23203117335450429</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>336203095.75002503</v>
+        <v>310362055.75002503</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>336203095.75002503</v>
+        <v>310362055.75002503</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>18677949.763890281</v>
+        <v>18256591.514707357</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>108828331.84418499</v>
+        <v>127666059.844179</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>32668296.128307998</v>
+        <v>40837106.988243997</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>141496627.97249299</v>
+        <v>168503166.832423</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.26083207631974475</v>
+        <v>0.31061539416965711</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>295188977.15581501</v>
+        <v>276351249.15582097</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>105796094.08968741</v>
+        <v>97627283.229751408</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>400985071.24550241</v>
+        <v>373978532.38557243</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>22276948.402527913</v>
+        <v>21998737.199151319</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>124610353.397696</v>
+        <v>153920681.22660801</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>22722918.039972</v>
+        <v>26441026.139972001</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>147333271.437668</v>
+        <v>180361707.36658001</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.2134116720990101</v>
+        <v>0.26125323340844042</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>507019242.60230398</v>
+        <v>477708914.77339196</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>36018682.570653267</v>
+        <v>32300574.470653266</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>543037925.1729573</v>
+        <v>510009489.24404526</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>30168773.62071985</v>
+        <v>30000558.190826192</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>77944829.396174997</v>
+        <v>90330395.193459004</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>6970810.6003719997</v>
+        <v>8137421.2493679998</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>84915639.996546999</v>
+        <v>98467816.442827001</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.18857269922154482</v>
+        <v>0.21866810323552369</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>308598193.60382497</v>
+        <v>296212627.80654097</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>56793344.199441805</v>
+        <v>55626733.55044581</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>365391537.80326682</v>
+        <v>351839361.35698682</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>20299529.877959266</v>
+        <v>20696433.020999223</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>227942417.85589701</v>
+        <v>253962994.37583601</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>95261276.348582998</v>
+        <v>112968670.74834301</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>323203694.20447999</v>
+        <v>366931665.12417901</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.35394064795177926</v>
+        <v>0.40182718711721027</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>355408524.14410299</v>
+        <v>329387947.62416399</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>234545668.6441344</v>
+        <v>216838274.24437439</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>589954192.78823733</v>
+        <v>546226221.86853838</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>32775232.932679851</v>
+        <v>32130954.227561083</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>63349366.195118003</v>
+        <v>99455498.264208004</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>62172993.828704998</v>
+        <v>66649448.201086998</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>125522360.02382299</v>
+        <v>166104946.46529502</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.24255729072234361</v>
+        <v>0.3209783960607116</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>196176322.80488199</v>
+        <v>160070190.73579198</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>195797038.07918137</v>
+        <v>191320583.70679939</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>391973360.88406336</v>
+        <v>351390774.44259137</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>21776297.826892409</v>
+        <v>20670045.55544655</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>1752715617.4493456</v>
+        <v>2091438775.9160492</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>349018988.678334</v>
+        <v>410322192.83439702</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>2101734606.1276798</v>
+        <v>2501760968.7504458</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.25277809181581029</v>
+        <v>0.30088973270757152</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>5086563714.5506544</v>
+        <v>4747840556.083951</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1126245835.5420277</v>
+        <v>1064942631.3859646</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>6212809550.0926819</v>
+        <v>5812783187.4699163</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>345156086.11626011</v>
+        <v>341928422.79234803</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>34577476.979999997</v>
+        <v>45358738.119999997</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>28486486.239999998</v>
+        <v>33718918.590000004</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>280222544.21996802</v>
+        <v>338000021.619968</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>19236936.719999999</v>
+        <v>72822521.819999993</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>100871170.77998</v>
+        <v>124450449.88998</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>58585511.899998002</v>
+        <v>67988214.499998003</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>21881081.52</v>
+        <v>24237838.32</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>617339586.21994603</v>
+        <v>780055080.71994603</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>116009536.39545999</v>
+        <v>119496802.195455</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.41720351646977288</v>
+        <v>0.42974472299320166</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>162055081.50874954</v>
+        <v>158567815.70875454</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9003060.0838194191</v>
+        <v>9327518.5711032078</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>127341080.376175</v>
+        <v>135847296.89607501</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.30492199018586336</v>
+        <v>0.32529037768923386</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>290277472.8103466</v>
+        <v>281771256.29044658</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16126526.267241478</v>
+        <v>16574779.781790975</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>252290532.04750901</v>
+        <v>263561198.787453</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.23203491590735426</v>
+        <v>0.24240069613699144</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>835005020.26601577</v>
+        <v>823734353.52607179</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>46389167.792556435</v>
+        <v>48454961.972121872</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,29 +23760,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>495641148.81914401</v>
+        <v>518905297.87898302</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.27798489253579667</v>
+        <v>0.29103280429966821</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1287337574.5851119</v>
+        <v>1264073425.5252728</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>71518754.143617332</v>
+        <v>74357260.325016052</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23790,6 +23785,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,11 +25835,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25847,6 +25842,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,11 +27892,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27904,6 +27899,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PENCAPAIAN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D56B04B-7FBF-4EDC-A4FC-CD5C25219900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -27,18 +28,8 @@
     <sheet name="NOV" sheetId="13" r:id="rId13"/>
     <sheet name="DES" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -602,16 +593,16 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 12 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 15 MEI 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.#0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.#0"/>
   </numFmts>
   <fonts count="43" x14ac:knownFonts="1">
     <font>
@@ -1230,7 +1221,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1268,7 +1259,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1555,7 +1546,7 @@
     <xf numFmtId="9" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1564,53 +1555,53 @@
     <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="41" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="33" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1661,19 +1652,19 @@
     <xf numFmtId="3" fontId="10" fillId="26" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1688,11 +1679,11 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="37" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1701,7 +1692,7 @@
     <xf numFmtId="0" fontId="37" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="37" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1716,47 +1707,47 @@
     <xf numFmtId="3" fontId="35" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="40" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1786,25 +1777,25 @@
     <xf numFmtId="0" fontId="41" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1813,7 +1804,7 @@
     <xf numFmtId="0" fontId="39" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="39" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1822,14 +1813,11 @@
     <xf numFmtId="0" fontId="26" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2702,7 +2690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:C18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2712,16 +2700,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="206" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="206"/>
+      <c r="B1" s="205" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="205"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="206"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2772,10 +2760,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="208"/>
+      <c r="C11" s="207"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -2845,7 +2833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3428,11 +3416,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -3556,10 +3544,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -3588,40 +3576,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -3629,13 +3617,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -3654,7 +3642,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -3664,7 +3652,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4457,10 +4445,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -4468,8 +4456,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -4663,13 +4651,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4902,7 +4890,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5485,11 +5473,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -5613,10 +5601,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -5645,40 +5633,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -5686,13 +5674,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -5711,7 +5699,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -5721,7 +5709,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6514,10 +6502,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -6525,8 +6513,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -6720,13 +6708,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6959,7 +6947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7542,11 +7530,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>167</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -7670,10 +7658,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -7702,40 +7690,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -7743,13 +7731,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -7768,7 +7756,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -7778,7 +7766,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8571,10 +8559,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -8582,8 +8570,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -8777,13 +8765,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -9016,7 +9004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9599,11 +9587,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -9727,10 +9715,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -9759,40 +9747,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -9800,13 +9788,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -9825,7 +9813,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -9835,7 +9823,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10628,10 +10616,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -10639,8 +10627,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -10834,13 +10822,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11073,7 +11061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11656,11 +11644,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -11783,10 +11771,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -11815,40 +11803,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -11856,13 +11844,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -11881,7 +11869,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -11891,7 +11879,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12670,10 +12658,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -12681,8 +12669,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -12876,13 +12864,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13115,7 +13103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA29"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13172,10 +13160,10 @@
       <c r="AA1" s="20"/>
     </row>
     <row r="3" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="206" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="207"/>
+      <c r="C3" s="206"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -14648,13 +14636,13 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="209" t="s">
+      <c r="B29" s="208" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="209"/>
-      <c r="F29" s="209"/>
+      <c r="C29" s="208"/>
+      <c r="D29" s="208"/>
+      <c r="E29" s="208"/>
+      <c r="F29" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14667,7 +14655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15186,10 +15174,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="210" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="211"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -15229,23 +15217,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="212" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="212" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="213" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="214"/>
+      <c r="F47" s="215"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="212" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -15253,13 +15241,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="209" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="212"/>
+      <c r="C48" s="212"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -15278,7 +15266,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="212"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -15288,7 +15276,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="209"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -16203,7 +16191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16721,10 +16709,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="211" t="s">
+      <c r="B44" s="210" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="212"/>
+      <c r="C44" s="211"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -16764,23 +16752,23 @@
       <c r="N46" s="100"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="212" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="213" t="s">
+      <c r="C47" s="212" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="213" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="216"/>
+      <c r="E47" s="214"/>
+      <c r="F47" s="215"/>
       <c r="G47" s="101" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="101"/>
       <c r="I47" s="101"/>
-      <c r="J47" s="213" t="s">
+      <c r="J47" s="212" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="102" t="s">
@@ -16788,13 +16776,13 @@
       </c>
       <c r="L47" s="102"/>
       <c r="M47" s="102"/>
-      <c r="N47" s="210" t="s">
+      <c r="N47" s="209" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
+      <c r="B48" s="212"/>
+      <c r="C48" s="212"/>
       <c r="D48" s="103" t="s">
         <v>150</v>
       </c>
@@ -16813,7 +16801,7 @@
       <c r="I48" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="213"/>
+      <c r="J48" s="212"/>
       <c r="K48" s="104" t="s">
         <v>143</v>
       </c>
@@ -16823,7 +16811,7 @@
       <c r="M48" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="210"/>
+      <c r="N48" s="209"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -17738,7 +17726,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:Q70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18408,10 +18396,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="221" t="s">
+      <c r="B44" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="222"/>
+      <c r="C44" s="221"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -18476,23 +18464,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="223" t="s">
+      <c r="B47" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="223" t="s">
+      <c r="C47" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="218" t="s">
+      <c r="D47" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="219"/>
-      <c r="F47" s="220"/>
+      <c r="E47" s="218"/>
+      <c r="F47" s="219"/>
       <c r="G47" s="70" t="s">
         <v>139</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="70"/>
-      <c r="J47" s="223" t="s">
+      <c r="J47" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -18500,13 +18488,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="217" t="s">
+      <c r="N47" s="216" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="223"/>
-      <c r="C48" s="223"/>
+      <c r="B48" s="222"/>
+      <c r="C48" s="222"/>
       <c r="D48" s="71" t="s">
         <v>150</v>
       </c>
@@ -18525,7 +18513,7 @@
       <c r="I48" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="J48" s="223"/>
+      <c r="J48" s="222"/>
       <c r="K48" s="34" t="s">
         <v>143</v>
       </c>
@@ -18535,7 +18523,7 @@
       <c r="M48" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N48" s="217"/>
+      <c r="N48" s="216"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -19514,7 +19502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:R94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20157,11 +20145,11 @@
       <c r="C38" s="85"/>
     </row>
     <row r="41" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -20279,10 +20267,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -20305,40 +20293,40 @@
       </c>
     </row>
     <row r="48" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="235"/>
-      <c r="L48" s="236"/>
-      <c r="M48" s="236"/>
-      <c r="N48" s="237"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="235"/>
+      <c r="M48" s="235"/>
+      <c r="N48" s="236"/>
     </row>
     <row r="49" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="234" t="s">
+      <c r="B49" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="234" t="s">
+      <c r="C49" s="233" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="231" t="s">
+      <c r="D49" s="230" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="232"/>
-      <c r="F49" s="233"/>
+      <c r="E49" s="231"/>
+      <c r="F49" s="232"/>
       <c r="G49" s="159" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="159"/>
       <c r="I49" s="159"/>
-      <c r="J49" s="234" t="s">
+      <c r="J49" s="233" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="160" t="s">
@@ -20346,13 +20334,13 @@
       </c>
       <c r="L49" s="160"/>
       <c r="M49" s="160"/>
-      <c r="N49" s="227" t="s">
+      <c r="N49" s="226" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="234"/>
-      <c r="C50" s="234"/>
+      <c r="B50" s="233"/>
+      <c r="C50" s="233"/>
       <c r="D50" s="161" t="s">
         <v>150</v>
       </c>
@@ -20371,7 +20359,7 @@
       <c r="I50" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="234"/>
+      <c r="J50" s="233"/>
       <c r="K50" s="163" t="s">
         <v>143</v>
       </c>
@@ -20381,7 +20369,7 @@
       <c r="M50" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="227"/>
+      <c r="N50" s="226"/>
     </row>
     <row r="51" spans="2:14" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="183" t="s">
@@ -21172,10 +21160,10 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -21186,8 +21174,8 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -21373,13 +21361,13 @@
       </c>
     </row>
     <row r="87" spans="2:9" s="158" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="228" t="s">
+      <c r="B87" s="227" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="229"/>
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="230"/>
+      <c r="C87" s="228"/>
+      <c r="D87" s="228"/>
+      <c r="E87" s="228"/>
+      <c r="F87" s="229"/>
       <c r="G87" s="167"/>
       <c r="H87" s="167"/>
       <c r="I87" s="168"/>
@@ -21612,7 +21600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -21661,7 +21649,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21731,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>86134461.094157994</v>
+        <v>112604837.314255</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>22140216.108477</v>
+        <v>24457774.658475999</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,151 +21753,151 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>187770500.990475</v>
+        <v>227558165.142396</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>30994065.455272</v>
+        <v>39427622.934717</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="205">
-        <v>90330395.193459004</v>
-      </c>
-      <c r="D10" s="205">
-        <v>8137421.2493679998</v>
-      </c>
-      <c r="E10" s="205">
-        <v>67988214.499998003</v>
-      </c>
-      <c r="F10" s="205">
-        <v>166456030.94282499</v>
+      <c r="C10" s="15">
+        <v>108591336.892453</v>
+      </c>
+      <c r="D10" s="15">
+        <v>13237421.249368001</v>
+      </c>
+      <c r="E10" s="15">
+        <v>83152214.019998997</v>
+      </c>
+      <c r="F10" s="15">
+        <v>204980972.16181999</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>249048066.50765699</v>
+        <v>304658045.987652</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>12242861.503951</v>
+        <v>13595672.313951001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="205">
-        <v>127666059.844179</v>
-      </c>
-      <c r="D11" s="205">
-        <v>40837106.988243997</v>
-      </c>
-      <c r="E11" s="205">
+      <c r="C11" s="15">
+        <v>165098050.07452199</v>
+      </c>
+      <c r="D11" s="15">
+        <v>47061462.078239001</v>
+      </c>
+      <c r="E11" s="15">
         <v>26756757</v>
       </c>
-      <c r="F11" s="205">
-        <v>195259923.832423</v>
+      <c r="F11" s="15">
+        <v>238916269.15276101</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>89427277.780000001</v>
+        <v>114350700.78</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>7082418.9199999999</v>
+        <v>18496237.719999999</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="205">
-        <v>93939827.095957994</v>
-      </c>
-      <c r="D12" s="205">
-        <v>23649853.735282</v>
-      </c>
-      <c r="E12" s="205">
-        <v>14414414</v>
-      </c>
-      <c r="F12" s="205">
-        <v>132004094.83124</v>
+      <c r="C12" s="15">
+        <v>111013927.90795401</v>
+      </c>
+      <c r="D12" s="15">
+        <v>26899767.214782</v>
+      </c>
+      <c r="E12" s="15">
+        <v>15987386.960000001</v>
+      </c>
+      <c r="F12" s="15">
+        <v>153901082.08273599</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>146645254.30481699</v>
+        <v>188104283.13257799</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>27700232.589857001</v>
+        <v>33735268.665836997</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="205">
-        <v>93830673.894517004</v>
-      </c>
-      <c r="D13" s="205">
-        <v>7344211.7199900001</v>
-      </c>
-      <c r="E13" s="205">
-        <v>13628828.68</v>
-      </c>
-      <c r="F13" s="205">
-        <v>114803714.294507</v>
+      <c r="C13" s="15">
+        <v>116544237.234442</v>
+      </c>
+      <c r="D13" s="15">
+        <v>12527855.719935</v>
+      </c>
+      <c r="E13" s="15">
+        <v>21552252.02</v>
+      </c>
+      <c r="F13" s="15">
+        <v>150624344.97437701</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>319031714.35037303</v>
+        <v>407270698.05517799</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>24841130.359965999</v>
+        <v>36349333.359916002</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="205">
-        <v>249048066.50765699</v>
-      </c>
-      <c r="D14" s="205">
-        <v>12242861.503951</v>
-      </c>
-      <c r="E14" s="205">
-        <v>33718918.590000004</v>
-      </c>
-      <c r="F14" s="205">
-        <v>255109846.60160801</v>
+      <c r="C14" s="15">
+        <v>304658045.987652</v>
+      </c>
+      <c r="D14" s="15">
+        <v>13595672.313951001</v>
+      </c>
+      <c r="E14" s="15">
+        <v>82499999.260000005</v>
+      </c>
+      <c r="F14" s="15">
+        <v>400753717.56160301</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>168120864.63430399</v>
+        <v>191588257.960246</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>30287594.56986</v>
+        <v>32230803.599858999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,140 +21913,140 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>127666059.844179</v>
+        <v>165098050.07452199</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>40837106.988243997</v>
+        <v>47061462.078239001</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="205">
-        <v>146645254.30481699</v>
-      </c>
-      <c r="D16" s="205">
-        <v>27700232.589857001</v>
-      </c>
-      <c r="E16" s="205">
-        <v>7175675.5999999996</v>
-      </c>
-      <c r="F16" s="205">
-        <v>181521162.494674</v>
+      <c r="C16" s="15">
+        <v>188104283.13257799</v>
+      </c>
+      <c r="D16" s="15">
+        <v>33735268.665836997</v>
+      </c>
+      <c r="E16" s="15">
+        <v>10797297.199999999</v>
+      </c>
+      <c r="F16" s="15">
+        <v>232636848.99841499</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>153920681.22660801</v>
+        <v>192566857.280359</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>26441026.139972001</v>
+        <v>28378087.389970999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="205">
-        <v>89427277.780000001</v>
-      </c>
-      <c r="D17" s="205">
-        <v>7082418.9199999999</v>
-      </c>
-      <c r="E17" s="205" t="s">
+      <c r="C17" s="15">
+        <v>114350700.78</v>
+      </c>
+      <c r="D17" s="15">
+        <v>18496237.719999999</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="205">
-        <v>96509696.700000003</v>
+      <c r="F17" s="15">
+        <v>132846938.5</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>90330395.193459004</v>
+        <v>108591336.892453</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>8137421.2493679998</v>
+        <v>13237421.249368001</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="205">
-        <v>478548075.04396403</v>
-      </c>
-      <c r="D18" s="205">
-        <v>5313981.1899769995</v>
-      </c>
-      <c r="E18" s="205">
-        <v>4043243.2</v>
-      </c>
-      <c r="F18" s="205">
-        <v>487905299.43394101</v>
+      <c r="C18" s="15">
+        <v>552081395.80396402</v>
+      </c>
+      <c r="D18" s="15">
+        <v>6945438.6219769996</v>
+      </c>
+      <c r="E18" s="15">
+        <v>5091891.84</v>
+      </c>
+      <c r="F18" s="15">
+        <v>564118726.26594102</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>253962994.37583601</v>
+        <v>382747313.217785</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>112968670.74834301</v>
+        <v>126707529.597831</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="205">
-        <v>319031714.35037303</v>
-      </c>
-      <c r="D19" s="205">
-        <v>24841130.359965999</v>
-      </c>
-      <c r="E19" s="205">
-        <v>338000021.619968</v>
-      </c>
-      <c r="F19" s="205">
-        <v>681872866.33030701</v>
+      <c r="C19" s="15">
+        <v>407270698.05517799</v>
+      </c>
+      <c r="D19" s="15">
+        <v>36349333.359916002</v>
+      </c>
+      <c r="E19" s="15">
+        <v>439943261.85992801</v>
+      </c>
+      <c r="F19" s="15">
+        <v>883563293.27502203</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>99455498.264208004</v>
+        <v>107988107.054208</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>66649448.201086998</v>
+        <v>73114987.120986998</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="205">
-        <v>75798478.264208004</v>
-      </c>
-      <c r="D20" s="205">
-        <v>16789142.409896001</v>
-      </c>
-      <c r="E20" s="205" t="s">
+      <c r="C20" s="15">
+        <v>83172487.054207996</v>
+      </c>
+      <c r="D20" s="15">
+        <v>19221574.809856001</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="205">
-        <v>92587620.674104005</v>
+      <c r="F20" s="15">
+        <v>102394061.86406399</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22075,24 +22063,24 @@
       <c r="B21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="205">
-        <v>23657020</v>
-      </c>
-      <c r="D21" s="205">
-        <v>49860305.791190997</v>
-      </c>
-      <c r="E21" s="205">
+      <c r="C21" s="15">
+        <v>24815620</v>
+      </c>
+      <c r="D21" s="15">
+        <v>53893412.311131001</v>
+      </c>
+      <c r="E21" s="15">
         <v>24237838.32</v>
       </c>
-      <c r="F21" s="205">
-        <v>97755164.111191005</v>
+      <c r="F21" s="15">
+        <v>102946870.63113099</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>263561198.787453</v>
+        <v>362012547.03633201</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22102,17 +22090,17 @@
       <c r="B22" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="205">
-        <v>26153399.100000001</v>
-      </c>
-      <c r="D22" s="205" t="s">
+      <c r="C22" s="15">
+        <v>58499359.200000003</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="205">
+      <c r="E22" s="15">
         <v>4036035.92</v>
       </c>
-      <c r="F22" s="205">
-        <v>30189435.02</v>
+      <c r="F22" s="15">
+        <v>62535395.119999997</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22122,17 +22110,17 @@
       <c r="B23" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="205">
-        <v>93771608.249974996</v>
-      </c>
-      <c r="D23" s="205" t="s">
+      <c r="C23" s="15">
+        <v>127633638.149975</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="205">
-        <v>3207207.12</v>
-      </c>
-      <c r="F23" s="205">
-        <v>96978815.369975001</v>
+      <c r="E23" s="15">
+        <v>5693693.54</v>
+      </c>
+      <c r="F23" s="15">
+        <v>133327331.68997499</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22142,17 +22130,17 @@
       <c r="B24" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="205">
-        <v>86134461.094157994</v>
-      </c>
-      <c r="D24" s="205">
-        <v>22140216.108477</v>
-      </c>
-      <c r="E24" s="205">
-        <v>45358738.119999997</v>
-      </c>
-      <c r="F24" s="205">
-        <v>153633415.32263499</v>
+      <c r="C24" s="15">
+        <v>112604837.314255</v>
+      </c>
+      <c r="D24" s="15">
+        <v>24457774.658475999</v>
+      </c>
+      <c r="E24" s="15">
+        <v>52237116.340000004</v>
+      </c>
+      <c r="F24" s="15">
+        <v>189299728.312731</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22162,17 +22150,17 @@
       <c r="B25" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="205">
-        <v>168120864.63430399</v>
-      </c>
-      <c r="D25" s="205">
-        <v>30287594.56986</v>
-      </c>
-      <c r="E25" s="205">
-        <v>72822521.819999993</v>
-      </c>
-      <c r="F25" s="205">
-        <v>271230981.02416402</v>
+      <c r="C25" s="15">
+        <v>191588257.960246</v>
+      </c>
+      <c r="D25" s="15">
+        <v>32230803.599858999</v>
+      </c>
+      <c r="E25" s="15">
+        <v>75525224.480000004</v>
+      </c>
+      <c r="F25" s="15">
+        <v>299344286.04010499</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22182,17 +22170,17 @@
       <c r="B26" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="205">
-        <v>153920681.22660801</v>
-      </c>
-      <c r="D26" s="205">
-        <v>26441026.139972001</v>
-      </c>
-      <c r="E26" s="205">
-        <v>124450449.88998</v>
-      </c>
-      <c r="F26" s="205">
-        <v>304812157.25656003</v>
+      <c r="C26" s="15">
+        <v>192566857.280359</v>
+      </c>
+      <c r="D26" s="15">
+        <v>28378087.389970999</v>
+      </c>
+      <c r="E26" s="15">
+        <v>177396394.809971</v>
+      </c>
+      <c r="F26" s="15">
+        <v>398341339.48030102</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22202,17 +22190,17 @@
       <c r="B27" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="205">
-        <v>253962994.37583601</v>
-      </c>
-      <c r="D27" s="205">
-        <v>112968670.74834301</v>
-      </c>
-      <c r="E27" s="205">
+      <c r="C27" s="15">
+        <v>382747313.217785</v>
+      </c>
+      <c r="D27" s="15">
+        <v>126707529.597831</v>
+      </c>
+      <c r="E27" s="15">
         <v>4259459.54</v>
       </c>
-      <c r="F27" s="205">
-        <v>371191124.66417903</v>
+      <c r="F27" s="15">
+        <v>513714302.35561597</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22258,8 +22246,8 @@
       <c r="B32" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="205">
-        <v>119496802.195455</v>
+      <c r="C32" s="15">
+        <v>124968693.85541201</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22269,8 +22257,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="205">
-        <v>135847296.89607501</v>
+      <c r="C33" s="15">
+        <v>156883432.39585999</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22280,8 +22268,8 @@
       <c r="B34" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="205">
-        <v>126972770.68896399</v>
+      <c r="C34" s="15">
+        <v>136863581.45894501</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22291,8 +22279,8 @@
       <c r="B35" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="205">
-        <v>136588428.09848899</v>
+      <c r="C35" s="15">
+        <v>225148965.57738701</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22334,17 +22322,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="237" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="238"/>
+      <c r="D41" s="239"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.38709677419354838</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22375,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>2091438775.9160492</v>
+        <v>2689259650.2416067</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.30579812205220358</v>
+        <v>0.39320804425386596</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>4747840556.083951</v>
+        <v>4150019681.7583933</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>279284738.59317356</v>
+        <v>296429977.26845664</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22404,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>410322192.83439702</v>
+        <v>486792200.689152</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.2781346007156657</v>
+        <v>0.32996936732793636</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>1064942631.3859646</v>
+        <v>988472623.53120971</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>62643684.199174389</v>
+        <v>70605187.395086408</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,46 +22433,46 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>518905297.87898302</v>
+        <v>643864673.28760397</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.29103280429966821</v>
+        <v>0.36111741819233145</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1264073425.5252728</v>
+        <v>1139114050.116652</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>74357260.325016052</v>
+        <v>81365289.294046566</v>
       </c>
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>3020666266.6294293</v>
+        <v>3819916524.2183623</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.29914923715842318</v>
+        <v>0.37830233907431066</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>7076856612.9951878</v>
+        <v>6277606355.4062557</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>416285683.11736399</v>
+        <v>448400453.95758969</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22494,40 +22482,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -22535,13 +22523,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -22560,7 +22548,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -22570,7 +22558,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22581,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>86134461.094157994</v>
+        <v>112604837.314255</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>22140216.108477</v>
+        <v>24457774.658475999</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>108274677.20263499</v>
+        <v>137062611.97273099</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.2232679886521125</v>
+        <v>0.28263020020171326</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>330549016.90584201</v>
+        <v>304078640.685745</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>46130185.112177312</v>
+        <v>43812626.562178314</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>376679202.01801932</v>
+        <v>347891267.24792331</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>22157600.11870702</v>
+        <v>24849376.231994521</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22633,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>187770500.990475</v>
+        <v>227558165.142396</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>30994065.455272</v>
+        <v>39427622.934717</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>218764566.44574699</v>
+        <v>266985788.077113</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.2929637405757205</v>
+        <v>0.35754032943458997</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>367411870.009525</v>
+        <v>327624205.85760403</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>160552718.54472801</v>
+        <v>152119161.065283</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>527964588.55425298</v>
+        <v>479743366.92288697</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>31056740.503191352</v>
+        <v>34267383.351634786</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22685,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>26153399.100000001</v>
+        <v>58499359.200000003</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22693,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>26153399.100000001</v>
+        <v>58499359.200000003</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.10830763718325956</v>
+        <v>0.24226018757488305</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>215319868.90000001</v>
+        <v>182973908.80000001</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22709,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>215319868.90000001</v>
+        <v>182973908.80000001</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>12665874.641176471</v>
+        <v>13069564.914285716</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22737,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>249048066.50765699</v>
+        <v>304658045.987652</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>12242861.503951</v>
+        <v>13595672.313951001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>261290928.011608</v>
+        <v>318253718.30160302</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.39734366383883268</v>
+        <v>0.48396666284055917</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>361664405.49234301</v>
+        <v>306054426.012348</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>34638965.313383892</v>
+        <v>33286154.50338389</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>396303370.80572689</v>
+        <v>339340580.51573187</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>23311962.988572169</v>
+        <v>24238612.89398085</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,35 +22789,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>89427277.780000001</v>
+        <v>114350700.78</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>7082418.9199999999</v>
+        <v>18496237.719999999</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>96509696.700000003</v>
+        <v>132846938.5</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.19779309039795853</v>
+        <v>0.27226493724772566</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>315636006.22000003</v>
+        <v>290712583.22000003</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>75786896.271524146</v>
+        <v>64373077.471524149</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>391422902.49152416</v>
+        <v>355085660.69152415</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>23024876.617148481</v>
+        <v>25363261.477966011</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22841,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>146645254.30481699</v>
+        <v>188104283.13257799</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>27700232.589857001</v>
+        <v>33735268.665836997</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>174345486.894674</v>
+        <v>221839551.79841498</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.31404648024823661</v>
+        <v>0.39959698219333051</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>327273577.69518304</v>
+        <v>285814548.86742198</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>53539161.532796606</v>
+        <v>47504125.456816606</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>380812739.2279796</v>
+        <v>333318674.32423866</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>22400749.366351742</v>
+        <v>23808476.737445619</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22893,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>319031714.35037303</v>
+        <v>407270698.05517799</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>24841130.359965999</v>
+        <v>36349333.359916002</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>343872844.71033901</v>
+        <v>443620031.41509402</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.32635201001954417</v>
+        <v>0.42101692868246526</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>642726630.64962697</v>
+        <v>554487646.94482207</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>67087445.979190394</v>
+        <v>55579242.979240388</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>709814076.62881732</v>
+        <v>610066889.92406237</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>41753769.213459842</v>
+        <v>43576206.423147313</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22945,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>168120864.63430399</v>
+        <v>191588257.960246</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>30287594.56986</v>
+        <v>32230803.599858999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>198408459.204164</v>
+        <v>223819061.560105</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.34865481414696492</v>
+        <v>0.39330779354768952</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>337166194.36569601</v>
+        <v>313698801.03975403</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>33493809.43014</v>
+        <v>31550600.400141001</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>370660003.79583597</v>
+        <v>345249401.43989503</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>21803529.635049175</v>
+        <v>24660671.531421073</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +22997,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>93771608.249974996</v>
+        <v>127633638.149975</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23005,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>93771608.249974996</v>
+        <v>127633638.149975</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.23203117335450429</v>
+        <v>0.31582035727163527</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>310362055.75002503</v>
+        <v>276500025.850025</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23021,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>310362055.75002503</v>
+        <v>276500025.850025</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>18256591.514707357</v>
+        <v>19750001.846430358</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23049,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>127666059.844179</v>
+        <v>165098050.07452199</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>40837106.988243997</v>
+        <v>47061462.078239001</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>168503166.832423</v>
+        <v>212159512.15276098</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.31061539416965711</v>
+        <v>0.39109063487044016</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>276351249.15582097</v>
+        <v>238919258.92547801</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>97627283.229751408</v>
+        <v>91402928.139756411</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>373978532.38557243</v>
+        <v>330322187.06523442</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>21998737.199151319</v>
+        <v>23594441.93323103</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23101,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>153920681.22660801</v>
+        <v>192566857.280359</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>26441026.139972001</v>
+        <v>28378087.389970999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>180361707.36658001</v>
+        <v>220944944.67032999</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.26125323340844042</v>
+        <v>0.32003789520052162</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>477708914.77339196</v>
+        <v>439062738.71964097</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>32300574.470653266</v>
+        <v>30363513.220654268</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>510009489.24404526</v>
+        <v>469426251.94029528</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>30000558.190826192</v>
+        <v>33530446.567163948</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23153,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>90330395.193459004</v>
+        <v>108591336.892453</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>8137421.2493679998</v>
+        <v>13237421.249368001</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>98467816.442827001</v>
+        <v>121828758.141821</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.21866810323552369</v>
+        <v>0.27054589433167009</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>296212627.80654097</v>
+        <v>277951686.10754699</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>55626733.55044581</v>
+        <v>50526733.55044581</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>351839361.35698682</v>
+        <v>328478419.65799284</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>20696433.020999223</v>
+        <v>23462744.261285204</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23205,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>253962994.37583601</v>
+        <v>382747313.217785</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>112968670.74834301</v>
+        <v>126707529.597831</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>366931665.12417901</v>
+        <v>509454842.81561601</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.40182718711721027</v>
+        <v>0.55790444354961699</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>329387947.62416399</v>
+        <v>200603628.782215</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>216838274.24437439</v>
+        <v>203099415.39488637</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>546226221.86853838</v>
+        <v>403703044.17710137</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>32130954.227561083</v>
+        <v>28835931.726935811</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23257,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>99455498.264208004</v>
+        <v>107988107.054208</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>66649448.201086998</v>
+        <v>73114987.120986998</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>166104946.46529502</v>
+        <v>181103094.17519498</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.3209783960607116</v>
+        <v>0.34996056364962891</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>160070190.73579198</v>
+        <v>151537581.94579202</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>191320583.70679939</v>
+        <v>184855044.78689939</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>351390774.44259137</v>
+        <v>336392626.73269141</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>20670045.55544655</v>
+        <v>24028044.766620815</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23307,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>2091438775.9160492</v>
+        <v>2689259650.2416067</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>410322192.83439702</v>
+        <v>486792200.689152</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>2501760968.7504458</v>
+        <v>3176051850.9307594</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.30088973270757152</v>
+        <v>0.38198748978374947</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>4747840556.083951</v>
+        <v>4150019681.7583933</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>1064942631.3859646</v>
+        <v>988472623.53120947</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>5812783187.4699163</v>
+        <v>5138492305.2896032</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>341928422.79234803</v>
+        <v>367035164.66354311</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23363,10 +23351,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -23374,8 +23362,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -23389,7 +23377,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>45358738.119999997</v>
+        <v>52237116.340000004</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23389,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>28043242.68</v>
+        <v>37539638.980000004</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23413,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>33718918.590000004</v>
+        <v>82499999.260000005</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23449,7 +23437,7 @@
       </c>
       <c r="D75" s="192">
         <f>IF(E16="",0,E16)</f>
-        <v>7175675.5999999996</v>
+        <v>10797297.199999999</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23449,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>338000021.619968</v>
+        <v>439943261.85992801</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23461,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>72822521.819999993</v>
+        <v>75525224.480000004</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23485,7 +23473,7 @@
       </c>
       <c r="D78" s="192">
         <f>IF(E23="",0,E23)</f>
-        <v>3207207.12</v>
+        <v>5693693.54</v>
       </c>
     </row>
     <row r="79" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23497,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>124450449.88998</v>
+        <v>177396394.809971</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23509,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>67988214.499998003</v>
+        <v>83152214.019998997</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23543,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>780055080.71994603</v>
+        <v>1024074931.2698979</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23557,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23605,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>119496802.195455</v>
+        <v>124968693.85541201</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.42974472299320166</v>
+        <v>0.44942321247956279</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>158567815.70875454</v>
+        <v>153095924.04879755</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9327518.5711032078</v>
+        <v>10935423.146342682</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23634,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>135847296.89607501</v>
+        <v>156883432.39585999</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.32529037768923386</v>
+        <v>0.37566202746215377</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>281771256.29044658</v>
+        <v>260735120.7906616</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>16574779.781790975</v>
+        <v>18623937.199332971</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23663,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>263561198.787453</v>
+        <v>362012547.03633201</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.24240069613699144</v>
+        <v>0.33294769418126402</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>823734353.52607179</v>
+        <v>725283005.27719271</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>48454961.972121872</v>
+        <v>51805928.948370911</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,19 +23748,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>518905297.87898302</v>
+        <v>643864673.28760397</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.29103280429966821</v>
+        <v>0.36111741819233145</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1264073425.5252728</v>
+        <v>1139114050.116652</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>74357260.325016052</v>
+        <v>81365289.294046566</v>
       </c>
       <c r="I94" s="116"/>
     </row>
@@ -23808,7 +23796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24391,11 +24379,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -24519,10 +24507,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -24551,40 +24539,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -24592,13 +24580,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -24617,7 +24605,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -24627,7 +24615,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25420,10 +25408,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -25431,8 +25419,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -25626,13 +25614,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25865,7 +25853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26448,11 +26436,11 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="225"/>
-      <c r="D41" s="226"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="225"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
@@ -26576,10 +26564,10 @@
       <c r="I45" s="116"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="221" t="s">
+      <c r="B46" s="220" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="222"/>
+      <c r="C46" s="221"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>0</v>
@@ -26608,40 +26596,40 @@
       <c r="I47" s="116"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="228" t="s">
+      <c r="B48" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="228"/>
+      <c r="E48" s="228"/>
+      <c r="F48" s="228"/>
+      <c r="G48" s="228"/>
+      <c r="H48" s="228"/>
+      <c r="I48" s="228"/>
+      <c r="J48" s="229"/>
+      <c r="K48" s="243"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="223" t="s">
+      <c r="B49" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="223" t="s">
+      <c r="C49" s="222" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="218" t="s">
+      <c r="D49" s="217" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="219"/>
-      <c r="F49" s="220"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="219"/>
       <c r="G49" s="120" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
-      <c r="J49" s="223" t="s">
+      <c r="J49" s="222" t="s">
         <v>140</v>
       </c>
       <c r="K49" s="132" t="s">
@@ -26649,13 +26637,13 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="246" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
       <c r="D50" s="71" t="s">
         <v>150</v>
       </c>
@@ -26674,7 +26662,7 @@
       <c r="I50" s="121" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="223"/>
+      <c r="J50" s="222"/>
       <c r="K50" s="133" t="s">
         <v>143</v>
       </c>
@@ -26684,7 +26672,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="246"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27477,10 +27465,10 @@
       <c r="D67" s="137"/>
     </row>
     <row r="68" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="223" t="s">
+      <c r="B68" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="223" t="s">
+      <c r="C68" s="222" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="134" t="s">
@@ -27488,8 +27476,8 @@
       </c>
     </row>
     <row r="69" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="223"/>
-      <c r="C69" s="223"/>
+      <c r="B69" s="222"/>
+      <c r="C69" s="222"/>
       <c r="D69" s="71" t="s">
         <v>172</v>
       </c>
@@ -27683,13 +27671,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="240" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="241"/>
+      <c r="D87" s="241"/>
+      <c r="E87" s="241"/>
+      <c r="F87" s="242"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="185">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 16 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 18 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1955,6 +1946,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,6 +4872,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4879,11 +4884,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,6 +6929,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6936,11 +6941,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,6 +8986,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8993,11 +8998,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,6 +11043,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11050,11 +11055,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,6 +13085,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13092,11 +13097,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,7 +21743,7 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>134348003.330715</v>
+        <v>139526856.460715</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>251681746.503654</v>
+        <v>266027245.83357799</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>41525501.324712999</v>
+        <v>48492178.001657002</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>145092012.90901601</v>
+        <v>150301886.71010399</v>
       </c>
       <c r="D10" s="205">
-        <v>14830325.769368</v>
+        <v>16708691.719342001</v>
       </c>
       <c r="E10" s="205">
-        <v>95356988.479999006</v>
+        <v>98568700.159998998</v>
       </c>
       <c r="F10" s="205">
-        <v>255279327.15838301</v>
+        <v>265579278.58944499</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>338619113.79265201</v>
+        <v>343838280.39265198</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>15757834.473927001</v>
+        <v>16023834.473927001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,23 +21805,23 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>188078180.53449199</v>
+        <v>208943511.124477</v>
       </c>
       <c r="D11" s="205">
-        <v>49132182.698238</v>
+        <v>51564741.228233002</v>
       </c>
       <c r="E11" s="205">
         <v>26756757</v>
       </c>
       <c r="F11" s="205">
-        <v>263967120.23273</v>
+        <v>287265009.35271001</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>149485835.28</v>
+        <v>196332681.28</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>126560684.737938</v>
+        <v>129230508.15793701</v>
       </c>
       <c r="D12" s="205">
-        <v>28730078.034777999</v>
+        <v>32246304.411772002</v>
       </c>
       <c r="E12" s="205">
         <v>18777386.960000001</v>
       </c>
       <c r="F12" s="205">
-        <v>174068149.73271599</v>
+        <v>180254199.52970901</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>214314928.272549</v>
+        <v>241961823.99011901</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>44241687.622334003</v>
+        <v>47644038.982330002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>125121061.765716</v>
+        <v>136796737.675641</v>
       </c>
       <c r="D13" s="205">
-        <v>12795423.289935</v>
+        <v>16245873.589885</v>
       </c>
       <c r="E13" s="205">
         <v>23076576.34</v>
       </c>
       <c r="F13" s="205">
-        <v>160993061.39565101</v>
+        <v>176119187.605526</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>453603227.62404603</v>
+        <v>510383402.37286103</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>37269133.359916002</v>
+        <v>40929133.359916002</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,23 +21889,23 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>338619113.79265201</v>
+        <v>343838280.39265198</v>
       </c>
       <c r="D14" s="205">
-        <v>15757834.473927001</v>
+        <v>16023834.473927001</v>
       </c>
       <c r="E14" s="205">
-        <v>96950449.560000002</v>
+        <v>103966665.72</v>
       </c>
       <c r="F14" s="205">
-        <v>451327397.82657897</v>
+        <v>463828780.58657902</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>223589370.84851599</v>
+        <v>229751949.23851499</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
@@ -21925,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>188078180.53449199</v>
+        <v>208943511.124477</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>49132182.698238</v>
+        <v>51564741.228233002</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>214314928.272549</v>
+        <v>241961823.99011901</v>
       </c>
       <c r="D16" s="205">
-        <v>44241687.622334003</v>
+        <v>47644038.982330002</v>
       </c>
       <c r="E16" s="205">
         <v>10797297.199999999</v>
       </c>
       <c r="F16" s="205">
-        <v>269353913.09488302</v>
+        <v>300403160.17244899</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>217129583.53588799</v>
+        <v>230336475.427122</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>28714087.389970999</v>
+        <v>29219087.389970999</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21965,7 +21965,7 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>149485835.28</v>
+        <v>196332681.28</v>
       </c>
       <c r="D17" s="205">
         <v>18496237.719999999</v>
@@ -21974,18 +21974,18 @@
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>167982073</v>
+        <v>214828919</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>145092012.90901601</v>
+        <v>150301886.71010399</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>14830325.769368</v>
+        <v>16708691.719342001</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>556515031.47396398</v>
+        <v>571165148.50393903</v>
       </c>
       <c r="D18" s="205">
         <v>7419438.6219769996</v>
       </c>
       <c r="E18" s="205">
-        <v>5091891.84</v>
+        <v>5391891.8399999999</v>
       </c>
       <c r="F18" s="205">
-        <v>569026361.93594098</v>
+        <v>583976478.96591604</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>434487058.73615497</v>
+        <v>439502423.57798398</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>131796178.197771</v>
+        <v>133255637.637747</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>453603227.62404603</v>
+        <v>510383402.37286103</v>
       </c>
       <c r="D19" s="205">
-        <v>37269133.359916002</v>
+        <v>40929133.359916002</v>
       </c>
       <c r="E19" s="205">
-        <v>453094614.35992801</v>
+        <v>489000019.35992301</v>
       </c>
       <c r="F19" s="205">
-        <v>943966975.34388995</v>
+        <v>1040312555.0927</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>149431304.212708</v>
+        <v>151562326.01270801</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>76701860.380957007</v>
+        <v>78926681.972957</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,16 +22049,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>121744010.212708</v>
+        <v>123395812.01270799</v>
       </c>
       <c r="D20" s="205">
-        <v>19221574.809856001</v>
-      </c>
-      <c r="E20" s="205" t="s">
-        <v>169</v>
+        <v>19725574.809856001</v>
+      </c>
+      <c r="E20" s="205">
+        <v>1027027.04</v>
       </c>
       <c r="F20" s="205">
-        <v>140965585.02256399</v>
+        <v>144148413.862564</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>27687294</v>
+        <v>28166514</v>
       </c>
       <c r="D21" s="205">
-        <v>57480285.571101002</v>
+        <v>59201107.163101003</v>
       </c>
       <c r="E21" s="205">
         <v>26313514.039999999</v>
       </c>
       <c r="F21" s="205">
-        <v>111481093.611101</v>
+        <v>113681135.20310099</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>412626483.91474801</v>
+        <v>434929553.98460102</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22123,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>127633638.149975</v>
+        <v>152247018.149975</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22132,7 +22132,7 @@
         <v>7297297.0999999996</v>
       </c>
       <c r="F23" s="205">
-        <v>134930935.249975</v>
+        <v>159544315.249975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>134348003.330715</v>
+        <v>139526856.460715</v>
       </c>
       <c r="D24" s="205">
         <v>25779936.818475999</v>
       </c>
       <c r="E24" s="205">
-        <v>55119999.140000001</v>
+        <v>65610990.020000003</v>
       </c>
       <c r="F24" s="205">
-        <v>215247939.28919101</v>
+        <v>230917783.299191</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,7 +22163,7 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>223589370.84851599</v>
+        <v>229751949.23851499</v>
       </c>
       <c r="D25" s="205">
         <v>34375803.599858999</v>
@@ -22172,7 +22172,7 @@
         <v>77012611.840000004</v>
       </c>
       <c r="F25" s="205">
-        <v>334977786.28837502</v>
+        <v>341140364.67837399</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>217129583.53588799</v>
+        <v>230336475.427122</v>
       </c>
       <c r="D26" s="205">
-        <v>28714087.389970999</v>
+        <v>29219087.389970999</v>
       </c>
       <c r="E26" s="205">
-        <v>206620358.629971</v>
+        <v>226352790.72995099</v>
       </c>
       <c r="F26" s="205">
-        <v>452464029.55583</v>
+        <v>485908353.54704398</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>434487058.73615497</v>
+        <v>439502423.57798398</v>
       </c>
       <c r="D27" s="205">
-        <v>131796178.197771</v>
+        <v>133255637.637747</v>
       </c>
       <c r="E27" s="205">
         <v>12199459.539999999</v>
       </c>
       <c r="F27" s="205">
-        <v>578482696.47392595</v>
+        <v>584957520.75573099</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>155621239.68527299</v>
+        <v>162874843.26519999</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>171066351.605681</v>
+        <v>175429613.008481</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>178536978.33743301</v>
+        <v>186957678.84739801</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>234089505.577315</v>
+        <v>247971875.13720301</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="245" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.5161290322580645</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>3085993362.9303665</v>
+        <v>3319215239.7708101</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.45121616081557736</v>
+        <v>0.4853165192772112</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>3753285969.0696335</v>
+        <v>3520064092.2291899</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>288714305.31304872</v>
+        <v>293338674.35243249</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>518620769.35553002</v>
+        <v>541416002.90441501</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.35154418436676771</v>
+        <v>0.36699580578052415</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>956644054.86483169</v>
+        <v>933848821.3159467</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>73588004.220371664</v>
+        <v>77820735.10966222</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>739314075.20570207</v>
+        <v>773234010.25828195</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.41465109229914066</v>
+        <v>0.43367539954820095</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1043664648.1985538</v>
+        <v>1009744713.1459739</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>80281896.015273362</v>
+        <v>84145392.762164488</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>4343928207.4915981</v>
+        <v>4633865252.933507</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.43019741170946335</v>
+        <v>0.45891109217330872</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>5753594672.1330194</v>
+        <v>5463657626.6911106</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>442584205.54869378</v>
+        <v>455304802.2242592</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>134348003.330715</v>
+        <v>139526856.460715</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
@@ -22601,15 +22601,15 @@
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>160127940.14919099</v>
+        <v>165306793.27919099</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.33019210075507549</v>
+        <v>0.3408711639648031</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>282335474.669285</v>
+        <v>277156621.539285</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
@@ -22617,11 +22617,11 @@
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>324825939.07146335</v>
+        <v>319647085.94146335</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>24986610.697804872</v>
+        <v>26637257.161788613</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>251681746.503654</v>
+        <v>266027245.83357799</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>41525501.324712999</v>
+        <v>48492178.001657002</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>293207247.82836699</v>
+        <v>314519423.835235</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.39265541711488017</v>
+        <v>0.42119612141732299</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>303500624.496346</v>
+        <v>289155125.16642201</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>150021282.67528701</v>
+        <v>143054605.99834299</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>453521907.17163301</v>
+        <v>432209731.164765</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>34886300.551664077</v>
+        <v>36017477.59706375</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22725,7 +22725,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>14074916.061538462</v>
+        <v>15247825.733333334</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>338619113.79265201</v>
+        <v>343838280.39265198</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>15757834.473927001</v>
+        <v>16023834.473927001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>354376948.26657903</v>
+        <v>359862114.866579</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.53889905813343597</v>
+        <v>0.54724032053468386</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>272093358.20734799</v>
+        <v>266874191.60734802</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>31123992.343407892</v>
+        <v>30857992.343407892</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>303217350.55075586</v>
+        <v>297732183.95075589</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>23324411.580827374</v>
+        <v>24811015.329229657</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>149485835.28</v>
+        <v>196332681.28</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
@@ -22809,15 +22809,15 @@
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>167982073</v>
+        <v>214828919</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.34427310919240994</v>
+        <v>0.44028400511865573</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>255577448.72</v>
+        <v>208730602.72</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
@@ -22825,11 +22825,11 @@
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>319950526.19152415</v>
+        <v>273103680.19152415</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24611578.937809549</v>
+        <v>22758640.015960347</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>214314928.272549</v>
+        <v>241961823.99011901</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>44241687.622334003</v>
+        <v>47644038.982330002</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>258556615.89488301</v>
+        <v>289605862.972449</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.46573499901226167</v>
+        <v>0.52166364352577399</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>259603903.727451</v>
+        <v>231957008.00988099</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>36997706.5003196</v>
+        <v>33595355.140323602</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>296601610.22777057</v>
+        <v>265552363.1502046</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>22815508.479059275</v>
+        <v>22129363.595850382</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>453603227.62404603</v>
+        <v>510383402.37286103</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>37269133.359916002</v>
+        <v>40929133.359916002</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>490872360.98396206</v>
+        <v>551312535.732777</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.46586168153259455</v>
+        <v>0.52322233916702743</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>508155117.37595397</v>
+        <v>451374942.62713897</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>54659442.979240388</v>
+        <v>50999442.979240388</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>562814560.35519433</v>
+        <v>502374385.60637939</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43293427.719630331</v>
+        <v>41864532.133864947</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>223589370.84851599</v>
+        <v>229751949.23851499</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
@@ -22965,15 +22965,15 @@
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>257965174.44837499</v>
+        <v>264127752.83837399</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.45331131703985322</v>
+        <v>0.46414055603424642</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>281697688.15148401</v>
+        <v>275535109.76148498</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
@@ -22981,11 +22981,11 @@
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>311103288.55162501</v>
+        <v>304940710.16162598</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>23931022.196278848</v>
+        <v>25411725.846802164</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>127633638.149975</v>
+        <v>152247018.149975</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>127633638.149975</v>
+        <v>152247018.149975</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.31582035727163527</v>
+        <v>0.37672441499447817</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>276500025.850025</v>
+        <v>251886645.850025</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>276500025.850025</v>
+        <v>251886645.850025</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>21269232.757694229</v>
+        <v>20990553.820835415</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>188078180.53449199</v>
+        <v>208943511.124477</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>49132182.698238</v>
+        <v>51564741.228233002</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>237210363.23272997</v>
+        <v>260508252.35271001</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.43726887667303105</v>
+        <v>0.48021574318219568</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>215939128.46550801</v>
+        <v>195073797.875523</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>89332207.519757405</v>
+        <v>86899648.989762396</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>305271335.98526543</v>
+        <v>281973446.8652854</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>23482410.460405033</v>
+        <v>23497787.238773782</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>217129583.53588799</v>
+        <v>230336475.427122</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>28714087.389970999</v>
+        <v>29219087.389970999</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>245843670.92585897</v>
+        <v>259555562.81709298</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.35610360358721155</v>
+        <v>0.37596522579647013</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>414500012.46411204</v>
+        <v>401293120.572878</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>30027513.220654268</v>
+        <v>29522513.220654268</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>444527525.68476629</v>
+        <v>430815633.79353225</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>34194425.052674331</v>
+        <v>35901302.816127688</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>145092012.90901601</v>
+        <v>150301886.71010399</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>14830325.769368</v>
+        <v>16708691.719342001</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>159922338.67838401</v>
+        <v>167010578.42944598</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.35514054974597414</v>
+        <v>0.37088144862681122</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>241451010.09098399</v>
+        <v>236241136.28989601</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>48933829.030445807</v>
+        <v>47055463.080471806</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>290384839.1214298</v>
+        <v>283296599.37036783</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>22337295.31703306</v>
+        <v>23608049.947530653</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>434487058.73615497</v>
+        <v>439502423.57798398</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>131796178.197771</v>
+        <v>133255637.637747</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>566283236.93392599</v>
+        <v>572758061.21573102</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.62013726760752619</v>
+        <v>0.62722785333649411</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>148863883.26384503</v>
+        <v>143848518.42201602</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>198010766.79494637</v>
+        <v>196551307.3549704</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>346874650.0587914</v>
+        <v>340399825.77698636</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>26682665.389137801</v>
+        <v>28366652.148082197</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>149431304.212708</v>
+        <v>151562326.01270801</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>76701860.380957007</v>
+        <v>78926681.972957</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>226133164.593665</v>
+        <v>230489007.98566502</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.43697591198810404</v>
+        <v>0.44539307026790237</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>110094384.787292</v>
+        <v>107963362.98729199</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>181268171.52692938</v>
+        <v>179043349.93492937</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>291362556.31422138</v>
+        <v>287006712.92222136</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>22412504.331863184</v>
+        <v>23917226.076851781</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>3085993362.9303665</v>
+        <v>3319215239.7708101</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>518620769.35553002</v>
+        <v>541416002.90441501</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>3604614132.2858958</v>
+        <v>3860631242.6752253</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.43353117916743211</v>
+        <v>0.4643226580000745</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>3753285969.069634</v>
+        <v>3520064092.2291903</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>956644054.86483169</v>
+        <v>933848821.31594658</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>4709930023.9344654</v>
+        <v>4453912913.5451365</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>362302309.53342044</v>
+        <v>371159409.46209472</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>55119999.140000001</v>
+        <v>65610990.020000003</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>96950449.560000002</v>
+        <v>103966665.72</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>453094614.35992801</v>
+        <v>489000019.35992301</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>206620358.629971</v>
+        <v>226352790.72995099</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>95356988.479999006</v>
+        <v>98568700.159998998</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>26313514.039999999</v>
+        <v>27340541.079999998</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1115427364.0698981</v>
+        <v>1192811146.929873</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>155621239.68527299</v>
+        <v>162874843.26519999</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.55965854576608853</v>
+        <v>0.58574458157531106</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>122443378.21893656</v>
+        <v>115189774.63900957</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9418721.4014566578</v>
+        <v>9599147.886584131</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>171066351.605681</v>
+        <v>175429613.008481</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.40962344776209542</v>
+        <v>0.4200714064782668</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>246552201.58084059</v>
+        <v>242188940.17804059</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>18965553.967756968</v>
+        <v>20182411.681503382</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>412626483.91474801</v>
+        <v>434929553.98460102</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.37949799669167228</v>
+        <v>0.40001042316338647</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>674669068.39877677</v>
+        <v>652365998.3289237</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>51897620.646059752</v>
+        <v>54363833.194076978</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,24 +23760,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>739314075.20570207</v>
+        <v>773234010.25828195</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.41465109229914066</v>
+        <v>0.43367539954820095</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1043664648.1985539</v>
+        <v>1009744713.1459739</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>80281896.015273377</v>
+        <v>84145392.762164488</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23785,11 +23790,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,6 +25835,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25842,11 +25847,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,6 +27892,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27899,11 +27904,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 18 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 19 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,6 +1927,15 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1946,15 +1955,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,11 +4872,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4884,6 +4879,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,11 +6929,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6941,6 +6936,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,11 +8986,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8998,6 +8993,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,11 +11043,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11055,6 +11050,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,11 +13085,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13097,6 +13092,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>139526856.460715</v>
+        <v>164522529.84539101</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>25779936.818475999</v>
+        <v>27797935.018475998</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>266027245.83357799</v>
+        <v>310308359.103576</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>48492178.001657002</v>
+        <v>50679002.341656998</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>150301886.71010399</v>
+        <v>167891886.64259699</v>
       </c>
       <c r="D10" s="205">
-        <v>16708691.719342001</v>
+        <v>18220691.719342001</v>
       </c>
       <c r="E10" s="205">
-        <v>98568700.159998998</v>
+        <v>106865997.11999901</v>
       </c>
       <c r="F10" s="205">
-        <v>265579278.58944499</v>
+        <v>292978575.481938</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>343838280.39265198</v>
+        <v>378518447.39824998</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>16023834.473927001</v>
+        <v>17578358.803927001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,16 +21805,16 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>208943511.124477</v>
+        <v>217517790.41167599</v>
       </c>
       <c r="D11" s="205">
-        <v>51564741.228233002</v>
+        <v>59306658.328172997</v>
       </c>
       <c r="E11" s="205">
         <v>26756757</v>
       </c>
       <c r="F11" s="205">
-        <v>287265009.35271001</v>
+        <v>303581205.73984897</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>129230508.15793701</v>
+        <v>163226531.427937</v>
       </c>
       <c r="D12" s="205">
-        <v>32246304.411772002</v>
+        <v>34433128.751772001</v>
       </c>
       <c r="E12" s="205">
-        <v>18777386.960000001</v>
+        <v>33191800.960000001</v>
       </c>
       <c r="F12" s="205">
-        <v>180254199.52970901</v>
+        <v>230851461.139709</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>241961823.99011901</v>
+        <v>260603268.55607399</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>47644038.982330002</v>
+        <v>50186238.982330002</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>136796737.675641</v>
+        <v>147081827.675639</v>
       </c>
       <c r="D13" s="205">
         <v>16245873.589885</v>
       </c>
       <c r="E13" s="205">
-        <v>23076576.34</v>
+        <v>25132432.16</v>
       </c>
       <c r="F13" s="205">
-        <v>176119187.605526</v>
+        <v>188460133.425524</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>510383402.37286103</v>
+        <v>541621049.35159302</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>40929133.359916002</v>
+        <v>45173673.849916004</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>343838280.39265198</v>
+        <v>378518447.39824998</v>
       </c>
       <c r="D14" s="205">
-        <v>16023834.473927001</v>
+        <v>17578358.803927001</v>
       </c>
       <c r="E14" s="205">
-        <v>103966665.72</v>
+        <v>119438737.64</v>
       </c>
       <c r="F14" s="205">
-        <v>463828780.58657902</v>
+        <v>515535543.84217697</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>229751949.23851499</v>
+        <v>257242893.13640299</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>34375803.599858999</v>
+        <v>39570034.279858999</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21925,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>208943511.124477</v>
+        <v>217517790.41167599</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>51564741.228233002</v>
+        <v>59306658.328172997</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>241961823.99011901</v>
+        <v>260603268.55607399</v>
       </c>
       <c r="D16" s="205">
-        <v>47644038.982330002</v>
+        <v>50186238.982330002</v>
       </c>
       <c r="E16" s="205">
         <v>10797297.199999999</v>
       </c>
       <c r="F16" s="205">
-        <v>300403160.17244899</v>
+        <v>321586804.73840398</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>230336475.427122</v>
+        <v>265420081.68098801</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>29219087.389970999</v>
+        <v>34985887.389971003</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21981,11 +21981,11 @@
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>150301886.71010399</v>
+        <v>167891886.64259699</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>16708691.719342001</v>
+        <v>18220691.719342001</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21993,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>571165148.50393903</v>
+        <v>591550323.03389704</v>
       </c>
       <c r="D18" s="205">
         <v>7419438.6219769996</v>
       </c>
       <c r="E18" s="205">
-        <v>5391891.8399999999</v>
+        <v>8112162.0800000001</v>
       </c>
       <c r="F18" s="205">
-        <v>583976478.96591604</v>
+        <v>607081923.73587406</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>439502423.57798398</v>
+        <v>464426328.464688</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>133255637.637747</v>
+        <v>138053124.35753101</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>510383402.37286103</v>
+        <v>541621049.35159302</v>
       </c>
       <c r="D19" s="205">
-        <v>40929133.359916002</v>
+        <v>45173673.849916004</v>
       </c>
       <c r="E19" s="205">
-        <v>489000019.35992301</v>
+        <v>495204525.35992301</v>
       </c>
       <c r="F19" s="205">
-        <v>1040312555.0927</v>
+        <v>1081999248.5614319</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>151562326.01270801</v>
+        <v>169736891.572678</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>78926681.972957</v>
+        <v>87020409.452937007</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,16 +22049,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>123395812.01270799</v>
+        <v>132866667.572678</v>
       </c>
       <c r="D20" s="205">
-        <v>19725574.809856001</v>
+        <v>20733574.809856001</v>
       </c>
       <c r="E20" s="205">
         <v>1027027.04</v>
       </c>
       <c r="F20" s="205">
-        <v>144148413.862564</v>
+        <v>154627269.42253399</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>28166514</v>
+        <v>36870224</v>
       </c>
       <c r="D21" s="205">
-        <v>59201107.163101003</v>
+        <v>66286834.643081002</v>
       </c>
       <c r="E21" s="205">
-        <v>26313514.039999999</v>
+        <v>34962162.840000004</v>
       </c>
       <c r="F21" s="205">
-        <v>113681135.20310099</v>
+        <v>138119221.48308101</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>434929553.98460102</v>
+        <v>462642272.44591904</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22103,7 +22103,7 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>58499359.200000003</v>
+        <v>84693979.200000003</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
@@ -22112,7 +22112,7 @@
         <v>6054053.8799999999</v>
       </c>
       <c r="F22" s="205">
-        <v>64553413.079999998</v>
+        <v>90748033.079999998</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22123,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>152247018.149975</v>
+        <v>156605928.149975</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22132,7 +22132,7 @@
         <v>7297297.0999999996</v>
       </c>
       <c r="F23" s="205">
-        <v>159544315.249975</v>
+        <v>163903225.249975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>139526856.460715</v>
+        <v>164522529.84539101</v>
       </c>
       <c r="D24" s="205">
-        <v>25779936.818475999</v>
+        <v>27797935.018475998</v>
       </c>
       <c r="E24" s="205">
-        <v>65610990.020000003</v>
+        <v>76512070.980000004</v>
       </c>
       <c r="F24" s="205">
-        <v>230917783.299191</v>
+        <v>268832535.843867</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>229751949.23851499</v>
+        <v>257242893.13640299</v>
       </c>
       <c r="D25" s="205">
-        <v>34375803.599858999</v>
+        <v>39570034.279858999</v>
       </c>
       <c r="E25" s="205">
-        <v>77012611.840000004</v>
+        <v>101030629.5</v>
       </c>
       <c r="F25" s="205">
-        <v>341140364.67837399</v>
+        <v>397843556.91626197</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>230336475.427122</v>
+        <v>265420081.68098801</v>
       </c>
       <c r="D26" s="205">
-        <v>29219087.389970999</v>
+        <v>34985887.389971003</v>
       </c>
       <c r="E26" s="205">
-        <v>226352790.72995099</v>
+        <v>253741979.629951</v>
       </c>
       <c r="F26" s="205">
-        <v>485908353.54704398</v>
+        <v>554147948.70090997</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>439502423.57798398</v>
+        <v>464426328.464688</v>
       </c>
       <c r="D27" s="205">
-        <v>133255637.637747</v>
+        <v>138053124.35753101</v>
       </c>
       <c r="E27" s="205">
         <v>12199459.539999999</v>
       </c>
       <c r="F27" s="205">
-        <v>584957520.75573099</v>
+        <v>614678912.36221898</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>162874843.26519999</v>
+        <v>175619708.38512</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>175429613.008481</v>
+        <v>221038560.34797901</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>186957678.84739801</v>
+        <v>207064992.308716</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>247971875.13720301</v>
+        <v>255577280.13720301</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="246"/>
-      <c r="D41" s="247"/>
+      <c r="C41" s="239"/>
+      <c r="D41" s="240"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.58064516129032262</v>
+        <v>0.61290322580645162</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>3319215239.7708101</v>
+        <v>3635442114.7938886</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.4853165192772112</v>
+        <v>0.53155339010415614</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>3520064092.2291899</v>
+        <v>3203837217.2061114</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>293338674.35243249</v>
+        <v>291257928.83691925</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>541416002.90441501</v>
+        <v>587068252.24411905</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.36699580578052415</v>
+        <v>0.39794092735476766</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>933848821.3159467</v>
+        <v>888196571.97624266</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>77820735.10966222</v>
+        <v>80745142.906931147</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>773234010.25828195</v>
+        <v>859300541.17901802</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.43367539954820095</v>
+        <v>0.48194660424121522</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>1009744713.1459739</v>
+        <v>923678182.22523785</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>84145392.762164488</v>
+        <v>83970743.83865799</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>4633865252.933507</v>
+        <v>5081810908.2170258</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.45891109217330872</v>
+        <v>0.50327302733538792</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>5463657626.6911106</v>
+        <v>5015711971.4075918</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>455304802.2242592</v>
+        <v>455973815.58250833</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>139526856.460715</v>
+        <v>164522529.84539101</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>25779936.818475999</v>
+        <v>27797935.018475998</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>165306793.27919099</v>
+        <v>192320464.86386701</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.3408711639648031</v>
+        <v>0.39657475299081191</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>277156621.539285</v>
+        <v>252160948.15460899</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>42490464.40217831</v>
+        <v>40472466.202178314</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>319647085.94146335</v>
+        <v>292633414.35678732</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>26637257.161788613</v>
+        <v>26603037.668798849</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>266027245.83357799</v>
+        <v>310308359.103576</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>48492178.001657002</v>
+        <v>50679002.341656998</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>314519423.835235</v>
+        <v>360987361.44523299</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.42119612141732299</v>
+        <v>0.48342475853274136</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>289155125.16642201</v>
+        <v>244874011.896424</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>143054605.99834299</v>
+        <v>140867781.65834302</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>432209731.164765</v>
+        <v>385741793.55476701</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>36017477.59706375</v>
+        <v>35067435.777706094</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>58499359.200000003</v>
+        <v>84693979.200000003</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>58499359.200000003</v>
+        <v>84693979.200000003</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.24226018757488305</v>
+        <v>0.35073853061035309</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>182973908.80000001</v>
+        <v>156779288.80000001</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>182973908.80000001</v>
+        <v>156779288.80000001</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>15247825.733333334</v>
+        <v>14252662.618181819</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>343838280.39265198</v>
+        <v>378518447.39824998</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>16023834.473927001</v>
+        <v>17578358.803927001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>359862114.866579</v>
+        <v>396096806.20217699</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.54724032053468386</v>
+        <v>0.60234221451515946</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>266874191.60734802</v>
+        <v>232194024.60175002</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>30857992.343407892</v>
+        <v>29303468.01340789</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>297732183.95075589</v>
+        <v>261497492.6151579</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>24811015.329229657</v>
+        <v>23772499.328650717</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>22758640.015960347</v>
+        <v>24827607.290138558</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>241961823.99011901</v>
+        <v>260603268.55607399</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>47644038.982330002</v>
+        <v>50186238.982330002</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>289605862.972449</v>
+        <v>310789507.53840399</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.52166364352577399</v>
+        <v>0.55982149397123382</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>231957008.00988099</v>
+        <v>213315563.44392601</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>33595355.140323602</v>
+        <v>31053155.140323602</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>265552363.1502046</v>
+        <v>244368718.58424962</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>22129363.595850382</v>
+        <v>22215338.053113602</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>510383402.37286103</v>
+        <v>541621049.35159302</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>40929133.359916002</v>
+        <v>45173673.849916004</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>551312535.732777</v>
+        <v>586794723.201509</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.52322233916702743</v>
+        <v>0.55689665622473261</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>451374942.62713897</v>
+        <v>420137295.64840698</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>50999442.979240388</v>
+        <v>46754902.489240386</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>502374385.60637939</v>
+        <v>466892198.13764739</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>41864532.133864947</v>
+        <v>42444745.285240673</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>229751949.23851499</v>
+        <v>257242893.13640299</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>34375803.599858999</v>
+        <v>39570034.279858999</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>264127752.83837399</v>
+        <v>296812927.41626197</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.46414055603424642</v>
+        <v>0.52157683427321111</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>275535109.76148498</v>
+        <v>248044165.86359701</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>29405600.400141001</v>
+        <v>24211369.720141001</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>304940710.16162598</v>
+        <v>272255535.58373803</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>25411725.846802164</v>
+        <v>24750503.234885275</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>152247018.149975</v>
+        <v>156605928.149975</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>152247018.149975</v>
+        <v>156605928.149975</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.37672441499447817</v>
+        <v>0.38751022768045129</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>251886645.850025</v>
+        <v>247527735.850025</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>251886645.850025</v>
+        <v>247527735.850025</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>20990553.820835415</v>
+        <v>22502521.440911364</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23061,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>208943511.124477</v>
+        <v>217517790.41167599</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>51564741.228233002</v>
+        <v>59306658.328172997</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>260508252.35271001</v>
+        <v>276824448.73984897</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.48021574318219568</v>
+        <v>0.51029269584374959</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>195073797.875523</v>
+        <v>186499518.58832401</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>86899648.989762396</v>
+        <v>79157731.889822409</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>281973446.8652854</v>
+        <v>265657250.47814643</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>23497787.238773782</v>
+        <v>24150659.134376947</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>230336475.427122</v>
+        <v>265420081.68098801</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>29219087.389970999</v>
+        <v>34985887.389971003</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>259555562.81709298</v>
+        <v>300405969.07095903</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.37596522579647013</v>
+        <v>0.43513688077631424</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>401293120.572878</v>
+        <v>366209514.31901199</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>29522513.220654268</v>
+        <v>23755713.220654264</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>430815633.79353225</v>
+        <v>389965227.53966624</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>35901302.816127688</v>
+        <v>35451384.321787842</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>150301886.71010399</v>
+        <v>167891886.64259699</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>16708691.719342001</v>
+        <v>18220691.719342001</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>167010578.42944598</v>
+        <v>186112578.36193898</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.37088144862681122</v>
+        <v>0.41330138078473228</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>236241136.28989601</v>
+        <v>218651136.35740301</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>47055463.080471806</v>
+        <v>45543463.080471806</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>283296599.37036783</v>
+        <v>264194599.43787482</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>23608049.947530653</v>
+        <v>24017690.857988622</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>439502423.57798398</v>
+        <v>464426328.464688</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>133255637.637747</v>
+        <v>138053124.35753101</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>572758061.21573102</v>
+        <v>602479452.82221901</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.62722785333649411</v>
+        <v>0.65977577525651254</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>143848518.42201602</v>
+        <v>118924613.535312</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>196551307.3549704</v>
+        <v>191753820.63518637</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>340399825.77698636</v>
+        <v>310678434.17049837</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>28366652.148082197</v>
+        <v>28243494.015499853</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>151562326.01270801</v>
+        <v>169736891.572678</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>78926681.972957</v>
+        <v>87020409.452937007</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>230489007.98566502</v>
+        <v>256757301.02561501</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.44539307026790237</v>
+        <v>0.49615347654501185</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>107963362.98729199</v>
+        <v>89788797.427322</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>179043349.93492937</v>
+        <v>170949622.45494938</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>287006712.92222136</v>
+        <v>260738419.88227138</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>23917226.076851781</v>
+        <v>23703492.716570124</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>3319215239.7708101</v>
+        <v>3635442114.7938886</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>541416002.90441501</v>
+        <v>587068252.24411905</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>3860631242.6752253</v>
+        <v>4222510367.0380082</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.4643226580000745</v>
+        <v>0.50784628570154622</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>3520064092.2291903</v>
+        <v>3203837217.206111</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>933848821.31594658</v>
+        <v>888196571.97624254</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>4453912913.5451365</v>
+        <v>4092033789.1823535</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>371159409.46209472</v>
+        <v>372003071.74385029</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>65610990.020000003</v>
+        <v>76512070.980000004</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>41853963.299999997</v>
+        <v>58324233.120000005</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>103966665.72</v>
+        <v>119438737.64</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>489000019.35992301</v>
+        <v>495204525.35992301</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>77012611.840000004</v>
+        <v>101030629.5</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>226352790.72995099</v>
+        <v>253741979.629951</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>98568700.159998998</v>
+        <v>106865997.11999901</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>27340541.079999998</v>
+        <v>35989189.880000003</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1192811146.929873</v>
+        <v>1310212227.949873</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>162874843.26519999</v>
+        <v>175619708.38512</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.58574458157531106</v>
+        <v>0.63157876650678091</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>115189774.63900957</v>
+        <v>102444909.51908955</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9599147.886584131</v>
+        <v>9313173.5926445052</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>175429613.008481</v>
+        <v>221038560.34797901</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.4200714064782668</v>
+        <v>0.52928338231480876</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>242188940.17804059</v>
+        <v>196579992.83854258</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>20182411.681503382</v>
+        <v>17870908.439867508</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>434929553.98460102</v>
+        <v>462642272.44591904</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.40001042316338647</v>
+        <v>0.42549817431104037</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>652365998.3289237</v>
+        <v>624653279.86760569</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>54363833.194076978</v>
+        <v>56786661.806145974</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,29 +23760,24 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>773234010.25828195</v>
+        <v>859300541.17901802</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.43367539954820095</v>
+        <v>0.48194660424121522</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>1009744713.1459739</v>
+        <v>923678182.22523785</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>84145392.762164488</v>
+        <v>83970743.83865799</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23790,6 +23785,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,11 +25835,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25847,6 +25842,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="242"/>
-      <c r="N48" s="243"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="246"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="244" t="s">
+      <c r="N49" s="247" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="244"/>
+      <c r="N50" s="247"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="238" t="s">
+      <c r="B87" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="239"/>
-      <c r="D87" s="239"/>
-      <c r="E87" s="239"/>
-      <c r="F87" s="240"/>
+      <c r="C87" s="242"/>
+      <c r="D87" s="242"/>
+      <c r="E87" s="242"/>
+      <c r="F87" s="243"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,11 +27892,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27904,6 +27899,11 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 19 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 20 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1927,15 +1927,6 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1955,6 +1946,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3599,10 +3599,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -4663,13 +4663,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -4872,6 +4872,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -4879,11 +4884,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -5656,10 +5656,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -6720,13 +6720,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -6929,6 +6929,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -6936,11 +6941,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -7713,10 +7713,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -8777,13 +8777,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -8986,6 +8986,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -8993,11 +8998,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -9770,10 +9770,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -10834,13 +10834,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -11043,6 +11043,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -11050,11 +11055,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11826,10 +11826,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -12876,13 +12876,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -13085,6 +13085,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -13092,11 +13097,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21743,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>164522529.84539101</v>
+        <v>193728052.55777201</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>27797935.018475998</v>
+        <v>29732159.813473001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21765,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>310308359.103576</v>
+        <v>340597245.07357001</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>50679002.341656998</v>
+        <v>52293732.082157001</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,27 +21777,27 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>167891886.64259699</v>
+        <v>178327048.7886</v>
       </c>
       <c r="D10" s="205">
-        <v>18220691.719342001</v>
+        <v>18591862.899342</v>
       </c>
       <c r="E10" s="205">
-        <v>106865997.11999901</v>
+        <v>108315546.639999</v>
       </c>
       <c r="F10" s="205">
-        <v>292978575.481938</v>
+        <v>305234458.327941</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>378518447.39824998</v>
+        <v>410992483.28824902</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
-        <v>17578358.803927001</v>
+        <v>19299582.641127001</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -21805,7 +21805,7 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>217517790.41167599</v>
+        <v>222570729.18966401</v>
       </c>
       <c r="D11" s="205">
         <v>59306658.328172997</v>
@@ -21814,18 +21814,18 @@
         <v>26756757</v>
       </c>
       <c r="F11" s="205">
-        <v>303581205.73984897</v>
+        <v>308634144.51783699</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>196332681.28</v>
+        <v>220179527.69999799</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>18496237.719999999</v>
+        <v>19090832.32</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -21833,27 +21833,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>163226531.427937</v>
+        <v>184503142.497931</v>
       </c>
       <c r="D12" s="205">
-        <v>34433128.751772001</v>
+        <v>34410750.382271998</v>
       </c>
       <c r="E12" s="205">
         <v>33191800.960000001</v>
       </c>
       <c r="F12" s="205">
-        <v>230851461.139709</v>
+        <v>252105693.84020299</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>260603268.55607399</v>
+        <v>269419401.431153</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>50186238.982330002</v>
+        <v>51766419.171329997</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21861,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>147081827.675639</v>
+        <v>156094102.57563901</v>
       </c>
       <c r="D13" s="205">
-        <v>16245873.589885</v>
+        <v>17882981.699885</v>
       </c>
       <c r="E13" s="205">
-        <v>25132432.16</v>
+        <v>26339639.34</v>
       </c>
       <c r="F13" s="205">
-        <v>188460133.425524</v>
+        <v>200316723.61552399</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>541621049.35159302</v>
+        <v>572685678.40666699</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>45173673.849916004</v>
+        <v>45816273.849916004</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21889,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>378518447.39824998</v>
+        <v>410992483.28824902</v>
       </c>
       <c r="D14" s="205">
-        <v>17578358.803927001</v>
+        <v>19299582.641127001</v>
       </c>
       <c r="E14" s="205">
-        <v>119438737.64</v>
+        <v>123071170.04000001</v>
       </c>
       <c r="F14" s="205">
-        <v>515535543.84217697</v>
+        <v>553363235.96937597</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>257242893.13640299</v>
+        <v>266657225.53848201</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>39570034.279858999</v>
+        <v>42467131.579859003</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,7 +21925,7 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>217517790.41167599</v>
+        <v>222570729.18966401</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
@@ -21937,27 +21937,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>260603268.55607399</v>
+        <v>269419401.431153</v>
       </c>
       <c r="D16" s="205">
-        <v>50186238.982330002</v>
+        <v>51766419.171329997</v>
       </c>
       <c r="E16" s="205">
         <v>10797297.199999999</v>
       </c>
       <c r="F16" s="205">
-        <v>321586804.73840398</v>
+        <v>331983117.80248302</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>265420081.68098801</v>
+        <v>270593460.01106203</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>34985887.389971003</v>
+        <v>35579977.479971997</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21965,27 +21965,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>196332681.28</v>
+        <v>220179527.69999799</v>
       </c>
       <c r="D17" s="205">
-        <v>18496237.719999999</v>
+        <v>19090832.32</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>214828919</v>
+        <v>239270360.01999801</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>167891886.64259699</v>
+        <v>178327048.7886</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>18220691.719342001</v>
+        <v>18591862.899342</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,7 +21993,7 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>591550323.03389704</v>
+        <v>774715655.04786694</v>
       </c>
       <c r="D18" s="205">
         <v>7419438.6219769996</v>
@@ -22002,18 +22002,18 @@
         <v>8112162.0800000001</v>
       </c>
       <c r="F18" s="205">
-        <v>607081923.73587406</v>
+        <v>790247255.74984396</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>464426328.464688</v>
+        <v>486173081.16347802</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>138053124.35753101</v>
+        <v>148831502.51741099</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22021,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>541621049.35159302</v>
+        <v>572685678.40666699</v>
       </c>
       <c r="D19" s="205">
-        <v>45173673.849916004</v>
+        <v>45816273.849916004</v>
       </c>
       <c r="E19" s="205">
-        <v>495204525.35992301</v>
+        <v>488438129.73994303</v>
       </c>
       <c r="F19" s="205">
-        <v>1081999248.5614319</v>
+        <v>1106940081.996526</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>169736891.572678</v>
+        <v>156825830.31347799</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>87020409.452937007</v>
+        <v>89668238.982917994</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,7 +22049,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>132866667.572678</v>
+        <v>118290806.31347799</v>
       </c>
       <c r="D20" s="205">
         <v>20733574.809856001</v>
@@ -22058,7 +22058,7 @@
         <v>1027027.04</v>
       </c>
       <c r="F20" s="205">
-        <v>154627269.42253399</v>
+        <v>140051408.16333401</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22076,23 +22076,23 @@
         <v>124</v>
       </c>
       <c r="C21" s="205">
-        <v>36870224</v>
+        <v>38535024</v>
       </c>
       <c r="D21" s="205">
-        <v>66286834.643081002</v>
+        <v>68934664.173061997</v>
       </c>
       <c r="E21" s="205">
         <v>34962162.840000004</v>
       </c>
       <c r="F21" s="205">
-        <v>138119221.48308101</v>
+        <v>142431851.013062</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>462642272.44591904</v>
+        <v>480244808.89564198</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22103,7 +22103,7 @@
         <v>173</v>
       </c>
       <c r="C22" s="205">
-        <v>84693979.200000003</v>
+        <v>120464485.8</v>
       </c>
       <c r="D22" s="205" t="s">
         <v>169</v>
@@ -22112,7 +22112,7 @@
         <v>6054053.8799999999</v>
       </c>
       <c r="F22" s="205">
-        <v>90748033.079999998</v>
+        <v>126518539.68000001</v>
       </c>
       <c r="H22" s="116"/>
       <c r="I22" s="116"/>
@@ -22123,7 +22123,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>156605928.149975</v>
+        <v>156137878.04997501</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22132,7 +22132,7 @@
         <v>7297297.0999999996</v>
       </c>
       <c r="F23" s="205">
-        <v>163903225.249975</v>
+        <v>163435175.149975</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22143,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>164522529.84539101</v>
+        <v>193728052.55777201</v>
       </c>
       <c r="D24" s="205">
-        <v>27797935.018475998</v>
+        <v>29732159.813473001</v>
       </c>
       <c r="E24" s="205">
-        <v>76512070.980000004</v>
+        <v>83676034.900000006</v>
       </c>
       <c r="F24" s="205">
-        <v>268832535.843867</v>
+        <v>307136247.271245</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22163,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>257242893.13640299</v>
+        <v>266657225.53848201</v>
       </c>
       <c r="D25" s="205">
-        <v>39570034.279858999</v>
+        <v>42467131.579859003</v>
       </c>
       <c r="E25" s="205">
-        <v>101030629.5</v>
+        <v>99733332.219999999</v>
       </c>
       <c r="F25" s="205">
-        <v>397843556.91626197</v>
+        <v>408857689.338341</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22183,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>265420081.68098801</v>
+        <v>270593460.01106203</v>
       </c>
       <c r="D26" s="205">
-        <v>34985887.389971003</v>
+        <v>35579977.479971997</v>
       </c>
       <c r="E26" s="205">
-        <v>253741979.629951</v>
+        <v>257587925.58995101</v>
       </c>
       <c r="F26" s="205">
-        <v>554147948.70090997</v>
+        <v>563761363.08098495</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22203,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>464426328.464688</v>
+        <v>486173081.16347802</v>
       </c>
       <c r="D27" s="205">
-        <v>138053124.35753101</v>
+        <v>148831502.51741099</v>
       </c>
       <c r="E27" s="205">
-        <v>12199459.539999999</v>
+        <v>12491351.439999999</v>
       </c>
       <c r="F27" s="205">
-        <v>614678912.36221898</v>
+        <v>647495935.12088895</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22259,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>175619708.38512</v>
+        <v>186126288.68503001</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22270,7 +22270,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="205">
-        <v>221038560.34797901</v>
+        <v>245411419.23768699</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22281,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>207064992.308716</v>
+        <v>213668249.15867499</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="205">
-        <v>255577280.13720301</v>
+        <v>266576559.736967</v>
       </c>
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
@@ -22334,17 +22334,17 @@
       <c r="I40" s="116"/>
     </row>
     <row r="41" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="238" t="s">
+      <c r="B41" s="245" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="239"/>
-      <c r="D41" s="240"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="247"/>
       <c r="E41" s="67" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.61290322580645162</v>
+        <v>0.64516129032258063</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22387,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>3635442114.7938886</v>
+        <v>3865352127.3121481</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.53155339010415614</v>
+        <v>0.56516950685530909</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>3203837217.2061114</v>
+        <v>2973927204.6878519</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>291257928.83691925</v>
+        <v>297392720.46878517</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22416,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>587068252.24411905</v>
+        <v>612444371.66567802</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.39794092735476766</v>
+        <v>0.41514198780502926</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>888196571.97624266</v>
+        <v>862820452.55468369</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>80745142.906931147</v>
+        <v>86282045.255468369</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22445,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>859300541.17901802</v>
+        <v>911782516.8183589</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.48194660424121522</v>
+        <v>0.5113816025114899</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>923678182.22523785</v>
+        <v>871196206.58589697</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>83970743.83865799</v>
+        <v>87119620.658589691</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22472,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>5081810908.2170258</v>
+        <v>5389579015.7961845</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.50327302733538792</v>
+        <v>0.53375259259591257</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>5015711971.4075918</v>
+        <v>4707943863.8284321</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>455973815.58250833</v>
+        <v>470794386.3828432</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22505,10 +22505,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
@@ -22593,35 +22593,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>164522529.84539101</v>
+        <v>193728052.55777201</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>27797935.018475998</v>
+        <v>29732159.813473001</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>192320464.86386701</v>
+        <v>223460212.37124503</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.39657475299081191</v>
+        <v>0.46078652413371146</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>252160948.15460899</v>
+        <v>222955425.44222799</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>40472466.202178314</v>
+        <v>38538241.407181308</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>292633414.35678732</v>
+        <v>261493666.84940928</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>26603037.668798849</v>
+        <v>26149366.684940927</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22645,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>310308359.103576</v>
+        <v>340597245.07357001</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>50679002.341656998</v>
+        <v>52293732.082157001</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>360987361.44523299</v>
+        <v>392890977.15572703</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.48342475853274136</v>
+        <v>0.52614923968748351</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>244874011.896424</v>
+        <v>214585125.92642999</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>140867781.65834302</v>
+        <v>139253051.91784298</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>385741793.55476701</v>
+        <v>353838177.84427297</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>35067435.777706094</v>
+        <v>35383817.7844273</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="G53" s="122">
         <f>C22</f>
-        <v>84693979.200000003</v>
+        <v>120464485.8</v>
       </c>
       <c r="H53" s="122">
         <f>IF(D22="",0,D22)</f>
@@ -22705,15 +22705,15 @@
       </c>
       <c r="I53" s="122">
         <f>G53+H53</f>
-        <v>84693979.200000003</v>
+        <v>120464485.8</v>
       </c>
       <c r="J53" s="61">
         <f>IFERROR(I53/F53,0)</f>
-        <v>0.35073853061035309</v>
+        <v>0.49887296758662331</v>
       </c>
       <c r="K53" s="54">
         <f>D53-G53</f>
-        <v>156779288.80000001</v>
+        <v>121008782.2</v>
       </c>
       <c r="L53" s="54">
         <f>E53-H53</f>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="M53" s="54">
         <f>F53-I53</f>
-        <v>156779288.80000001</v>
+        <v>121008782.2</v>
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>14252662.618181819</v>
+        <v>12100878.220000001</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,35 +22749,35 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>378518447.39824998</v>
+        <v>410992483.28824902</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
-        <v>17578358.803927001</v>
+        <v>19299582.641127001</v>
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>396096806.20217699</v>
+        <v>430292065.92937601</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.60234221451515946</v>
+        <v>0.65434275616933468</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>232194024.60175002</v>
+        <v>199719988.71175098</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
-        <v>29303468.01340789</v>
+        <v>27582244.176207889</v>
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>261497492.6151579</v>
+        <v>227302232.88795888</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>23772499.328650717</v>
+        <v>22730223.288795888</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,35 +22801,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>196332681.28</v>
+        <v>220179527.69999799</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>18496237.719999999</v>
+        <v>19090832.32</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>214828919</v>
+        <v>239270360.01999798</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.44028400511865573</v>
+        <v>0.49037584374656462</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>208730602.72</v>
+        <v>184883756.30000201</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>64373077.471524149</v>
+        <v>63778482.871524148</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>273103680.19152415</v>
+        <v>248662239.17152616</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24827607.290138558</v>
+        <v>24866223.917152617</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22853,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>260603268.55607399</v>
+        <v>269419401.431153</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>50186238.982330002</v>
+        <v>51766419.171329997</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>310789507.53840399</v>
+        <v>321185820.60248297</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.55982149397123382</v>
+        <v>0.5785482507315346</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>213315563.44392601</v>
+        <v>204499430.568847</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>31053155.140323602</v>
+        <v>29472974.951323606</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>244368718.58424962</v>
+        <v>233972405.52017063</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>22215338.053113602</v>
+        <v>23397240.552017063</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22905,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>541621049.35159302</v>
+        <v>572685678.40666699</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>45173673.849916004</v>
+        <v>45816273.849916004</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>586794723.201509</v>
+        <v>618501952.25658298</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.55689665622473261</v>
+        <v>0.58698835463432897</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>420137295.64840698</v>
+        <v>389072666.59333301</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>46754902.489240386</v>
+        <v>46112302.489240386</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>466892198.13764739</v>
+        <v>435184969.08257341</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>42444745.285240673</v>
+        <v>43518496.908257343</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22957,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>257242893.13640299</v>
+        <v>266657225.53848201</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>39570034.279858999</v>
+        <v>42467131.579859003</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>296812927.41626197</v>
+        <v>309124357.11834103</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.52157683427321111</v>
+        <v>0.54321119024714082</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>248044165.86359701</v>
+        <v>238629833.46151799</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>24211369.720141001</v>
+        <v>21314272.420140997</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>272255535.58373803</v>
+        <v>259944105.88165897</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>24750503.234885275</v>
+        <v>25994410.588165898</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>156605928.149975</v>
+        <v>156137878.04997501</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23017,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>156605928.149975</v>
+        <v>156137878.04997501</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.38751022768045129</v>
+        <v>0.38635207100682167</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>247527735.850025</v>
+        <v>247995785.95002499</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23033,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>247527735.850025</v>
+        <v>247995785.95002499</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>22502521.440911364</v>
+        <v>24799578.595002498</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>217517790.41167599</v>
+        <v>222570729.18966401</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
@@ -23069,15 +23069,15 @@
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>276824448.73984897</v>
+        <v>281877387.51783699</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.51029269584374959</v>
+        <v>0.51960718292280128</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>186499518.58832401</v>
+        <v>181446579.81033599</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
@@ -23085,11 +23085,11 @@
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>265657250.47814643</v>
+        <v>260604311.70015842</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>24150659.134376947</v>
+        <v>26060431.170015842</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23113,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>265420081.68098801</v>
+        <v>270593460.01106203</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>34985887.389971003</v>
+        <v>35579977.479971997</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>300405969.07095903</v>
+        <v>306173437.49103403</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.43513688077631424</v>
+        <v>0.44349103640793724</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>366209514.31901199</v>
+        <v>361036135.98893797</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>23755713.220654264</v>
+        <v>23161623.13065327</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>389965227.53966624</v>
+        <v>384197759.11959124</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>35451384.321787842</v>
+        <v>38419775.911959127</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23165,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>167891886.64259699</v>
+        <v>178327048.7886</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>18220691.719342001</v>
+        <v>18591862.899342</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>186112578.36193898</v>
+        <v>196918911.687942</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.41330138078473228</v>
+        <v>0.43729907360144998</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>218651136.35740301</v>
+        <v>208215974.2114</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>45543463.080471806</v>
+        <v>45172291.900471807</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>264194599.43787482</v>
+        <v>253388266.11187181</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>24017690.857988622</v>
+        <v>25338826.611187182</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23217,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>464426328.464688</v>
+        <v>486173081.16347802</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>138053124.35753101</v>
+        <v>148831502.51741099</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>602479452.82221901</v>
+        <v>635004583.68088901</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.65977577525651254</v>
+        <v>0.69539407448161628</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>118924613.535312</v>
+        <v>97177860.836521983</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>191753820.63518637</v>
+        <v>180975442.47530639</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>310678434.17049837</v>
+        <v>278153303.31182837</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>28243494.015499853</v>
+        <v>27815330.331182837</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23269,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>169736891.572678</v>
+        <v>156825830.31347799</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>87020409.452937007</v>
+        <v>89668238.982917994</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>256757301.02561501</v>
+        <v>246494069.29639599</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.49615347654501185</v>
+        <v>0.47632098071062434</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>89788797.427322</v>
+        <v>102699858.68652201</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>170949622.45494938</v>
+        <v>168301792.92496839</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>260738419.88227138</v>
+        <v>271001651.61149037</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>23703492.716570124</v>
+        <v>27100165.161149036</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23319,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>3635442114.7938886</v>
+        <v>3865352127.3121481</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>587068252.24411905</v>
+        <v>612444371.66567802</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>4222510367.0380082</v>
+        <v>4477796498.9778261</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.50784628570154622</v>
+        <v>0.53854984889674928</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>3203837217.206111</v>
+        <v>2973927204.6878519</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>888196571.97624254</v>
+        <v>862820452.55468357</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>4092033789.1823535</v>
+        <v>3836747657.2425356</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>372003071.74385029</v>
+        <v>383674765.72425354</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>76512070.980000004</v>
+        <v>83676034.900000006</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>58324233.120000005</v>
+        <v>59531440.299999997</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>119438737.64</v>
+        <v>123071170.04000001</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>495204525.35992301</v>
+        <v>488438129.73994303</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>101030629.5</v>
+        <v>99733332.219999999</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>253741979.629951</v>
+        <v>257587925.58995101</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>106865997.11999901</v>
+        <v>108315546.639999</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>12199459.539999999</v>
+        <v>12491351.439999999</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23555,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1310212227.949873</v>
+        <v>1319739525.929893</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23569,13 +23569,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -23617,19 +23617,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>175619708.38512</v>
+        <v>186126288.68503001</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.63157876650678091</v>
+        <v>0.66936343821042577</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>102444909.51908955</v>
+        <v>91938329.219179541</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9313173.5926445052</v>
+        <v>9193832.9219179545</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23646,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>221038560.34797901</v>
+        <v>245411419.23768699</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.52928338231480876</v>
+        <v>0.58764491511486683</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>196579992.83854258</v>
+        <v>172207133.9488346</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17870908.439867508</v>
+        <v>17220713.394883461</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23675,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>462642272.44591904</v>
+        <v>480244808.89564198</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.42549817431104037</v>
+        <v>0.44168745827552325</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>624653279.86760569</v>
+        <v>607050743.41788268</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>56786661.806145974</v>
+        <v>60705074.34178827</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,24 +23760,29 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>859300541.17901802</v>
+        <v>911782516.8183589</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.48194660424121522</v>
+        <v>0.5113816025114899</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>923678182.22523785</v>
+        <v>871196206.58589685</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>83970743.83865799</v>
+        <v>87119620.658589691</v>
       </c>
       <c r="I94" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -23785,11 +23790,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -24562,10 +24562,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -24627,7 +24627,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -25626,13 +25626,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -25835,6 +25835,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -25842,11 +25847,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -26619,10 +26619,10 @@
       <c r="H48" s="229"/>
       <c r="I48" s="229"/>
       <c r="J48" s="230"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="245"/>
-      <c r="M48" s="245"/>
-      <c r="N48" s="246"/>
+      <c r="K48" s="241"/>
+      <c r="L48" s="242"/>
+      <c r="M48" s="242"/>
+      <c r="N48" s="243"/>
     </row>
     <row r="49" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="223" t="s">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="L49" s="132"/>
       <c r="M49" s="132"/>
-      <c r="N49" s="247" t="s">
+      <c r="N49" s="244" t="s">
         <v>149</v>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       <c r="M50" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="N50" s="247"/>
+      <c r="N50" s="244"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -27683,13 +27683,13 @@
       <c r="I86" s="116"/>
     </row>
     <row r="87" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="241" t="s">
+      <c r="B87" s="238" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="242"/>
-      <c r="D87" s="242"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="C87" s="239"/>
+      <c r="D87" s="239"/>
+      <c r="E87" s="239"/>
+      <c r="F87" s="240"/>
       <c r="G87" s="124"/>
       <c r="H87" s="124"/>
       <c r="I87" s="116"/>
@@ -27892,6 +27892,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="C68:C69"/>
     <mergeCell ref="B87:F87"/>
@@ -27899,11 +27904,6 @@
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="N49:N50"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA_PENCAPAIAN_2026.xlsx
+++ b/uploads/DATA_PENCAPAIAN_2026.xlsx
@@ -602,7 +602,7 @@
     <t>DATA PENCAPAIAN — GLOBAL — 30 APRIL 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — 20 MEI 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL — 21 MEI 2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1957,6 +1957,7 @@
     <xf numFmtId="0" fontId="24" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -21661,7 +21662,7 @@
       </c>
       <c r="C3" s="78">
         <f ca="1">NETWORKDAYS.INTL(TODAY(),EOMONTH(TODAY(),0),11)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="79" t="s">
         <v>104</v>
@@ -21743,11 +21744,11 @@
       <c r="J8" s="116"/>
       <c r="M8" s="11">
         <f>C24</f>
-        <v>193728052.55777201</v>
+        <v>198874466.95777199</v>
       </c>
       <c r="N8" s="11">
         <f>D24</f>
-        <v>29732159.813473001</v>
+        <v>32839506.683463</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -21765,11 +21766,11 @@
       <c r="J9" s="116"/>
       <c r="M9" s="11">
         <f>C12+C13</f>
-        <v>340597245.07357001</v>
+        <v>343396010.84356898</v>
       </c>
       <c r="N9" s="11">
         <f>D12+D13</f>
-        <v>52293732.082157001</v>
+        <v>53106196.052157</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -21777,23 +21778,23 @@
         <v>113</v>
       </c>
       <c r="C10" s="205">
-        <v>178327048.7886</v>
+        <v>184471534.469396</v>
       </c>
       <c r="D10" s="205">
-        <v>18591862.899342</v>
+        <v>22535662.899342</v>
       </c>
       <c r="E10" s="205">
-        <v>108315546.639999</v>
+        <v>116419150.11999901</v>
       </c>
       <c r="F10" s="205">
-        <v>305234458.327941</v>
+        <v>323426347.48873699</v>
       </c>
       <c r="H10" s="116"/>
       <c r="I10" s="116"/>
       <c r="J10" s="116"/>
       <c r="M10" s="11">
         <f>C14</f>
-        <v>410992483.28824902</v>
+        <v>429167713.405325</v>
       </c>
       <c r="N10" s="11">
         <f>D14</f>
@@ -21805,27 +21806,27 @@
         <v>114</v>
       </c>
       <c r="C11" s="205">
-        <v>222570729.18966401</v>
+        <v>250272862.009635</v>
       </c>
       <c r="D11" s="205">
-        <v>59306658.328172997</v>
+        <v>61442334.004658997</v>
       </c>
       <c r="E11" s="205">
         <v>26756757</v>
       </c>
       <c r="F11" s="205">
-        <v>308634144.51783699</v>
+        <v>338471953.01429403</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
       <c r="J11" s="116"/>
       <c r="M11" s="11">
         <f>C17</f>
-        <v>220179527.69999799</v>
+        <v>255314662.19999799</v>
       </c>
       <c r="N11" s="11">
         <f>D17</f>
-        <v>19090832.32</v>
+        <v>33550551.18</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -21833,27 +21834,27 @@
         <v>70</v>
       </c>
       <c r="C12" s="205">
-        <v>184503142.497931</v>
+        <v>186504610.96792999</v>
       </c>
       <c r="D12" s="205">
         <v>34410750.382271998</v>
       </c>
       <c r="E12" s="205">
-        <v>33191800.960000001</v>
+        <v>36891800.960000001</v>
       </c>
       <c r="F12" s="205">
-        <v>252105693.84020299</v>
+        <v>257807162.310202</v>
       </c>
       <c r="H12" s="116"/>
       <c r="I12" s="116"/>
       <c r="J12" s="116"/>
       <c r="M12" s="11">
         <f>C16</f>
-        <v>269419401.431153</v>
+        <v>285480633.74615097</v>
       </c>
       <c r="N12" s="11">
         <f>D16</f>
-        <v>51766419.171329997</v>
+        <v>52968401.151327997</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -21861,27 +21862,27 @@
         <v>115</v>
       </c>
       <c r="C13" s="205">
-        <v>156094102.57563901</v>
+        <v>156891399.87563899</v>
       </c>
       <c r="D13" s="205">
-        <v>17882981.699885</v>
+        <v>18695445.669884998</v>
       </c>
       <c r="E13" s="205">
-        <v>26339639.34</v>
+        <v>27974774.460000001</v>
       </c>
       <c r="F13" s="205">
-        <v>200316723.61552399</v>
+        <v>203561620.00552401</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
       <c r="M13" s="11">
         <f>C19</f>
-        <v>572685678.40666699</v>
+        <v>599215529.42203498</v>
       </c>
       <c r="N13" s="11">
         <f>D19</f>
-        <v>45816273.849916004</v>
+        <v>46766273.849916004</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -21889,27 +21890,27 @@
         <v>116</v>
       </c>
       <c r="C14" s="205">
-        <v>410992483.28824902</v>
+        <v>429167713.405325</v>
       </c>
       <c r="D14" s="205">
         <v>19299582.641127001</v>
       </c>
       <c r="E14" s="205">
-        <v>123071170.04000001</v>
+        <v>131857656.44</v>
       </c>
       <c r="F14" s="205">
-        <v>553363235.96937597</v>
+        <v>580324952.48645198</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
       <c r="M14" s="11">
         <f>C25</f>
-        <v>266657225.53848201</v>
+        <v>275775148.99845499</v>
       </c>
       <c r="N14" s="11">
         <f>D25</f>
-        <v>42467131.579859003</v>
+        <v>44631802.779844001</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -21925,11 +21926,11 @@
       <c r="J15" s="116"/>
       <c r="M15" s="11">
         <f>C11</f>
-        <v>222570729.18966401</v>
+        <v>250272862.009635</v>
       </c>
       <c r="N15" s="11">
         <f>D11</f>
-        <v>59306658.328172997</v>
+        <v>61442334.004658997</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -21937,27 +21938,27 @@
         <v>74</v>
       </c>
       <c r="C16" s="205">
-        <v>269419401.431153</v>
+        <v>285480633.74615097</v>
       </c>
       <c r="D16" s="205">
-        <v>51766419.171329997</v>
+        <v>52968401.151327997</v>
       </c>
       <c r="E16" s="205">
         <v>10797297.199999999</v>
       </c>
       <c r="F16" s="205">
-        <v>331983117.80248302</v>
+        <v>349246332.09747899</v>
       </c>
       <c r="H16" s="116"/>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="M16" s="11">
         <f>C26</f>
-        <v>270593460.01106203</v>
+        <v>289623919.43200803</v>
       </c>
       <c r="N16" s="11">
         <f>D26</f>
-        <v>35579977.479971997</v>
+        <v>38245635.119948</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -21965,27 +21966,27 @@
         <v>118</v>
       </c>
       <c r="C17" s="205">
-        <v>220179527.69999799</v>
+        <v>255314662.19999799</v>
       </c>
       <c r="D17" s="205">
-        <v>19090832.32</v>
+        <v>33550551.18</v>
       </c>
       <c r="E17" s="205" t="s">
         <v>169</v>
       </c>
       <c r="F17" s="205">
-        <v>239270360.01999801</v>
+        <v>288865213.37999803</v>
       </c>
       <c r="H17" s="116"/>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="M17" s="11">
         <f>C10</f>
-        <v>178327048.7886</v>
+        <v>184471534.469396</v>
       </c>
       <c r="N17" s="11">
         <f>D10</f>
-        <v>18591862.899342</v>
+        <v>22535662.899342</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -21993,27 +21994,27 @@
         <v>119</v>
       </c>
       <c r="C18" s="205">
-        <v>774715655.04786694</v>
+        <v>845495566.01786697</v>
       </c>
       <c r="D18" s="205">
-        <v>7419438.6219769996</v>
+        <v>7656438.6219769996</v>
       </c>
       <c r="E18" s="205">
         <v>8112162.0800000001</v>
       </c>
       <c r="F18" s="205">
-        <v>790247255.74984396</v>
+        <v>861264166.71984398</v>
       </c>
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
       <c r="M18" s="11">
         <f>C27</f>
-        <v>486173081.16347802</v>
+        <v>501331949.98337102</v>
       </c>
       <c r="N18" s="11">
         <f>D27</f>
-        <v>148831502.51741099</v>
+        <v>149543402.51741099</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -22021,27 +22022,27 @@
         <v>121</v>
       </c>
       <c r="C19" s="205">
-        <v>572685678.40666699</v>
+        <v>599215529.42203498</v>
       </c>
       <c r="D19" s="205">
-        <v>45816273.849916004</v>
+        <v>46766273.849916004</v>
       </c>
       <c r="E19" s="205">
-        <v>488438129.73994303</v>
+        <v>491088941.98994303</v>
       </c>
       <c r="F19" s="205">
-        <v>1106940081.996526</v>
+        <v>1137070745.261894</v>
       </c>
       <c r="H19" s="116"/>
       <c r="I19" s="116"/>
       <c r="J19" s="116"/>
       <c r="M19" s="11">
         <f>C20+C21</f>
-        <v>156825830.31347799</v>
+        <v>161255289.11341798</v>
       </c>
       <c r="N19" s="11">
         <f>D20+D21</f>
-        <v>89668238.982917994</v>
+        <v>95462833.522836</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
@@ -22049,16 +22050,16 @@
         <v>123</v>
       </c>
       <c r="C20" s="205">
-        <v>118290806.31347799</v>
+        <v>122720265.113418</v>
       </c>
       <c r="D20" s="205">
         <v>20733574.809856001</v>
       </c>
       <c r="E20" s="205">
-        <v>1027027.04</v>
+        <v>2972973.04</v>
       </c>
       <c r="F20" s="205">
-        <v>140051408.16333401</v>
+        <v>146426812.963274</v>
       </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
@@ -22079,20 +22080,20 @@
         <v>38535024</v>
       </c>
       <c r="D21" s="205">
-        <v>68934664.173061997</v>
+        <v>74729258.712980002</v>
       </c>
       <c r="E21" s="205">
-        <v>34962162.840000004</v>
+        <v>36767568.280000001</v>
       </c>
       <c r="F21" s="205">
-        <v>142431851.013062</v>
+        <v>150031850.99298</v>
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="M21" s="14">
         <f>IFERROR(C34,0)+IFERROR(C35,0)+M20</f>
-        <v>480244808.89564198</v>
+        <v>488697007.205603</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>122</v>
@@ -22123,7 +22124,7 @@
         <v>174</v>
       </c>
       <c r="C23" s="205">
-        <v>156137878.04997501</v>
+        <v>157901166.34997499</v>
       </c>
       <c r="D23" s="205" t="s">
         <v>169</v>
@@ -22132,7 +22133,7 @@
         <v>7297297.0999999996</v>
       </c>
       <c r="F23" s="205">
-        <v>163435175.149975</v>
+        <v>165198463.44997501</v>
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116"/>
@@ -22143,16 +22144,16 @@
         <v>125</v>
       </c>
       <c r="C24" s="205">
-        <v>193728052.55777201</v>
+        <v>198874466.95777199</v>
       </c>
       <c r="D24" s="205">
-        <v>29732159.813473001</v>
+        <v>32839506.683463</v>
       </c>
       <c r="E24" s="205">
-        <v>83676034.900000006</v>
+        <v>87589548.400000006</v>
       </c>
       <c r="F24" s="205">
-        <v>307136247.271245</v>
+        <v>319303522.04123503</v>
       </c>
       <c r="H24" s="116"/>
       <c r="I24" s="116"/>
@@ -22163,16 +22164,16 @@
         <v>126</v>
       </c>
       <c r="C25" s="205">
-        <v>266657225.53848201</v>
+        <v>275775148.99845499</v>
       </c>
       <c r="D25" s="205">
-        <v>42467131.579859003</v>
+        <v>44631802.779844001</v>
       </c>
       <c r="E25" s="205">
-        <v>99733332.219999999</v>
+        <v>127983962.62</v>
       </c>
       <c r="F25" s="205">
-        <v>408857689.338341</v>
+        <v>448390914.39829898</v>
       </c>
       <c r="H25" s="116"/>
       <c r="I25" s="116"/>
@@ -22183,16 +22184,16 @@
         <v>127</v>
       </c>
       <c r="C26" s="205">
-        <v>270593460.01106203</v>
+        <v>289623919.43200803</v>
       </c>
       <c r="D26" s="205">
-        <v>35579977.479971997</v>
+        <v>38245635.119948</v>
       </c>
       <c r="E26" s="205">
-        <v>257587925.58995101</v>
+        <v>270041439.19995099</v>
       </c>
       <c r="F26" s="205">
-        <v>563761363.08098495</v>
+        <v>597910993.75190699</v>
       </c>
       <c r="H26" s="116"/>
       <c r="I26" s="116"/>
@@ -22203,16 +22204,16 @@
         <v>128</v>
       </c>
       <c r="C27" s="205">
-        <v>486173081.16347802</v>
+        <v>501331949.98337102</v>
       </c>
       <c r="D27" s="205">
-        <v>148831502.51741099</v>
+        <v>149543402.51741099</v>
       </c>
       <c r="E27" s="205">
-        <v>12491351.439999999</v>
+        <v>13464324.439999999</v>
       </c>
       <c r="F27" s="205">
-        <v>647495935.12088895</v>
+        <v>664339676.94078195</v>
       </c>
       <c r="H27" s="116"/>
       <c r="I27" s="116"/>
@@ -22259,7 +22260,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="205">
-        <v>186126288.68503001</v>
+        <v>194444846.924934</v>
       </c>
       <c r="G32" s="116"/>
       <c r="H32" s="116"/>
@@ -22269,8 +22270,8 @@
       <c r="B33" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="205">
-        <v>245411419.23768699</v>
+      <c r="C33" s="248">
+        <v>281580352.837192</v>
       </c>
       <c r="G33" s="116"/>
       <c r="H33" s="116"/>
@@ -22281,7 +22282,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="205">
-        <v>213668249.15867499</v>
+        <v>222120447.46863601</v>
       </c>
       <c r="G34" s="116"/>
       <c r="H34" s="116"/>
@@ -22344,7 +22345,7 @@
       </c>
       <c r="F41" s="73">
         <f ca="1">IF(MONTH(TODAY())=5,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;5,1,0))</f>
-        <v>0.64516129032258063</v>
+        <v>0.67741935483870963</v>
       </c>
       <c r="G41" s="117"/>
       <c r="H41" s="117"/>
@@ -22387,19 +22388,19 @@
       </c>
       <c r="E43" s="46">
         <f>G65</f>
-        <v>3865352127.3121481</v>
+        <v>4052545372.7311082</v>
       </c>
       <c r="F43" s="44">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.56516950685530909</v>
+        <v>0.59253982415513196</v>
       </c>
       <c r="G43" s="118">
         <f>D43-E43</f>
-        <v>2973927204.6878519</v>
+        <v>2786733959.2688918</v>
       </c>
       <c r="H43" s="118">
         <f ca="1">IFERROR(G43/C3,0)</f>
-        <v>297392720.46878517</v>
+        <v>309637106.58543241</v>
       </c>
       <c r="I43" s="116"/>
     </row>
@@ -22416,19 +22417,19 @@
       </c>
       <c r="E44" s="46">
         <f>N8+N9+N10+N11+N12+N13+N14+N15+N16+N17+N18+N19</f>
-        <v>612444371.66567802</v>
+        <v>650392182.40203094</v>
       </c>
       <c r="F44" s="44">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.41514198780502926</v>
+        <v>0.44086469881483548</v>
       </c>
       <c r="G44" s="118">
         <f>D44-E44</f>
-        <v>862820452.55468369</v>
+        <v>824872641.81833076</v>
       </c>
       <c r="H44" s="118">
         <f ca="1">IFERROR(G44/C3,0)</f>
-        <v>86282045.255468369</v>
+        <v>91652515.757592306</v>
       </c>
       <c r="I44" s="116"/>
     </row>
@@ -22445,19 +22446,19 @@
       </c>
       <c r="E45" s="46">
         <f>IFERROR(C32,0)+IFERROR(C33,0)+M21+F9</f>
-        <v>911782516.8183589</v>
+        <v>964722206.96772897</v>
       </c>
       <c r="F45" s="44">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.5113816025114899</v>
+        <v>0.54107331417044446</v>
       </c>
       <c r="G45" s="118">
         <f>D45-E45</f>
-        <v>871196206.58589697</v>
+        <v>818256516.43652689</v>
       </c>
       <c r="H45" s="118">
         <f ca="1">IFERROR(G45/C3,0)</f>
-        <v>87119620.658589691</v>
+        <v>90917390.715169653</v>
       </c>
       <c r="I45" s="116"/>
     </row>
@@ -22472,19 +22473,19 @@
       </c>
       <c r="E46" s="47">
         <f>E43+E44+E45</f>
-        <v>5389579015.7961845</v>
+        <v>5667659762.1008673</v>
       </c>
       <c r="F46" s="43">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.53375259259591257</v>
+        <v>0.56129209407758884</v>
       </c>
       <c r="G46" s="119">
         <f>G43+G44+G45</f>
-        <v>4707943863.8284321</v>
+        <v>4429863117.5237494</v>
       </c>
       <c r="H46" s="119">
         <f ca="1">IFERROR(G46/C3,0)</f>
-        <v>470794386.3828432</v>
+        <v>492207013.0581944</v>
       </c>
       <c r="I46" s="116"/>
     </row>
@@ -22593,35 +22594,35 @@
       </c>
       <c r="G51" s="122">
         <f>M8</f>
-        <v>193728052.55777201</v>
+        <v>198874466.95777199</v>
       </c>
       <c r="H51" s="122">
         <f>N8</f>
-        <v>29732159.813473001</v>
+        <v>32839506.683463</v>
       </c>
       <c r="I51" s="122">
         <f t="shared" ref="I51:I64" si="1">G51+H51</f>
-        <v>223460212.37124503</v>
+        <v>231713973.64123499</v>
       </c>
       <c r="J51" s="61">
         <f t="shared" ref="J51:J64" si="2">IFERROR(I51/F51,0)</f>
-        <v>0.46078652413371146</v>
+        <v>0.47780620708429267</v>
       </c>
       <c r="K51" s="51">
         <f t="shared" ref="K51:M64" si="3">D51-G51</f>
-        <v>222955425.44222799</v>
+        <v>217809011.04222801</v>
       </c>
       <c r="L51" s="51">
         <f t="shared" si="3"/>
-        <v>38538241.407181308</v>
+        <v>35430894.537191309</v>
       </c>
       <c r="M51" s="51">
         <f t="shared" si="3"/>
-        <v>261493666.84940928</v>
+        <v>253239905.57941931</v>
       </c>
       <c r="N51" s="51">
         <f ca="1">IFERROR(M51/C3,0)</f>
-        <v>26149366.684940927</v>
+        <v>28137767.286602147</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,35 +22646,35 @@
       </c>
       <c r="G52" s="122">
         <f>M9</f>
-        <v>340597245.07357001</v>
+        <v>343396010.84356898</v>
       </c>
       <c r="H52" s="122">
         <f>N9</f>
-        <v>52293732.082157001</v>
+        <v>53106196.052157</v>
       </c>
       <c r="I52" s="122">
         <f t="shared" si="1"/>
-        <v>392890977.15572703</v>
+        <v>396502206.89572597</v>
       </c>
       <c r="J52" s="61">
         <f t="shared" si="2"/>
-        <v>0.52614923968748351</v>
+        <v>0.5309853033603944</v>
       </c>
       <c r="K52" s="54">
         <f t="shared" si="3"/>
-        <v>214585125.92642999</v>
+        <v>211786360.15643102</v>
       </c>
       <c r="L52" s="54">
         <f t="shared" si="3"/>
-        <v>139253051.91784298</v>
+        <v>138440587.94784302</v>
       </c>
       <c r="M52" s="54">
         <f t="shared" si="3"/>
-        <v>353838177.84427297</v>
+        <v>350226948.10427403</v>
       </c>
       <c r="N52" s="54">
         <f ca="1">IFERROR(M52/C3,0)</f>
-        <v>35383817.7844273</v>
+        <v>38914105.344919339</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22725,7 +22726,7 @@
       </c>
       <c r="N53" s="54">
         <f ca="1">IFERROR(M53/C3,0)</f>
-        <v>12100878.220000001</v>
+        <v>13445420.244444445</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22749,7 +22750,7 @@
       </c>
       <c r="G54" s="122">
         <f>M10</f>
-        <v>410992483.28824902</v>
+        <v>429167713.405325</v>
       </c>
       <c r="H54" s="122">
         <f t="shared" ref="H54:H58" si="4">N10</f>
@@ -22757,15 +22758,15 @@
       </c>
       <c r="I54" s="122">
         <f t="shared" si="1"/>
-        <v>430292065.92937601</v>
+        <v>448467296.04645199</v>
       </c>
       <c r="J54" s="61">
         <f t="shared" si="2"/>
-        <v>0.65434275616933468</v>
+        <v>0.68198172772027976</v>
       </c>
       <c r="K54" s="54">
         <f>D54-G54</f>
-        <v>199719988.71175098</v>
+        <v>181544758.594675</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="3"/>
@@ -22773,11 +22774,11 @@
       </c>
       <c r="M54" s="54">
         <f t="shared" si="3"/>
-        <v>227302232.88795888</v>
+        <v>209127002.7708829</v>
       </c>
       <c r="N54" s="54">
         <f ca="1">IFERROR(M54/C3,0)</f>
-        <v>22730223.288795888</v>
+        <v>23236333.641209211</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22801,35 +22802,35 @@
       </c>
       <c r="G55" s="122">
         <f>M11</f>
-        <v>220179527.69999799</v>
+        <v>255314662.19999799</v>
       </c>
       <c r="H55" s="122">
         <f t="shared" si="4"/>
-        <v>19090832.32</v>
+        <v>33550551.18</v>
       </c>
       <c r="I55" s="122">
         <f t="shared" si="1"/>
-        <v>239270360.01999798</v>
+        <v>288865213.37999797</v>
       </c>
       <c r="J55" s="61">
         <f t="shared" si="2"/>
-        <v>0.49037584374656462</v>
+        <v>0.59201868015916703</v>
       </c>
       <c r="K55" s="54">
         <f t="shared" si="3"/>
-        <v>184883756.30000201</v>
+        <v>149748621.80000201</v>
       </c>
       <c r="L55" s="54">
         <f t="shared" si="3"/>
-        <v>63778482.871524148</v>
+        <v>49318764.011524148</v>
       </c>
       <c r="M55" s="54">
         <f t="shared" si="3"/>
-        <v>248662239.17152616</v>
+        <v>199067385.81152618</v>
       </c>
       <c r="N55" s="54">
         <f ca="1">IFERROR(M55/C3,0)</f>
-        <v>24866223.917152617</v>
+        <v>22118598.423502907</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22853,35 +22854,35 @@
       </c>
       <c r="G56" s="122">
         <f>M12</f>
-        <v>269419401.431153</v>
+        <v>285480633.74615097</v>
       </c>
       <c r="H56" s="122">
         <f t="shared" si="4"/>
-        <v>51766419.171329997</v>
+        <v>52968401.151327997</v>
       </c>
       <c r="I56" s="122">
         <f t="shared" si="1"/>
-        <v>321185820.60248297</v>
+        <v>338449034.89747894</v>
       </c>
       <c r="J56" s="61">
         <f t="shared" si="2"/>
-        <v>0.5785482507315346</v>
+        <v>0.60964427612156802</v>
       </c>
       <c r="K56" s="54">
         <f t="shared" si="3"/>
-        <v>204499430.568847</v>
+        <v>188438198.25384903</v>
       </c>
       <c r="L56" s="54">
         <f t="shared" si="3"/>
-        <v>29472974.951323606</v>
+        <v>28270992.971325606</v>
       </c>
       <c r="M56" s="54">
         <f t="shared" si="3"/>
-        <v>233972405.52017063</v>
+        <v>216709191.22517467</v>
       </c>
       <c r="N56" s="54">
         <f ca="1">IFERROR(M56/C3,0)</f>
-        <v>23397240.552017063</v>
+        <v>24078799.025019407</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22905,35 +22906,35 @@
       </c>
       <c r="G57" s="122">
         <f>M13</f>
-        <v>572685678.40666699</v>
+        <v>599215529.42203498</v>
       </c>
       <c r="H57" s="122">
         <f t="shared" si="4"/>
-        <v>45816273.849916004</v>
+        <v>46766273.849916004</v>
       </c>
       <c r="I57" s="122">
         <f t="shared" si="1"/>
-        <v>618501952.25658298</v>
+        <v>645981803.27195096</v>
       </c>
       <c r="J57" s="61">
         <f t="shared" si="2"/>
-        <v>0.58698835463432897</v>
+        <v>0.61306806622498167</v>
       </c>
       <c r="K57" s="54">
         <f t="shared" si="3"/>
-        <v>389072666.59333301</v>
+        <v>362542815.57796502</v>
       </c>
       <c r="L57" s="54">
         <f t="shared" si="3"/>
-        <v>46112302.489240386</v>
+        <v>45162302.489240386</v>
       </c>
       <c r="M57" s="54">
         <f t="shared" si="3"/>
-        <v>435184969.08257341</v>
+        <v>407705118.06720543</v>
       </c>
       <c r="N57" s="54">
         <f ca="1">IFERROR(M57/C3,0)</f>
-        <v>43518496.908257343</v>
+        <v>45300568.674133934</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22957,35 +22958,35 @@
       </c>
       <c r="G58" s="122">
         <f>M14</f>
-        <v>266657225.53848201</v>
+        <v>275775148.99845499</v>
       </c>
       <c r="H58" s="122">
         <f t="shared" si="4"/>
-        <v>42467131.579859003</v>
+        <v>44631802.779844001</v>
       </c>
       <c r="I58" s="122">
         <f>G58+H58</f>
-        <v>309124357.11834103</v>
+        <v>320406951.77829897</v>
       </c>
       <c r="J58" s="61">
         <f>IFERROR(I58/F58,0)</f>
-        <v>0.54321119024714082</v>
+        <v>0.56303761780996631</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="3"/>
-        <v>238629833.46151799</v>
+        <v>229511910.00154501</v>
       </c>
       <c r="L58" s="54">
         <f t="shared" si="3"/>
-        <v>21314272.420140997</v>
+        <v>19149601.220155999</v>
       </c>
       <c r="M58" s="54">
         <f t="shared" si="3"/>
-        <v>259944105.88165897</v>
+        <v>248661511.22170103</v>
       </c>
       <c r="N58" s="54">
         <f ca="1">IFERROR(M58/C3,0)</f>
-        <v>25994410.588165898</v>
+        <v>27629056.802411225</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23009,7 +23010,7 @@
       </c>
       <c r="G59" s="122">
         <f>C23</f>
-        <v>156137878.04997501</v>
+        <v>157901166.34997499</v>
       </c>
       <c r="H59" s="122">
         <f>IF(D23="",0,D23)</f>
@@ -23017,15 +23018,15 @@
       </c>
       <c r="I59" s="122">
         <f>G59+H59</f>
-        <v>156137878.04997501</v>
+        <v>157901166.34997499</v>
       </c>
       <c r="J59" s="61">
         <f>IFERROR(I59/F59,0)</f>
-        <v>0.38635207100682167</v>
+        <v>0.39071520245830099</v>
       </c>
       <c r="K59" s="54">
         <f>D59-G59</f>
-        <v>247995785.95002499</v>
+        <v>246232497.65002501</v>
       </c>
       <c r="L59" s="54">
         <f>E59-H59</f>
@@ -23033,11 +23034,11 @@
       </c>
       <c r="M59" s="54">
         <f>F59-I59</f>
-        <v>247995785.95002499</v>
+        <v>246232497.65002501</v>
       </c>
       <c r="N59" s="54">
         <f ca="1">IFERROR(M59/C3,0)</f>
-        <v>24799578.595002498</v>
+        <v>27359166.405558333</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23061,35 +23062,35 @@
       </c>
       <c r="G60" s="122">
         <f>M15</f>
-        <v>222570729.18966401</v>
+        <v>250272862.009635</v>
       </c>
       <c r="H60" s="122">
         <f t="shared" ref="H60:H64" si="5">N15</f>
-        <v>59306658.328172997</v>
+        <v>61442334.004658997</v>
       </c>
       <c r="I60" s="122">
         <f t="shared" si="1"/>
-        <v>281877387.51783699</v>
+        <v>311715196.01429403</v>
       </c>
       <c r="J60" s="61">
         <f t="shared" si="2"/>
-        <v>0.51960718292280128</v>
+        <v>0.57460960704046127</v>
       </c>
       <c r="K60" s="54">
         <f t="shared" si="3"/>
-        <v>181446579.81033599</v>
+        <v>153744446.990365</v>
       </c>
       <c r="L60" s="54">
         <f t="shared" si="3"/>
-        <v>79157731.889822409</v>
+        <v>77022056.213336408</v>
       </c>
       <c r="M60" s="54">
         <f t="shared" si="3"/>
-        <v>260604311.70015842</v>
+        <v>230766503.20370138</v>
       </c>
       <c r="N60" s="54">
         <f ca="1">IFERROR(M60/C3,0)</f>
-        <v>26060431.170015842</v>
+        <v>25640722.578189041</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23113,35 +23114,35 @@
       </c>
       <c r="G61" s="122">
         <f>M16</f>
-        <v>270593460.01106203</v>
+        <v>289623919.43200803</v>
       </c>
       <c r="H61" s="122">
         <f t="shared" si="5"/>
-        <v>35579977.479971997</v>
+        <v>38245635.119948</v>
       </c>
       <c r="I61" s="122">
         <f t="shared" si="1"/>
-        <v>306173437.49103403</v>
+        <v>327869554.55195606</v>
       </c>
       <c r="J61" s="61">
         <f t="shared" si="2"/>
-        <v>0.44349103640793724</v>
+        <v>0.47491777780074018</v>
       </c>
       <c r="K61" s="54">
         <f t="shared" si="3"/>
-        <v>361036135.98893797</v>
+        <v>342005676.56799197</v>
       </c>
       <c r="L61" s="54">
         <f t="shared" si="3"/>
-        <v>23161623.13065327</v>
+        <v>20495965.490677267</v>
       </c>
       <c r="M61" s="54">
         <f t="shared" si="3"/>
-        <v>384197759.11959124</v>
+        <v>362501642.05866921</v>
       </c>
       <c r="N61" s="54">
         <f ca="1">IFERROR(M61/C3,0)</f>
-        <v>38419775.911959127</v>
+        <v>40277960.22874102</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23165,35 +23166,35 @@
       </c>
       <c r="G62" s="122">
         <f>M17</f>
-        <v>178327048.7886</v>
+        <v>184471534.469396</v>
       </c>
       <c r="H62" s="122">
         <f t="shared" si="5"/>
-        <v>18591862.899342</v>
+        <v>22535662.899342</v>
       </c>
       <c r="I62" s="122">
         <f t="shared" si="1"/>
-        <v>196918911.687942</v>
+        <v>207007197.368738</v>
       </c>
       <c r="J62" s="61">
         <f t="shared" si="2"/>
-        <v>0.43729907360144998</v>
+        <v>0.45970219346750901</v>
       </c>
       <c r="K62" s="54">
         <f t="shared" si="3"/>
-        <v>208215974.2114</v>
+        <v>202071488.530604</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="3"/>
-        <v>45172291.900471807</v>
+        <v>41228491.900471807</v>
       </c>
       <c r="M62" s="54">
         <f t="shared" si="3"/>
-        <v>253388266.11187181</v>
+        <v>243299980.43107581</v>
       </c>
       <c r="N62" s="54">
         <f ca="1">IFERROR(M62/C3,0)</f>
-        <v>25338826.611187182</v>
+        <v>27033331.159008425</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,35 +23218,35 @@
       </c>
       <c r="G63" s="122">
         <f>M18</f>
-        <v>486173081.16347802</v>
+        <v>501331949.98337102</v>
       </c>
       <c r="H63" s="122">
         <f t="shared" si="5"/>
-        <v>148831502.51741099</v>
+        <v>149543402.51741099</v>
       </c>
       <c r="I63" s="122">
         <f t="shared" si="1"/>
-        <v>635004583.68088901</v>
+        <v>650875352.50078201</v>
       </c>
       <c r="J63" s="61">
         <f t="shared" si="2"/>
-        <v>0.69539407448161628</v>
+        <v>0.71277416728480036</v>
       </c>
       <c r="K63" s="54">
         <f t="shared" si="3"/>
-        <v>97177860.836521983</v>
+        <v>82018992.016628981</v>
       </c>
       <c r="L63" s="54">
         <f t="shared" si="3"/>
-        <v>180975442.47530639</v>
+        <v>180263542.47530639</v>
       </c>
       <c r="M63" s="54">
         <f t="shared" si="3"/>
-        <v>278153303.31182837</v>
+        <v>262282534.49193537</v>
       </c>
       <c r="N63" s="54">
         <f ca="1">IFERROR(M63/C3,0)</f>
-        <v>27815330.331182837</v>
+        <v>29142503.832437262</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23269,35 +23270,35 @@
       </c>
       <c r="G64" s="122">
         <f>M19</f>
-        <v>156825830.31347799</v>
+        <v>161255289.11341798</v>
       </c>
       <c r="H64" s="122">
         <f t="shared" si="5"/>
-        <v>89668238.982917994</v>
+        <v>95462833.522836</v>
       </c>
       <c r="I64" s="122">
         <f t="shared" si="1"/>
-        <v>246494069.29639599</v>
+        <v>256718122.63625398</v>
       </c>
       <c r="J64" s="61">
         <f t="shared" si="2"/>
-        <v>0.47632098071062434</v>
+        <v>0.49607776888642041</v>
       </c>
       <c r="K64" s="54">
         <f t="shared" si="3"/>
-        <v>102699858.68652201</v>
+        <v>98270399.886582017</v>
       </c>
       <c r="L64" s="54">
         <f t="shared" si="3"/>
-        <v>168301792.92496839</v>
+        <v>162507198.38505039</v>
       </c>
       <c r="M64" s="54">
         <f t="shared" si="3"/>
-        <v>271001651.61149037</v>
+        <v>260777598.2716324</v>
       </c>
       <c r="N64" s="54">
         <f ca="1">IFERROR(M64/C3,0)</f>
-        <v>27100165.161149036</v>
+        <v>28975288.696848046</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23319,35 +23320,35 @@
       </c>
       <c r="G65" s="152">
         <f>SUM(G51:G64)</f>
-        <v>3865352127.3121481</v>
+        <v>4052545372.7311082</v>
       </c>
       <c r="H65" s="152">
         <f>SUM(H51:H64)</f>
-        <v>612444371.66567802</v>
+        <v>650392182.40203094</v>
       </c>
       <c r="I65" s="152">
         <f>SUM(I51:I64)</f>
-        <v>4477796498.9778261</v>
+        <v>4702937555.1331396</v>
       </c>
       <c r="J65" s="153">
         <f>IFERROR(I65/F65,0)</f>
-        <v>0.53854984889674928</v>
+        <v>0.56562782838969339</v>
       </c>
       <c r="K65" s="154">
         <f>SUM(K51:K64)</f>
-        <v>2973927204.6878519</v>
+        <v>2786733959.2688918</v>
       </c>
       <c r="L65" s="154">
         <f>SUM(L51:L64)</f>
-        <v>862820452.55468357</v>
+        <v>824872641.81833065</v>
       </c>
       <c r="M65" s="154">
         <f>SUM(M51:M64)</f>
-        <v>3836747657.2425356</v>
+        <v>3611606601.0872226</v>
       </c>
       <c r="N65" s="154">
         <f ca="1">IFERROR(M65/C3,0)</f>
-        <v>383674765.72425354</v>
+        <v>401289622.34302473</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
@@ -23389,7 +23390,7 @@
       </c>
       <c r="D70" s="191">
         <f>IF(E24="",0,E24)</f>
-        <v>83676034.900000006</v>
+        <v>87589548.400000006</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23401,7 +23402,7 @@
       </c>
       <c r="D71" s="192">
         <f>IF(E12="",0,E12)+IF(E13="",0,E13)</f>
-        <v>59531440.299999997</v>
+        <v>64866575.420000002</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23425,7 +23426,7 @@
       </c>
       <c r="D73" s="191">
         <f>IF(E14="",0,E14)</f>
-        <v>123071170.04000001</v>
+        <v>131857656.44</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23462,7 @@
       </c>
       <c r="D76" s="192">
         <f>IF(E19="",0,E19)</f>
-        <v>488438129.73994303</v>
+        <v>491088941.98994303</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23473,7 +23474,7 @@
       </c>
       <c r="D77" s="191">
         <f>IF(E25="",0,E25)</f>
-        <v>99733332.219999999</v>
+        <v>127983962.62</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,7 +23510,7 @@
       </c>
       <c r="D80" s="191">
         <f>IF(E26="",0,E26)</f>
-        <v>257587925.58995101</v>
+        <v>270041439.19995099</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,7 +23522,7 @@
       </c>
       <c r="D81" s="192">
         <f>IF(E10="",0,E10)</f>
-        <v>108315546.639999</v>
+        <v>116419150.11999901</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23533,7 +23534,7 @@
       </c>
       <c r="D82" s="192">
         <f>IF(E27="",0,E27)</f>
-        <v>12491351.439999999</v>
+        <v>13464324.439999999</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23545,7 +23546,7 @@
       </c>
       <c r="D83" s="192">
         <f>IF(E20="",0,E20)+IF(E21="",0,E21)</f>
-        <v>35989189.880000003</v>
+        <v>39740541.32</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23555,7 +23556,7 @@
       <c r="C84" s="58"/>
       <c r="D84" s="129">
         <f>SUM(D70:D83)</f>
-        <v>1319739525.929893</v>
+        <v>1393957545.1298928</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
@@ -23617,19 +23618,19 @@
       </c>
       <c r="E89" s="122">
         <f>IFERROR(C32,0)</f>
-        <v>186126288.68503001</v>
+        <v>194444846.924934</v>
       </c>
       <c r="F89" s="61">
         <f t="shared" ref="F89:F94" si="7">IFERROR(E89/D89,0)</f>
-        <v>0.66936343821042577</v>
+        <v>0.69927935596580748</v>
       </c>
       <c r="G89" s="125">
         <f>D89-E89</f>
-        <v>91938329.219179541</v>
+        <v>83619770.979275554</v>
       </c>
       <c r="H89" s="125">
         <f ca="1">IFERROR(G89/C3,0)</f>
-        <v>9193832.9219179545</v>
+        <v>9291085.6643639505</v>
       </c>
       <c r="I89" s="116"/>
     </row>
@@ -23646,19 +23647,19 @@
       </c>
       <c r="E90" s="122">
         <f>IFERROR(C33,0)</f>
-        <v>245411419.23768699</v>
+        <v>281580352.837192</v>
       </c>
       <c r="F90" s="61">
         <f t="shared" si="7"/>
-        <v>0.58764491511486683</v>
+        <v>0.67425249833531542</v>
       </c>
       <c r="G90" s="126">
         <f>D90-E90</f>
-        <v>172207133.9488346</v>
+        <v>136038200.34932959</v>
       </c>
       <c r="H90" s="126">
         <f ca="1">IFERROR(G90/C3,0)</f>
-        <v>17220713.394883461</v>
+        <v>15115355.594369955</v>
       </c>
       <c r="I90" s="116"/>
     </row>
@@ -23675,19 +23676,19 @@
       </c>
       <c r="E91" s="122">
         <f>M21+M7</f>
-        <v>480244808.89564198</v>
+        <v>488697007.205603</v>
       </c>
       <c r="F91" s="61">
         <f t="shared" si="7"/>
-        <v>0.44168745827552325</v>
+        <v>0.44946105607234732</v>
       </c>
       <c r="G91" s="125">
         <f>D91-E91</f>
-        <v>607050743.41788268</v>
+        <v>598598545.10792172</v>
       </c>
       <c r="H91" s="125">
         <f ca="1">IFERROR(G91/C3,0)</f>
-        <v>60705074.34178827</v>
+        <v>66510949.456435747</v>
       </c>
       <c r="I91" s="116"/>
     </row>
@@ -23760,19 +23761,19 @@
       </c>
       <c r="E94" s="123">
         <f>SUM(E89:E93)</f>
-        <v>911782516.8183589</v>
+        <v>964722206.96772897</v>
       </c>
       <c r="F94" s="43">
         <f t="shared" si="7"/>
-        <v>0.5113816025114899</v>
+        <v>0.54107331417044446</v>
       </c>
       <c r="G94" s="119">
         <f>SUM(G89:G93)</f>
-        <v>871196206.58589685</v>
+        <v>818256516.43652689</v>
       </c>
       <c r="H94" s="119">
         <f ca="1">IFERROR(G94/C3,0)</f>
-        <v>87119620.658589691</v>
+        <v>90917390.715169653</v>
       </c>
       <c r="I94" s="116"/>
     </row>
